--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emretasci\antigravity\scm-project-portal\dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/TZY Gelişim Planı/Gelişim Planı/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88CDDE07-6F8E-479C-8564-C720F537BCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{88CDDE07-6F8E-479C-8564-C720F537BCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E67805D-608C-45A2-8294-74CBB0A29906}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="537" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
@@ -2237,257 +2237,240 @@
         <v>269</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="4">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="G2" s="4">
-        <v>46157</v>
+        <v>46112</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>243</v>
+        <v>92</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>337</v>
+        <v>394</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="4">
-        <v>46173</v>
+        <v>46113</v>
       </c>
       <c r="G3" s="4">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>66</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="17" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>92</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>338</v>
+        <v>29</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>342</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="E4" s="8"/>
       <c r="F4" s="4">
-        <v>46023</v>
+        <v>46174</v>
       </c>
       <c r="G4" s="4">
-        <v>46357</v>
+        <v>46265</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>209</v>
+        <v>66</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="17" t="s">
-        <v>260</v>
+        <v>96</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>338</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="F5" s="4">
         <v>46023</v>
       </c>
       <c r="G5" s="4">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>257</v>
+        <v>88</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>338</v>
+        <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="F6" s="4">
-        <v>46023</v>
+        <v>46174</v>
       </c>
       <c r="G6" s="4">
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>209</v>
+        <v>66</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>281</v>
+        <v>395</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>323</v>
+        <v>28</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="4">
-        <v>46023</v>
+        <v>46235</v>
       </c>
       <c r="G7" s="4">
-        <v>46082</v>
+        <v>46295</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+        <v>91</v>
+      </c>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>52</v>
+        <v>395</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="F8" s="4">
-        <v>46023</v>
+        <v>46327</v>
       </c>
       <c r="G8" s="4">
-        <v>46357</v>
+        <v>46387</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>209</v>
+        <v>66</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>253</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>56</v>
+      </c>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>281</v>
+        <v>396</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="4">
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="G9" s="4">
         <v>46112</v>
@@ -2496,66 +2479,62 @@
         <v>54</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>76</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>281</v>
+        <v>396</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="4">
-        <v>45901</v>
+        <v>45778</v>
       </c>
       <c r="G10" s="4">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>247</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>208</v>
+        <v>396</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>346</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="E11" s="8"/>
       <c r="F11" s="4">
-        <v>45931</v>
+        <v>46054</v>
       </c>
       <c r="G11" s="4">
         <v>46112</v>
@@ -2564,1564 +2543,1537 @@
         <v>54</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>377</v>
-      </c>
-      <c r="K11" s="14"/>
-    </row>
-    <row r="12" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>9</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>208</v>
+        <v>397</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>346</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E12" s="8"/>
       <c r="F12" s="4">
-        <v>46023</v>
+        <v>45839</v>
       </c>
       <c r="G12" s="4">
-        <v>46387</v>
+        <v>45930</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>71</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>208</v>
+        <v>397</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>346</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="E13" s="8"/>
       <c r="F13" s="4">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="G13" s="4">
-        <v>46387</v>
+        <v>46022</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>74</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>211</v>
+        <v>397</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>45</v>
+        <v>296</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I14" s="7"/>
+      <c r="I14" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>210</v>
+        <v>397</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I15" s="7"/>
+      <c r="I15" s="8" t="s">
+        <v>80</v>
+      </c>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>50</v>
+        <v>397</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>349</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="E16" s="8"/>
       <c r="F16" s="4">
-        <v>46204</v>
+        <v>46054</v>
       </c>
       <c r="G16" s="4">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>82</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="F17" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G17" s="4">
-        <v>46387</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
       <c r="H17" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>69</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>49</v>
+        <v>292</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F18" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G18" s="4">
-        <v>46142</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
       <c r="H18" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>69</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="F19" s="4">
-        <v>45992</v>
-      </c>
-      <c r="G19" s="4">
-        <v>46142</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
       <c r="H19" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="216" x14ac:dyDescent="0.55000000000000004">
+        <v>69</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F20" s="4">
-        <v>45931</v>
-      </c>
-      <c r="G20" s="4">
-        <v>46053</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
       <c r="H20" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>69</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F21" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G21" s="4">
-        <v>46112</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
       <c r="H21" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>69</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:11" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="7" t="s">
-        <v>207</v>
+        <v>24</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>340</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E22" s="8"/>
       <c r="F22" s="4">
-        <v>46023</v>
+        <v>45809</v>
       </c>
       <c r="G22" s="4">
         <v>46203</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>209</v>
+        <v>55</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+        <v>57</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="4">
+        <v>45962</v>
+      </c>
+      <c r="G23" s="4">
+        <v>46234</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="4">
+        <v>46113</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46265</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="F25" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46326</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="9"/>
+      <c r="K25" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="7"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:11" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F23" s="4">
-        <v>46174</v>
-      </c>
-      <c r="G23" s="4">
-        <v>46295</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="J23" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="F24" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G24" s="4">
-        <v>46142</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="F25" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G25" s="4">
-        <v>46357</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="4">
-        <v>45962</v>
-      </c>
-      <c r="G26" s="4">
-        <v>46265</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="7" t="s">
-        <v>134</v>
-      </c>
       <c r="B27" s="7" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>380</v>
+        <v>337</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="4">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="G27" s="4">
-        <v>46295</v>
+        <v>46157</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>379</v>
+        <v>337</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="4">
-        <v>45870</v>
+        <v>46173</v>
       </c>
       <c r="G28" s="4">
-        <v>46234</v>
+        <v>46387</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="J28" s="9"/>
+      <c r="K28" s="17" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="E29" s="8"/>
+        <v>286</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>342</v>
+      </c>
       <c r="F29" s="4">
-        <v>45962</v>
+        <v>46023</v>
       </c>
       <c r="G29" s="4">
-        <v>46265</v>
+        <v>46357</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>259</v>
+      </c>
+      <c r="J29" s="9"/>
+      <c r="K29" s="17" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="8"/>
+        <v>324</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>343</v>
+      </c>
       <c r="F30" s="4">
         <v>46023</v>
       </c>
       <c r="G30" s="4">
-        <v>46173</v>
+        <v>46295</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>255</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31" s="8"/>
+        <v>285</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>344</v>
+      </c>
       <c r="F31" s="4">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="G31" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="J31" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>23</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>379</v>
+        <v>281</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="4">
-        <v>45809</v>
+        <v>46023</v>
       </c>
       <c r="G32" s="4">
-        <v>46326</v>
+        <v>46082</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>249</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="187.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>378</v>
+        <v>52</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="F33" s="4">
-        <v>45962</v>
+        <v>46023</v>
       </c>
       <c r="G33" s="4">
-        <v>46356</v>
+        <v>46357</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="J33" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>252</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>162</v>
+        <v>322</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="4">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="G34" s="4">
-        <v>46265</v>
+        <v>46112</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>244</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="4">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="G35" s="4">
-        <v>46387</v>
+        <v>46112</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>382</v>
+        <v>208</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E36" s="8"/>
+        <v>374</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>346</v>
+      </c>
       <c r="F36" s="4">
         <v>45931</v>
       </c>
       <c r="G36" s="4">
-        <v>46203</v>
+        <v>46112</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>54</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" s="15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>273</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="K36" s="14"/>
+    </row>
+    <row r="37" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>383</v>
+        <v>208</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E37" s="8"/>
+        <v>372</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>346</v>
+      </c>
       <c r="F37" s="4">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="G37" s="4">
         <v>46387</v>
       </c>
       <c r="H37" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="F38" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46387</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39" s="7"/>
+      <c r="J39" s="9"/>
+    </row>
+    <row r="40" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I40" s="7"/>
+      <c r="J40" s="9"/>
+    </row>
+    <row r="41" spans="1:11" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F41" s="4">
+        <v>46204</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46387</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="F42" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46387</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F43" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G43" s="4">
+        <v>46142</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="F44" s="4">
+        <v>45992</v>
+      </c>
+      <c r="G44" s="4">
+        <v>46142</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="216" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F45" s="4">
+        <v>45931</v>
+      </c>
+      <c r="G45" s="4">
+        <v>46053</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F46" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G46" s="4">
+        <v>46112</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F47" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G47" s="4">
+        <v>46203</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F48" s="4">
+        <v>46174</v>
+      </c>
+      <c r="G48" s="4">
+        <v>46295</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F49" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G49" s="4">
+        <v>46142</v>
+      </c>
+      <c r="H49" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="F50" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G50" s="4">
+        <v>46357</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J50" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E51" s="8"/>
+      <c r="F51" s="4">
+        <v>45962</v>
+      </c>
+      <c r="G51" s="4">
+        <v>46265</v>
+      </c>
+      <c r="H51" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="K37" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="7" t="s">
+      <c r="I51" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="4">
-        <v>45931</v>
-      </c>
-      <c r="G38" s="4">
-        <v>46265</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="230.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="4">
-        <v>45839</v>
-      </c>
-      <c r="G39" s="4">
-        <v>46203</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="J39" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="115.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="4">
-        <v>45992</v>
-      </c>
-      <c r="G40" s="4">
-        <v>46142</v>
-      </c>
-      <c r="H40" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="J40" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="K40" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="4">
-        <v>45809</v>
-      </c>
-      <c r="G41" s="4">
-        <v>46173</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="J41" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="K41" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G42" s="4">
-        <v>46173</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="J42" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="4">
-        <v>45962</v>
-      </c>
-      <c r="G43" s="4">
-        <v>46022</v>
-      </c>
-      <c r="H43" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="K43" s="15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F44" s="4">
-        <v>45778</v>
-      </c>
-      <c r="G44" s="4">
-        <v>46203</v>
-      </c>
-      <c r="H44" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J44" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="K44" s="15" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="I45" s="7"/>
-      <c r="J45" s="9"/>
-    </row>
-    <row r="46" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="I46" s="7"/>
-      <c r="J46" s="9"/>
-    </row>
-    <row r="47" spans="1:11" ht="216" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F47" s="4">
-        <v>46174</v>
-      </c>
-      <c r="G47" s="4">
-        <v>46356</v>
-      </c>
-      <c r="H47" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J47" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="172.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G48" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H48" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="158.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="4">
-        <v>46113</v>
-      </c>
-      <c r="G49" s="4">
-        <v>46203</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="J49" s="14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="F50" s="4">
-        <v>45839</v>
-      </c>
-      <c r="G50" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H50" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="I51" s="7"/>
-      <c r="J51" s="9"/>
-    </row>
-    <row r="52" spans="1:11" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="B52" s="7" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>3</v>
+        <v>380</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>360</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="E52" s="8"/>
       <c r="F52" s="4">
         <v>46023</v>
       </c>
       <c r="G52" s="4">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J52" s="14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>158</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="K52" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="7" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>3</v>
+        <v>379</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" s="9"/>
+        <v>311</v>
+      </c>
+      <c r="E53" s="8"/>
       <c r="F53" s="4">
-        <v>46023</v>
+        <v>45870</v>
       </c>
       <c r="G53" s="4">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="J53" s="14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="230.4" x14ac:dyDescent="0.55000000000000004">
+        <v>136</v>
+      </c>
+      <c r="J53" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="K53" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="7" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>3</v>
+        <v>379</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="4">
-        <v>45870</v>
+        <v>45962</v>
       </c>
       <c r="G54" s="4">
-        <v>46142</v>
+        <v>46265</v>
       </c>
       <c r="H54" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="J54" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+        <v>139</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="K54" s="15" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="7" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>310</v>
+        <v>42</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="4">
         <v>46023</v>
       </c>
       <c r="G55" s="4">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="J55" s="14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>142</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="7" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>277</v>
+        <v>145</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="4">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G56" s="4">
-        <v>46326</v>
+        <v>46265</v>
       </c>
       <c r="H56" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="K56" s="15" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>146</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="7" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>24</v>
+        <v>379</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="4">
-        <v>46113</v>
+        <v>45809</v>
       </c>
       <c r="G57" s="4">
-        <v>46356</v>
+        <v>46326</v>
       </c>
       <c r="H57" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="J57" s="15" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="7" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>24</v>
+        <v>378</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="E58" s="8"/>
+        <v>332</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>353</v>
+      </c>
       <c r="F58" s="4">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="G58" s="4">
-        <v>46234</v>
+        <v>46356</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>199</v>
+        <v>151</v>
       </c>
       <c r="J58" s="15" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="7" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>24</v>
+        <v>381</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="4">
         <v>45931</v>
       </c>
       <c r="G59" s="4">
-        <v>46112</v>
+        <v>46265</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>202</v>
+        <v>16</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>163</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="7" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>36</v>
+        <v>275</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="4">
@@ -4134,131 +4086,127 @@
         <v>55</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="J60" s="15" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="7" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="4">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="G61" s="4">
+        <v>46203</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="8"/>
+      <c r="F62" s="4">
+        <v>45992</v>
+      </c>
+      <c r="G62" s="4">
         <v>46387</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="J61" s="9"/>
-    </row>
-    <row r="62" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="F62" s="4">
-        <v>45931</v>
-      </c>
-      <c r="G62" s="4">
-        <v>46203</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J62" s="15" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="7" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>391</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="E63" s="8"/>
       <c r="F63" s="4">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G63" s="4">
-        <v>46387</v>
+        <v>46265</v>
       </c>
       <c r="H63" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="J63" s="16" t="s">
-        <v>178</v>
+        <v>18</v>
+      </c>
+      <c r="J63" s="15" t="s">
+        <v>172</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="230.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>391</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="E64" s="8"/>
       <c r="F64" s="4">
-        <v>45931</v>
+        <v>45839</v>
       </c>
       <c r="G64" s="4">
         <v>46203</v>
@@ -4267,350 +4215,340 @@
         <v>55</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>180</v>
+        <v>327</v>
       </c>
       <c r="J64" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="K64" s="15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>115</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>392</v>
+        <v>41</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>391</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="E65" s="8"/>
       <c r="F65" s="4">
-        <v>45931</v>
+        <v>45992</v>
       </c>
       <c r="G65" s="4">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="H65" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="J65" s="15" t="s">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="4">
-        <v>46054</v>
+        <v>45809</v>
       </c>
       <c r="G66" s="4">
-        <v>46356</v>
+        <v>46173</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>192</v>
+        <v>14</v>
       </c>
       <c r="E67" s="8"/>
       <c r="F67" s="4">
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="G67" s="4">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="J67" s="15" t="s">
-        <v>194</v>
+        <v>121</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="7" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="4">
         <v>45962</v>
       </c>
       <c r="G68" s="4">
-        <v>46112</v>
+        <v>46022</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="K68" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>124</v>
+      </c>
+      <c r="J68" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="K68" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="7" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="E69" s="8"/>
+        <v>127</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>354</v>
+      </c>
       <c r="F69" s="4">
-        <v>46113</v>
+        <v>45778</v>
       </c>
       <c r="G69" s="4">
         <v>46203</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>53</v>
+      </c>
+      <c r="J69" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="K69" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="E70" s="8"/>
-      <c r="F70" s="4">
-        <v>46174</v>
-      </c>
-      <c r="G70" s="4">
-        <v>46265</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
       <c r="H70" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I70" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>78</v>
+      </c>
+      <c r="I70" s="7"/>
+      <c r="J70" s="9"/>
+    </row>
+    <row r="71" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="F71" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G71" s="4">
-        <v>46234</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
       <c r="H71" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I71" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="K71" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>78</v>
+      </c>
+      <c r="I71" s="7"/>
+      <c r="J71" s="9"/>
+    </row>
+    <row r="72" spans="1:11" ht="216" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F72" s="4">
         <v>46174</v>
       </c>
       <c r="G72" s="4">
-        <v>46295</v>
+        <v>46356</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>66</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J72" s="9"/>
-    </row>
-    <row r="73" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>11</v>
+      </c>
+      <c r="J72" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="4">
-        <v>46235</v>
+        <v>46023</v>
       </c>
       <c r="G73" s="4">
-        <v>46295</v>
+        <v>46112</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="J73" s="9"/>
-    </row>
-    <row r="74" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>98</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>355</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E74" s="8"/>
       <c r="F74" s="4">
-        <v>46327</v>
+        <v>46113</v>
       </c>
       <c r="G74" s="4">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="J74" s="9"/>
-    </row>
-    <row r="75" spans="1:11" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>100</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>396</v>
+        <v>3</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="E75" s="8"/>
+        <v>308</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>358</v>
+      </c>
       <c r="F75" s="4">
-        <v>45992</v>
+        <v>45839</v>
       </c>
       <c r="G75" s="4">
         <v>46112</v>
@@ -4619,497 +4557,559 @@
         <v>54</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="K75" s="8"/>
-    </row>
-    <row r="76" spans="1:11" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>104</v>
+      </c>
+      <c r="J75" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>396</v>
+        <v>3</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="E76" s="8"/>
-      <c r="F76" s="4">
-        <v>45778</v>
-      </c>
-      <c r="G76" s="4">
+        <v>325</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I76" s="7"/>
+      <c r="J76" s="9"/>
+    </row>
+    <row r="77" spans="1:11" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="F77" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G77" s="4">
         <v>46203</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="H77" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="I76" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="K76" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="E77" s="8"/>
-      <c r="F77" s="4">
-        <v>46054</v>
-      </c>
-      <c r="G77" s="4">
-        <v>46112</v>
-      </c>
-      <c r="H77" s="12" t="s">
-        <v>54</v>
-      </c>
       <c r="I77" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-    </row>
-    <row r="78" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+      <c r="J77" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="244.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>397</v>
+        <v>3</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E78" s="8"/>
+        <v>107</v>
+      </c>
+      <c r="E78" s="9"/>
       <c r="F78" s="4">
-        <v>45839</v>
+        <v>46023</v>
       </c>
       <c r="G78" s="4">
-        <v>45930</v>
+        <v>46295</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K78" s="8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>108</v>
+      </c>
+      <c r="J78" s="14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="230.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>397</v>
+        <v>3</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="E79" s="8"/>
       <c r="F79" s="4">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="G79" s="4">
-        <v>46022</v>
+        <v>46142</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="J79" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="K79" s="8"/>
-    </row>
-    <row r="80" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>110</v>
+      </c>
+      <c r="J79" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
-      <c r="H80" s="13" t="s">
-        <v>78</v>
+        <v>310</v>
+      </c>
+      <c r="E80" s="8"/>
+      <c r="F80" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G80" s="4">
+        <v>46265</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="J80" s="9"/>
-    </row>
-    <row r="81" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>112</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
-      <c r="H81" s="13" t="s">
-        <v>78</v>
+        <v>277</v>
+      </c>
+      <c r="E81" s="8"/>
+      <c r="F81" s="4">
+        <v>45962</v>
+      </c>
+      <c r="G81" s="4">
+        <v>46326</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J81" s="9"/>
+        <v>204</v>
+      </c>
+      <c r="J81" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="82" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B82" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>397</v>
-      </c>
       <c r="D82" s="8" t="s">
-        <v>81</v>
+        <v>316</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="4">
-        <v>46054</v>
+        <v>46113</v>
       </c>
       <c r="G82" s="4">
-        <v>46203</v>
+        <v>46356</v>
       </c>
       <c r="H82" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="J82" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="K82" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>196</v>
+      </c>
+      <c r="J82" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="K82" s="15" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B83" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>398</v>
-      </c>
       <c r="D83" s="8" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E83" s="8"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
+      <c r="F83" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G83" s="4">
+        <v>46234</v>
+      </c>
       <c r="H83" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I83" s="7"/>
-      <c r="J83" s="9"/>
-    </row>
-    <row r="84" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>55</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J83" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="K83" s="15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C84" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>398</v>
-      </c>
       <c r="D84" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="E84" s="8"/>
+      <c r="F84" s="4">
+        <v>45931</v>
+      </c>
+      <c r="G84" s="4">
+        <v>46112</v>
+      </c>
       <c r="H84" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I84" s="7"/>
-      <c r="J84" s="9"/>
-    </row>
-    <row r="85" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>54</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J84" s="15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>293</v>
+        <v>36</v>
       </c>
       <c r="E85" s="8"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
+      <c r="F85" s="4">
+        <v>45931</v>
+      </c>
+      <c r="G85" s="4">
+        <v>46387</v>
+      </c>
       <c r="H85" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I85" s="7"/>
-      <c r="J85" s="9"/>
-    </row>
-    <row r="86" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>55</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="J85" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>27</v>
+        <v>336</v>
       </c>
       <c r="E86" s="8"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
+      <c r="F86" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G86" s="4">
+        <v>46387</v>
+      </c>
       <c r="H86" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I86" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>189</v>
+      </c>
       <c r="J86" s="9"/>
     </row>
-    <row r="87" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="E87" s="8"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
+        <v>272</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="F87" s="4">
+        <v>45931</v>
+      </c>
+      <c r="G87" s="4">
+        <v>46203</v>
+      </c>
       <c r="H87" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I87" s="7"/>
-      <c r="J87" s="9"/>
-    </row>
-    <row r="88" spans="1:11" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>55</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="J87" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="K87" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E88" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>391</v>
+      </c>
       <c r="F88" s="4">
-        <v>45809</v>
+        <v>45962</v>
       </c>
       <c r="G88" s="4">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="H88" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J88" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="K88" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>177</v>
+      </c>
+      <c r="J88" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="K88" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="E89" s="8"/>
+        <v>334</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>391</v>
+      </c>
       <c r="F89" s="4">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G89" s="4">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="H89" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J89" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K89" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>180</v>
+      </c>
+      <c r="J89" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="K89" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="E90" s="8"/>
+        <v>314</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>391</v>
+      </c>
       <c r="F90" s="4">
-        <v>46113</v>
+        <v>45931</v>
       </c>
       <c r="G90" s="4">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="H90" s="12" t="s">
         <v>55</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="K90" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>183</v>
+      </c>
+      <c r="J90" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="K90" s="15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>366</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="E91" s="8"/>
       <c r="F91" s="4">
-        <v>46204</v>
+        <v>46054</v>
       </c>
       <c r="G91" s="4">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="H91" s="12" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="J91" s="9"/>
-      <c r="K91" s="8" t="s">
-        <v>68</v>
+        <v>13</v>
+      </c>
+      <c r="J91" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="K91" s="15" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
+        <v>192</v>
+      </c>
+      <c r="E92" s="8"/>
+      <c r="F92" s="4">
+        <v>46023</v>
+      </c>
+      <c r="G92" s="4">
+        <v>46203</v>
+      </c>
       <c r="H92" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I92" s="7"/>
-      <c r="J92" s="9"/>
+        <v>55</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="J92" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="K92" s="15" t="s">
+        <v>195</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K92">
-    <sortCondition ref="A2:A92"/>
-    <sortCondition ref="B2:B92"/>
-    <sortCondition ref="C2:C92"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A27:K92">
+    <sortCondition ref="A27:A92"/>
+    <sortCondition ref="B27:B92"/>
+    <sortCondition ref="C27:C92"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emretasci\antigravity\scm-project-portal\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14EFD87-0232-443D-8663-C5A0EBC57200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="420">
   <si>
     <t>Tahminleme</t>
   </si>
@@ -67,15 +67,6 @@
   </si>
   <si>
     <t>Dijital Dönüşüm Merkezi</t>
-  </si>
-  <si>
-    <t>Mevcut taleplerin karşılanmasının ötesinde, belirli müşteri-ürün gruplarına yönelik yüksek kar oluşturan çalışma şeklinin ortaya çıkarılması ve gerçekleştirilmesini sağlayacak şekilde, farklı amaç fonksiyonlarına sahip optimizasyon aracı geliştirilecektir. Bu araç hat yetenekleri ve talep kısıtlarına göre maksimum kar için talep planının oluşturulmasını sağlayacaktır.</t>
-  </si>
-  <si>
-    <t>S&amp;OP süreci talep ve tedarik planlama adımlarından çıkan bilgilerin fiyat, maliyet, başta olmak üzere diğer finansal girdilerin kullanılarak tutarsal hale getirilmesi ve raporlanması çalışmasıdır. Buradan çıkan farklı senaryolar bazındaki finansalların değerlendirilmesi ile operasyonel planlara karar verilmesi sağlanacaktır. Bu çalışma In-house olarak yapılmaktadır.</t>
-  </si>
-  <si>
-    <t>SAP sistemi içinde saklamalı sipariş, teyit-termin gibi şirkete özel olarak oluşturulmuş ve standart akışın dışına çıkan yaklaşımlar yerine aATP gibi (Advanced Available-to-Promise) standart çözümlerin kullanımına geçilmesi hedeflenmektedir. Bu çalışma kapsamında sipariş önceliklendirme için parametrelerin belirlenmesi, optimizasyon modelinin oluşturulması ve entegre planlama sürecine sipariş önceliklendirme fonksiyonunun entegrasyonu da hedeflenmektedir.</t>
   </si>
   <si>
     <t>Bu çalışma ile planlama sürecine şirket içindeki bilgilere ilave olarak, bayi ağımızdaki KS ürünleri satış ve stok bilgilerinin de eklenerek planlama sürecinin etkinliğinin artırılması hedeflenmektedir.</t>
@@ -147,9 +138,6 @@
     <t>Satınalma</t>
   </si>
   <si>
-    <t>SRM DÖF Modülünün Devreye Alınması</t>
-  </si>
-  <si>
     <t>Tedarikçi Geliştirme</t>
   </si>
   <si>
@@ -211,10 +199,6 @@
   </si>
   <si>
     <t>Devam Ediyor</t>
-  </si>
-  <si>
-    <t>Mevcutta kullanılan talep tahmin uygulaması, geliştirilmesi devam eden finansallaştırma rapor uygulaması, geliştirilmesi planlanan talep planlama uygulaması çözümlerinin bir paket olarak birbirine bağlanmış bir ürün hale getirilmesi çalışmasıdır.
-In-house olarak ürünleştirme çalışmasından verim alınamaması durumunda yapılmış olan RFP çalışmasına istinaden ürün araştırılması çalışması yine bu çalışma kapsamındadır.</t>
   </si>
   <si>
     <t>Ürün ve palet kg bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
@@ -241,16 +225,6 @@
   </si>
   <si>
     <t>Satış tahmin fonksiyonunun şirket iş süreçlerinde kullanımı ve tahmin yetkinliğinin arttırılmasına yönelik çalışmaları kapsamaktadır.  Tahmin sonuçlarının S&amp;OP, BE ve bütçe çalışmalarında girdi olarak kullanılması, ilerleyen süreçlerde ise SKU seviyesinde tahminlerin yapılması ve bu tahminlerin entegre planlama sürecinde kullanılması amaçlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Tahmin modelinin tekrar eğitilmesine yönelik çalışmalar tamamlanmıştır.
-Tahmin sonuçlarının raporlanmasına ilişkin isterler belirlenerek piyasa ve DFU bazlı tahmin raporları oluşturulmuştur.
-Tahmin sonuçlarının S&amp;OP döngüsüne girdi olarak kullanılmasına ilişkin çalışmalar başlatılmıştır.
-Baz tahminler piyasalar ile paylaşılarak talep zenginleştirme çalışmaları yürütülmektedir.
-Tahmin sonuçlarının düzenli olarak çalıştırılarak takip edilmektedir.
-Tahmin doğruluğu metriklerinin belirlenmiştir. Düzenli olarak hesaplanarak takip edilmektedir.
-Baz tahmin, revize baz tahmin, revize tahmin, nihai tahmin sonuçlarının ve tahmin sapmalarının görüntülenmesine ilişkin Power BI raporlama dashboardu oluşturulmuştur.
-SKU seviyesinde tahmin sonuçlarının planlama süreçlerinde kullanılmaktadır.</t>
   </si>
   <si>
     <t>İptal</t>
@@ -274,9 +248,6 @@
     <t>Finansallaştırma adımının eklenmesi ile birlikte S&amp;OP döngüsünün tamamlanması</t>
   </si>
   <si>
-    <t>Mevcut talep tahmin uygulamasının çıktısını kullanarak tedarik planlama adımına girdi olacak ve mutabakat sağlanmış talep değerlerinin oluşturulmasını sağlayacak talep zenginleştirme ve mutabakat uygulamasının geliştirilmesi çalışmasıdır. Tahmin sonuçlarının girdi olarak alınabildiği, belirli hiyerarşilerde düzeltme yapılabildiği, belirli kişilerin üzerinde çalışabildiği ve veri girişi yapabildiği esnek bir ortam geliştirme çalışmasıdır. Farklı senaryoların oluşturulabilmesi ve loglama özelliklerini de içermelidir. Low-code platformlar ile In-house olarak geliştirilmesi düşünülmektedir.</t>
-  </si>
-  <si>
     <t>İstekler belirlenerek kavramsal tasarım dokümanı IT birimine iletilmiştir.
 Yazılım ve KS ekibi kavramsal tasarım üzerinde mutabakat sağlamıştır.
 İş akış dokümanı oluşturulmuştur ve IT ekibine iletilmiştir.
@@ -290,9 +261,6 @@
     <t>Talep tahmini, talep zenginleştirme, tedarik planlama, finansallaştırma, optimizasyon özelliklerini içeren komple bir entegre planlama süreci için tool araştırmaya kaynak olacak KS ihtiyaçlarının belirlenmesi çalışmasıdır.</t>
   </si>
   <si>
-    <t>Tedarik zinciri süreçlerinin, beklenen hizmet seviyesini karşılayacak şekilde çalışabilmesi için öncelikle müşteri-ürün boyutlarında farklılaşan beklenen hizmet seviyelerinin tanımlanması gerekmektedir. Bu projede müşteri-ürün boyutları bazında belirlenmiş gruplar/ kanallar için bu servis seviyelerinin tanımlanması amaçlamaktadır. Bu şekilde genel çalışma (standart hizmet) ve metrik takibinden, kategorize edilmiş ve tanımlanmış ihtiyaçların karşılandığı ve bunların ölçümü ile performans takibinin yapıldığı sisteme geçilebilecektir.</t>
-  </si>
-  <si>
     <t>Hizmet seviyesinin belirlenebilmesi için çalışma yapılacak boyutlara karar verilmesi (müşteri, ürün, sipariş tipi),
 Bu boyutlar bazında piyasa bazlı çalışma gruplarının oluşturulması (yapı market, mağaza, bayi kanalı gibi)
 Müşteri, ürün ya da sipariş bazında farklılaşan hizmet seviyesini belirlemeye yardımcı olacak tanımlamaların oluşturulması (çalışılan ürünler, sipariş süreçleri, teslim/nakliye şartları, beklenen stok seviyeleri, lead time vb)</t>
@@ -306,37 +274,10 @@
     <t>Tanımlanan hizmet seviyelerini sağlayacak şekilde tedarik zinciri aksiyon planlarının oluşturulması</t>
   </si>
   <si>
-    <t>Müşteri / Ürün boyutlarında hizmet seviyelerinin tanımlanması çalışmasından sonra bu seviyeleri karşılayacak tedarik zinciri aksiyonlarının oluşturulması çalışmasıdır. Bu şekilde genel çalışma (standart hizmet) ve metrik takibinden, kategorize edilmiş ve tanımlanmış ihtiyaçların karşılandığı ve bunların ölçümü ile performans takibinin yapıldığı sisteme geçilebilecektir.</t>
-  </si>
-  <si>
     <t>Tanımlanan hizmet seviyelerinin kontrolü amacıyla tedarik zinciri performans metriklerinin oluşturulması ve takibi</t>
   </si>
   <si>
-    <t xml:space="preserve">S&amp;OE süreci, onaylanmış S&amp;OP /Ana Üretim Planı çerçevesinde; kısa vadeli (günlük / haftalık) dönemde oluşan talep, stok ve sevkiyat sapmalarını hızlı kontrollü şekilde yönetmeyi amaçlayan, operasyonel bir karar alma sürecidir. </t>
-  </si>
-  <si>
-    <t>S&amp;OP toplantıları aylık olarak devam etmektedir. Bu toplantılarda stok seviyesi (müşterili/serbest), üretim planları, talep değişkenlikleri, üretim öncelikleri, stok varken sevkiyat aksaması veya stok artışı gibi bilgiler kontrol edilmektedir. 
-Süreç Kapsamının ve Zaman Ufku haftalık olarak belirlendi
-Kritik karar konuları tamamlandı.
-Roller ve sorumluluklar netleştirildi. Paylaşılacak tablolar netleştirildi.
-Planlama olarak güncel tutulan tablolar üzerinden veri setleri oluşturuldu.
-Önceliklendirme ve Karar Kurallarının oluşturuldu.
-Toplantı yapısı katılımcılar ve periyotları belirlendi.KPI ve Başarı Göstergeleri S&amp;OP toplantılarında konuşulan aylık hedeflerin haftalık periyotlara bölünmüş hali olarak belirlendi. (Plana Uyum, Fazla Üretim vs.)
-Pilot Uygulama 7 Şubat tarihinde yapılacak ve Salı günleri haftalık olarak devam edecek.</t>
-  </si>
-  <si>
     <t>Bu proje kapsamında; tanımlanan Sales &amp; Operations Execution (S&amp;OE) süreci, belirlenen kapsam, roller, veri setleri ve karar kuralları doğrultusunda operasyonel olarak devreye alınacaktır. Amaç; onaylanmış S&amp;OP ve ana üretim planları çerçevesinde, kısa vadede (günlük / haftalık) oluşan talep, üretim, stok ve sevkiyat sapmalarını standart bir toplantı ritmi ve veri seti ile yönetmek, alınan kararların sahada fiilen uygulanmasını ve takibini sağlamaktır.</t>
-  </si>
-  <si>
-    <t>S&amp;OP toplantıları aylık olarak devam etmektedir. Bu toplantılarda stok seviyesi (müşterili/serbest), üretim planları, talep değişkenlikleri, üretim öncelikleri, stok varken sevkiyat aksaması veya stok artışı gibi bilgiler kontrol edilmektedir. 
-Pilot kapsamın netleştirilmesi
-S&amp;OE Toplantı Ritminin başlatılması (1 Mart itibariyle başlatılacaktır)
-Standart veri seti ile operasyonun yürütülmesi
-Önceliklendirme ve karar kurallarının uygulanması
-Aksiyon Takibi ve Disiplinin Sağlanması
-Eskalasyon Mekanizmasının İşletilmesi
-KPI takibi ve ilk etki ölçümü
-Geri Bildirim ve iyileştirme</t>
   </si>
   <si>
     <t>Teyit-Termin Yapısının  İyileştirilmesi</t>
@@ -729,72 +670,16 @@
     <t>E-İhale faaliyetlerinin dijital, şeffaf, izlenebilir ve standart bir yapıya kavuşturulması amaçlanmaktadır. İhale planlama, teklif toplama, değerlendirme, onay ve raporlama süreçlerinin sistem üzerinden yönetilmesi, manuel ve e-posta bazlı süreçlerin ortadan kaldırılması hedeflenmektedir.</t>
   </si>
   <si>
-    <t xml:space="preserve">*Teknik SA kategorisinde teklifler, siparişler ihaleler dijital olarak SRM üzerinden toplanmaktadır. (3600+ işlem)
- *Yeni cari tanımlarında vSRM dijital uygulaması ve BP entegrasyonu devreye alınmış ve 87 yeni cari kaydı vSRM üzerinden yapılmıştır.
-*Satın alma ihalesinde açık artırma parametresinin uygulamaya dahil edilmesi.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Satış ihalesi sürecinin SRM’ e tanımlanması. 
-* SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır.
-</t>
-  </si>
-  <si>
     <t>Tedarikçi kaynaklı uygunsuzluklar, denetim bulguları, performans düşüşleri ve şikâyetler sonucunda başlatılan Düzeltici ve Önleyici Faaliyet (DÖF) süreçlerinin SRM sistemi üzerinden dijital, izlenebilir ve standart bir yapıya kavuşturulması amaçlanmaktadır. DÖF açma, takip etme, aksiyonların izlenmesi ve kapanış süreçlerinin manuel ve dağınık yöntemler yerine tek bir merkezi sistem üzerinden yönetilmesi hedeflenmektedir.</t>
   </si>
   <si>
-    <t>*Ambalaj kategorisinde Kalite Birimi tarafından aktif kullanılmaktadır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Diğer SA kategorilerinde DÖF modülünün kullanılması yaygınlaştırılacaktır. Örnek Hammadde için Ar-Ge girdi kontrol kullanımı.
-* Kategorilerde denetim kayıtlarının vSRM üzerinden yürütülmesi ve tedarikçiye iletilmesi.
-</t>
-  </si>
-  <si>
     <t>SRM Sipariş Modülünün kullanım etkinliğini artırmak, mevcut kullanım problemlerini gidermek ve satın alma–tedarikçi süreçleri arasında daha hızlı, hatasız ve izlenebilir bir sipariş yönetimi sağlamak amaçlanmaktadır.</t>
   </si>
   <si>
-    <t xml:space="preserve">* Faz 1; Tedarikçi bazında kullanım (siparişlerin onayı ve irsaliye girişleri) oranlarının arttırılması ve süreç işlemlerin (SAS) iyileştirilmesi sağlanmıştır. 32 tedarikçinin % 58’ inde kullanıma geçilmiştir. 
-* Teknik Satın alma kategorisinde hizmet alanında teklif ve siparişlerin oluşturulması %100 oranında devreye alınmıştır, stok kodlu alımlarda da kullanılmaya başlanmıştır.
-* Bölgesel ve Merkezi Hizmet kategorisinde ilgili sipariş modulü eğitimi alınmıştır.
-* Teknik hizmet iş kabullerinde VSRM üzerinden gerekli süreç tamamlanmıştır, 01.04.2026 tarihinde devreye alınmıştır.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Bölgesel Hizmet ve Merkezi Satın alma kategorilerinde sipariş modülü kullanıma başlanacaktır.
-* Bölgesel Hizmet kategorisi için ilgili kullanıcılara (talep sahibi, tedarikçi) süreç hakkında bilgi verilecektir. Talepler vSRM üzerinden alınarak satın alma süreci başlatılacaktır.        
-*vSRM dışı talep kabul edilmeyecektir. Taleplerin vSRM üzerinden alınması planlanmaktadır.
-*vSRM kullanımı sipariş girişi sağlayan ambar birimlerine yaygınlaştırılacaktır.
-*Siparişlerin hızlanması için vSRM üzerinden SAT açılması işlemlerinin otomatik olarak çalışması yapılmaktadır. Mayıs ayına kadar tamamlanması planlanmaktadır.
-</t>
-  </si>
-  <si>
     <t>Mevcut tedarikçi değerlendirme yapısını gözden geçirerek; daha objektif, ölçülebilir, şeffaf ve sürdürülebilir bir değerlendirme sistemi oluşturmak amaçlanmaktadır. Tedarikçi değerlendirme kriterlerinin standartlaştırılması, dijitalleştirilmesi ve satın alma kararlarına doğrudan girdi sağlayacak bir yapıya kavuşturulması hedeflenmektedir.</t>
   </si>
   <si>
-    <t xml:space="preserve">* Tedarikçi Değerlendirme Sistemi yeniden kurgulandı. Performans kriterleri ve puanlama yapısı oluşturuldu.
-* 2025 yılı tedarikçi değerlendirmesi 2026 Ocak ayı içinde tamamlandı.
-* Tedarikçi değerlendirme sonuçları iç müşteriler ve tedarikçiler  ile paylaşıldı.
-* Tedarikçi değerlendirme süreci ITG firması tarafından örnek bir model gösterimiyle anlatıldı, KPI listesi paylaşıldı. 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Tedarikçi değerlendirme sürecinde kullanılabilecek vSRM sisteminde yer alan KPI listesi kontrolü ve sisteme entegre edilmesi. 
-</t>
-  </si>
-  <si>
     <t>Mevcut tedarikçilerin performans, kalite, maliyet, teslimat, sürdürülebilirlik ve uyum kriterleri doğrultusunda geliştirilmesini sağlamak; tedarik zincirinin genel verimliliğini ve sürekliliğini artırmak amaçlanmaktadır. Tedarikçi performansının sistematik olarak izlenmesi, gelişim alanlarının belirlenmesi ve bu alanlara yönelik yapılandırılmış geliştirme planlarının hayata geçirilmesi hedeflenmektedir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Tedarikçilerimizin verdiği teknik eğitimlerle hem kendi kullanıcımız hem de tedarikçimizin ürününün doğru kullanılması ile optimum sonuçlara ulaşılmaktadır.
-* Ambalaj ve Tamamlayıcılar kategorisinde tedarikçilerimize açtığımız DÖF’ler ile ilgili malzeme geliştirmeleri yapılmakta ve bilgiler vSRM sistemi üzerinden kayda alınmaktadır.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* DÖF yapısının vSRM modülü üzerinden Bölgesel ve Merkezi hizmet, Ambalaj ve Tamamlayıcılar, Hammadde ve Kimyasallar kategorisine de yaygınlaştırılması sağlanacaktır.
-*Tedarikçi performans verilerinin vSRM (kalite, maliyet, teslimat, hizmet vb.) değerlendirilmesi.
-* Yapılan tedarikçi değerlendirmeleri sonucunda tedarikçilerle paylaşılan sonuçlara istinaden gelişim alanlarının belirlenmesi. Örneğin termin anlamında düşük puan alan tedarikçilerin geliştirilmesi vs.
-</t>
   </si>
   <si>
     <t xml:space="preserve">Bu çalışma ile tedarikçi değerlendirme ve diğer verilerin yapay zeka ve ileri analitik çözümlerde kullanılması ile maliyet, kalite, sürdürülebilirlik ve risk kriterleri doğrultusunda tedarikçi ağı optimizasyonunun yapılması hedeflenmektedir. 
@@ -802,77 +687,22 @@
 </t>
   </si>
   <si>
-    <t>*Tedarikçi Benchmark çalışmaları yapılmıştır. 2 grup halinde farklı iki firma olan Sofra firması ve Dalgakıran firmaları satınalma yapısı olarak incelenmiştir. Sofra firmasından tedarikçi değerlendirme anlamında örnekler alınmıştır. 
-*Çin pazarı tedarik ürünler satınalmasında Know how gelişimi için Trome firmasıyla aktif çalışmaya başlanılmıştır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Maliyet yapıları ve fiyat kırılımları bilgisinin geliştirilmesi.
-Piyasa Emtialarının ve artış tahmin oranlarının bir bülten üzerinden takibinin yapılması ve geliştirilmesi.
-*Kategori bazlı tedarikçilerin üretim hatlarının görüleceği ve teknik değerlendirilmesinin yapılabileceği ziyaret planlaması yapılacaktır. 
-</t>
-  </si>
-  <si>
     <t>Fiyat Geçiş Sistemini  Oluşturulması</t>
   </si>
   <si>
     <t>Tedarikçilerden gelen fiyat değişiklik taleplerinin (artış/azalış) standart, şeffaf, kontrollü ve izlenebilir bir sistematik ile yönetilmesi amaçlanmaktadır.</t>
   </si>
   <si>
-    <t xml:space="preserve">*FRM.GEN.SAT.031 form kodu ile Satın alma Fiyat Değişim Onay Formu oluşturulmuştur.
- *İŞT.GEN.SAT.002 form kodu ile Satın alma Fiyat Değişim Onay Talimatı oluşturulmuştur.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Fiyat Değişim Onay hiyerarşisinin SAP kurgusu Strateji birimiyle görüşülecektir. 
-</t>
-  </si>
-  <si>
     <t>Satın alma taleplerinin standart, doğru, eksiksiz ve izlenebilir şekilde oluşturulmasını sağlamak; satın alma süreçlerinde yaşanan gecikmeleri, tekrarları ve hatalı talepleri azaltmak amaçlanmaktadır.</t>
   </si>
   <si>
-    <t xml:space="preserve">* Satın alma taleplerinin Teknik SA kategorisinde e-posta/telefon yerine SRM sistemi üzerinden alınıp yürütülmektedir.
-* Teknik satınalma kategorisinde talepler teknik dokümanlar la birlikte SRM sistemi üzerinden alınmaya başlanmış ve tedarikçiye yine SRM sistemi üzerinden ihale, teklif toplama vb. şeklinde iletilmektedir. 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* SRM sistemi işlemlerinde Hizmet SAT’ larının talep sahibi onayı ile otomatik olarak SAP sisteminde yaratılması ve SRM sistemi ile entegre olması planlanmaktadır. 
-</t>
-  </si>
-  <si>
     <t>Teknik hizmetlerin (bakım, onarım, montaj, mühendislik, servis vb.) sözleşme, teknik şartname ve kalite beklentilerine uygunluğunun sistematik, standart ve izlenebilir şekilde kontrol sürecinin SRM sisteminde yapılması amaçlanmaktadır.</t>
   </si>
   <si>
-    <t xml:space="preserve">* Teknik hizmet alımlarında alınan hizmetin kontrolü E-flow sisteminde yer alan uygulama ile yapılmakta; talep sahipleri faturalara dijital onay vermektedir.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRM sisteminde ilgili kurgunun tanımlanması  
-    - Firma tarafından hizmet teslimi onayı
-    - Talep sahibi ve üst amir onayı
-    - Firmaya fatura düzenlenmesi için bilgi kaydı 
-    - Faturanın sistem tarafından ön kaydının yapılması
-Bu kurgu devreye alındığında E-flow süreci sonlanacaktır. 
-</t>
-  </si>
-  <si>
     <t>Satın alma siparişlerinin (SAS) tutar hiyerarşisine göre onay yetkilendirmelerinin oluşturulması, sürecin işletilmesi ve yaygınlaştırılması amaçlanmaktadır.</t>
   </si>
   <si>
-    <t xml:space="preserve">* Stok kodlu ve hizmet siparişlerinde SAS onay sistemi kullanılmaktadır.
-* Strateji tarafında SAS onay limitleri ve yetki tablosu belirlenmiştir. 
-</t>
-  </si>
-  <si>
     <t>Fatura kayıt süreçlerinde gerçekleştirilen manuel, tekrarlayan ve zaman alan işlemlerin Robotik Proses Otomasyonu (RPA) ile otomatikleştirilerek; işlem sürelerinin kısaltılması, hata oranlarının azaltılması ve satın alma/mali işler süreçlerinde verimliliğin artırılması amaçlanmaktadır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Robot tarafından kayıt edilmesi planlanan tedarikçiler belirlenmiş, sisteme ……….. cari tanımlanmıştır.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* Döviz bazlı faturaların RPA sürecine dahil edilmesi.
-* Robot tarafından yapılan kayıtların miktarının artırılması.
-</t>
   </si>
   <si>
     <t>Dijital Dönüşüm</t>
@@ -894,286 +724,46 @@
 Kurutuculardan toplanan operasyonel verilerin (sepet no, sepet id, tur bilgisi, çıkış sıcaklığı, doğalgaz sarfiyatı vb.) analitik yöntemlerle işlenmesi ve yapay zekâ destekli modeller kullanılarak  dikey kurutucunun her bir çevirimi için verimlilik artırımı ve enerji tasarrufu sağlanması.</t>
   </si>
   <si>
-    <t>IoT sensörlerinden pres ve kurutucuya ait anlık veriler toplanmaktadır.​
-Makine parametreleri ile hat duruş bilgileri zaman etiketi üzerinden eşleştirilmiştir.​
-Dikey kurutucunun tüm raflarının aktif kullanımı için zaman serisi analizi tamamlanmıştır.​
-Veri görselleştirme dashboard’ları geliştirilmiştir​
-Rapor her gün süreç sahipleri ile paylaşılmaktadır.​
-OEE (Overall Equipment Effectiveness) artışı gerçekleşmiştir​
-Enerji tüketimi %3 azalma sağlanmıştır​
-​</t>
-  </si>
-  <si>
-    <t>Makine öğrenmesi tabanlı tahminleme (enerji tüketimi, duruş, fire riski, verimlilik)​
-Kurutma bilgileri ile Faz-2 olarak fire korelasyonu çalışması yapılacaktır.​
-Kurutma yaşam döngüsü verileri ile kestirimci kalite çalışmaları</t>
-  </si>
-  <si>
     <t>Masse hazırlık süreci ile karo üretim sürecini tek bir dijital izlenebilirlik zincirinde birleştirmek. Hammadde dozajından başlayıp, öğütme – kurutma – stoklama – presleme – sırlama – pişirim – fırın sonrası işlemler aşamalarına kadar tüm değer zincirini uçtan uca dijital olarak izlemek, veriye dayalı karar alma ve optimizasyon sağlamak.</t>
   </si>
   <si>
-    <t>MES ve SAP entegrasyonu tamamlandı​
-IoT sensörleri ve SCADA sistemlerinden veri toplama süreci tamamlandı​
-Verinin depolanması ve veri kullanım senaryoları oluşturuldu​
-Gerçek zamanlı dashboard’lar (enerji, kalite, fire, OEE) oluşturuldu​</t>
-  </si>
-  <si>
-    <t>Reçete ve tüm (Masse+Üretim) proses parametreleri ile ürün kalitesi arasındaki korelasyon analizi yapılacak​
-En çok yaşanan firelerin veri gölü içindeki sebep sonuç korelasyonları araştırılarak kök neden analizi yapılacak​
-Makine öğrenmesi ile oluşturulan modeller kullanılarak canlı makine parametreleri için kurallar tanımlanıp kestirimci kalite uyarıları hazırlanacak​
-Fırın çıkışında fire olacağı öngörülen karoların pişirim öncesi bertaraf edilerek ham kırık olarak geri kazanılması ​</t>
-  </si>
-  <si>
     <t>Seramik üretiminde en fazla enerji tüketimi bulunan pişirim sürecinin verimliliğinin sürekli olarak izlenmesi, olası verimlilik düşüklüklerinin bildirilmesi</t>
   </si>
   <si>
-    <t>Fırın halı besleme veriminin çıkarılabilmesi için gerekli veriler toplanmıştır​
-Fırın besleme verileri istatistiksel analizi sonucunda optimum besleme süresi 13,96 sn olarak hesaplanmıştır.​
-Fırın girişi 7 farklı inverter ve 2 kompanzatör ile beslenmektedir. Bu karmaşık yapı içerisinde fırın besleme formülüzasyonu oluşturulmuştur.​
-Yapılan otomasyon iyileştirmesi ile iki karo arasındaki mesafeyi 0,01 sn hassasiyetiyle ölçülebilen sistem geliştirilmiştir ​
-Fırın halı besleme oranının canlı takibi ve verimlilik düşüşü (fırın devrinde ürün ağacından sapma, aralıklı besleme, vb) durumlarında ölçüm ve raporlama sistemi kuruldu​
-Duruş ve boşluklu besleme kaynaklı kapasite kayıpları ölçülerek günlük olarak raprolanmaya başlandı.​
-​</t>
-  </si>
-  <si>
-    <t>Farklı üretimlerde farklı fırın rejimleri kod içerisine eklenerek dinamik kontrol geliştirilecektir.​
-Fırın besleme sisteminin operatör kontrolünden çıkarılarak 24 saat canlı izlenmesi sağlanacaktır​
-KB7 yaygınlaştırması planlanacaktır.</t>
-  </si>
-  <si>
     <t>Mevcut sistemde ürün ağacına göre boya girilerek yapılan masse renklendirme işlemi yerine hazırlanan çamura uygun miktarda boya tahminlemesi modeli kurularak deneme miktarının azaltılması ve verimliliğin artırılması.</t>
   </si>
   <si>
-    <t>Masse çamuru içerisine reçeteye göre boya girme işlemi yapılarak çamur renklendirilir. ​
-Renk ölçümü sonrasında tekrar müdahale edilerek hedefe ulaşılmaya çalışılmaktadır. ​
-Hammaddeler girdi kontrol şartlarını sağlasalar da renk performansları her partide farklı olabilmekte ve ürün ağacına uymamaktadır. ​
-​
-​
-​
-​</t>
-  </si>
-  <si>
-    <t>Girdi kontrol QM verileri ve MES sistemi laboratuvar kontrol verileri ile model geliştirilecektir. ​
-Hazırlanan çamura uygun boya ihtiyacının dinamik reçete ile tahminlenmesi için ileri analitik çalışması yapılacaktır.​
-​</t>
-  </si>
-  <si>
     <t>Değirmenlerde kullanılan bilya ve iç kaplama kaynaklı verimsizliklerin yapay zekâ destekli tahminlenmesi ve kestirimci bakım planı için çalışması.</t>
   </si>
   <si>
-    <t>Öğütme öncesi tüm hammaddelerin QM verileri alınmıştır. ​
-Kullanılan reçeteler ile hangi hammaddeden ne oranda kullanıldığı mevcuttur.​
-Değirmenin dönme süresi bilinmektedir.​
-Değirmene ek müdahale verileri alınmıştır.​
-Laboratuvar ölçümleri ile ek tur öncesi ve sonrası kabakum miktarı bilinmektedir.​
-​</t>
-  </si>
-  <si>
-    <t>Fabrikalar içerisinde çalışan tüm makinaların yaptıkları her öğütme döngüsü sonrası birbirleri ile kıyaslamalı data seti oluşturulacaktır.​
-Farklı değirmenlere giren farklı reçetelerin çıktıları toplanarak dinamik work index çıkarılabilmekte ve kıyaslamalı olarak değirmen verimine ulaşılacaktır.​
-Sürekli izlenen verimde azalma tespit edildiğinde alarm oluşturulabilecektir.​
-Envanter takip ekranları ile değirmenlere yapılan bilya beslemeleri kaydedilecektir.​</t>
-  </si>
-  <si>
     <t>Canlı Rutubet Ölçümü ile Model kurularak Sprey kurutucu ısılarına müdahale eden robot geliştirilerek sprey çıkışı rutubetin sürekli stabil tutulması sağlanacaktır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rutubet cihazının kurulumu ve PC bağlantıları tamamlandı​
-Üretilen farklı reçetelerdeki hammaddeler için cihaz kalibrasyonu ve ölçüm reçetesi oluşturulması tamamlandı​
-Veri doğrulama ve veri seti oluşturma tamamlandı.​
-MES sistemi ile sprey kurutucu makine parametreleri toplandı.​
-Sprey dryer ve rutubet ölçüm cihazı arasındaki gecikme farkı hesaplandı.​
-Sprey dryer da önemli parametrelerin belirlenmesi için analiz çalışması yapıldı.​
-Canlı rutubet takibi ile canlı makine verileri arasındaki korelasyon için veri analitiği çalışmaları yapılarak model oluşturulmuştur. Modelin doğruluğu sahada test edilecektir.​
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oluşturulan modelin canlı veri üzerinden testleri yapılarak güvenilirlik kontrolü yapılacak.​
-Model saha entegrasyonu yapılacak.​
-Kurutma makine parametreleri ile rutubet ölçümü arasındaki gecikme zaman farkı hesaplanarak veri eşleşmesi yapılacaktır. ​
-</t>
-  </si>
-  <si>
     <t>Mevcutta yapılan parti bazlı ürün ve ürün ağacı takibinin tekil karo bazlı yapılması hedeflenmektedir.</t>
   </si>
   <si>
-    <t>MES sistemi ile tekil karo bazlı takip yapılabilmektedir. ​
-Granit fabrikası ve granit masse üretimi arasında pilot çalışma planlanmıştır.​
-Tüketim datalarının SAP üzerinden anlık çıkışı için algoritma düzenlenmiştir. ​
-Dijital tartım ünitelerine takılan IOT cihazları SCADA akışını bozduğundan dolayı yeni çalışma yapılması planlanmıştır.​
-​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Her bir karonun tüm yaşam döngüsü bilindiğinden canlı makine verileri ile ürün ağacı kıyaslaması yapılacaktır.​
-Karo üretiminde kullanılan masse, sır, doğalgaz, elektrik, işçilik vb. veriler canlı ve otomatik sarf edilecektir.​
-İş emrinin ürün ağacına göre çıkarılan fiili standart maaliyet oranı her bir karo çözünürlüğünde bakılarak trend analizi yapılacaktır. ​
-</t>
-  </si>
-  <si>
     <t>Masse ve sır için geçmiş üretim verilerinden öğrenen bir yapay zekâ sistemine dayanacaktır.    Modelin amacı deneme-yanılma sürecini ortadan kaldırmak, üretim verimliliğini artırmak, ürün kalitesinde sürdürülebilirliği garanti altına almak, hammadde kullanımında optimizasyon sağlamaktır.</t>
   </si>
   <si>
-    <t>Gerekli olan tüm veriler MES sistemi içinde toplanmaya başlamıştır.​
-Modeli oluşturacak uygun veri seti büyüklüğü için tespit çalışmaları devam etmektedir.​
-Proje için üç konsorsiyum ile Horizon ön başvurusu yapılmış, sonuçları beklenmektedir.​</t>
-  </si>
-  <si>
-    <t>Nihai ürün kalite kontrol verileri ile tüm girdilerin korelasyonu sağlanacak​
-Reçete hammadde ve/veya oran değişimlerinin nihai ürüne etkisinin analizi yapılacak ​
-Üretim şartlarına uygun hammadde ihtiyacı öneri sistemi kurulacak​
-Projenin yazılım bütçesinin AB fonlarından karşılanması planlanmaktadır.​</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fırın verimliliğinin canlı takibi projesinin tamamlanmasından sonra Faz-2 olarak canlı takip sonuçlarının üretim sarf, reçete bilgisi ile optimize edilerek AI destekli izleme sisteminin kurulması hedeflenmektedir. </t>
   </si>
   <si>
-    <t>Parkur içerisindeki tüm makinaların canlı takip verileri gcp de bulunmaktadır.​
-Hat duruşları sahada bulunan kamera ve fotosel çiftleri ile otomatik tespit edilebilmektedir.​
-Envanter bilgileri ile mevcutta bulunan tüm kalıp ve set bilgileri tekil karo bazlı takip edilmektedir.​
-Fırın halı besleme veriminin çıkarılabilmesi için gerekli veriler toplanmaya başlamıştır.​
-Pres envanter sayfası üzerinden üretimi yapılan ürünün ebadı(60x120, 61x121)​
-Fırın kontrol panosu üzerinden fırın devir süresi​
-Barkod takip üzerinden fırına aktif giren üretimin tespiti​</t>
-  </si>
-  <si>
-    <t>Fırın halı besleme oranının canlı takibi ve verimlilik düşüşü (fırın devrinde ürün ağacından sapma, aralıklı besleme, vb) durumlarında erken uyarı sistemi kurulması​
-Fırın besleme sisteminin operatör kontrolünden çıkarılarak 24 saat canlı izlenmesi sağlanacak.​
-Üretim parametrelerinin kurulacak sisteme entegrasyonuyla Agentic AI modellemesi yapılarak fırının izlenmesi ve kontrolü sağlanacaktır.​</t>
-  </si>
-  <si>
     <t>CWYF Uygulaması Geliştirilmesi</t>
   </si>
   <si>
-    <t>Başvuru tamamlanmıştır. ​
-Amaç: Kaleseramik üretim hatlarında dijital dönüşüm ile uçtan uca izlenebilirlik ve karar destek sistemleri kurmak.​
-Yenilik: IoT tabanlı veri toplama, yapay zekâ modelleri ve akıllı dijital asistanların üretim kararlarını desteklemesi.​
-Kapsam: Hammadde dozajlama, değirmenler, kurutucular, presler, fırınlar ve son işlem hatlarında veri analitiği uygulamaları.​
-Katkı: Firelerin ve plansız duruşların azaltılması, kalite tutarlılığının artması, enerji tüketiminde düşüş ve çevresel sürdürülebilirlik.​
-Başvurumuz onaylanmıştır.​
-Proje Kick-Off u yapılmış, çalışmalar başlatılmıştır.​</t>
-  </si>
-  <si>
-    <t>Veri Toplama Altyapısı: IoT sensörleri, SCADA/MES entegrasyonu ile anlık veri akışının sağlanması.​
-Veri Ambarı ve Analitik: Toplanan verilerin merkezi platformda saklanması, temizlenmesi ve analize hazır hale getirilmesi.​
-Model Geliştirme: Makine öğrenmesi ve yapay zekâ algoritmaları ile kalite, enerji ve bakım tahminleme modellerinin geliştirilmesi.​
-Karar Destek Asistanı: Operatörler ve yöneticiler için etkileşimli dijital asistan ve dashboard’ların tasarımı.​
-Pilot Uygulama: Seçilen hatlarda (ör. masse değirmenleri ve kurutucular) test ve validasyon çalışmaları.​
-Yaygınlaştırma: Tüm üretim tesislerine entegrasyon, ERP sistemleri ile bütünleşme.​
-Sürdürülebilirlik &amp; Raporlama: Enerji ve hammadde tasarruflarının ölçülmesi, yönetim raporlarının hazırlanması.​</t>
-  </si>
-  <si>
-    <t>Dijital olgunluk değerlendirmesi yapılmıştır.​
-Değerlendirme sonrası tüm birimler için gelişime açık noktalar belirlenmiştir​
-Dijital dönüşüm yol haritası hazırlanmıştır.​
-5 yıllık dönemi kapsayan bir yatırım planı hazırlanmıştır.​
-MEXT ile başvuru süreci terar başlatılmıştır. Nisan ayı içerisinde dosya STB ye teslim edileektir.​
-​</t>
-  </si>
-  <si>
-    <t>Dijital Dönüşüm Merkezi unvanı kazandıktan sonra:​
-Dijital dönüşüm yatırımlarının takibi yapılacak​
-6 aylık dönemlerde tüm birimler için gelişime açık noktalar tekrar değerlendirilecek  gerekirse yatırım planlarına dahil edilecek​
-Gelişimi takip edebilmek için her yıl iç kaynaklar ile  olgunluk değerlendirmesi yapılacak ​</t>
-  </si>
-  <si>
     <t>Mali işler birimi tarafından talep edilen fagid Bütçe-Fiili raporu, günlük stok analiz raporu ve VSM maliyet raporu gibi çeşitli birimlerin ihtiyaç duyduğu raporların PowerBI üzerinden kod sistematiği içeren şekilde özelleştirilerek oluşturulması ve birimlerin bu konudaki yetkinliklerinin artırılması bu projenin çalışma konusunu oluşturmaktadır.</t>
   </si>
   <si>
-    <t>Fagid Bütçe-Fiili raporu faaliyette olup gerçek zamanlı güncellenerek yayımlanmaktadır. ​
-Günlük stok analiz raporu faaliyette olup gerçek zamanlı güncellenerek yayımlanmaktadır. ​
-VSM Maliyet raporu yapımı tamamlanarak yayımlanmıştır.​
-Mali işlerin ihtiyaçlarına yönelik raporların alt yapısı oluşturulmuştur. ​
-​</t>
-  </si>
-  <si>
-    <t>​
-Farklı birimlerden gelen verilerin birleştirilerek ortak platformda görünürlüğü sağlanacaktır.​
-Sürecin devam ettirilmesi için Mali İşler'den veri beklenmektedir.​
-​
-​</t>
-  </si>
-  <si>
-    <t>TZY - Bütçe -Fiili Üretim Raporu ​
-KKO ve Teyitsiz siparişler raporu oluşturulmuştur​
-Fabrika doluluk raporu oluşturulmuştur.​
-TZY - Performans Göstergeleri Raporu ​
-TZY - Müşteri Raporu ​
-TZY - Envanter Yönetimi ​
-TZY - Ürün Raporu ​
-Talep Yönetimi Raporu tamamlandı​
-Inbound lojistik ve Outbound lojistik raporu​</t>
-  </si>
-  <si>
-    <t>Satın alma raporu ​
-Proje yönetimi raporu​
-Sipariş Yönetimi Raporu​
-KN raporu ​
-Tüm TZY raporlarının tek bir platformda toplanması tamamlanmış, veri girişi beklenmektedir.​
-UYGULAMA KULLANILABİLİR HALE GETİRİLMİŞTİR.​</t>
-  </si>
-  <si>
     <t>Mühendislik birimi tarafından oluşturulan fabrikalara ait kalite, hata analizi, duruş raporlarının PowerBI üzerinden kod sistematiği içeren şekilde özelleştirilerek oluşturulması ve birimlerin bu konudaki yetkinliklerinin artırılması bu projenin çalışma konusunu oluşturmaktadır.</t>
   </si>
   <si>
-    <t>Mühendislik tarafından oluşturulan fabrikalara ait kalite, hata analizi, duruş raporlarını içeren raporlar teslim alınarak, kod sistematiği kontrol edilmiş ve gerekli düzenlemeler yapılarak günlük takibi yapılmaktadır. ​
-Fabrika tüm raporları (hata, kalite, duruş)  güncel olarak takibi yapılıp yayımlanmaktadır.​
-Fabrika PowerBI raporlarının veri kaynağının değiştirilmiştir.​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farklı birimlerden gelen verilerin birleştirilerek ortak platformda görünürlüğü sağlanacaktır.​
-Raporlama arayüzleri revize edilecektir.​
-MES verileri işlenerek PowerBI a aktarılacaktır.​
-</t>
-  </si>
-  <si>
     <t>Fabrikanın fiziksel süreçlerini gerçek zamanlı veriyle beslenen sanal modeller aracılığıyla temsil edilmesi hedeflenmektedir. </t>
-  </si>
-  <si>
-    <t>Microsoft Azure Digital Twins uygulaması ön çalışması tamamlanmıştır.​
-Görselleştirme yöntemleri olarak Microsoft 3D Scenes ve simülasyon için Unity araştırılmıştır.​
-Fabrika hatlarının taslağı çıkarılmıştır (DrawIO uyglaması)​
-Fabrka grafik tasarımının Part-1 tamamlanmıştır (Blender 3D)​
-Mic. Azure üzerinde makinelerin parametreleri ile beraber iş akış modelinin sinir ağları oluşturulmuştur.​
-​
-​</t>
-  </si>
-  <si>
-    <t>Sahadan alınan sensör dataları ile varlık dataları uyumlu hale getirilecektir.​
-Soğuk veri akışı simüle edilecektir.​
-Canlı veriye geçiş çalışmaları başlatılacaktır (HOLDING IT)​
-Fabrika hatlarındaki değişikliklerin tahminleneceği mantık katmanı eklenecektir.​
-Olası arızaları önceden tahmin edilecek ve bakım planları otomatik olarak optimize edilecektir.​
-Çalışma in-house yönetilecektir.​</t>
-  </si>
-  <si>
-    <t>Kurumsal veri kaynaklarının (SAP, BW, v.b.) büyük dil modellerine bağlanarak anlık rapor ihtiyaçları ile veri analizi ve içgörülerin alınabildiği platformun oluşturulması/kullanılması çalışmasıdır. Seçili use case ler için geliştirilecektir._x000B_Malzeme, müşteri, ürün ağacı, iş planı, gibi veri yapılarındaki farklı alanlardaki bilgileri analiz ederek veri anomali tespitleri yapabilmek,  Ürün satış performansları, şirket ve bayilerimizdeki stok durumlarını analiz ederek ürünler için planlama ve envanter stratejilerini belirleyebilir öneriler sunmak için model geliştirilmesi planlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Stok, mal hareket, bayi stoğu, bayi satışı ve malzeme ana ver,ye ilişkin veri setleri hazırlanarak paylaşılmıştır.​
-POC için soru seti hazırlandı ve paylaşıldı.​
-Soru seti için hazırlanan modeller tedarikçi tarafından paylaşıldı ve Kale ekipleri ile birlikte değerlendirildi.​</t>
-  </si>
-  <si>
-    <t>POC nin tamamlanması ve sonuçların analiz edilmesi.​
-POC sonrası belirli bir plan dahilinde gerçek kullanıma geçiş.​
-Yapay zeka ajanları kullanımı için detaylı kullanım durumlarının oluşturulması.​</t>
-  </si>
-  <si>
-    <t>Her iki yaklaşım için örnek kullanım durumları belirlendi.​
-İş verilerinin büyük dil modeline bağlanması konusu için bir şirket ile gizlilik sözleşmesi yapıldı.​
-POC için çalışmalar devam ediyor.​</t>
   </si>
   <si>
     <t>Bu proje kapsamında, Kaleseramik üretim ve yönetim ekosisteminde oluşan büyük hacimli operasyonel verilerin ileri veri analitiği, makine öğrenmesi ve yapay zekâ yöntemleriyle analiz edilmesi hedeflenmektedir.
 Amaç; mevcut verilerden öngörü üreten, karar destek sağlayan ve operasyonel verimlilik yaratan veri odaklı kullanım durumlarını sistematik olarak keşfetmek, önceliklendirmek ve iş değerine dönüştürmektir.</t>
   </si>
   <si>
-    <t>Karar alma süreçleri sezgisel yaklaşımdan veri ve öngörü temelli yönetime taşınacak,​
-Dijital dönüşüm yol haritasındaki AI/ML ve dijital ikiz projeleri için ölçeklenebilir analitik bir temel oluşturulacak,​
-Üretim, kalite, bakım ve enerji ekiplerinin aynı veri dili üzerinden konuşabildiği ortak bir analitik çerçeve oluşturulacaktır.​
-​</t>
-  </si>
-  <si>
     <t>department</t>
   </si>
   <si>
@@ -1207,18 +797,12 @@
     <t>digital_initiative</t>
   </si>
   <si>
-    <t>SRM İhale Modülü ve BP Ent. Devreye Alınması</t>
-  </si>
-  <si>
     <t>Bu proje, Kaleseramik SKM üretim süreçlerini uçtan uca dijitalleştirerek, tekil ürün bazında gerçek zamanlı veri akışına dayalı akıllı üretim yönetimi ve yapay zekâ destekli karar destek sistemleri kurmayı hedeflemektedir. Amaç; kaliteyi artırmak, verimliliği yükseltmek, maliyetleri azaltmak ve müşteri memnuniyetini güçlendirmektir.</t>
   </si>
   <si>
     <t>MİP Sürecinin Geliştirilmesi</t>
   </si>
   <si>
-    <t>SLAB Lojistik Yetkinlikleri ve Depoların Gel.</t>
-  </si>
-  <si>
     <t>Teknik Hizmet Alınan Hizmetin Kontrolü</t>
   </si>
   <si>
@@ -1243,75 +827,18 @@
     <t>Dijital İkiz Çalışmasının Oluşturulması</t>
   </si>
   <si>
-    <t>Kullanım Durumları için AI Fonksiyonları Gel.</t>
-  </si>
-  <si>
-    <t>Kullanım Durumları için Veri Analitiği Çal.</t>
-  </si>
-  <si>
     <t>Ürün Ambalaj Bilgilerinin Tanımlanması</t>
   </si>
   <si>
-    <t>Tahminin Süreçlerde Kullanımı</t>
-  </si>
-  <si>
     <t>S&amp;OP Sürecinin Gel. ve Standardizasyonu</t>
   </si>
   <si>
-    <t>Talep Optimizasyon Aracının Gel.</t>
-  </si>
-  <si>
-    <t>S&amp;OP Talep Planlama Uygulamasının Gel.</t>
-  </si>
-  <si>
-    <t>S&amp;OP Finansallaştırma Uygulamasının Gel.</t>
-  </si>
-  <si>
-    <t>S&amp;OP Aracının Gel. (In-House)</t>
-  </si>
-  <si>
-    <t>Beklenen Hizmet Seviyelerinin Tan.</t>
-  </si>
-  <si>
-    <t>Hizmet için TZ Aksiyonlarının Ol.</t>
-  </si>
-  <si>
-    <t>PI'ların Oluşturulması ve Takibi</t>
-  </si>
-  <si>
-    <t>Global Entegre Planlama Aracının İmp.</t>
-  </si>
-  <si>
-    <t>Sipariş Önceliklendirme Opt. ve Çiz.</t>
-  </si>
-  <si>
-    <t>Envanter Yönetimi ve Planlama Str. Uyg.</t>
-  </si>
-  <si>
     <t xml:space="preserve">KBY Verisi Planlama Entegrasyonu </t>
   </si>
   <si>
-    <t>Ambalaj Malzemeleri Depolamasının İy.</t>
-  </si>
-  <si>
-    <t>Filo ve Spot Araç Kullanımının İy.</t>
-  </si>
-  <si>
-    <t>Sevkiyat Kapı Yenileme ve Saha Yapısı İy.</t>
-  </si>
-  <si>
-    <t>Denizyolu Filosu ve İş Hacminin Gel.</t>
-  </si>
-  <si>
-    <t>Tedarikçi Değerlendirme Yapısının İy.</t>
-  </si>
-  <si>
     <t>Kategori Bazlı Know-How Gel. Sağlanması</t>
   </si>
   <si>
-    <t>Satınalma Talebi Sistematiğinin İy.</t>
-  </si>
-  <si>
     <t>Vitrifiye Üretimi MES Yapısının Kurulumu</t>
   </si>
   <si>
@@ -1327,19 +854,7 @@
     <t>AI Destekli Fırın İzleme Sistemi</t>
   </si>
   <si>
-    <t>Mali İşler PowerBI Dashboard Gel.</t>
-  </si>
-  <si>
     <t>Üretim Verileri PowerBI Aktarımları</t>
-  </si>
-  <si>
-    <t>Envanter Yönetimi için Fonksiyonun Ol.</t>
-  </si>
-  <si>
-    <t>Planlama Str. Güncelleme Yazılımı Gel.</t>
-  </si>
-  <si>
-    <t>AGSW Uygulaması İmp.</t>
   </si>
   <si>
     <t>Autonomous Global Single Window (Declerant-İthalat, Logicust). Bu çalışmada, ithalat gümrük sürecinin müşavir ile entegrasyonu sağlanmaktadır. Declerant'ın hedefi SAP teslimat adımından başlayarak ithalat beyannamesi oluşturuluncaya kadar olan sürecin dijitalleşmesidir. Logicust'ın hedefi beyanname tescili sonrasında anlık veya periyodik olarak geriye yönelik hata taramasının yapılması ve olası risklerin sonradan kontrol öncesinde belirlenerek gümrük idaresi nezdinde aksiyonların alınmasıdır.
@@ -1350,33 +865,9 @@
 Uçtan Uça Çözüm - İhracattan ithalata kadar tüm süreci otomatikleştirirek tüm paydaşlar için kapsamlı bir çözüm sunulacal.</t>
   </si>
   <si>
-    <t>Sevk Planı ve Müş. Stok Sür. İy.​</t>
-  </si>
-  <si>
-    <t>Mobilya Lojistik Süreçleri İmp.</t>
-  </si>
-  <si>
     <t>ISO 28000 TZ Güvenliği Yön. Sis. Belgesi</t>
   </si>
   <si>
-    <t>Nakliye Hesaplama Modelinin İy.</t>
-  </si>
-  <si>
-    <t>Nakliyeci Atama ve Takip Uyg. Gel.</t>
-  </si>
-  <si>
-    <t>Depo Stok Hareket Akışlarının Ol.</t>
-  </si>
-  <si>
-    <t>SRM Sipariş Modülü İyileştirme ve Yayg.</t>
-  </si>
-  <si>
-    <t>Teşhir Sürecinin Yap. ve Atölye Kurulumu</t>
-  </si>
-  <si>
-    <t>Tedarikçi Ağı Opt. ve Alt. Tedarikçi  Gel.</t>
-  </si>
-  <si>
     <t>STB Dijital Dönüşüm Merkezi</t>
   </si>
   <si>
@@ -1486,20 +977,11 @@
   </si>
   <si>
     <t xml:space="preserve">SuperA MES Yapısının Kurulması </t>
-  </si>
-  <si>
-    <t>KB3, KB7, GR İkincil, Yer Masse Kurulumu</t>
   </si>
   <si>
     <t>Yeni yatırımı yapılan System ve Sacmi kalite kontrol cihazlarının entegrasyonu başlatılacak. Gerekli kontrollerin tamamlanmasından sonra; Toplanan tüm makine verileri ile tekil karo bazında ileri analitik çalışmaları başlatılacak.​
 Yapay zekâ algoritmaları ile minimum fire ve maksimum verim sağlanacak.​
 Üretim hattı yöneticileri, dijital panellerden anlık KPI’ları görecek (verimlilik, kalite, fire oranı, OEE vb.).​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 yıllık yatırım projeksiyonu DDM üzerinden yönetilecek.​
-Merkez bünyesinde gösterilecek çalışanlar için bildiirm yapılacaktır.​
-2026 yılı sonu dijital olgunluk değerlendirilmesi tekrarlanacaktır.​
-</t>
   </si>
   <si>
     <t>KB7, KB3  fabrikası iş analizi tamamlanmış olup backlog listesi tamamlanmıştır.​
@@ -1738,6 +1220,511 @@
   </si>
   <si>
     <t>Piyasa büyüklügüne bağlı olarak genel talep tahminleme modelinin oluşturulması çalışmasıdır. Öncelikle ihtiyacın hangi seviyede olduğu belirlenecek ve sonrasında Türkiye ve/veya dünya için toplam bir talep tahmin modeli çalışması yürütülecektir.</t>
+  </si>
+  <si>
+    <t>Tahmin Fonksiyonunun Süreçlerde Kullanımı</t>
+  </si>
+  <si>
+    <t>Modelinin tekrar eğitilmesine yönelik çalışmalar tamamlanmıştır.
+Sonuçlarının raporlanmasına ilişkin isterler belirlenerek piyasa ve DFU bazlı raporlar oluşturulmuştur.
+Tahmin sonuçlarının S&amp;OP döngüsüne girdi olarak kullanılmasına ilişkin çalışmalar başlatılmıştır.
+Baz tahminler piyasalar ile paylaşılarak talep zenginleştirme çalışmaları yürütülmektedir.
+Tahmin sonuçları düzenli olarak takip edilmektedir.
+Tahmin doğruluğu metriklerinin belirlenmiştir. Düzenli olarak hesaplanarak takip edilmektedir.
+Baz tahmin, revize baz tahmin, revize tahmin, nihai tahmin sonuçlarının ve tahmin sapmalarının görüntülenmesine ilişkin Power BI raporlama dashboardu oluşturulmuştur.
+SKU seviyesinde tahmin sonuçlarının planlama süreçlerinde kullanılmaktadır.</t>
+  </si>
+  <si>
+    <t>Talep Optimizasyon Aracının Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Mevcut taleplerin karşılanmasının ötesinde, belirli müşteri-ürün gruplarına yönelik yüksek kar oluşturan çalışma şeklinin ortaya çıkarılmasını sağlayacak şekilde optimizasyon aracının geliştirilmesi çalışmasıdır. Araç hat yetenekleri ve talep kısıtlarına göre maksimum kar için talep planının oluşturulmasını sağlayacaktır.</t>
+  </si>
+  <si>
+    <t>Optimizasyon modelinin oluşturulması tamamlandı.
+Modelin çözümüne ilişkin python kodu geliştirildi.
+Veri girişi, veri export, optimizasyon ve raporlama özellikleri eklenerek komple bir web uygulaması çözümü oluşturuldu.
+Çözüm ve uygulama Kale Masters Doğrusal Programlama eğitimi kapsamında geliştirilmiştir.</t>
+  </si>
+  <si>
+    <t>S&amp;OP Talep Planlama Uyg. Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Talep tahmin uygulamasının çıktısını kullanarak tedarik planlama adımına girdi olacak ve mutabakat sağlanmış talep değerlerinin oluşturulmasını sağlayacak talep zenginleştirme ve mutabakat uygulamasının geliştirilmesi çalışmasıdır. Tahmin sonuçlarının girdi olarak alınabildiği, belirli hiyerarşilerde düzeltme yapılabildiği, belirli kişilerin üzerinde çalışabildiği ve veri girişi yapabildiği esnek bir ortam geliştirme çalışmasıdır. Odoo platformu üzerinde In-house olarak geliştirilmektedir.</t>
+  </si>
+  <si>
+    <t>S&amp;OP Finansallaştırma Uyg. Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>S&amp;OP süreci talep ve tedarik planlama adımlarından çıkan bilgilerin fiyat, maliyet, başta olmak üzere diğer finansal girdilerin kullanılarak tutarsal hale getirilmesi ve raporlanması çalışmasıdır. Buradan çıkan farklı senaryolar bazındaki finansalların değerlendirilmesi ile operasyonel planlara karar verilmesi sağlanacaktır. Bu çalışma In-house olarak planlanmaktadır.</t>
+  </si>
+  <si>
+    <t>Kullanılan talep tahmin uygulaması, geliştirilmesi devam eden talep planlama uygulaması, geliştirilmesi planlanan finansallaştırma uygulaması çözümlerinin bir paket olarak birbirine bağlanmış bir ürün hale getirilmesi çalışmasıdır.
+In-house olarak ürünleştirme çalışmasından verim alınamaması durumunda yapılmış olan RFP çalışmasına istinaden ürün araştırılması yine bu çalışma kapsamındadır.</t>
+  </si>
+  <si>
+    <t>S&amp;OP Aracının Geliştirilmesi (In-House)</t>
+  </si>
+  <si>
+    <t>Beklenen Hizmet Sev. Tanımlanması</t>
+  </si>
+  <si>
+    <t>TZ süreçlerinin, beklenen hizmet seviyesini karşılayacak şekilde çalışabilmesi için müşteri-ürün boyutlarında farklılaşan beklenen hizmet seviyelerinin tanımlanması gerekmektedir. Bu proje ile müşteri-ürün boyutları bazında, belirlenmiş gruplar/kanallar için hizmet seviyelerinin tanımlanması amaçlamaktadır. Bu şekilde genel çalışma (standart hizmet) ve metrik takibinden, kategorize edilmiş ve tanımlanmış ihtiyaçların karşılandığı ve bunların ölçümü ile performans takibinin yapıldığı sisteme geçilebilecektir.</t>
+  </si>
+  <si>
+    <t>Hizmet için TZ Aks. Oluşturulması</t>
+  </si>
+  <si>
+    <t>Beklenen Hizmet Seviyelerinin Tanımlanması projesinde oluşturulan, kategorize edilmiş hizmet seviyesi tanımlarının, karşılanmasına yönelik olarak aksiyonların oluşturulduğu ve takibinin yapıldığı çalışmadır.</t>
+  </si>
+  <si>
+    <t>PI ların Oluşturulması ve Takibi</t>
+  </si>
+  <si>
+    <t>Hizmet için Tedarik Zinciri Aksiyonlarının Oluşturulması projesinde oluşturulan, aksiyonların performans sonuçlarının ölçümü ve takibine yönelik çalışmaların yürütüldüğü projedir.</t>
+  </si>
+  <si>
+    <t>Global Entegre Planlama Aracının İmplementasyonu</t>
+  </si>
+  <si>
+    <t>S&amp;OE süreci, onaylanmış S&amp;OP / Ana Üretim Planı çerçevesinde; kısa vadeli (günlük / haftalık) dönemde oluşan talep, stok ve sevkiyat sapmalarını hızlı kontrollü şekilde yönetmeyi amaçlayan, operasyonel bir karar alma sürecidir. Bu proje KS nin ihtiyaçlarına uygun S&amp;OE sürecinin geliştirilmesi ve tanımlanması çalışmasını içermektedir.</t>
+  </si>
+  <si>
+    <t>S&amp;OP toplantıları aylık olarak devam etmektedir. Toplantılarda stoklar, üretim planları, talep değişkenlikleri, üretim öncelikleri gibi bilgiler kontrol edilmektedir. 
+Süreç Kapsamının ve Zaman Ufku haftalık olarak belirlendi.
+Kritik karar konuları tamamlandı.
+Roller ve sorumluluklar netleştirildi. Paylaşılacak tablolar netleştirildi.
+Planlama olarak güncel tutulan tablolar üzerinden veri setleri oluşturuldu.
+Önceliklendirme ve Karar Kurallarının oluşturuldu.
+Toplantı yapısı katılımcılar ve periyotları belirlendi.
+KPI ve Başarı Göstergeleri S&amp;OP toplantılarında konuşulan aylık hedeflerin haftalık periyotlara bölünmüş hali olarak belirlendi. (Plana Uyum, Fazla Üretim vs.)</t>
+  </si>
+  <si>
+    <t>Pilot kapsamın netleştirilmesi
+S&amp;OE Toplantı Ritminin başlatılması (1 Mart itibariyle başlatılacaktır)
+Standart veri seti ile operasyonun yürütülmesi
+Önceliklendirme ve karar kurallarının uygulanması
+Aksiyon Takibi ve Disiplinin Sağlanması
+Eskalasyon Mekanizmasının İşletilmesi
+KPI takibi ve ilk etki ölçümü
+Geri Bildirim ve iyileştirme</t>
+  </si>
+  <si>
+    <t>Sipariş Önceliklendirme Optimizasyonu ve Çizelgeleme</t>
+  </si>
+  <si>
+    <t>S&amp;OP Aracının Geliştirilmesi (In-House) çalışmasında beklenen sonucun alınamaması durumunda hazırlanan RFP e göre global bir entegre planlama aracının tedariği ve şirkete implementasyonu çalışmasını içeren projedir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP sistemi içinde saklamalı sipariş, teyit-termin gibi şirkete özel olarak oluşturulmuş ve standart akışın dışına çıkan yaklaşımlar yerine aATP gibi (Advanced Available-to-Promise) standart çözümlerin kullanımına geçilmesi hedeflenmektedir. Bu çalışma kapsamında sipariş önceliklendirme için parametrelerin belirlenmesi, optimizasyon modelinin oluşturulması ve entegre planlama sürecine sipariş önceliklendirme fonksiyonunun entegrasyonu da hedeflenmektedir.
+</t>
+  </si>
+  <si>
+    <t>Sipariş önceliklendirme için parametrelerin belirlenmesi, optimizasyon modelinin oluşturulması ve entegre planlama sürecine sipariş önceliklendirme fonksiyonunun entegrasyonu hedeflenmektedir.</t>
+  </si>
+  <si>
+    <t>Envanter ve Planlama Str. Uygulanması</t>
+  </si>
+  <si>
+    <t>Planlama Str. Güncelleme Yazılımı Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Belirli veriler kullanılarak yapılan hesaplamalar doğrultusunda ve yine belirli kurallara göre olarak yapılan ürünlerinlerin planlama strateji gruplarının belirlenmesi sürecinin bir tool a aktarılarak otomatik olarak yapılması çalışmasıdır.</t>
+  </si>
+  <si>
+    <t>Ambalaj Mal. Depolamasının İyileştirilmesi</t>
+  </si>
+  <si>
+    <t>AGSW Uyg. İmplementasyonu</t>
+  </si>
+  <si>
+    <t>Mobilya Lojistik Süreçleri İmplementasyonu</t>
+  </si>
+  <si>
+    <t>Nakliye Hesaplama Modelinin İyileştirilmesi</t>
+  </si>
+  <si>
+    <t>Filo ve Spot Araç Kullanımı İyileştirilmesi</t>
+  </si>
+  <si>
+    <t>Sevkiyat Kapı ve Saha Yapısı İyileştirilmesi</t>
+  </si>
+  <si>
+    <t>Nakliyeci Atama ve Takip Uyg. Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Denizyolu Filo ve İş Hacminin Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Depo Stok Hareket Akışlarının Oluşturulması</t>
+  </si>
+  <si>
+    <t>SLAB Lojistik Yetkinliklerin Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Teşhir Süreci Yapılandırma ve Atölye Kurulumu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknik SA kategorisinde teklifler, siparişler ihaleler dijital olarak SRM üzerinden toplanmaktadır. (3600+ işlem)
+Yeni cari tanımlarında vSRM dijital uygulaması ve BP entegrasyonu devreye alınmış ve 87 yeni cari kaydı vSRM üzerinden yapılmıştır.
+Satın alma ihalesinde açık artırma parametresinin uygulamaya dahil edilmesi.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satış ihalesi sürecinin SRM’ e tanımlanması. 
+SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır.
+</t>
+  </si>
+  <si>
+    <t>İhale Modülü ve SAP BP İmplementasyonu</t>
+  </si>
+  <si>
+    <t>DÖF Modülünün Devreye Alınması</t>
+  </si>
+  <si>
+    <t>Ambalaj kategorisinde Kalite Birimi tarafından aktif kullanılmaktadır.</t>
+  </si>
+  <si>
+    <t>Diğer SA kategorilerinde DÖF modülünün kullanılması yaygınlaştırılacaktır. Örnek Hammadde için Ar-Ge girdi kontrol kullanımı.
+Kategorilerde denetim kayıtlarının vSRM üzerinden yürütülmesi ve tedarikçiye iletilmesi.</t>
+  </si>
+  <si>
+    <t>Sipariş Modülü İyileştirme ve Yaygınlaştırma</t>
+  </si>
+  <si>
+    <t>Faz 1; Tedarikçi bazında kullanım (siparişlerin onayı ve irsaliye girişleri) oranlarının arttırılması ve süreç işlemlerin (SAS) iyileştirilmesi sağlanmıştır. 32 tedarikçinin % 58’ inde kullanıma geçilmiştir. 
+Teknik Satın alma kategorisinde hizmet alanında teklif ve siparişlerin oluşturulması %100 oranında devreye alınmıştır, stok kodlu alımlarda da kullanılmaya başlanmıştır.
+Bölgesel ve Merkezi Hizmet kategorisinde ilgili sipariş modulü eğitimi alınmıştır.
+Teknik hizmet iş kabullerinde VSRM üzerinden gerekli süreç tamamlanmıştır, 01.04.2026 tarihinde devreye alınmıştır.</t>
+  </si>
+  <si>
+    <t>Bölgesel Hizmet ve Merkezi Satın alma kategorilerinde sipariş modülü kullanıma başlanacaktır.
+Bölgesel Hizmet kategorisi için ilgili kullanıcılara (talep sahibi, tedarikçi) süreç hakkında bilgi verilecektir. Talepler vSRM üzerinden alınarak satın alma süreci başlatılacaktır.        
+vSRM dışı talep kabul edilmeyecektir. Taleplerin vSRM üzerinden alınması planlanmaktadır.
+vSRM kullanımı sipariş girişi sağlayan ambar birimlerine yaygınlaştırılacaktır.
+Siparişlerin hızlanması için vSRM üzerinden SAT açılması işlemlerinin otomatik olarak çalışması yapılmaktadır. Mayıs ayına kadar tamamlanması planlanmaktadır.</t>
+  </si>
+  <si>
+    <t>Sevk Planı ve Müş. Stok Süreci İyileştirilmesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tedarikçi Değerlendirme Sistemi yeniden kurgulandı. Performans kriterleri ve puanlama yapısı oluşturuldu.
+2025 yılı tedarikçi değerlendirmesi 2026 Ocak ayı içinde tamamlandı.
+Tedarikçi değerlendirme sonuçları iç müşteriler ve tedarikçiler  ile paylaşıldı.
+Tedarikçi değerlendirme süreci ITG firması tarafından örnek bir model gösterimiyle anlatıldı, KPI listesi paylaşıldı. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tedarikçi değerlendirme sürecinde kullanılabilecek vSRM sisteminde yer alan KPI listesi kontrolü ve sisteme entegre edilmesi. 
+</t>
+  </si>
+  <si>
+    <t>Tedarikçi Değerlendirme Sür. İyileştirilmesi</t>
+  </si>
+  <si>
+    <t>Tedarikçilerimizin verdiği teknik eğitimlerle hem kendi kullanıcımız hem de tedarikçimizin ürününün doğru kullanılması ile optimum sonuçlara ulaşılmaktadır.
+Ambalaj ve Tamamlayıcılar kategorisinde tedarikçilerimize açtığımız DÖF’ler ile ilgili malzeme geliştirmeleri yapılmakta ve bilgiler vSRM sistemi üzerinden kayda alınmaktadır.</t>
+  </si>
+  <si>
+    <t>DÖF yapısının vSRM modülü üzerinden Bölgesel ve Merkezi hizmet, Ambalaj ve Tamamlayıcılar, Hammadde ve Kimyasallar kategorisine de yaygınlaştırılması sağlanacaktır.
+Tedarikçi performans verilerinin vSRM (kalite, maliyet, teslimat, hizmet vb.) değerlendirilmesi.
+Yapılan tedarikçi değerlendirmeleri sonucunda tedarikçilerle paylaşılan sonuçlara istinaden gelişim alanlarının belirlenmesi. Örneğin termin anlamında düşük puan alan tedarikçilerin geliştirilmesi vs.</t>
+  </si>
+  <si>
+    <t>Tedarikçi Ağı Opt. ve Alt. Ted. Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Tedarikçi Benchmark çalışmaları yapılmıştır. 2 grup halinde farklı iki firma olan Sofra firması ve Dalgakıran firmaları satınalma yapısı olarak incelenmiştir. Sofra firmasından tedarikçi değerlendirme anlamında örnekler alınmıştır. 
+Çin pazarı tedarik ürünler satınalmasında Know how gelişimi için Trome firmasıyla aktif çalışmaya başlanılmıştır.</t>
+  </si>
+  <si>
+    <t>Maliyet yapıları ve fiyat kırılımları bilgisinin geliştirilmesi.
+Piyasa Emtialarının ve artış tahmin oranlarının bir bülten üzerinden takibinin yapılması ve geliştirilmesi.
+Kategori bazlı tedarikçilerin üretim hatlarının görüleceği ve teknik değerlendirilmesinin yapılabileceği ziyaret planlaması yapılacaktır.</t>
+  </si>
+  <si>
+    <t>FRM.GEN.SAT.031 form kodu ile Satın alma Fiyat Değişim Onay Formu oluşturulmuştur.
+İŞT.GEN.SAT.002 form kodu ile Satın alma Fiyat Değişim Onay Talimatı oluşturulmuştur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiyat Değişim Onay hiyerarşisinin SAP kurgusu Strateji birimiyle görüşülecektir. </t>
+  </si>
+  <si>
+    <t>Robot tarafından kayıt edilmesi planlanan tedarikçiler belirlenmiş, sisteme ……….. cari tanımlanmıştır.</t>
+  </si>
+  <si>
+    <t>Döviz bazlı faturaların RPA sürecine dahil edilmesi.
+Robot tarafından yapılan kayıtların miktarının artırılması.</t>
+  </si>
+  <si>
+    <t>Satın alma taleplerinin Teknik SA kategorisinde e-posta/telefon yerine SRM sistemi üzerinden alınıp yürütülmektedir.
+Teknik satınalma kategorisinde talepler teknik dokümanlar la birlikte SRM sistemi üzerinden alınmaya başlanmış ve tedarikçiye yine SRM sistemi üzerinden ihale, teklif toplama vb. şeklinde iletilmektedir.</t>
+  </si>
+  <si>
+    <t>SRM sistemi işlemlerinde Hizmet SAT’ larının talep sahibi onayı ile otomatik olarak SAP sisteminde yaratılması ve SRM sistemi ile entegre olması planlanmaktadır.</t>
+  </si>
+  <si>
+    <t>Teknik hizmet alımlarında alınan hizmetin kontrolü E-flow sisteminde yer alan uygulama ile yapılmakta; talep sahipleri faturalara dijital onay vermektedir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stok kodlu ve hizmet siparişlerinde SAS onay sistemi kullanılmaktadır.
+Strateji tarafında SAS onay limitleri ve yetki tablosu belirlenmiştir. </t>
+  </si>
+  <si>
+    <t>SA Talebi Sistematiğinin İyileştirilmesi</t>
+  </si>
+  <si>
+    <t>Firma tarafından hizmet teslimi onayı
+Talep sahibi ve üst amir onayı
+Firmaya fatura düzenlenmesi için bilgi kaydı 
+Faturanın sistem tarafından ön kaydının yapılması</t>
+  </si>
+  <si>
+    <t>Granit Masse, Sır Üretim, Granit Kurulumu</t>
+  </si>
+  <si>
+    <t>KB3, KB7 Kurulumu</t>
+  </si>
+  <si>
+    <t>YK Masse, GR İkincil İşlemler Kurulumu</t>
+  </si>
+  <si>
+    <t>KSFX Yapısının Kurulması</t>
+  </si>
+  <si>
+    <t>Parkur içerisindeki tüm makinaların canlı takip verileri gcp de bulunmaktadır.​
+Hat duruşları sahada bulunan kamera ve fotosel çiftleri ile otomatik tespit edilebilmektedir.​
+Envanter bilgileri ile mevcutta bulunan tüm kalıp ve set bilgileri tekil karo bazlı takip edilmektedir.​
+Fırın halı besleme veriminin çıkarılabilmesi için gerekli veriler toplanmaya başlamıştır.​
+Pres envanter sayfası üzerinden üretimi yapılan ürünün ebadı(60x120, 61x121)​
+Fırın kontrol panosu üzerinden fırın devir süresi​
+Barkod takip üzerinden fırına aktif giren üretimin tespiti​</t>
+  </si>
+  <si>
+    <t>Fırın halı besleme oranının canlı takibi ve verimlilik düşüşü (fırın devrinde ürün ağacından sapma, aralıklı besleme, vb) durumlarında erken uyarı sistemi kurulması​
+Fırın besleme sisteminin operatör kontrolünden çıkarılarak 24 saat canlı izlenmesi sağlanacak.​
+Üretim parametrelerinin kurulacak sisteme entegrasyonuyla Agentic AI modellemesi yapılarak fırının izlenmesi ve kontrolü sağlanacaktır.​</t>
+  </si>
+  <si>
+    <t>Rutubet cihazının kurulumu ve PC bağlantıları tamamlandı​
+Üretilen farklı reçetelerdeki hammaddeler için cihaz kalibrasyonu ve ölçüm reçetesi oluşturulması tamamlandı​
+Veri doğrulama ve veri seti oluşturma tamamlandı.​
+MES sistemi ile sprey kurutucu makine parametreleri toplandı.​
+Sprey dryer ve rutubet ölçüm cihazı arasındaki gecikme farkı hesaplandı.​
+Sprey dryer da önemli parametrelerin belirlenmesi için analiz çalışması yapıldı.​
+Canlı rutubet takibi ile canlı makine verileri arasındaki korelasyon için veri analitiği çalışmaları yapılarak model oluşturulmuştur. Modelin doğruluğu sahada test edilecektir.​</t>
+  </si>
+  <si>
+    <t>Oluşturulan modelin canlı veri üzerinden testleri yapılarak güvenilirlik kontrolü yapılacak.​
+Model saha entegrasyonu yapılacak.​
+Kurutma makine parametreleri ile rutubet ölçümü arasındaki gecikme zaman farkı hesaplanarak veri eşleşmesi yapılacaktır. ​</t>
+  </si>
+  <si>
+    <t>MES sistemi ile tekil karo bazlı takip yapılabilmektedir. ​
+Granit fabrikası ve granit masse üretimi arasında pilot çalışma planlanmıştır.​
+Tüketim datalarının SAP üzerinden anlık çıkışı için algoritma düzenlenmiştir. ​
+Dijital tartım ünitelerine takılan IOT cihazları SCADA akışını bozduğundan dolayı yeni çalışma yapılması planlanmıştır.​</t>
+  </si>
+  <si>
+    <t>Her bir karonun tüm yaşam döngüsü bilindiğinden canlı makine verileri ile ürün ağacı kıyaslaması yapılacaktır.​
+Karo üretiminde kullanılan masse, sır, doğalgaz, elektrik, işçilik vb. veriler canlı ve otomatik sarf edilecektir.​
+İş emrinin ürün ağacına göre çıkarılan fiili standart maaliyet oranı her bir karo çözünürlüğünde bakılarak trend analizi yapılacaktır. ​</t>
+  </si>
+  <si>
+    <t>Gerekli olan tüm veriler MES sistemi içinde toplanmaya başlamıştır.​
+Modeli oluşturacak uygun veri seti büyüklüğü için tespit çalışmaları devam etmektedir.​
+Proje için üç konsorsiyum ile Horizon ön başvurusu yapılmış, sonuçları beklenmektedir.​</t>
+  </si>
+  <si>
+    <t>Nihai ürün kalite kontrol verileri ile tüm girdilerin korelasyonu sağlanacak​
+Reçete hammadde ve/veya oran değişimlerinin nihai ürüne etkisinin analizi yapılacak ​
+Üretim şartlarına uygun hammadde ihtiyacı öneri sistemi kurulacak​
+Projenin yazılım bütçesinin AB fonlarından karşılanması planlanmaktadır.​</t>
+  </si>
+  <si>
+    <t>Başvuru tamamlanmıştır. ​
+Amaç: Kaleseramik üretim hatlarında dijital dönüşüm ile uçtan uca izlenebilirlik ve karar destek sistemleri kurmak.​
+Yenilik: IoT tabanlı veri toplama, yapay zekâ modelleri ve akıllı dijital asistanların üretim kararlarını desteklemesi.​
+Kapsam: Hammadde dozajlama, değirmenler, kurutucular, presler, fırınlar ve son işlem hatlarında veri analitiği uygulamaları.​
+Katkı: Firelerin ve plansız duruşların azaltılması, kalite tutarlılığının artması, enerji tüketiminde düşüş ve çevresel sürdürülebilirlik.​
+Başvurumuz onaylanmıştır.​
+Proje Kick-Off u yapılmış, çalışmalar başlatılmıştır.​</t>
+  </si>
+  <si>
+    <t>Veri Toplama Altyapısı: IoT sensörleri, SCADA/MES entegrasyonu ile anlık veri akışının sağlanması.​
+Veri Ambarı ve Analitik: Toplanan verilerin merkezi platformda saklanması, temizlenmesi ve analize hazır hale getirilmesi.​
+Model Geliştirme: Makine öğrenmesi ve yapay zekâ algoritmaları ile kalite, enerji ve bakım tahminleme modellerinin geliştirilmesi.​
+Karar Destek Asistanı: Operatörler ve yöneticiler için etkileşimli dijital asistan ve dashboard’ların tasarımı.​
+Pilot Uygulama: Seçilen hatlarda (ör. masse değirmenleri ve kurutucular) test ve validasyon çalışmaları.​
+Yaygınlaştırma: Tüm üretim tesislerine entegrasyon, ERP sistemleri ile bütünleşme.​
+Sürdürülebilirlik &amp; Raporlama: Enerji ve hammadde tasarruflarının ölçülmesi, yönetim raporlarının hazırlanması.​</t>
+  </si>
+  <si>
+    <t>IoT sensörlerinden pres ve kurutucuya ait anlık veriler toplanmaktadır.​
+Makine parametreleri ile hat duruş bilgileri zaman etiketi üzerinden eşleştirilmiştir.​
+Dikey kurutucunun tüm raflarının aktif kullanımı için zaman serisi analizi tamamlanmıştır.​
+Veri görselleştirme dashboard’ları geliştirilmiştir​
+Rapor her gün süreç sahipleri ile paylaşılmaktadır.​
+OEE (Overall Equipment Effectiveness) artışı gerçekleşmiştir​
+Enerji tüketimi %3 azalma sağlanmıştır​</t>
+  </si>
+  <si>
+    <t>Makine öğrenmesi tabanlı tahminleme (enerji tüketimi, duruş, fire riski, verimlilik)​
+Kurutma bilgileri ile Faz-2 olarak fire korelasyonu çalışması yapılacaktır.​
+Kurutma yaşam döngüsü verileri ile kestirimci kalite çalışmaları</t>
+  </si>
+  <si>
+    <t>MES ve SAP entegrasyonu tamamlandı​
+IoT sensörleri ve SCADA sistemlerinden veri toplama süreci tamamlandı​
+Verinin depolanması ve veri kullanım senaryoları oluşturuldu​
+Gerçek zamanlı dashboard’lar (enerji, kalite, fire, OEE) oluşturuldu​</t>
+  </si>
+  <si>
+    <t>Reçete ve tüm (Masse+Üretim) proses parametreleri ile ürün kalitesi arasındaki korelasyon analizi yapılacak​
+En çok yaşanan firelerin veri gölü içindeki sebep sonuç korelasyonları araştırılarak kök neden analizi yapılacak​
+Makine öğrenmesi ile oluşturulan modeller kullanılarak canlı makine parametreleri için kurallar tanımlanıp kestirimci kalite uyarıları hazırlanacak​
+Fırın çıkışında fire olacağı öngörülen karoların pişirim öncesi bertaraf edilerek ham kırık olarak geri kazanılması ​</t>
+  </si>
+  <si>
+    <t>Fırın halı besleme veriminin çıkarılabilmesi için gerekli veriler toplanmıştır​
+Fırın besleme verileri istatistiksel analizi sonucunda optimum besleme süresi 13,96 sn olarak hesaplanmıştır.​
+Fırın girişi 7 farklı inverter ve 2 kompanzatör ile beslenmektedir. Bu karmaşık yapı içerisinde fırın besleme formülüzasyonu oluşturulmuştur.​
+Yapılan otomasyon iyileştirmesi ile iki karo arasındaki mesafeyi 0,01 sn hassasiyetiyle ölçülebilen sistem geliştirilmiştir ​
+Fırın halı besleme oranının canlı takibi ve verimlilik düşüşü (fırın devrinde ürün ağacından sapma, aralıklı besleme, vb) durumlarında ölçüm ve raporlama sistemi kuruldu​
+Duruş ve boşluklu besleme kaynaklı kapasite kayıpları ölçülerek günlük olarak raprolanmaya başlandı.​</t>
+  </si>
+  <si>
+    <t>Farklı üretimlerde farklı fırın rejimleri kod içerisine eklenerek dinamik kontrol geliştirilecektir.​
+Fırın besleme sisteminin operatör kontrolünden çıkarılarak 24 saat canlı izlenmesi sağlanacaktır​
+KB7 yaygınlaştırması planlanacaktır.</t>
+  </si>
+  <si>
+    <t>Masse çamuru içerisine reçeteye göre boya girme işlemi yapılarak çamur renklendirilir. ​
+Renk ölçümü sonrasında tekrar müdahale edilerek hedefe ulaşılmaya çalışılmaktadır. ​
+Hammaddeler girdi kontrol şartlarını sağlasalar da renk performansları her partide farklı olabilmekte ve ürün ağacına uymamaktadır.</t>
+  </si>
+  <si>
+    <t>Girdi kontrol QM verileri ve MES sistemi laboratuvar kontrol verileri ile model geliştirilecektir. ​
+Hazırlanan çamura uygun boya ihtiyacının dinamik reçete ile tahminlenmesi için ileri analitik çalışması yapılacaktır.​</t>
+  </si>
+  <si>
+    <t>Öğütme öncesi tüm hammaddelerin QM verileri alınmıştır. ​
+Kullanılan reçeteler ile hangi hammaddeden ne oranda kullanıldığı mevcuttur.​
+Değirmenin dönme süresi bilinmektedir.​
+Değirmene ek müdahale verileri alınmıştır.​
+Laboratuvar ölçümleri ile ek tur öncesi ve sonrası kabakum miktarı bilinmektedir.​</t>
+  </si>
+  <si>
+    <t>Fabrikalar içerisinde çalışan tüm makinaların yaptıkları her öğütme döngüsü sonrası birbirleri ile kıyaslamalı data seti oluşturulacaktır.​
+Farklı değirmenlere giren farklı reçetelerin çıktıları toplanarak dinamik work index çıkarılabilmekte ve kıyaslamalı olarak değirmen verimine ulaşılacaktır.​
+Sürekli izlenen verimde azalma tespit edildiğinde alarm oluşturulabilecektir.​
+Envanter takip ekranları ile değirmenlere yapılan bilya beslemeleri kaydedilecektir.​</t>
+  </si>
+  <si>
+    <t>Dijital olgunluk değerlendirmesi yapılmıştır.​
+Değerlendirme sonrası tüm birimler için gelişime açık noktalar belirlenmiştir​
+Dijital dönüşüm yol haritası hazırlanmıştır.​
+5 yıllık dönemi kapsayan bir yatırım planı hazırlanmıştır.​
+MEXT ile başvuru süreci terar başlatılmıştır. Nisan ayı içerisinde dosya STB ye teslim edileektir.​</t>
+  </si>
+  <si>
+    <t>Dijital Dönüşüm Merkezi unvanı kazandıktan sonra:​
+Dijital dönüşüm yatırımlarının takibi yapılacak​
+6 aylık dönemlerde tüm birimler için gelişime açık noktalar tekrar değerlendirilecek  gerekirse yatırım planlarına dahil edilecek​
+Gelişimi takip edebilmek için her yıl iç kaynaklar ile  olgunluk değerlendirmesi yapılacak ​</t>
+  </si>
+  <si>
+    <t>3 yıllık yatırım projeksiyonu DDM üzerinden yönetilecek.​
+Merkez bünyesinde gösterilecek çalışanlar için bildiirm yapılacaktır.​
+2026 yılı sonu dijital olgunluk değerlendirilmesi tekrarlanacaktır.​</t>
+  </si>
+  <si>
+    <t>Microsoft Azure Digital Twins uygulaması ön çalışması tamamlanmıştır.​
+Görselleştirme yöntemleri olarak Microsoft 3D Scenes ve simülasyon için Unity araştırılmıştır.​
+Fabrika hatlarının taslağı çıkarılmıştır (DrawIO uyglaması)​
+Fabrka grafik tasarımının Part-1 tamamlanmıştır (Blender 3D)​
+Mic. Azure üzerinde makinelerin parametreleri ile beraber iş akış modelinin sinir ağları oluşturulmuştur.​</t>
+  </si>
+  <si>
+    <t>Sahadan alınan sensör dataları ile varlık dataları uyumlu hale getirilecektir.​
+Soğuk veri akışı simüle edilecektir.​
+Canlı veriye geçiş çalışmaları başlatılacaktır (HOLDING IT)​
+Fabrika hatlarındaki değişikliklerin tahminleneceği mantık katmanı eklenecektir.​
+Olası arızaları önceden tahmin edilecek ve bakım planları otomatik olarak optimize edilecektir.​
+Çalışma in-house yönetilecektir.​</t>
+  </si>
+  <si>
+    <t>Mühendislik tarafından oluşturulan fabrikalara ait kalite, hata analizi, duruş raporlarını içeren raporlar teslim alınarak, kod sistematiği kontrol edilmiş ve gerekli düzenlemeler yapılarak günlük takibi yapılmaktadır. ​
+Fabrika tüm raporları (hata, kalite, duruş)  güncel olarak takibi yapılıp yayımlanmaktadır.​
+Fabrika PowerBI raporlarının veri kaynağının değiştirilmiştir.​</t>
+  </si>
+  <si>
+    <t>Farklı birimlerden gelen verilerin birleştirilerek ortak platformda görünürlüğü sağlanacaktır.​
+Raporlama arayüzleri revize edilecektir.​
+MES verileri işlenerek PowerBI a aktarılacaktır.​</t>
+  </si>
+  <si>
+    <t>Fagid Bütçe-Fiili raporu faaliyette olup gerçek zamanlı güncellenerek yayımlanmaktadır. ​
+Günlük stok analiz raporu faaliyette olup gerçek zamanlı güncellenerek yayımlanmaktadır. ​
+VSM Maliyet raporu yapımı tamamlanarak yayımlanmıştır.​
+Mali işlerin ihtiyaçlarına yönelik raporların alt yapısı oluşturulmuştur. ​</t>
+  </si>
+  <si>
+    <t>Farklı birimlerden gelen verilerin birleştirilerek ortak platformda görünürlüğü sağlanacaktır.​
+Sürecin devam ettirilmesi için Mali İşler'den veri beklenmektedir.​</t>
+  </si>
+  <si>
+    <t>TZY - Bütçe -Fiili Üretim Raporu ​
+KKO ve Teyitsiz siparişler raporu oluşturulmuştur​
+Fabrika doluluk raporu oluşturulmuştur.​
+TZY - Performans Göstergeleri Raporu ​
+TZY - Müşteri Raporu ​
+TZY - Envanter Yönetimi ​
+TZY - Ürün Raporu ​
+Talep Yönetimi Raporu tamamlandı​
+Inbound lojistik ve Outbound lojistik raporu​</t>
+  </si>
+  <si>
+    <t>Satın alma raporu ​
+Proje yönetimi raporu​
+Sipariş Yönetimi Raporu​
+KN raporu ​
+Tüm TZY raporlarının tek bir platformda toplanması tamamlanmış, veri girişi beklenmektedir.​
+UYGULAMA KULLANILABİLİR HALE GETİRİLMİŞTİR.​</t>
+  </si>
+  <si>
+    <t>Stok, mal hareket, bayi stoğu, bayi satışı ve malzeme ana ver,ye ilişkin veri setleri hazırlanarak paylaşılmıştır.​
+POC için soru seti hazırlandı ve paylaşıldı.​
+Soru seti için hazırlanan modeller tedarikçi tarafından paylaşıldı ve Kale ekipleri ile birlikte değerlendirildi.​</t>
+  </si>
+  <si>
+    <t>POC nin tamamlanması ve sonuçların analiz edilmesi.​
+POC sonrası belirli bir plan dahilinde gerçek kullanıma geçiş.​
+Yapay zeka ajanları kullanımı için detaylı kullanım durumlarının oluşturulması.​</t>
+  </si>
+  <si>
+    <t>Her iki yaklaşım için örnek kullanım durumları belirlendi.​
+İş verilerinin büyük dil modeline bağlanması konusu için bir şirket ile gizlilik sözleşmesi yapıldı.​
+POC için çalışmalar devam ediyor.​</t>
+  </si>
+  <si>
+    <t>Karar alma süreçleri sezgisel yaklaşımdan veri ve öngörü temelli yönetime taşınacak,​
+Dijital dönüşüm yol haritasındaki AI/ML ve dijital ikiz projeleri için ölçeklenebilir analitik bir temel oluşturulacak,​
+Üretim, kalite, bakım ve enerji ekiplerinin aynı veri dili üzerinden konuşabildiği ortak bir analitik çerçeve oluşturulacaktır.​</t>
+  </si>
+  <si>
+    <t>Finans PowerBI Dashboard Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Envanter Yön. AI Kullanım Fonk. Oluşturulması</t>
+  </si>
+  <si>
+    <t>Kurumsal veri kaynaklarının (SAP, BW, v.b.) büyük dil modellerine bağlanarak anlık rapor ihtiyaçları ile veri analizi ve içgörülerin alınabildiği platformun oluşturulması/kullanılması çalışmasıdır. Seçili use case ler için geliştirilecektir. Malzeme, müşteri, ürün ağacı, iş planı, gibi veri yapılarındaki farklı alanlardaki bilgileri analiz ederek veri anomali tespitleri yapabilmek,  Ürün satış performansları, şirket ve bayilerimizdeki stok durumlarını analiz ederek ürünler için planlama ve envanter stratejilerini belirleyebilir öneriler sunmak için model geliştirilmesi planlanmaktadır.</t>
+  </si>
+  <si>
+    <t>Genel AI Kullanım Fonksiyonları Oluşturulması</t>
+  </si>
+  <si>
+    <t>Genel Veri Analitiği Çalışmaları</t>
   </si>
 </sst>
 </file>
@@ -2197,7 +2184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.83984375" style="10" customWidth="1"/>
@@ -2209,52 +2196,52 @@
     <col min="7" max="7" width="14.05078125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.734375" style="13" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.47265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="54.20703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="60.3671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="90.3125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="71.47265625" style="1" customWidth="1"/>
     <col min="13" max="13" width="81.05078125" style="4" customWidth="1"/>
     <col min="14" max="14" width="8.83984375" style="11" customWidth="1"/>
     <col min="15" max="16384" width="8.83984375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" s="9" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
-        <v>377</v>
+        <v>274</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>378</v>
+        <v>275</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>247</v>
+        <v>179</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>254</v>
+        <v>186</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>248</v>
+        <v>180</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>249</v>
+        <v>181</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>250</v>
+        <v>182</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>253</v>
+        <v>185</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>251</v>
+        <v>183</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>252</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
@@ -2262,19 +2249,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C2" s="11">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>374</v>
+        <v>271</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="12">
@@ -2284,36 +2271,36 @@
         <v>46203</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>384</v>
+        <v>281</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>385</v>
+        <v>282</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="10">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="11">
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>374</v>
+        <v>271</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>269</v>
+        <v>197</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="12">
@@ -2323,16 +2310,16 @@
         <v>46234</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>388</v>
+        <v>285</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>386</v>
+        <v>283</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
@@ -2340,19 +2327,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="11">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>374</v>
+        <v>271</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>379</v>
+        <v>276</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="12">
@@ -2362,39 +2349,39 @@
         <v>46265</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="93.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="11">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>374</v>
+        <v>271</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>380</v>
+        <v>277</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="H5" s="12">
         <v>46204</v>
@@ -2403,206 +2390,206 @@
         <v>46326</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>390</v>
+        <v>287</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="10">
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="11">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="10">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="11">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>373</v>
+        <v>270</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>391</v>
+        <v>288</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>394</v>
+        <v>291</v>
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" s="11">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>372</v>
+        <v>269</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>392</v>
+        <v>289</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>395</v>
+        <v>292</v>
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="10">
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>371</v>
+        <v>268</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>381</v>
+        <v>278</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>396</v>
+        <v>293</v>
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10">
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" s="11">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>371</v>
+        <v>268</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>397</v>
+        <v>294</v>
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="10">
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" s="11">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>375</v>
+        <v>272</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>383</v>
+        <v>280</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>340</v>
+        <v>239</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>398</v>
+        <v>295</v>
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="10">
         <v>1</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" s="10">
         <v>2</v>
@@ -2611,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>370</v>
+        <v>267</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>399</v>
+        <v>296</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="12">
@@ -2624,24 +2611,24 @@
         <v>45930</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>400</v>
+        <v>297</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>401</v>
+        <v>298</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="10">
         <v>1</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C13" s="10">
         <v>2</v>
@@ -2650,10 +2637,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>370</v>
+        <v>267</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>404</v>
+        <v>301</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="12">
@@ -2663,22 +2650,22 @@
         <v>46022</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>402</v>
+        <v>299</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>403</v>
+        <v>300</v>
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="10">
         <v>1</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" s="10">
         <v>2</v>
@@ -2687,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>370</v>
+        <v>267</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="12">
@@ -2700,24 +2687,24 @@
         <v>46203</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>405</v>
+        <v>302</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>406</v>
+        <v>303</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="10">
         <v>1</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15" s="10">
         <v>2</v>
@@ -2726,30 +2713,30 @@
         <v>0</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>370</v>
+        <v>267</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>408</v>
+        <v>305</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>409</v>
+        <v>306</v>
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="10">
         <v>1</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C16" s="10">
         <v>2</v>
@@ -2758,30 +2745,30 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>370</v>
+        <v>267</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>336</v>
+        <v>235</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:13" ht="216" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="10">
         <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C17" s="10">
         <v>3</v>
@@ -2790,10 +2777,10 @@
         <v>1</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>369</v>
+        <v>266</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>270</v>
+        <v>309</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="12">
@@ -2803,13 +2790,13 @@
         <v>46112</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>65</v>
+        <v>310</v>
       </c>
       <c r="M17" s="3"/>
     </row>
@@ -2818,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" s="10">
         <v>3</v>
@@ -2827,10 +2814,10 @@
         <v>1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>369</v>
+        <v>266</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="12">
@@ -2840,16 +2827,16 @@
         <v>46203</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
@@ -2857,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C19" s="10">
         <v>3</v>
@@ -2866,10 +2853,10 @@
         <v>1</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>369</v>
+        <v>266</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="12">
@@ -2879,20 +2866,22 @@
         <v>46112</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L19" s="3"/>
+        <v>312</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C20" s="10">
         <v>3</v>
@@ -2901,13 +2890,13 @@
         <v>1</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>368</v>
+        <v>265</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>334</v>
+        <v>233</v>
       </c>
       <c r="H20" s="12">
         <v>46023</v>
@@ -2916,24 +2905,24 @@
         <v>46234</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>71</v>
+        <v>315</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="10">
         <v>1</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
@@ -2942,13 +2931,13 @@
         <v>1</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>368</v>
+        <v>265</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>335</v>
+        <v>234</v>
       </c>
       <c r="H21" s="12">
         <v>46174</v>
@@ -2957,19 +2946,19 @@
         <v>46295</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>10</v>
+        <v>317</v>
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="10">
         <v>1</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C22" s="10">
         <v>3</v>
@@ -2978,10 +2967,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>368</v>
+        <v>265</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="12">
@@ -2991,19 +2980,19 @@
         <v>46295</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="10">
         <v>1</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C23" s="10">
         <v>3</v>
@@ -3012,13 +3001,13 @@
         <v>1</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>368</v>
+        <v>265</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>328</v>
+        <v>227</v>
       </c>
       <c r="H23" s="12">
         <v>46327</v>
@@ -3027,31 +3016,31 @@
         <v>46387</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>56</v>
+        <v>318</v>
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="10">
         <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C24" s="10">
         <v>4</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>367</v>
+        <v>264</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="12">
@@ -3061,36 +3050,36 @@
         <v>46112</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="10">
         <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C25" s="10">
         <v>4</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>367</v>
+        <v>264</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="12">
@@ -3100,34 +3089,34 @@
         <v>46203</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>75</v>
+        <v>323</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="10">
         <v>1</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C26" s="10">
         <v>4</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>367</v>
+        <v>264</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>278</v>
+        <v>324</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="12">
@@ -3137,22 +3126,22 @@
         <v>46265</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="10">
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C27" s="10">
         <v>1</v>
@@ -3161,28 +3150,34 @@
         <v>2</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>360</v>
+        <v>258</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I27" s="12">
+        <v>46112</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="28" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="10">
         <v>2</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
@@ -3191,28 +3186,34 @@
         <v>2</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>360</v>
+        <v>258</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="G28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="12">
+        <v>46113</v>
+      </c>
+      <c r="I28" s="12">
+        <v>46203</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K28" s="5"/>
-      <c r="L28" s="4"/>
-    </row>
-    <row r="29" spans="1:13" ht="316.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="10">
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
@@ -3221,36 +3222,30 @@
         <v>2</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>360</v>
+        <v>257</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>85</v>
+        <v>326</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="H29" s="12">
-        <v>46174</v>
-      </c>
-      <c r="I29" s="12">
-        <v>46356</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
       <c r="J29" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="K29" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="10">
         <v>2</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C30" s="10">
         <v>1</v>
@@ -3259,34 +3254,30 @@
         <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="12">
-        <v>46023</v>
-      </c>
-      <c r="I30" s="12">
-        <v>46112</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
       <c r="J30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="L30" s="4"/>
+    </row>
+    <row r="31" spans="1:13" ht="125.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="10">
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
@@ -3295,34 +3286,36 @@
         <v>2</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>229</v>
+      </c>
       <c r="H31" s="12">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="I31" s="12">
-        <v>46203</v>
+        <v>46356</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>55</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="10">
         <v>2</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
@@ -3334,10 +3327,10 @@
         <v>3</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>331</v>
+        <v>230</v>
       </c>
       <c r="H32" s="12">
         <v>45839</v>
@@ -3346,21 +3339,21 @@
         <v>46112</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="10">
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C33" s="10">
         <v>2</v>
@@ -3372,25 +3365,27 @@
         <v>3</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>332</v>
+        <v>231</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K33" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>336</v>
+      </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:13" ht="360" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:13" ht="316.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="10">
         <v>2</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C34" s="10">
         <v>2</v>
@@ -3402,10 +3397,10 @@
         <v>3</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>282</v>
+        <v>199</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>333</v>
+        <v>232</v>
       </c>
       <c r="H34" s="12">
         <v>46023</v>
@@ -3414,21 +3409,21 @@
         <v>46203</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.55000000000000004">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="132.30000000000001" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="10">
         <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C35" s="10">
         <v>2</v>
@@ -3440,7 +3435,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="12">
@@ -3450,21 +3445,21 @@
         <v>46295</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="302.39999999999998" x14ac:dyDescent="0.55000000000000004">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="113.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="10">
         <v>2</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C36" s="10">
         <v>2</v>
@@ -3476,7 +3471,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="12">
@@ -3486,21 +3481,21 @@
         <v>46142</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="10">
         <v>2</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C37" s="10">
         <v>3</v>
@@ -3509,10 +3504,10 @@
         <v>4</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>362</v>
+        <v>259</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>283</v>
+        <v>337</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="12">
@@ -3522,33 +3517,33 @@
         <v>46265</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="10">
         <v>3</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C38" s="10">
         <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>358</v>
+        <v>255</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="12">
@@ -3558,36 +3553,36 @@
         <v>46203</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>300</v>
+        <v>207</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="10">
         <v>3</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C39" s="10">
         <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>301</v>
+        <v>357</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="12">
@@ -3597,36 +3592,36 @@
         <v>46173</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="10">
         <v>3</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C40" s="10">
         <v>2</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="12">
@@ -3636,16 +3631,16 @@
         <v>46173</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
@@ -3653,19 +3648,19 @@
         <v>3</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C41" s="10">
         <v>2</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="12">
@@ -3675,39 +3670,39 @@
         <v>46022</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="10">
         <v>3</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>359</v>
+        <v>256</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>327</v>
+        <v>226</v>
       </c>
       <c r="H42" s="12">
         <v>45778</v>
@@ -3716,16 +3711,16 @@
         <v>46203</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
@@ -3733,19 +3728,19 @@
         <v>3</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C43" s="10">
         <v>3</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>303</v>
+        <v>208</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="12">
@@ -3755,135 +3750,133 @@
         <v>46142</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="10">
         <v>4</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C44" s="10">
         <v>1</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>353</v>
+        <v>249</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="12">
-        <v>45962</v>
+        <v>45870</v>
       </c>
       <c r="I44" s="12">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="10">
         <v>4</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C45" s="10">
         <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>353</v>
+        <v>249</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>140</v>
+        <v>340</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="12">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="I45" s="12">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="10">
         <v>4</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C46" s="10">
         <v>1</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>351</v>
+        <v>249</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>326</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G46" s="3"/>
       <c r="H46" s="12">
-        <v>45962</v>
+        <v>46023</v>
       </c>
       <c r="I46" s="12">
-        <v>46356</v>
+        <v>46173</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
@@ -3891,68 +3884,70 @@
         <v>4</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C47" s="10">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>352</v>
+        <v>249</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>284</v>
+        <v>116</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="12">
-        <v>45870</v>
+        <v>45931</v>
       </c>
       <c r="I47" s="12">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K47" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M47" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="48" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="10">
         <v>4</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>352</v>
+        <v>248</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G48" s="3"/>
+        <v>343</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="H48" s="12">
         <v>45962</v>
       </c>
       <c r="I48" s="12">
-        <v>46265</v>
+        <v>46356</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>122</v>
@@ -3964,34 +3959,34 @@
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="10">
         <v>4</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C49" s="10">
         <v>1</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>352</v>
+        <v>250</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>42</v>
+        <v>344</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="12">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="I49" s="12">
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>125</v>
@@ -4003,34 +3998,34 @@
         <v>127</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="10">
         <v>4</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C50" s="10">
         <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>352</v>
+        <v>250</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>128</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="12">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="I50" s="12">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>129</v>
@@ -4038,7 +4033,7 @@
       <c r="L50" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="M50" s="4" t="s">
+      <c r="M50" s="1" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4047,58 +4042,55 @@
         <v>4</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C51" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>352</v>
+        <v>252</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="12">
-        <v>45809</v>
+        <v>45931</v>
       </c>
       <c r="I51" s="12">
-        <v>46326</v>
+        <v>46203</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="M51" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="52" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="10">
         <v>4</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C52" s="10">
         <v>2</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>354</v>
+        <v>251</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="12">
@@ -4108,36 +4100,36 @@
         <v>46265</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="10">
         <v>4</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C53" s="10">
         <v>2</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>354</v>
+        <v>251</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>258</v>
+        <v>346</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="12">
@@ -4147,52 +4139,55 @@
         <v>46387</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="10">
         <v>4</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C54" s="10">
         <v>2</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>355</v>
+        <v>253</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="12">
-        <v>45931</v>
+        <v>45809</v>
       </c>
       <c r="I54" s="12">
-        <v>46203</v>
+        <v>46326</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>144</v>
+        <v>120</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
@@ -4200,19 +4195,19 @@
         <v>4</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C55" s="10">
         <v>2</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>356</v>
+        <v>253</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="12">
@@ -4222,36 +4217,36 @@
         <v>46387</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="10">
         <v>4</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C56" s="10">
         <v>3</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>357</v>
+        <v>254</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>308</v>
+        <v>347</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="12">
@@ -4261,24 +4256,24 @@
         <v>46265</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="10">
         <v>5</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C57" s="10">
         <v>1</v>
@@ -4287,13 +4282,13 @@
         <v>5</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>365</v>
+        <v>262</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>364</v>
+        <v>261</v>
       </c>
       <c r="H57" s="12">
         <v>45931</v>
@@ -4302,24 +4297,24 @@
         <v>46203</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>158</v>
+        <v>348</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="10">
         <v>5</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C58" s="10">
         <v>1</v>
@@ -4328,13 +4323,13 @@
         <v>5</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>365</v>
+        <v>262</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>34</v>
+        <v>351</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>364</v>
+        <v>261</v>
       </c>
       <c r="H58" s="12">
         <v>45962</v>
@@ -4343,24 +4338,24 @@
         <v>46387</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>161</v>
+        <v>352</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="10">
         <v>5</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C59" s="10">
         <v>1</v>
@@ -4369,13 +4364,13 @@
         <v>5</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>365</v>
+        <v>262</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>307</v>
+        <v>354</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>364</v>
+        <v>261</v>
       </c>
       <c r="H59" s="12">
         <v>45931</v>
@@ -4384,24 +4379,24 @@
         <v>46203</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>164</v>
+        <v>355</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="10">
         <v>5</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C60" s="10">
         <v>1</v>
@@ -4410,13 +4405,13 @@
         <v>5</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>365</v>
+        <v>262</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>287</v>
+        <v>360</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>364</v>
+        <v>261</v>
       </c>
       <c r="H60" s="12">
         <v>45931</v>
@@ -4425,36 +4420,36 @@
         <v>46295</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>167</v>
+        <v>358</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="10">
         <v>5</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C61" s="10">
         <v>2</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>363</v>
+        <v>260</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="12">
@@ -4464,40 +4459,40 @@
         <v>46387</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>170</v>
+        <v>361</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="10">
         <v>5</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C62" s="10">
         <v>2</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E62" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>309</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="12">
-        <v>46023</v>
+        <v>46174</v>
       </c>
       <c r="I62" s="12">
         <v>46387</v>
@@ -4506,28 +4501,28 @@
         <v>55</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="10">
         <v>5</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C63" s="10">
         <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>366</v>
+        <v>263</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>288</v>
+        <v>200</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="12">
@@ -4537,36 +4532,36 @@
         <v>46356</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>173</v>
+        <v>364</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="10">
         <v>5</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C64" s="10">
         <v>3</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>366</v>
+        <v>263</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="12">
@@ -4576,36 +4571,36 @@
         <v>46203</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>177</v>
+        <v>366</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="10">
         <v>5</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C65" s="10">
         <v>4</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>355</v>
+        <v>252</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="12">
@@ -4615,36 +4610,36 @@
         <v>46326</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>188</v>
+        <v>368</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="10">
         <v>5</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C66" s="10">
         <v>4</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>289</v>
+        <v>374</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="12">
@@ -4654,36 +4649,36 @@
         <v>46356</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>180</v>
+        <v>370</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="10">
         <v>5</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C67" s="10">
         <v>4</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="12">
@@ -4693,16 +4688,16 @@
         <v>46234</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>183</v>
+        <v>372</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>184</v>
+        <v>375</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -4710,19 +4705,19 @@
         <v>5</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C68" s="10">
         <v>4</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="12">
@@ -4732,21 +4727,21 @@
         <v>46112</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="10">
         <v>6</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C69" s="10">
         <v>1</v>
@@ -4755,37 +4750,34 @@
         <v>6</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>319</v>
+        <v>218</v>
       </c>
       <c r="H69" s="12">
-        <v>45931</v>
+        <v>45778</v>
       </c>
       <c r="I69" s="12">
-        <v>46112</v>
+        <v>45869</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>350</v>
+        <v>187</v>
       </c>
       <c r="M69" s="1"/>
     </row>
-    <row r="70" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="10">
         <v>6</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C70" s="10">
         <v>1</v>
@@ -4794,36 +4786,34 @@
         <v>6</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>319</v>
+        <v>218</v>
       </c>
       <c r="H70" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I70" s="12">
-        <v>46387</v>
+        <v>46053</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="M70" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>187</v>
+      </c>
+      <c r="M70" s="1"/>
+    </row>
+    <row r="71" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="10">
         <v>6</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C71" s="10">
         <v>1</v>
@@ -4832,36 +4822,37 @@
         <v>6</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>319</v>
+        <v>218</v>
       </c>
       <c r="H71" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I71" s="12">
-        <v>46387</v>
+        <v>46112</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>187</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="M71" s="1"/>
+    </row>
+    <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="10">
         <v>6</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
@@ -4870,28 +4861,36 @@
         <v>6</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>45</v>
+        <v>244</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="H72" s="12"/>
-      <c r="I72" s="12"/>
+        <v>218</v>
+      </c>
+      <c r="H72" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I72" s="12">
+        <v>46387</v>
+      </c>
       <c r="J72" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K72" s="5"/>
-      <c r="L72" s="4"/>
-    </row>
-    <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>159</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="10">
         <v>6</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C73" s="10">
         <v>1</v>
@@ -4900,151 +4899,126 @@
         <v>6</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H73" s="12"/>
-      <c r="I73" s="12"/>
+        <v>218</v>
+      </c>
+      <c r="H73" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I73" s="12">
+        <v>46387</v>
+      </c>
       <c r="J73" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K73" s="5"/>
-      <c r="L73" s="4"/>
-    </row>
-    <row r="74" spans="1:13" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>159</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="10">
         <v>6</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C74" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>294</v>
+        <v>379</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="H74" s="12">
-        <v>46204</v>
-      </c>
-      <c r="I74" s="12">
-        <v>46387</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
       <c r="J74" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K74" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="M74" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
+      <c r="K74" s="5"/>
+      <c r="L74" s="4"/>
+    </row>
+    <row r="75" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="10">
         <v>6</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C75" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>341</v>
+        <v>161</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="H75" s="12">
-        <v>46023</v>
-      </c>
-      <c r="I75" s="12">
-        <v>46142</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
       <c r="J75" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+      <c r="K75" s="5"/>
+      <c r="L75" s="4"/>
+    </row>
+    <row r="76" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="10">
         <v>6</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>341</v>
+        <v>160</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>292</v>
+        <v>201</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="H76" s="12">
-        <v>45992</v>
-      </c>
-      <c r="I76" s="12">
-        <v>46142</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
       <c r="J76" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+      <c r="K76" s="5"/>
+      <c r="L76" s="4"/>
+    </row>
+    <row r="77" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="10">
         <v>6</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C77" s="10">
         <v>2</v>
@@ -5053,39 +5027,39 @@
         <v>7</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>344</v>
+        <v>46</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>293</v>
+        <v>205</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>323</v>
+        <v>221</v>
       </c>
       <c r="H77" s="12">
-        <v>46023</v>
+        <v>46204</v>
       </c>
       <c r="I77" s="12">
         <v>46387</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>217</v>
+        <v>380</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="10">
         <v>6</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C78" s="10">
         <v>2</v>
@@ -5094,39 +5068,39 @@
         <v>7</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>314</v>
+        <v>240</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>222</v>
+        <v>45</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>325</v>
+        <v>212</v>
       </c>
       <c r="H78" s="12">
         <v>46023</v>
       </c>
       <c r="I78" s="12">
-        <v>46357</v>
+        <v>46142</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>223</v>
+        <v>382</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="10">
         <v>6</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C79" s="10">
         <v>2</v>
@@ -5135,39 +5109,39 @@
         <v>7</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>342</v>
+        <v>240</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>261</v>
+        <v>203</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>313</v>
+        <v>223</v>
       </c>
       <c r="H79" s="12">
-        <v>45931</v>
+        <v>45992</v>
       </c>
       <c r="I79" s="12">
-        <v>46053</v>
+        <v>46142</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>196</v>
+        <v>384</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="10">
         <v>6</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C80" s="10">
         <v>2</v>
@@ -5176,39 +5150,39 @@
         <v>7</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>342</v>
+        <v>243</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>291</v>
+        <v>204</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>313</v>
+        <v>222</v>
       </c>
       <c r="H80" s="12">
         <v>46023</v>
       </c>
       <c r="I80" s="12">
-        <v>46112</v>
+        <v>46387</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="M80" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
+        <v>386</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="10">
         <v>6</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C81" s="10">
         <v>2</v>
@@ -5217,39 +5191,39 @@
         <v>7</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>342</v>
+        <v>213</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>313</v>
+        <v>224</v>
       </c>
       <c r="H81" s="12">
         <v>46023</v>
       </c>
       <c r="I81" s="12">
-        <v>46203</v>
+        <v>46357</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="L81" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="M81" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="230.4" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="10">
         <v>6</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
@@ -5258,39 +5232,39 @@
         <v>7</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>342</v>
+        <v>241</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>313</v>
+        <v>212</v>
       </c>
       <c r="H82" s="12">
-        <v>46174</v>
+        <v>45931</v>
       </c>
       <c r="I82" s="12">
-        <v>46295</v>
+        <v>46053</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="L82" s="1" t="s">
-        <v>205</v>
+        <v>162</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="10">
         <v>6</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C83" s="10">
         <v>2</v>
@@ -5299,347 +5273,349 @@
         <v>7</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>342</v>
+        <v>241</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>313</v>
+        <v>212</v>
       </c>
       <c r="H83" s="12">
         <v>46023</v>
       </c>
       <c r="I83" s="12">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+        <v>392</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="10">
         <v>6</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C84" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="G84" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="H84" s="12">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="I84" s="12">
-        <v>46157</v>
+        <v>46203</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>164</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="10">
         <v>6</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C85" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G85" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="H85" s="12">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="I85" s="12">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L85" s="4"/>
+        <v>165</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="M85" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="216" x14ac:dyDescent="0.55000000000000004">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="10">
         <v>6</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C86" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>266</v>
+        <v>44</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>318</v>
+        <v>212</v>
       </c>
       <c r="H86" s="12">
         <v>46023</v>
       </c>
       <c r="I86" s="12">
-        <v>46357</v>
+        <v>46142</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>235</v>
+        <v>166</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>236</v>
+        <v>398</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="10">
         <v>6</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C87" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>264</v>
+        <v>209</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="G87" s="3"/>
       <c r="H87" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I87" s="12">
-        <v>46082</v>
+        <v>46157</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>233</v>
+        <v>400</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="10">
         <v>6</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C88" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>264</v>
+        <v>209</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>295</v>
+        <v>193</v>
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="12">
-        <v>45901</v>
+        <v>46173</v>
       </c>
       <c r="I88" s="12">
-        <v>46112</v>
+        <v>46387</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="L88" s="4"/>
       <c r="M88" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="10">
         <v>6</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C89" s="10">
         <v>4</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>264</v>
+        <v>48</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G89" s="3"/>
+        <v>196</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="H89" s="12">
-        <v>45901</v>
+        <v>46023</v>
       </c>
       <c r="I89" s="12">
-        <v>46112</v>
+        <v>46357</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>230</v>
+        <v>403</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="10">
         <v>6</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C90" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>311</v>
+        <v>47</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>343</v>
+        <v>194</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>316</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="G90" s="3"/>
       <c r="H90" s="12">
         <v>46023</v>
       </c>
       <c r="I90" s="12">
-        <v>46295</v>
+        <v>46082</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>239</v>
+        <v>405</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="10">
         <v>6</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C91" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>311</v>
+        <v>47</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>312</v>
+        <v>194</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>317</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="G91" s="3"/>
       <c r="H91" s="12">
-        <v>46023</v>
+        <v>45901</v>
       </c>
       <c r="I91" s="12">
-        <v>46266</v>
+        <v>46112</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>241</v>
+        <v>407</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>240</v>
+        <v>408</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
@@ -5647,45 +5623,166 @@
         <v>6</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="C92" s="10">
+        <v>4</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G92" s="3"/>
+      <c r="H92" s="12">
+        <v>45901</v>
+      </c>
+      <c r="I92" s="12">
+        <v>46112</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="10">
+        <v>6</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C93" s="10">
         <v>5</v>
       </c>
-      <c r="D92" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="H92" s="12">
+      <c r="D93" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H93" s="12">
         <v>46023</v>
       </c>
-      <c r="I92" s="12">
+      <c r="I93" s="12">
+        <v>46295</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="10">
+        <v>6</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C94" s="10">
+        <v>5</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H94" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I94" s="12">
+        <v>46266</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="10">
+        <v>6</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C95" s="10">
+        <v>5</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H95" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I95" s="12">
         <v>46357</v>
       </c>
-      <c r="J92" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="L92" s="4"/>
-      <c r="M92" s="2" t="s">
-        <v>243</v>
+      <c r="J95" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L95" s="4"/>
+      <c r="M95" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M92">
-    <sortCondition ref="A9:A92"/>
-    <sortCondition ref="C9:C92"/>
-    <sortCondition ref="E9:E92"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M95">
+    <sortCondition ref="A9:A95"/>
+    <sortCondition ref="C9:C95"/>
+    <sortCondition ref="E9:E95"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emretasci\antigravity\scm-project-portal\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{257BABEA-FDF5-43DC-8E2D-61D4597C19B1}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
@@ -42,70 +42,43 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="420">
   <si>
-    <t>Tahminleme</t>
-  </si>
-  <si>
-    <t>S&amp;OP</t>
-  </si>
-  <si>
-    <t>Entegre Planlama</t>
-  </si>
-  <si>
-    <t>Envanter Yönetimi</t>
-  </si>
-  <si>
-    <t>Malzeme Depo Yönetimi</t>
-  </si>
-  <si>
-    <t>Tedarikçi İlişkileri Yönetimi</t>
-  </si>
-  <si>
-    <t>MES</t>
-  </si>
-  <si>
-    <t>MES Uygulamaları</t>
-  </si>
-  <si>
-    <t>Dijital Dönüşüm Merkezi</t>
-  </si>
-  <si>
-    <t>Bu çalışma ile planlama sürecine şirket içindeki bilgilere ilave olarak, bayi ağımızdaki KS ürünleri satış ve stok bilgilerinin de eklenerek planlama sürecinin etkinliğinin artırılması hedeflenmektedir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belirli bir geliştirme planına bağlı olarak önceliklendirilen kategori, malzeme ve hizmet gruplarında en iyi uygulamaları öğrenmek, yetkinlikleri geliştirmek ve grup için kırılımlı maliyet yapısının sistematik veri olarak elde edilmesini de sağlayacak faaliyetleri içeren çalışmadır. </t>
-  </si>
-  <si>
-    <t>Sipariş Kurallarının Güncellenmesi</t>
-  </si>
-  <si>
-    <t>Elleçleme, hurda, fırsat, outlet, iade, kalite gibi ana süreci destekleyici fonksiyonu bulunan kaydi depoların akış kural setlerinin oluşturulmasını ve kullanıcı yetki tanımlarının güncellenmesi amaçlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Slab &amp; SFX kapsamı, büyük ebat mamullerin fabrikadan teslim alınmasından, müşteriye ulaşmasına kadar tüm yükleme, boşaltma, stoklama ve elleçleme süreçlerinde İSG açısından riskleri ve olası verimsizlikleri değerlendirerek, süreci tanımlama ve bu operasyonlarda görev yapan personelin yetkinliği ve farkındalığını artırma hedeflenmektedir.</t>
-  </si>
-  <si>
-    <t>Sevkiyat kapı araç girişi, saha planlama, yükleme ve araç çıkış süreçlerini içeren tüm akışın süreçsel ve yapısal olarak yenilenmesi aksiyonlarını içermektedir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slab &amp; SFX stand hazırlık bölümü ile SKM teşhir bölümünü birleştirilerek tüm tanıtım materyalleri kapsamında, stok, sipariş, üretim ve sevkiyat süreçlerinin yönetildiği bir atölye hedeflenmektedir.
-Numune ürün, stand, el panosu, binder, teşhir ünitesi, katalog, broşür, promosyon vb. tüm pazarlama materyalleri bu kapsama girmektedir. </t>
-  </si>
-  <si>
-    <t>CeramIQ - Gerçek Zamanlı Üretim Verisi ve Akıllı Ajanları ile Desteklenen Endüstriyel Yapay Zekâ Modellerinin Geliştirilmesi ve Etkileşimli Karar Destek Asistanlarının Tasarımı
-Seramik üretim süreçlerinde (masse hazırlık, karo üretim ve fırın sonrası işlemler dahil) gerçek zamanlı üretim verilerinin toplanması, yapay zekâ tabanlı analitik modellerin geliştirilmesi ve etkileşimli karar destek asistanlarının kullanıma alınmasıyla; verimlilik, kalite, enerji optimizasyonu ve sürdürülebilirlik hedeflerini gerçekleştirmeyi amaçlamaktadır.</t>
-  </si>
-  <si>
-    <t>Dijital Dönüşüm Destek Programı ile teknolojik ürün ve çözümlerin işletme süreçlerine entegre edilmesi, işletmelerin üretim ve tedarik zinciri süreçlerinde verimliliklerinin artırılması, işletmelere küresel rekabette üstünlük kazandırılması ve Türkiye'nin teknolojik yetkinliğini yükselterek katma değerli ürünler üretilmesi amaçlanmaktadır.
-Kaleseramik olarak 5. Bölge teşviklerinden yararlanmak ve Dijital Dönüşüm Merkezi ünvanı alabilmek için başvuru yapılması planlanmıştır.</t>
-  </si>
-  <si>
-    <t>Dijital Dönüşüm Merkezi ünvanı alındıktan sonra ilgili projelerin yürütülmesi konusundaki proje yönetimi faaliyetlerini kapsamaktadır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TZY Görünürlük Raporları ile üretim, stok, müşteri ve performans verilerinin bütünsel ve şeffaf bir şekilde izlenmesi, veriye dayalı karar alma süreçlerinin güçlendirilmesi ve her kategori için standart raporların hazırlanarak sürdürülebilir bir raporlama altyapısının oluşturulması hedeflenmektedir . Bu hedef doğrultusunda her kategori için kod sistematiği içeren PowerBI raporları oluşturulmaktadır. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bu proje TZ süreçlerinde yapay zeka kullanımın yaklaşımını tanımlayan genel projeyi ifade etmektedir.  Veri analitiği dışında yapay zekanın kullanımına yönelik iki yaklaşım benimsenmiştir. İlki iş verilerinin büyük dil modellerine bağlanması ile bir ara yüz dahilinde hızlı raporlama ve içgörülerin alınmasıdır. Diğer ise kullanım durumu bazında yapay zeka ajanlarının iş süreçlerinde kullanılması ve çözümler oluşturulmasıdır. </t>
+    <t>department order</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>function order</t>
+  </si>
+  <si>
+    <t>function</t>
+  </si>
+  <si>
+    <t>project_group</t>
+  </si>
+  <si>
+    <t>project_name</t>
+  </si>
+  <si>
+    <t>digital_initiative</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>end_date</t>
+  </si>
+  <si>
+    <t>project_status</t>
+  </si>
+  <si>
+    <t>project_desc</t>
+  </si>
+  <si>
+    <t>done_list</t>
+  </si>
+  <si>
+    <t>todo_list</t>
   </si>
   <si>
     <t>Talep Yönetimi</t>
@@ -114,123 +87,258 @@
     <t>Veri Yönetimi</t>
   </si>
   <si>
+    <t>Ürün Ana Verisi</t>
+  </si>
+  <si>
     <t>Ürün Ana Veri Tanımlarının Düzenlenmesi</t>
   </si>
   <si>
-    <t>Web Crawling ile Verilerin Toplanması</t>
-  </si>
-  <si>
-    <t>S&amp;OP Aracı için RFP Oluşturulması</t>
-  </si>
-  <si>
-    <t>Hizmet Seviyesi Yönetimi</t>
-  </si>
-  <si>
-    <t>Planlama</t>
-  </si>
-  <si>
-    <t>S&amp;OE Sürecinin Tanımlanması</t>
-  </si>
-  <si>
-    <t>S&amp;OE Sürecinin Devreye Alınması</t>
-  </si>
-  <si>
-    <t>Satınalma</t>
-  </si>
-  <si>
-    <t>Tedarikçi Geliştirme</t>
-  </si>
-  <si>
-    <t>Mevcut Tedarikçilerin Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Yetkinlik Geliştirme</t>
-  </si>
-  <si>
-    <t>Talep Yönetimi ve Operasyonel Satınalma</t>
-  </si>
-  <si>
-    <t>SAS Onay Sisteminin Genişletilmesi</t>
-  </si>
-  <si>
-    <t>Lojistik</t>
-  </si>
-  <si>
-    <t>Yönetim Sistemi</t>
-  </si>
-  <si>
-    <t>Kiralık Araçlar Optimizasyonu</t>
-  </si>
-  <si>
-    <t>Mamul Depo Yönetimi</t>
-  </si>
-  <si>
-    <t>Teşhir Operasyonları</t>
-  </si>
-  <si>
-    <t>Mobilya Üretimi MES Yapısının Kurulması</t>
-  </si>
-  <si>
-    <t>Fırın Verimliliğinin Canlı Takibi</t>
-  </si>
-  <si>
-    <t>Masse Boya Tahminleme Modeli</t>
-  </si>
-  <si>
-    <t>Bilya Performans Takibi</t>
-  </si>
-  <si>
-    <t>Püskürtmeli Kurutucu Otomasyonu</t>
-  </si>
-  <si>
-    <t>Fırın İzleme Sistemi</t>
-  </si>
-  <si>
-    <t>İş Zekası ve Görünürlük</t>
-  </si>
-  <si>
-    <t>Dijital İkiz</t>
-  </si>
-  <si>
-    <t>SAP TM Loading Optimization Application'dan yararlanarak rota planlamasının optimizasyonu (araştırma ve entegrasyon) ve araç doluluk verimliğinin artırılması.</t>
-  </si>
-  <si>
-    <t>Tamamlandı</t>
-  </si>
-  <si>
     <t>Devam Ediyor</t>
+  </si>
+  <si>
+    <t>Ürün ana veri yapısının incelenerek geliştirme/iyileştirme alanları ile hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Talep tahmin veri analitiği, SKU rasyonalizasyonu,  görünürlük, planlama stratejileri gibi pek çok çalışma için ürün ana veri yapısının iyileştirilmesi ihtiyacı ön koşul olarak bulunmaktadır.</t>
+  </si>
+  <si>
+    <t>Ana ebat tanımlarındaki eksikliklerin giderilmesi
+Faturalama için ambalaj tipi tanımlarının yapılması
+Piyasa kanalı tanımlarının revizyonu
+Üretim kontrol notu tanımlarındaki eksikliklerin giderilmesi
+Ürün hiyerarşisi uyumsuzluklarının tespiti ve düzeltilmesi
+Ürün hiyerarşisi tanımı yanlış olan kodların tespiti ve düzeltilmesi
+Gömme rezervuar ürün grubunda set kodlarının ayrıştırılması
+UP kodları için Marka bilgilerinin düzeltilmesi ve tamamlanması
+Orijin kodu bilgisinin düzenlenmesi ile ilgili çalışmaların başlatılması
+Ürün karakteristiklerinde yer alan kalite tanımı bilgilerinin düzenlenmesi</t>
+  </si>
+  <si>
+    <t>Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-Vitrifiye
+Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-Mobilya
+Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-SKM 
+Farklı kalitedeki ürünlerin stok kodları arasında bağlantı oluşturulması</t>
+  </si>
+  <si>
+    <t>Ürün Ambalaj Bilgilerinin Tanımlanması</t>
+  </si>
+  <si>
+    <t>Ürün ana veri yapısında bulunan ambalaj bilgilerinin incelenerek hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Yükleme-rotalama optimizasyonu ve nakliye hesaplaması gibi pek çok çalışma için ürün ambalaj bilgilerinin tanımlanması ihtiyacı ön koşul olarak bulunmaktadır.</t>
+  </si>
+  <si>
+    <t>Palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
+Ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
+Ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - Mobilya
+Palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - SKM</t>
   </si>
   <si>
     <t>Ürün ve palet kg bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
 Palet içi miktar bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye</t>
   </si>
   <si>
+    <t>Ürünler Arası İlişki Tanımlarının Oluşturulması</t>
+  </si>
+  <si>
     <t>Birbirleri ile satış ve fonksiyonellik açısından bağı bulunun ancak mevcutta ürün ağacı, pack, vb. bir veri yapısında bu ilişkisi tanımlanmamış olan ürünlerin ilgili veri yapısının kurumsal veri olarak yapılandırılması çalışmasıdır.</t>
   </si>
   <si>
     <t>Örnek veri yapısının oluşturularak IT ile paylaşılması</t>
   </si>
   <si>
+    <t>İlgili ürünlerin ve ilişkilerin belirlenmesi
+İlgili veri yapısının şirket içindeki kullanım şeklinin netleştirilmesi
+MRP tarafındaki kullanımının araştırılması
+Planlamadaki miktar bilgilerinde kullanılması
+Raporlamalardaki kullanım
+B2B'de öneri şeklinde sunulması
+Kalecore sayfasında öneri şeklinde sunulması
+Mevcut veri yapısının araştırılması (kataloglar ve fiyat listeleri gibi)
+İlişkilerin Tanımına dair ana veri yapısı çalışmasının yürütülmesi (IT ile)
+Gerekli tanımlamaların yapılması</t>
+  </si>
+  <si>
+    <t>Ürün İlişki Tanımları Aracının Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>KS2026-16</t>
+  </si>
+  <si>
     <t>Başlamadı</t>
   </si>
   <si>
+    <t>"Ürünler Arası İlişki Tanımlarının Oluşturulması" projesi kapsamında oluşturulan verinin kurumsal olarak saklanması ve yönetimi için için yönetim aracı geliştirilmedi çalışmasıdır.</t>
+  </si>
+  <si>
     <t>İlişki Verileri Yönetim Aracının Oluşturulması</t>
   </si>
   <si>
+    <t>Tahmin Dış Verisi</t>
+  </si>
+  <si>
+    <t>Web Crawling ile Verilerin Toplanması</t>
+  </si>
+  <si>
     <t>Takip</t>
+  </si>
+  <si>
+    <t>Müşteri ziyaretlerinden SF üzerinde toplanan veriler, web crawling yöntemleriyle edinilen sektörel bilgiler ve GFK gibi dış kaynaklardan sağlanan veri setlerinin birlikte değerlendirilerek bir veri gölü yapısı oluşturulması çalışmasıdır. Konut istatistikleri, çıkarılan ruhsat sayıları, beyaz eşya satışları ve evlilik oranları gibi makro göstergelerle ilişkilendirilerek ileri analizler için altyapı hazırlanması.</t>
+  </si>
+  <si>
+    <t>Teşhir Envanteri</t>
+  </si>
+  <si>
+    <t>SF Teşhir Verisi Giriş Teknolojisinin Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Müşteri temsilcilerinin teşhir envanter bilgilerini daha hızlı ve pratik bir şekilde SF sistemine aktarabilmelerini sağlamak amacıyla yapılan çalışmadır.</t>
+  </si>
+  <si>
+    <t>Müşteri Temas
+Verisi</t>
+  </si>
+  <si>
+    <t>SF Temas Verisi Giriş Teknolojisinin Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Müşteri temsilcilerinin müşteri temas verilerini daha hızlı ve pratik bir şekilde SF sistemine aktarabilmelerini sağlamak amacıyla yapılan çalışmadır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kampanya Verisi
+</t>
+  </si>
+  <si>
+    <t>Kampanya Modül İhtiyaçlarının Belirlenmesi</t>
+  </si>
+  <si>
+    <t>Kampanya süreçlerinin analizi, iş birimlerinden ihtiyaç toplanması ve hedeflenen kampanya yönetimi fonksiyonlarının belirlenmesi ile modül tasarım kriterlerinin oluşturulması çalışmasıdır.</t>
+  </si>
+  <si>
+    <t>Kampanya Modül Tasarımının Oluşturulması</t>
+  </si>
+  <si>
+    <t>KKIM26-9</t>
+  </si>
+  <si>
+    <t>"Kampanya Modül İhtiyaçlarının Belirlenmesi" proje kapsamında belirlenen ihtiyaç ve kriterlere uygun olarak kampanya yönetim modülünün oluşturulması ve/veya geliştirilmesi çalışmasıdır.</t>
+  </si>
+  <si>
+    <t>Ürün Yaşam Döngüsü Verisi</t>
+  </si>
+  <si>
+    <t>Ürün Yaşam Döngüsü Bilgisinin Oluşturulması</t>
+  </si>
+  <si>
+    <t>KS2026-57</t>
+  </si>
+  <si>
+    <t>Ürün yaşam döngüsü takibine yönelik olarak windchill PLM akışında, talebin piyasa dağılımlı miktarsal ve tutarsal planı ve gerçekleşme durumu ve diğer ilgili bilgilerin eklenmesi çalışmasıdır.</t>
+  </si>
+  <si>
+    <t>Tahminleme</t>
+  </si>
+  <si>
+    <t>Tahmin Yeteneği</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahmin DFU Yapısının Güncellenmesi
+</t>
+  </si>
+  <si>
+    <t>Tamamlandı</t>
+  </si>
+  <si>
+    <t>Satış miktarlarındaki değişimler, palet konumu değişimleri ve tahmin doğruluk değerlerine göre DFU yapılarının güncellenme ihtiyacı bulunmaktadır. Bu güncellemelerde maliyet, fiyat, marka, üretim kaynağı-ticari, fabrika gibi unsurlar göz önünde bulundurulmaktadır. Bu proje ilgili ihtiyacı karşılamaya yönelik olarak DFU-SKU eşleşmesinin güncellenmesi içeren çalışmadır.</t>
+  </si>
+  <si>
+    <t>Satış verileri incelenerek DFU’ların etkinliğine ilişkin analizler oluşturuldu.
+Analizler sonucunda oluşturulan öneriler satış, kategori pazarlama ve planlama ekipleri ile paylaşıldı.
+Yapılan toplantılar ile kaldırılması, birleştirilmesi ya da yeni oluşturulması gereken DFU’lar belirlendi.
+Yeni DFU kodlarının SAP tanımları yapılarak eski DFU’lar kaldırıldı.
+SAP’de stok kodu ve yeni DFU eşleşmeleri tanımlandı.
+Yeni tanımlanan stok kodlarına ilişkin DFU tanımlarının güncel DFU’lar ile oluşturulması sağlanmaktadır.
+Periyodik olarak SAP’de tanımlı olan DFU’ların kontrolü ve tanımlanması sağlanmaktadır.</t>
   </si>
   <si>
     <t xml:space="preserve">
 </t>
   </si>
   <si>
+    <t>Yeni DFU Yapısı ile Modelin Eğitilmesi</t>
+  </si>
+  <si>
+    <t>Bu proje; değişen DFU yapıları doğrultusunda tahmin modelinin yeniden eğitilmesi ve mevcut tahmin uygulamasının yeni DFU’lar ile devreye alınması çalışmalarını kapsamaktadır.</t>
+  </si>
+  <si>
+    <t>Modelin eğitilmesine yönelik çalışma takvimi ve proje adımları belirlenmiştir.
+Modele beslenen dış verilere ait güncel değerler oluşturulmuştur.
+Model eğitiminin tamamlanması ile birlikte çıkan tahmin sonuçları incelenerek, tespit edilen hatalar doğrultusunda gerekli revizyonlar yaptırılmıştır.
+Sonuçların raporlanmasına ilişkin isterler belirlenerek piyasa ve DFU bazlı tahmin raporları oluşturulmuştur.
+Tahmin sonuçlarının düzenli olarak çalıştırılarak takip edilmektedir.
+Tahmin metrikleri hesaplanarak düzenli takip edilmektedir.
+SKU seviyesindeki sonuçlar planlama süreçlerinde kullanılmaktadır.</t>
+  </si>
+  <si>
+    <t>Talep Tahmin Modelinin Oluşturulması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahmin yetkinliğinin arttırılmasına yönelik olarak tahmin veri setinin değiştirilerek müşteri siparişi, fiyat, dış veriler, bayi satış verileri gibi bilgilerin kullanılarak yeni tahmin modelinin oluşturulmasına yönelik çalışmaları kapsamaktadır. </t>
+  </si>
+  <si>
+    <t>Tahmin modelinin oluşturulmasına yönelik kavramsal çalışmalar başlatılmıştır.
+Müşteri sipariş verilerine yönelik veri seti oluşturulmuştur.
+In-house talep tahmin çalışması başlatılmıştır.
+Model ve uygulamanın oluşturulmasına yönelik danışman firma ile proje takvimi ve adımlarının belirlenmesi devam etmektedir.</t>
+  </si>
+  <si>
+    <t>Modele beslenecek dış veriler belirlenecektir.
+Veri setinin analizi ve yeni tahmin modelinin tasarımı oluşturulacaktır. 
+Modelin eğitimi tamamlanarak sonuçlar değerlendirilecektir.
+Uygulama testleri ile uygulama devreye alınacaktır.</t>
+  </si>
+  <si>
+    <t>Tahminde Müşteri, Kampanya, Teşhir Bilgilerinin Kullanımı</t>
+  </si>
+  <si>
+    <t>KS2026-18</t>
+  </si>
+  <si>
+    <t>İptal</t>
+  </si>
+  <si>
+    <t>Müşteri: Farklı müşteri eğilimlerini katmak üzere müşteri boyutunda satış organizasyonuna ilave dağıtım kanalı ve satış grubunun eklenmesi çalışmasıdır.
+Kampanya: Satış tahmin modeline kampanya etkisinin eklenmesi çalışmasıdır.
+Teşhir: Satış tahmin modeline bayi teşhir bilgisinin eklenmesi çalışmasıdır.</t>
+  </si>
+  <si>
+    <t>Genel Talep Tahmin Modelinin Oluşturulması</t>
+  </si>
+  <si>
+    <t>KS2026-17</t>
+  </si>
+  <si>
+    <t>Piyasa büyüklügüne bağlı olarak genel talep tahminleme modelinin oluşturulması çalışmasıdır. Öncelikle ihtiyacın hangi seviyede olduğu belirlenecek ve sonrasında Türkiye ve/veya dünya için toplam bir talep tahmin modeli çalışması yürütülecektir.</t>
+  </si>
+  <si>
+    <t>S&amp;OP</t>
+  </si>
+  <si>
+    <t>S&amp;OP Olgunluğu</t>
+  </si>
+  <si>
+    <t>Tahmin Fonksiyonunun Süreçlerde Kullanımı</t>
+  </si>
+  <si>
     <t>Satış tahmin fonksiyonunun şirket iş süreçlerinde kullanımı ve tahmin yetkinliğinin arttırılmasına yönelik çalışmaları kapsamaktadır.  Tahmin sonuçlarının S&amp;OP, BE ve bütçe çalışmalarında girdi olarak kullanılması, ilerleyen süreçlerde ise SKU seviyesinde tahminlerin yapılması ve bu tahminlerin entegre planlama sürecinde kullanılması amaçlanmaktadır.</t>
   </si>
   <si>
-    <t>İptal</t>
-  </si>
-  <si>
-    <t>Talep Tahmin Modelinin Oluşturulması</t>
+    <t>Modelinin tekrar eğitilmesine yönelik çalışmalar tamamlanmıştır.
+Sonuçlarının raporlanmasına ilişkin isterler belirlenerek piyasa ve DFU bazlı raporlar oluşturulmuştur.
+Tahmin sonuçlarının S&amp;OP döngüsüne girdi olarak kullanılmasına ilişkin çalışmalar başlatılmıştır.
+Baz tahminler piyasalar ile paylaşılarak talep zenginleştirme çalışmaları yürütülmektedir.
+Tahmin sonuçları düzenli olarak takip edilmektedir.
+Tahmin doğruluğu metriklerinin belirlenmiştir. Düzenli olarak hesaplanarak takip edilmektedir.
+Baz tahmin, revize baz tahmin, revize tahmin, nihai tahmin sonuçlarının ve tahmin sapmalarının görüntülenmesine ilişkin Power BI raporlama dashboardu oluşturulmuştur.
+SKU seviyesinde tahmin sonuçlarının planlama süreçlerinde kullanılmaktadır.</t>
+  </si>
+  <si>
+    <t>S&amp;OP Sürecinin Gel. ve Standardizasyonu</t>
   </si>
   <si>
     <t>S&amp;OP sürecinin şirket genelinde standart, entegre ve sürdürülebilir hale getirilerek kültürün yayılımının sağlanması, karar alma hızının ve doğruluğunun artırılmasına yönelik çalışmaları kapsamaktadır.</t>
@@ -248,6 +356,30 @@
     <t>Finansallaştırma adımının eklenmesi ile birlikte S&amp;OP döngüsünün tamamlanması</t>
   </si>
   <si>
+    <t>Talep Optimizasyon Aracının Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Mevcut taleplerin karşılanmasının ötesinde, belirli müşteri-ürün gruplarına yönelik yüksek kar oluşturan çalışma şeklinin ortaya çıkarılmasını sağlayacak şekilde optimizasyon aracının geliştirilmesi çalışmasıdır. Araç hat yetenekleri ve talep kısıtlarına göre maksimum kar için talep planının oluşturulmasını sağlayacaktır.</t>
+  </si>
+  <si>
+    <t>Optimizasyon modelinin oluşturulması tamamlandı.
+Modelin çözümüne ilişkin python kodu geliştirildi.
+Veri girişi, veri export, optimizasyon ve raporlama özellikleri eklenerek komple bir web uygulaması çözümü oluşturuldu.
+Çözüm ve uygulama Kale Masters Doğrusal Programlama eğitimi kapsamında geliştirilmiştir.</t>
+  </si>
+  <si>
+    <t>S&amp;OP Tool</t>
+  </si>
+  <si>
+    <t>S&amp;OP Talep Planlama Uyg. Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>KS2026-25</t>
+  </si>
+  <si>
+    <t>Talep tahmin uygulamasının çıktısını kullanarak tedarik planlama adımına girdi olacak ve mutabakat sağlanmış talep değerlerinin oluşturulmasını sağlayacak talep zenginleştirme ve mutabakat uygulamasının geliştirilmesi çalışmasıdır. Tahmin sonuçlarının girdi olarak alınabildiği, belirli hiyerarşilerde düzeltme yapılabildiği, belirli kişilerin üzerinde çalışabildiği ve veri girişi yapabildiği esnek bir ortam geliştirme çalışmasıdır. Odoo platformu üzerinde In-house olarak geliştirilmektedir.</t>
+  </si>
+  <si>
     <t>İstekler belirlenerek kavramsal tasarım dokümanı IT birimine iletilmiştir.
 Yazılım ve KS ekibi kavramsal tasarım üzerinde mutabakat sağlamıştır.
 İş akış dokümanı oluşturulmuştur ve IT ekibine iletilmiştir.
@@ -258,7 +390,41 @@
     <t>Proje takvimine uygun olarak aksiyon takibi ve test çalışmaları yürütülecektir.</t>
   </si>
   <si>
+    <t>S&amp;OP Finansallaştırma Uyg. Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>KS2026-26</t>
+  </si>
+  <si>
+    <t>S&amp;OP süreci talep ve tedarik planlama adımlarından çıkan bilgilerin fiyat, maliyet, başta olmak üzere diğer finansal girdilerin kullanılarak tutarsal hale getirilmesi ve raporlanması çalışmasıdır. Buradan çıkan farklı senaryolar bazındaki finansalların değerlendirilmesi ile operasyonel planlara karar verilmesi sağlanacaktır. Bu çalışma In-house olarak planlanmaktadır.</t>
+  </si>
+  <si>
+    <t>S&amp;OP Aracı için RFP Oluşturulması</t>
+  </si>
+  <si>
     <t>Talep tahmini, talep zenginleştirme, tedarik planlama, finansallaştırma, optimizasyon özelliklerini içeren komple bir entegre planlama süreci için tool araştırmaya kaynak olacak KS ihtiyaçlarının belirlenmesi çalışmasıdır.</t>
+  </si>
+  <si>
+    <t>S&amp;OP Aracının Geliştirilmesi (In-House)</t>
+  </si>
+  <si>
+    <t>KS2026-27</t>
+  </si>
+  <si>
+    <t>Kullanılan talep tahmin uygulaması, geliştirilmesi devam eden talep planlama uygulaması, geliştirilmesi planlanan finansallaştırma uygulaması çözümlerinin bir paket olarak birbirine bağlanmış bir ürün hale getirilmesi çalışmasıdır.
+In-house olarak ürünleştirme çalışmasından verim alınamaması durumunda yapılmış olan RFP çalışmasına istinaden ürün araştırılması yine bu çalışma kapsamındadır.</t>
+  </si>
+  <si>
+    <t>Hizmet Seviyesi Yönetimi</t>
+  </si>
+  <si>
+    <t>Hizmet Seviyesi</t>
+  </si>
+  <si>
+    <t>Beklenen Hizmet Sev. Tanımlanması</t>
+  </si>
+  <si>
+    <t>TZ süreçlerinin, beklenen hizmet seviyesini karşılayacak şekilde çalışabilmesi için müşteri-ürün boyutlarında farklılaşan beklenen hizmet seviyelerinin tanımlanması gerekmektedir. Bu proje ile müşteri-ürün boyutları bazında, belirlenmiş gruplar/kanallar için hizmet seviyelerinin tanımlanması amaçlamaktadır. Bu şekilde genel çalışma (standart hizmet) ve metrik takibinden, kategorize edilmiş ve tanımlanmış ihtiyaçların karşılandığı ve bunların ölçümü ile performans takibinin yapıldığı sisteme geçilebilecektir.</t>
   </si>
   <si>
     <t>Hizmet seviyesinin belirlenebilmesi için çalışma yapılacak boyutlara karar verilmesi (müşteri, ürün, sipariş tipi),
@@ -271,16 +437,91 @@
 Gruplar bazında özelleştirilmiş metrik sisteminin oluşturulması</t>
   </si>
   <si>
+    <t>Hizmet için TZ Aks. Oluşturulması</t>
+  </si>
+  <si>
+    <t>Beklenen Hizmet Seviyelerinin Tanımlanması projesinde oluşturulan, kategorize edilmiş hizmet seviyesi tanımlarının, karşılanmasına yönelik olarak aksiyonların oluşturulduğu ve takibinin yapıldığı çalışmadır.</t>
+  </si>
+  <si>
     <t>Tanımlanan hizmet seviyelerini sağlayacak şekilde tedarik zinciri aksiyon planlarının oluşturulması</t>
   </si>
   <si>
+    <t>PI ların Oluşturulması ve Takibi</t>
+  </si>
+  <si>
+    <t>Hizmet için Tedarik Zinciri Aksiyonlarının Oluşturulması projesinde oluşturulan, aksiyonların performans sonuçlarının ölçümü ve takibine yönelik çalışmaların yürütüldüğü projedir.</t>
+  </si>
+  <si>
     <t>Tanımlanan hizmet seviyelerinin kontrolü amacıyla tedarik zinciri performans metriklerinin oluşturulması ve takibi</t>
   </si>
   <si>
+    <t>Planlama</t>
+  </si>
+  <si>
+    <t>Entegre Planlama</t>
+  </si>
+  <si>
+    <t>S&amp;OE Süreci</t>
+  </si>
+  <si>
+    <t>S&amp;OE Sürecinin Tanımlanması</t>
+  </si>
+  <si>
+    <t>S&amp;OE süreci, onaylanmış S&amp;OP / Ana Üretim Planı çerçevesinde; kısa vadeli (günlük / haftalık) dönemde oluşan talep, stok ve sevkiyat sapmalarını hızlı kontrollü şekilde yönetmeyi amaçlayan, operasyonel bir karar alma sürecidir. Bu proje KS nin ihtiyaçlarına uygun S&amp;OE sürecinin geliştirilmesi ve tanımlanması çalışmasını içermektedir.</t>
+  </si>
+  <si>
+    <t>S&amp;OP toplantıları aylık olarak devam etmektedir. Toplantılarda stoklar, üretim planları, talep değişkenlikleri, üretim öncelikleri gibi bilgiler kontrol edilmektedir. 
+Süreç Kapsamının ve Zaman Ufku haftalık olarak belirlendi.
+Kritik karar konuları tamamlandı.
+Roller ve sorumluluklar netleştirildi. Paylaşılacak tablolar netleştirildi.
+Planlama olarak güncel tutulan tablolar üzerinden veri setleri oluşturuldu.
+Önceliklendirme ve Karar Kurallarının oluşturuldu.
+Toplantı yapısı katılımcılar ve periyotları belirlendi.
+KPI ve Başarı Göstergeleri S&amp;OP toplantılarında konuşulan aylık hedeflerin haftalık periyotlara bölünmüş hali olarak belirlendi. (Plana Uyum, Fazla Üretim vs.)</t>
+  </si>
+  <si>
+    <t>S&amp;OE Sürecinin Devreye Alınması</t>
+  </si>
+  <si>
     <t>Bu proje kapsamında; tanımlanan Sales &amp; Operations Execution (S&amp;OE) süreci, belirlenen kapsam, roller, veri setleri ve karar kuralları doğrultusunda operasyonel olarak devreye alınacaktır. Amaç; onaylanmış S&amp;OP ve ana üretim planları çerçevesinde, kısa vadede (günlük / haftalık) oluşan talep, üretim, stok ve sevkiyat sapmalarını standart bir toplantı ritmi ve veri seti ile yönetmek, alınan kararların sahada fiilen uygulanmasını ve takibini sağlamaktır.</t>
   </si>
   <si>
+    <t>Pilot kapsamın netleştirilmesi
+S&amp;OE Toplantı Ritminin başlatılması (1 Mart itibariyle başlatılacaktır)
+Standart veri seti ile operasyonun yürütülmesi
+Önceliklendirme ve karar kurallarının uygulanması
+Aksiyon Takibi ve Disiplinin Sağlanması
+Eskalasyon Mekanizmasının İşletilmesi
+KPI takibi ve ilk etki ölçümü
+Geri Bildirim ve iyileştirme</t>
+  </si>
+  <si>
+    <t>Entegre Planlama Yapısı</t>
+  </si>
+  <si>
+    <t>Global Entegre Planlama Aracının İmplementasyonu</t>
+  </si>
+  <si>
+    <t>S&amp;OP Aracının Geliştirilmesi (In-House) çalışmasında beklenen sonucun alınamaması durumunda hazırlanan RFP e göre global bir entegre planlama aracının tedariği ve şirkete implementasyonu çalışmasını içeren projedir.</t>
+  </si>
+  <si>
+    <t>Sipariş Önceliklendirme Optimizasyonu ve Çizelgeleme</t>
+  </si>
+  <si>
+    <t>KS2026-20</t>
+  </si>
+  <si>
+    <t>Sipariş önceliklendirme için parametrelerin belirlenmesi, optimizasyon modelinin oluşturulması ve entegre planlama sürecine sipariş önceliklendirme fonksiyonunun entegrasyonu hedeflenmektedir.</t>
+  </si>
+  <si>
     <t>Teyit-Termin Yapısının  İyileştirilmesi</t>
+  </si>
+  <si>
+    <t>KS2026-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP sistemi içinde saklamalı sipariş, teyit-termin gibi şirkete özel olarak oluşturulmuş ve standart akışın dışına çıkan yaklaşımlar yerine aATP gibi (Advanced Available-to-Promise) standart çözümlerin kullanımına geçilmesi hedeflenmektedir. Bu çalışma kapsamında sipariş önceliklendirme için parametrelerin belirlenmesi, optimizasyon modelinin oluşturulması ve entegre planlama sürecine sipariş önceliklendirme fonksiyonunun entegrasyonu da hedeflenmektedir.
+</t>
   </si>
   <si>
     <t>Siparişler satış ekibi tarafından sisteme girilmektedir ancak öncelik kriterleri net tanımlı değildir.
@@ -295,6 +536,15 @@
 Sistemin Yaygınlaştırılması: Tüm ürün gruplarında uygulanması. Satış ve planlama ekibi için süreç eğitimleri</t>
   </si>
   <si>
+    <t>Envanter Yönetimi</t>
+  </si>
+  <si>
+    <t>Envanter ve Planlama Str. Uygulanması</t>
+  </si>
+  <si>
+    <t>KS2026-22</t>
+  </si>
+  <si>
     <t>Tüm ürün gruplarında beklenen müşteri hizmet seviyelerini sağlamak ve stok seviyelerini optimize etmek  amacıyla ürünlerin üretim periyot ve stok seviyelerinin belirlenmesi ve bu kurallara uygun şekilde yönetilmesi yaklaşımıdır. Tanımlı hizmet seviyelerini sağlamak, üretim verimliliğini artırmak (setup maliyetleri) ve doğru bir stok yönetimi yapabilmek için planlama sürecinde, planlama stratejileri yapısının devreye alınması bu proje kapsamında sağlanacaktır.</t>
   </si>
   <si>
@@ -303,6 +553,24 @@
 Stok seviyelerinin takibi yapılarak azaltılmasına yönelik hedeflerin belirlenmesi ve uygulamaya alınması
 MTO-APB ürün gruplarında yer alan özel müşteriler için yapılan ESM altı üretimlerde yaklaşımın nasıl olacağına karar verilecek. 
 Pazarlama ve Satış ile mutabık kalındıktan sonra sistemsel tanımlamaların yapılması,</t>
+  </si>
+  <si>
+    <t>Planlama Str. Güncelleme Yazılımı Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>KS2026-19</t>
+  </si>
+  <si>
+    <t>Belirli veriler kullanılarak yapılan hesaplamalar doğrultusunda ve yine belirli kurallara göre olarak yapılan ürünlerinlerin planlama strateji gruplarının belirlenmesi sürecinin bir tool a aktarılarak otomatik olarak yapılması çalışmasıdır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KBY Verisi Planlama Entegrasyonu </t>
+  </si>
+  <si>
+    <t>KS2026-13</t>
+  </si>
+  <si>
+    <t>Bu çalışma ile planlama sürecine şirket içindeki bilgilere ilave olarak, bayi ağımızdaki KS ürünleri satış ve stok bilgilerinin de eklenerek planlama sürecinin etkinliğinin artırılması hedeflenmektedir.</t>
   </si>
   <si>
     <t>Mevcut durumda KBY verileri üretim planlama ve stok yönetimine bir girdi sağlamamaktadır.
@@ -341,6 +609,9 @@
     Müşteri yakınında sonlandırma (Ürünün son haline sevke en yakın zamanda getirme)</t>
   </si>
   <si>
+    <t>MİP Sürecinin Geliştirilmesi</t>
+  </si>
+  <si>
     <t>Şirketin üretim süreçlerinde kullanılan Malzeme İhtiyaç Planlaması (MRP) sisteminin mevcut yapısını analiz ederek daha etkin, esnek ve verimli bir planlama mekanizması oluşturmayı amaçlamaktadır. Proje kapsamında; talep tahminleri, stok seviyeleri, satın alma siparişleri ve üretim planları arasındaki entegrasyonun güçlendirilmesi hedeflenmektedir. Böylece, doğru malzemenin doğru zamanda ve doğru miktarda temin edilmesi sağlanarak maliyetlerin azaltılması, stok devir hızının artırılması ve müşteri teslim sürelerinin iyileştirilmesi planlanmaktadır.</t>
   </si>
   <si>
@@ -356,6 +627,15 @@
 İşletme malzemeleri görsel arşiv (SKU Kimlik Kartı) çalışmaları devam etmektedir. İlgili stoklu malzemelerin %50 sinin görselleştirme çalışmaları tamamlanmıştır. Bu çalışmanın devamında AI destekli ürün yönlendirme çalışmaları devam etmektedir.</t>
   </si>
   <si>
+    <t>Malzeme Depo Yönetimi</t>
+  </si>
+  <si>
+    <t>Malzeme Depolama Süreci</t>
+  </si>
+  <si>
+    <t>Ambalaj Mal. Depolamasının İyileştirilmesi</t>
+  </si>
+  <si>
     <t>Ambalaj Malzemeleri Depolamasının İyileştirilmesi Projesi; üretimde kullanılan ambalaj malzemelerinin depolanması, stoklanması ve hatlara beslenmesi süreçlerinin daha düzenli, izlenebilir ve verimli hale getirilmesini amaçlayan operasyonel bir iyileştirme çalışmasıdır.
 Bu proje ile; farklı tipteki ambalaj malzemelerinin mevcut depolama alanlarında yarattığı karmaşa, stok doğruluğu sorunları ve üretim besleme riskleri ortadan kaldırılarak, standart, sürdürülebilir ve güvenli bir depolama yapısı kurulması hedeflenmektedir.
 Proje kapsamında; ambalaj malzemelerinin depolama alanları, yerleşim düzeni, stok takibi ve hat besleme yöntemleri detaylı olarak analiz edilerek; alan kullanımını optimize eden, malzeme bulunurluğunu artıran ve üretim akışını kesintiye uğratmayacak bir depo yapısı tasarlanacaktır.</t>
@@ -373,26 +653,55 @@
 KPI Takibi ve Süreç Stabilizasyonu devam etmektedir.</t>
   </si>
   <si>
+    <t>Lojistik</t>
+  </si>
+  <si>
     <t>Inbound Lojistik</t>
+  </si>
+  <si>
+    <t>İthalat Süreci</t>
+  </si>
+  <si>
+    <t>AGSW Uyg. İmplementasyonu</t>
+  </si>
+  <si>
+    <t>Autonomous Global Single Window (Declerant-İthalat, Logicust). Bu çalışmada, ithalat gümrük sürecinin müşavir ile entegrasyonu sağlanmaktadır. Declerant'ın hedefi SAP teslimat adımından başlayarak ithalat beyannamesi oluşturuluncaya kadar olan sürecin dijitalleşmesidir. Logicust'ın hedefi beyanname tescili sonrasında anlık veya periyodik olarak geriye yönelik hata taramasının yapılması ve olası risklerin sonradan kontrol öncesinde belirlenerek gümrük idaresi nezdinde aksiyonların alınmasıdır.
+Daha Hızlı Gümrükleme - Gümrük süreçlerini hızlandırmak için sınırlardaki bekleme sürelerini önemli ölçüde azalacak.
+Daha Düşük Maliyetler - Operasyonel giderleri azaltmak ve verimliliği artırmak için manuel görevleri otomatikleşecek.
+Kağıtsız İş Akışları - Gümrük ve lojistik süreçlerini daha verimli hale getirmek için belgeleri dijitalleşecek.
+Mevzuata Uyumluluk - Ticaret operasyonları boyunca gerçek zamanlı mevzuat uyumu ve riski tespiti sağlanacak.
+Uçtan Uça Çözüm - İhracattan ithalata kadar tüm süreci otomatikleştirirek tüm paydaşlar için kapsamlı bir çözüm sunulacal.</t>
   </si>
   <si>
     <t>İthalat Süreçleri Analizi – İthalat Operasyon
 İthalat Süreçleri Analizi – Muhasebe
-Entegrasyon ve Geliştirme Başlangıcı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kale SAP sistemindeki GTIP bilgilerinin kontrol edilecek.
-ATEZ sisteminden GTIP bilgisi Kale SAP geliyor mu kontrol edilecek.
-Kale'den ATEZ sistemine GTIP bilgisi geliyor mu kontrol edilecek.
+Entegrasyon ve Geliştirme Başlangıcı
+Kale SAP sistemindeki GTIP bilgilerinin kontrol edildi. Eksiklikler tamamlandı.
+GTİP akışları karşılıklı olarak test edildi.
+İthalat Süreci Kavramsal çalışması tamamlandı.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 VPN Bağlantı ve KEQ sistemine kullanıcı bağlantı. (Merkezi gümrükleme uçtan uca ihracat-ithalat süreci için)
-İthalat Süreci Kavramsal çalışması tamamlanacak.
 Geliştirme adımı, kavramsal onayı sonrası, geliştirme yönlendirmesi Kale tarafından yapıldıktan sonra başlayacak.
 OGİ İşlemler Menusü, kullanım dokumanı gibi, SAP'deki kurgunun kullanıcı dokumanı hazırlanacak.
 MM03’teki GTIP tanımlarının girişi incelenecek.
+SAP’te VL31N ile oluşturulan Alınan Teslimatların, gümrük sistemine otomatik olarak aktarılması
+*Her bir Alınan Teslimat kaydı, gümrük tarafında ayrı bir dosya olarak ele alınacaktır.
+Gümrük sistemi üzerindeki statü bilgilerinin, SAP’ye geri akması
+*Bu bilgilerin, SAP tarafında Alınan Teslimat başlık ekranındaki “İthalat – İrsaliye” sekmesine güncellenmesi beklenmektedir.
+SAP’te ZMMR0029 işlem kodu ile oluşturulan ödeme emrine ait,
+*Bankadan dönen ödeme gerçekleşme bilgisinin, SAP üzerinden gümrük sistemine iletilmesi.
 </t>
   </si>
   <si>
     <t>Outbound  Lojistik</t>
+  </si>
+  <si>
+    <t>Sevkiyat Süreci</t>
+  </si>
+  <si>
+    <t>Sevk Planı ve Müş. Stok Süreci İyileştirilmesi</t>
   </si>
   <si>
     <t>B2B üzerinden müşteri ile iletişim sağlanarak haftalık olarak sevkini istediği ürünlerin teyidini yapacağı ve teminatına göre ürün sevk listesinden talepte bulunacağı rapor ve/veya SAP/B2B geliştirmesi. Müşterili stok oluşma sebeplerinin belirleneceği, kök neden analizinin yapılarak bu sebeplerin ortadan kaldırılacağı ve müşterili stok olarak sadece operasyonel stok (araç doluluğu ve rota planlaması bekleyen araçlar) kalacak şekilde yapılacak olan çalışmadır. Operasyonel sebepler ile bekleme süresi de belirli kurallara bağlanıp, ürünler hareketlendirilecektir.</t>
@@ -415,6 +724,9 @@
 Rota ve araç doluluğu kaynaklı beklemelerin belirli kural ve sürelere bağlanıp, bu süreler sonucunda belirlenmiş aksiyonların yürütülmesi</t>
   </si>
   <si>
+    <t>Sipariş Kurallarının Güncellenmesi</t>
+  </si>
+  <si>
     <t>SLA kapsamında müşteri ve KS gerekliliklerini, kurallarını, uygulama esaslarının tanımlandığı metnin güncel ihtiyaçlara göre gözden geçirilmesi, uygulanmayan kuralların kaldırılması, uygulanması gerekenlerin eklenmesi, anlaşılır ve sade bir dille metnin tekrar hazırlanması.</t>
   </si>
   <si>
@@ -422,6 +734,9 @@
   </si>
   <si>
     <t>TZY, satış ve diğer satış sürecine dahil birimlerin SLA'yı arttırmak amacı ile önerileri değerlendirilerek kural setine dönüştürülecek ve müşterilere duyurusu yapılacak.</t>
+  </si>
+  <si>
+    <t>Mobilya Lojistik Süreçleri İmplementasyonu</t>
   </si>
   <si>
     <t>Yurtiçi ve yurtdışı piyasalara hizmet veren lojistik ekibinin konjonktüre uyumlu olarak yapısının değerlendirilmesi, aynı/benzer işlerin sadeleştirilmesi, karmaşıklığın ortadan kaldırılması, çeviklik kazanması, maliyetlerin kontrol altına alınması ve net görev delegasyonu ile ekip motivasyonunun arttırılması.</t>
@@ -442,6 +757,12 @@
     <t>Yükleme-Rotalama Optimizasyonu​</t>
   </si>
   <si>
+    <t>KS2026-23</t>
+  </si>
+  <si>
+    <t>SAP TM Loading Optimization Application'dan yararlanarak rota planlamasının optimizasyonu (araştırma ve entegrasyon) ve araç doluluk verimliğinin artırılması.</t>
+  </si>
+  <si>
     <t>CubeMaster denendi ancak verimli sonuçlar elde edilmedi. SAP entegrasyonu bulunmuyor.
 Tırport ile Cube IQ denemeleri yapıldı. Simülasyonun sunumu ve sonuçlarının değerlendirildi. Verimsiz olduğu gözlendi. SAP entegrasyonu bulunmuyor.		
 MD Group saha ziyareti ve işlem listesi görüşmesi yapıldı.
@@ -456,6 +777,12 @@
   </si>
   <si>
     <t>Kalite Belgesi</t>
+  </si>
+  <si>
+    <t>Yönetim Sistemi</t>
+  </si>
+  <si>
+    <t>ISO 28000 TZ Güvenliği Yön. Sis. Belgesi</t>
   </si>
   <si>
     <t>28001 Tedarik Zinciri Güvenliği Yönetim Sistemi belgelendirmesi. tedarik zincirinde karşılaşabileceğimiz güvenlik tehditlerini önceden belirleyip kontrol altına almayı, uluslararası pazarda iş ortaklarımıza güven vererek, rekabet gücümüzü artırmayı, risklerimizi etkin şekilde yönetmeyi, acil durumlara karşı hazırlıklı olmayı, yürürlükteki yasalara tam uyum sağlamayı ve mevcut iş süreçlerimizi daha verimli ve güvenli hale getirmeyi hedeflediğimiz çalışmadır.</t>
@@ -467,7 +794,8 @@
 GAP analizi ve standart gereklilikleri bir çalıştay ile gözden geçirildi.
 ​Proje takvimi netleştirildi.​
 Bölümler arası bilgilendirme ve görevlendirme yapıldı.
-Sistem kurulumu ve uygulanmas için alınacak aksiyonlar belirlendi.</t>
+Sistem kurulumu ve uygulanmas için alınacak aksiyonlar belirlendi.
+Bağlam ve İlgili Taraflar Analizi 16 Nisan'da başladı. Belgelendirme firması yönlendirmesi ile haftalık güncellemeler yapılıyor.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -480,6 +808,12 @@
   </si>
   <si>
     <t>Lojistik Operasyon Yönetimi</t>
+  </si>
+  <si>
+    <t>Karayolu Gelişim</t>
+  </si>
+  <si>
+    <t>Filo ve Spot Araç Kullanımı İyileştirilmesi</t>
   </si>
   <si>
     <t>Kalenakliyat’ın mevcut karayolu nakliye modeli iyileştirilerek, ana filo ve dış (spot) filo yapıları geliştirilecektir. Bu çalışmanın temelinde, ana filonun dış müşterilere de hizmet vermesinin yanı sıra spot araçların KN  yönetimiyle maliyet avantajı sağlanması yer almaktadır.</t>
@@ -498,6 +832,9 @@
 Etkin bir sektör network yönetim alt yapısı hazırlanacak. (KaleGo uygulaması ile birlikte)</t>
   </si>
   <si>
+    <t>Nakliye Hesaplama Modelinin İyileştirilmesi</t>
+  </si>
+  <si>
     <t>Mevcut durumda tüm taşıma modlarında, gidiş - dönüş, ana filo ve dış filo nakliye fiyat listeleri, eskalasyon yapılarına göre tl/ton şeklinde çalışmaktadır. Lojistik sektörü FTL taşımalarda büyük oranda «ton» ölçü birimi kullanır. LTL ve PTL modellerde ise desi, m3 gibi birimlere de ihtiyaç duyulmaktadır.</t>
   </si>
   <si>
@@ -506,6 +843,9 @@
   <si>
     <t>Anaveri İyileştirme projesinin tamamlanmasını takiben desi ve m3 bazında sevk noktası bazında nakliye fiyat listesi oluşturulacak.​
 Yükleme optimizasyon projesinin devreye alınmasıyla oluşacak max. verimlilikle yüklemeler ile hacim veya kilogram cinsinden en ideal yükleme ve fiyatlama modeli oluşması sağlanacak.</t>
+  </si>
+  <si>
+    <t>Kiralık Araçlar Optimizasyonu</t>
   </si>
   <si>
     <t>Mevcut kiralık araç filosunun verimlilik analizi yapılarak, rota yapısı, dönüş yükü potansiyelleri de göz önüne alınarak kiralık araç optimizasyon çalışması yapılacaktır.</t>
@@ -539,18 +879,13 @@
     <t>Nakliye sigorta yapıları oluşturulacak.</t>
   </si>
   <si>
-    <t>Ön keşif tamamlandı.​
-Kantar ve otomasyon teklifleri alındı.​
-İlgili fonksiyonda görevlendirilecek personel planı ve iş akışları oluşturuldu.
-Mimari ve statik proje çalışmaları tamamlandı ve imalat aşamasına gelindi.
-İmar yapısındaki kısmi değişikliğe bağlı olarak mimari projede değişiklik yapıldı.</t>
-  </si>
-  <si>
-    <t>Alt yapı hazırlığı ve 2. kantarın kurulumu yapılacak.​
-Mevcut kantar revizyonu ile yer değişimi yapılacak.​
-Sevkiyat kapı ve sevk yönetim bina inşası için süreç başlatılacak.​
-Süreç talimat ve prosedürler oluşturulacak.​
-SKM-BANYO kombine yükleme hacminin artması ile Semedeli lokasyonundaki kantarın 4-12 vardiyası aktif edilecek. KM ile ortak çalışma yöntemi ve kantar sistem entegrasyon yapısı oluşturulacak.​</t>
+    <t>KaleGo</t>
+  </si>
+  <si>
+    <t>Nakliyeci Atama ve Takip Uyg. Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>KS2026-24</t>
   </si>
   <si>
     <t>KaleGo, nakliye süreçlerini; sürece dâhil olan tüm paydaşların entegre olduğu uçtan uca bir akış içerisinde, anlık statü takibi ile yöneten dijital bir platform olarak konumlanmaktadır. Platform, operasyonel ve performans sonuçlarını esnek ve raporlanabilir bir yapı ile sunmayı hedeflemektedir.</t>
@@ -565,6 +900,12 @@
 Uygulama lisans ve sözleşme süreçleri netleştirilecek.
 Proje detaylı kavramsal tasarımı oluşturulacak.
 Proje takvimi belirlenecek.</t>
+  </si>
+  <si>
+    <t>Diğer Modlarda Gelişim</t>
+  </si>
+  <si>
+    <t>Denizyolu Filo ve İş Hacminin Geliştirilmesi</t>
   </si>
   <si>
     <t>KN-2 gemisinin satışı sonra Kale ve potansiyel dış müşteri hacimlerinin değerlendirilerek, yeni gemi yatırımı fizibilitesi yapılacaktır.</t>
@@ -597,6 +938,18 @@
 Potansiyel dış müşteri araştırmalarına devam edilecek.</t>
   </si>
   <si>
+    <t>Mamul Depo Yönetimi</t>
+  </si>
+  <si>
+    <t>Kaydi Yapı</t>
+  </si>
+  <si>
+    <t>Depo Stok Hareket Akışlarının Oluşturulması</t>
+  </si>
+  <si>
+    <t>Elleçleme, hurda, fırsat, outlet, iade, kalite gibi ana süreci destekleyici fonksiyonu bulunan kaydi depoların akış kural setlerinin oluşturulmasını ve kullanıcı yetki tanımlarının güncellenmesi amaçlanmaktadır.</t>
+  </si>
+  <si>
     <t>Üretim yeri bazında elleçleme depo ve hurda depo akışları incelendi ve neden setleri oluşturuldu.​
 Yeni akışta kullanılacak depo kodları belirlendi.​
 Depo yetkileri gözden geçirildi.
@@ -604,7 +957,13 @@
 ​Elleçleme depolar stok hareket akışları belirlendi.</t>
   </si>
   <si>
+    <t>Büyük Ebat Lojistiği</t>
+  </si>
+  <si>
     <t xml:space="preserve">Büyük Ebat Lojistik İyileştirme </t>
+  </si>
+  <si>
+    <t>Slab &amp; SFX kapsamı, büyük ebat mamullerin fabrikadan teslim alınmasından, müşteriye ulaşmasına kadar tüm yükleme, boşaltma, stoklama ve elleçleme süreçlerinde İSG açısından riskleri ve olası verimsizlikleri değerlendirerek, süreci tanımlama ve bu operasyonlarda görev yapan personelin yetkinliği ve farkındalığını artırma hedeflenmektedir.</t>
   </si>
   <si>
     <t>İSG ile sahada yükleme, boşaltma operasyonları izlendi ve talimat oluşturularak yayınlandı.​
@@ -619,6 +978,9 @@
 Hasar tazminlerde risk yaşamamak için sigortaya dokunan noktalar belirlenecek, gerekirse poliçelere ilave edilmesi sağlanacak.</t>
   </si>
   <si>
+    <t>SLAB Lojistik Yetkinliklerin Geliştirilmesi</t>
+  </si>
+  <si>
     <t>Büyük ebat lojistik yetkinlikleri ve depoların geliştirilmesi projesinde; kapalı depolar, stok sahaları, iş makinaları, elleçleme donanımları, stok hareket otomasyonları, saha hareket akışları, yükleme alanları, saha personel profili ve yetkinlikleri, araç giriş-çıkış güvenlik kontrol yetkinleri gibi baştan sona tüm sürecin, seramik sektöründeki bu devrimsel değişime adapte olmasını sağlayacak aksiyonları içermektedir.</t>
   </si>
   <si>
@@ -629,6 +991,29 @@
     <t>Mevcut durum için Slab&amp;SFX depo elleçleme kabiliyet ve kapasiteleri netleştirilecek.​
 Avrupa başta olmak üzere sektördeki alternatif stoklama modelleri incelenecek. ​
 Önümüzdeki 5 yıllık projeksiyona bakılarak Slab&amp;SFX ürünleri için depo kapasitesi tahminlemesi yapılacak.</t>
+  </si>
+  <si>
+    <t>Saha Süreç ve Tesis Yönetimi</t>
+  </si>
+  <si>
+    <t>Sevkiyat Kapı ve Saha Yapısı İyileştirilmesi</t>
+  </si>
+  <si>
+    <t>Sevkiyat kapı araç girişi, saha planlama, yükleme ve araç çıkış süreçlerini içeren tüm akışın süreçsel ve yapısal olarak yenilenmesi aksiyonlarını içermektedir.</t>
+  </si>
+  <si>
+    <t>Ön keşif tamamlandı.​
+Kantar ve otomasyon teklifleri alındı.​
+İlgili fonksiyonda görevlendirilecek personel planı ve iş akışları oluşturuldu.
+Mimari ve statik proje çalışmaları tamamlandı ve imalat aşamasına gelindi.
+İmar yapısındaki kısmi değişikliğe bağlı olarak mimari projede değişiklik yapıldı.</t>
+  </si>
+  <si>
+    <t>Alt yapı hazırlığı ve 2. kantarın kurulumu yapılacak.​
+Mevcut kantar revizyonu ile yer değişimi yapılacak.​
+Sevkiyat kapı ve sevk yönetim bina inşası için süreç başlatılacak.​
+Süreç talimat ve prosedürler oluşturulacak.​
+SKM-BANYO kombine yükleme hacminin artması ile Semedeli lokasyonundaki kantarın 4-12 vardiyası aktif edilecek. KM ile ortak çalışma yöntemi ve kantar sistem entegrasyon yapısı oluşturulacak.​</t>
   </si>
   <si>
     <t>Fiziki Sahaların İyileştirilmesi</t>
@@ -653,6 +1038,19 @@
 Eski Granit altındaki yol depo alana dahil edilerek bölge yeniden kurgulanacak.</t>
   </si>
   <si>
+    <t>Teşhir Operasyonları</t>
+  </si>
+  <si>
+    <t>Teşhir Süreci</t>
+  </si>
+  <si>
+    <t>Teşhir Süreci Yapılandırma ve Atölye Kurulumu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slab &amp; SFX stand hazırlık bölümü ile SKM teşhir bölümünü birleştirilerek tüm tanıtım materyalleri kapsamında, stok, sipariş, üretim ve sevkiyat süreçlerinin yönetildiği bir atölye hedeflenmektedir.
+Numune ürün, stand, el panosu, binder, teşhir ünitesi, katalog, broşür, promosyon vb. tüm pazarlama materyalleri bu kapsama girmektedir. </t>
+  </si>
+  <si>
     <t>Raflı depo alanında düzenlemeler tamamlandı.​
 Atölye alanı bakım, onarım ve fiziki hazırlığı yapıldı​.
 Kaydi depolardaki karışıklık giderildi, WM’li ve WM’siz olarak tek depoya düşürüldü.​
@@ -667,19 +1065,105 @@
 Sipariş yönetimi ve atölye üretim planlama kuralları belirlenecek.</t>
   </si>
   <si>
+    <t>Satınalma</t>
+  </si>
+  <si>
+    <t>Tedarikçi İlişkileri Yönetimi</t>
+  </si>
+  <si>
+    <t>vSRM</t>
+  </si>
+  <si>
+    <t>İhale Modülü ve SAP BP İmplementasyonu</t>
+  </si>
+  <si>
+    <t>KS2026-56</t>
+  </si>
+  <si>
     <t>E-İhale faaliyetlerinin dijital, şeffaf, izlenebilir ve standart bir yapıya kavuşturulması amaçlanmaktadır. İhale planlama, teklif toplama, değerlendirme, onay ve raporlama süreçlerinin sistem üzerinden yönetilmesi, manuel ve e-posta bazlı süreçlerin ortadan kaldırılması hedeflenmektedir.</t>
   </si>
   <si>
+    <t xml:space="preserve">Teknik SA kategorisinde teklifler, siparişler ihaleler dijital olarak SRM üzerinden toplanmaktadır. (3600+ işlem)
+Yeni cari tanımlarında vSRM dijital uygulaması ve BP entegrasyonu devreye alınmış ve 87 yeni cari kaydı vSRM üzerinden yapılmıştır.
+Satın alma ihalesinde açık artırma parametresinin uygulamaya dahil edilmesi.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Satış ihalesi sürecinin SRM’ e tanımlanması. 
+SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır.
+</t>
+  </si>
+  <si>
+    <t>DÖF Modülünün Devreye Alınması</t>
+  </si>
+  <si>
     <t>Tedarikçi kaynaklı uygunsuzluklar, denetim bulguları, performans düşüşleri ve şikâyetler sonucunda başlatılan Düzeltici ve Önleyici Faaliyet (DÖF) süreçlerinin SRM sistemi üzerinden dijital, izlenebilir ve standart bir yapıya kavuşturulması amaçlanmaktadır. DÖF açma, takip etme, aksiyonların izlenmesi ve kapanış süreçlerinin manuel ve dağınık yöntemler yerine tek bir merkezi sistem üzerinden yönetilmesi hedeflenmektedir.</t>
   </si>
   <si>
+    <t>Ambalaj kategorisinde Kalite Birimi tarafından aktif kullanılmaktadır.</t>
+  </si>
+  <si>
+    <t>Diğer SA kategorilerinde DÖF modülünün kullanılması yaygınlaştırılacaktır. Örnek Hammadde için Ar-Ge girdi kontrol kullanımı.
+Kategorilerde denetim kayıtlarının vSRM üzerinden yürütülmesi ve tedarikçiye iletilmesi.</t>
+  </si>
+  <si>
+    <t>Sipariş Modülü İyileştirme ve Yaygınlaştırma</t>
+  </si>
+  <si>
     <t>SRM Sipariş Modülünün kullanım etkinliğini artırmak, mevcut kullanım problemlerini gidermek ve satın alma–tedarikçi süreçleri arasında daha hızlı, hatasız ve izlenebilir bir sipariş yönetimi sağlamak amaçlanmaktadır.</t>
   </si>
   <si>
+    <t>Faz 1; Tedarikçi bazında kullanım (siparişlerin onayı ve irsaliye girişleri) oranlarının arttırılması ve süreç işlemlerin (SAS) iyileştirilmesi sağlanmıştır. 32 tedarikçinin % 58’ inde kullanıma geçilmiştir. 
+Teknik Satın alma kategorisinde hizmet alanında teklif ve siparişlerin oluşturulması %100 oranında devreye alınmıştır, stok kodlu alımlarda da kullanılmaya başlanmıştır.
+Bölgesel ve Merkezi Hizmet kategorisinde ilgili sipariş modulü eğitimi alınmıştır.
+Teknik hizmet iş kabullerinde VSRM üzerinden gerekli süreç tamamlanmıştır, 01.04.2026 tarihinde devreye alınmıştır.</t>
+  </si>
+  <si>
+    <t>Bölgesel Hizmet ve Merkezi Satın alma kategorilerinde sipariş modülü kullanıma başlanacaktır.
+Bölgesel Hizmet kategorisi için ilgili kullanıcılara (talep sahibi, tedarikçi) süreç hakkında bilgi verilecektir. Talepler vSRM üzerinden alınarak satın alma süreci başlatılacaktır.        
+vSRM dışı talep kabul edilmeyecektir. Taleplerin vSRM üzerinden alınması planlanmaktadır.
+vSRM kullanımı sipariş girişi sağlayan ambar birimlerine yaygınlaştırılacaktır.
+Siparişlerin hızlanması için vSRM üzerinden SAT açılması işlemlerinin otomatik olarak çalışması yapılmaktadır. Mayıs ayına kadar tamamlanması planlanmaktadır.</t>
+  </si>
+  <si>
+    <t>Tedarikçi Değerlendirme Sür. İyileştirilmesi</t>
+  </si>
+  <si>
     <t>Mevcut tedarikçi değerlendirme yapısını gözden geçirerek; daha objektif, ölçülebilir, şeffaf ve sürdürülebilir bir değerlendirme sistemi oluşturmak amaçlanmaktadır. Tedarikçi değerlendirme kriterlerinin standartlaştırılması, dijitalleştirilmesi ve satın alma kararlarına doğrudan girdi sağlayacak bir yapıya kavuşturulması hedeflenmektedir.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tedarikçi Değerlendirme Sistemi yeniden kurgulandı. Performans kriterleri ve puanlama yapısı oluşturuldu.
+2025 yılı tedarikçi değerlendirmesi 2026 Ocak ayı içinde tamamlandı.
+Tedarikçi değerlendirme sonuçları iç müşteriler ve tedarikçiler  ile paylaşıldı.
+Tedarikçi değerlendirme süreci ITG firması tarafından örnek bir model gösterimiyle anlatıldı, KPI listesi paylaşıldı. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tedarikçi değerlendirme sürecinde kullanılabilecek vSRM sisteminde yer alan KPI listesi kontrolü ve sisteme entegre edilmesi. 
+</t>
+  </si>
+  <si>
+    <t>Tedarikçi Geliştirme</t>
+  </si>
+  <si>
+    <t>Tedarikçi Gelişimi</t>
+  </si>
+  <si>
+    <t>Mevcut Tedarikçilerin Geliştirilmesi</t>
+  </si>
+  <si>
     <t>Mevcut tedarikçilerin performans, kalite, maliyet, teslimat, sürdürülebilirlik ve uyum kriterleri doğrultusunda geliştirilmesini sağlamak; tedarik zincirinin genel verimliliğini ve sürekliliğini artırmak amaçlanmaktadır. Tedarikçi performansının sistematik olarak izlenmesi, gelişim alanlarının belirlenmesi ve bu alanlara yönelik yapılandırılmış geliştirme planlarının hayata geçirilmesi hedeflenmektedir.</t>
+  </si>
+  <si>
+    <t>Tedarikçilerimizin verdiği teknik eğitimlerle hem kendi kullanıcımız hem de tedarikçimizin ürününün doğru kullanılması ile optimum sonuçlara ulaşılmaktadır.
+Ambalaj ve Tamamlayıcılar kategorisinde tedarikçilerimize açtığımız DÖF’ler ile ilgili malzeme geliştirmeleri yapılmakta ve bilgiler vSRM sistemi üzerinden kayda alınmaktadır.</t>
+  </si>
+  <si>
+    <t>DÖF yapısının vSRM modülü üzerinden Bölgesel ve Merkezi hizmet, Ambalaj ve Tamamlayıcılar, Hammadde ve Kimyasallar kategorisine de yaygınlaştırılması sağlanacaktır.
+Tedarikçi performans verilerinin vSRM (kalite, maliyet, teslimat, hizmet vb.) değerlendirilmesi.
+Yapılan tedarikçi değerlendirmeleri sonucunda tedarikçilerle paylaşılan sonuçlara istinaden gelişim alanlarının belirlenmesi. Örneğin termin anlamında düşük puan alan tedarikçilerin geliştirilmesi vs.</t>
+  </si>
+  <si>
+    <t>Tedarikçi Ağı Opt. ve Alt. Ted. Geliştirilmesi</t>
   </si>
   <si>
     <t xml:space="preserve">Bu çalışma ile tedarikçi değerlendirme ve diğer verilerin yapay zeka ve ileri analitik çözümlerde kullanılması ile maliyet, kalite, sürdürülebilirlik ve risk kriterleri doğrultusunda tedarikçi ağı optimizasyonunun yapılması hedeflenmektedir. 
@@ -687,301 +1171,116 @@
 </t>
   </si>
   <si>
+    <t>Yetkinlik Geliştirme</t>
+  </si>
+  <si>
+    <t>Yetkinlik Gelişimi</t>
+  </si>
+  <si>
+    <t>Kategori Bazlı Know-How Gel. Sağlanması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belirli bir geliştirme planına bağlı olarak önceliklendirilen kategori, malzeme ve hizmet gruplarında en iyi uygulamaları öğrenmek, yetkinlikleri geliştirmek ve grup için kırılımlı maliyet yapısının sistematik veri olarak elde edilmesini de sağlayacak faaliyetleri içeren çalışmadır. </t>
+  </si>
+  <si>
+    <t>Tedarikçi Benchmark çalışmaları yapılmıştır. 2 grup halinde farklı iki firma olan Sofra firması ve Dalgakıran firmaları satınalma yapısı olarak incelenmiştir. Sofra firmasından tedarikçi değerlendirme anlamında örnekler alınmıştır. 
+Çin pazarı tedarik ürünler satınalmasında Know how gelişimi için Trome firmasıyla aktif çalışmaya başlanılmıştır.</t>
+  </si>
+  <si>
+    <t>Maliyet yapıları ve fiyat kırılımları bilgisinin geliştirilmesi.
+Piyasa Emtialarının ve artış tahmin oranlarının bir bülten üzerinden takibinin yapılması ve geliştirilmesi.
+Kategori bazlı tedarikçilerin üretim hatlarının görüleceği ve teknik değerlendirilmesinin yapılabileceği ziyaret planlaması yapılacaktır.</t>
+  </si>
+  <si>
     <t>Fiyat Geçiş Sistemini  Oluşturulması</t>
   </si>
   <si>
     <t>Tedarikçilerden gelen fiyat değişiklik taleplerinin (artış/azalış) standart, şeffaf, kontrollü ve izlenebilir bir sistematik ile yönetilmesi amaçlanmaktadır.</t>
   </si>
   <si>
+    <t>FRM.GEN.SAT.031 form kodu ile Satın alma Fiyat Değişim Onay Formu oluşturulmuştur.
+İŞT.GEN.SAT.002 form kodu ile Satın alma Fiyat Değişim Onay Talimatı oluşturulmuştur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiyat Değişim Onay hiyerarşisinin SAP kurgusu Strateji birimiyle görüşülecektir. </t>
+  </si>
+  <si>
+    <t>Talep Yönetimi ve Operasyonel Satınalma</t>
+  </si>
+  <si>
+    <t>RPA Kullanımının Artırılması</t>
+  </si>
+  <si>
+    <t>Fatura kayıt süreçlerinde gerçekleştirilen manuel, tekrarlayan ve zaman alan işlemlerin Robotik Proses Otomasyonu (RPA) ile otomatikleştirilerek; işlem sürelerinin kısaltılması, hata oranlarının azaltılması ve satın alma/mali işler süreçlerinde verimliliğin artırılması amaçlanmaktadır.</t>
+  </si>
+  <si>
+    <t>Robot tarafından kayıt edilmesi planlanan tedarikçiler belirlenmiş, sisteme ……….. cari tanımlanmıştır.</t>
+  </si>
+  <si>
+    <t>Döviz bazlı faturaların RPA sürecine dahil edilmesi.
+Robot tarafından yapılan kayıtların miktarının artırılması.</t>
+  </si>
+  <si>
+    <t>SA Talebi Sistematiğinin İyileştirilmesi</t>
+  </si>
+  <si>
     <t>Satın alma taleplerinin standart, doğru, eksiksiz ve izlenebilir şekilde oluşturulmasını sağlamak; satın alma süreçlerinde yaşanan gecikmeleri, tekrarları ve hatalı talepleri azaltmak amaçlanmaktadır.</t>
   </si>
   <si>
+    <t>Satın alma taleplerinin Teknik SA kategorisinde e-posta/telefon yerine SRM sistemi üzerinden alınıp yürütülmektedir.
+Teknik satınalma kategorisinde talepler teknik dokümanlar la birlikte SRM sistemi üzerinden alınmaya başlanmış ve tedarikçiye yine SRM sistemi üzerinden ihale, teklif toplama vb. şeklinde iletilmektedir.</t>
+  </si>
+  <si>
+    <t>SRM sistemi işlemlerinde Hizmet SAT’ larının talep sahibi onayı ile otomatik olarak SAP sisteminde yaratılması ve SRM sistemi ile entegre olması planlanmaktadır.</t>
+  </si>
+  <si>
+    <t>Teknik Hizmet Alınan Hizmetin Kontrolü</t>
+  </si>
+  <si>
     <t>Teknik hizmetlerin (bakım, onarım, montaj, mühendislik, servis vb.) sözleşme, teknik şartname ve kalite beklentilerine uygunluğunun sistematik, standart ve izlenebilir şekilde kontrol sürecinin SRM sisteminde yapılması amaçlanmaktadır.</t>
   </si>
   <si>
+    <t>Teknik hizmet alımlarında alınan hizmetin kontrolü E-flow sisteminde yer alan uygulama ile yapılmakta; talep sahipleri faturalara dijital onay vermektedir.</t>
+  </si>
+  <si>
+    <t>Firma tarafından hizmet teslimi onayı
+Talep sahibi ve üst amir onayı
+Firmaya fatura düzenlenmesi için bilgi kaydı 
+Faturanın sistem tarafından ön kaydının yapılması</t>
+  </si>
+  <si>
+    <t>SAS Onay Sisteminin Genişletilmesi</t>
+  </si>
+  <si>
     <t>Satın alma siparişlerinin (SAS) tutar hiyerarşisine göre onay yetkilendirmelerinin oluşturulması, sürecin işletilmesi ve yaygınlaştırılması amaçlanmaktadır.</t>
   </si>
   <si>
-    <t>Fatura kayıt süreçlerinde gerçekleştirilen manuel, tekrarlayan ve zaman alan işlemlerin Robotik Proses Otomasyonu (RPA) ile otomatikleştirilerek; işlem sürelerinin kısaltılması, hata oranlarının azaltılması ve satın alma/mali işler süreçlerinde verimliliğin artırılması amaçlanmaktadır.</t>
+    <t xml:space="preserve">Stok kodlu ve hizmet siparişlerinde SAS onay sistemi kullanılmaktadır.
+Strateji tarafında SAS onay limitleri ve yetki tablosu belirlenmiştir. </t>
   </si>
   <si>
     <t>Dijital Dönüşüm</t>
   </si>
   <si>
+    <t>MES</t>
+  </si>
+  <si>
     <t>Kale99  SKM</t>
   </si>
   <si>
-    <t>Devam ediyor</t>
-  </si>
-  <si>
-    <t>MES IOT Vitrifiye</t>
-  </si>
-  <si>
-    <t>MES IOT Mobilya</t>
-  </si>
-  <si>
-    <t>Karonun kurutucu içinde görünürlüğünü sağlayarak tüm sepet ve raflarının aktif kullanımını sağlamak, verimliliğini ölçmek ve canlı izlemek için;
-Kurutuculardan toplanan operasyonel verilerin (sepet no, sepet id, tur bilgisi, çıkış sıcaklığı, doğalgaz sarfiyatı vb.) analitik yöntemlerle işlenmesi ve yapay zekâ destekli modeller kullanılarak  dikey kurutucunun her bir çevirimi için verimlilik artırımı ve enerji tasarrufu sağlanması.</t>
-  </si>
-  <si>
-    <t>Masse hazırlık süreci ile karo üretim sürecini tek bir dijital izlenebilirlik zincirinde birleştirmek. Hammadde dozajından başlayıp, öğütme – kurutma – stoklama – presleme – sırlama – pişirim – fırın sonrası işlemler aşamalarına kadar tüm değer zincirini uçtan uca dijital olarak izlemek, veriye dayalı karar alma ve optimizasyon sağlamak.</t>
-  </si>
-  <si>
-    <t>Seramik üretiminde en fazla enerji tüketimi bulunan pişirim sürecinin verimliliğinin sürekli olarak izlenmesi, olası verimlilik düşüklüklerinin bildirilmesi</t>
-  </si>
-  <si>
-    <t>Mevcut sistemde ürün ağacına göre boya girilerek yapılan masse renklendirme işlemi yerine hazırlanan çamura uygun miktarda boya tahminlemesi modeli kurularak deneme miktarının azaltılması ve verimliliğin artırılması.</t>
-  </si>
-  <si>
-    <t>Değirmenlerde kullanılan bilya ve iç kaplama kaynaklı verimsizliklerin yapay zekâ destekli tahminlenmesi ve kestirimci bakım planı için çalışması.</t>
-  </si>
-  <si>
-    <t>Canlı Rutubet Ölçümü ile Model kurularak Sprey kurutucu ısılarına müdahale eden robot geliştirilerek sprey çıkışı rutubetin sürekli stabil tutulması sağlanacaktır.</t>
-  </si>
-  <si>
-    <t>Mevcutta yapılan parti bazlı ürün ve ürün ağacı takibinin tekil karo bazlı yapılması hedeflenmektedir.</t>
-  </si>
-  <si>
-    <t>Masse ve sır için geçmiş üretim verilerinden öğrenen bir yapay zekâ sistemine dayanacaktır.    Modelin amacı deneme-yanılma sürecini ortadan kaldırmak, üretim verimliliğini artırmak, ürün kalitesinde sürdürülebilirliği garanti altına almak, hammadde kullanımında optimizasyon sağlamaktır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fırın verimliliğinin canlı takibi projesinin tamamlanmasından sonra Faz-2 olarak canlı takip sonuçlarının üretim sarf, reçete bilgisi ile optimize edilerek AI destekli izleme sisteminin kurulması hedeflenmektedir. </t>
-  </si>
-  <si>
-    <t>CWYF Uygulaması Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Mali işler birimi tarafından talep edilen fagid Bütçe-Fiili raporu, günlük stok analiz raporu ve VSM maliyet raporu gibi çeşitli birimlerin ihtiyaç duyduğu raporların PowerBI üzerinden kod sistematiği içeren şekilde özelleştirilerek oluşturulması ve birimlerin bu konudaki yetkinliklerinin artırılması bu projenin çalışma konusunu oluşturmaktadır.</t>
-  </si>
-  <si>
-    <t>Mühendislik birimi tarafından oluşturulan fabrikalara ait kalite, hata analizi, duruş raporlarının PowerBI üzerinden kod sistematiği içeren şekilde özelleştirilerek oluşturulması ve birimlerin bu konudaki yetkinliklerinin artırılması bu projenin çalışma konusunu oluşturmaktadır.</t>
-  </si>
-  <si>
-    <t>Fabrikanın fiziksel süreçlerini gerçek zamanlı veriyle beslenen sanal modeller aracılığıyla temsil edilmesi hedeflenmektedir. </t>
-  </si>
-  <si>
-    <t>Bu proje kapsamında, Kaleseramik üretim ve yönetim ekosisteminde oluşan büyük hacimli operasyonel verilerin ileri veri analitiği, makine öğrenmesi ve yapay zekâ yöntemleriyle analiz edilmesi hedeflenmektedir.
-Amaç; mevcut verilerden öngörü üreten, karar destek sağlayan ve operasyonel verimlilik yaratan veri odaklı kullanım durumlarını sistematik olarak keşfetmek, önceliklendirmek ve iş değerine dönüştürmektir.</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>function</t>
-  </si>
-  <si>
-    <t>project_group</t>
-  </si>
-  <si>
-    <t>project_name</t>
-  </si>
-  <si>
-    <t>start_date</t>
-  </si>
-  <si>
-    <t>end_date</t>
-  </si>
-  <si>
-    <t>project_status</t>
-  </si>
-  <si>
-    <t>done_list</t>
-  </si>
-  <si>
-    <t>todo_list</t>
-  </si>
-  <si>
-    <t>project_desc</t>
-  </si>
-  <si>
-    <t>digital_initiative</t>
+    <t>Granit Masse, Sır Üretim, Granit Kurulumu</t>
+  </si>
+  <si>
+    <t>KS2026-29</t>
   </si>
   <si>
     <t>Bu proje, Kaleseramik SKM üretim süreçlerini uçtan uca dijitalleştirerek, tekil ürün bazında gerçek zamanlı veri akışına dayalı akıllı üretim yönetimi ve yapay zekâ destekli karar destek sistemleri kurmayı hedeflemektedir. Amaç; kaliteyi artırmak, verimliliği yükseltmek, maliyetleri azaltmak ve müşteri memnuniyetini güçlendirmektir.</t>
   </si>
   <si>
-    <t>MİP Sürecinin Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Teknik Hizmet Alınan Hizmetin Kontrolü</t>
-  </si>
-  <si>
-    <t>RPA Kullanımının Artırılması</t>
-  </si>
-  <si>
-    <t>Granit Kurutucu Verimlilik Optimizasyonu</t>
-  </si>
-  <si>
-    <t>STB DDM Başvuru Sürecinin Yürütülmesi</t>
-  </si>
-  <si>
-    <t>STB DDM Projelerinin Yürütülmesi</t>
-  </si>
-  <si>
-    <t>PowerBI Dashboard</t>
-  </si>
-  <si>
-    <t>TZY PowerBI Dashboard Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Dijital İkiz Çalışmasının Oluşturulması</t>
-  </si>
-  <si>
-    <t>Ürün Ambalaj Bilgilerinin Tanımlanması</t>
-  </si>
-  <si>
-    <t>S&amp;OP Sürecinin Gel. ve Standardizasyonu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KBY Verisi Planlama Entegrasyonu </t>
-  </si>
-  <si>
-    <t>Kategori Bazlı Know-How Gel. Sağlanması</t>
-  </si>
-  <si>
-    <t>Vitrifiye Üretimi MES Yapısının Kurulumu</t>
-  </si>
-  <si>
-    <t>Masse  Verilerinin Granite Bağlanması</t>
-  </si>
-  <si>
-    <t>Masse ve Sır Stok Hareket İşlemleri</t>
-  </si>
-  <si>
-    <t>Granit Bünye Reçete Opt. Çalışması</t>
-  </si>
-  <si>
-    <t>AI Destekli Fırın İzleme Sistemi</t>
-  </si>
-  <si>
-    <t>Üretim Verileri PowerBI Aktarımları</t>
-  </si>
-  <si>
-    <t>Autonomous Global Single Window (Declerant-İthalat, Logicust). Bu çalışmada, ithalat gümrük sürecinin müşavir ile entegrasyonu sağlanmaktadır. Declerant'ın hedefi SAP teslimat adımından başlayarak ithalat beyannamesi oluşturuluncaya kadar olan sürecin dijitalleşmesidir. Logicust'ın hedefi beyanname tescili sonrasında anlık veya periyodik olarak geriye yönelik hata taramasının yapılması ve olası risklerin sonradan kontrol öncesinde belirlenerek gümrük idaresi nezdinde aksiyonların alınmasıdır.
-Daha Hızlı Gümrükleme - Gümrük süreçlerini hızlandırmak için sınırlardaki bekleme sürelerini önemli ölçüde azalacak.
-Daha Düşük Maliyetler - Operasyonel giderleri azaltmak ve verimliliği artırmak için manuel görevleri otomatikleşecek.
-Kağıtsız İş Akışları - Gümrük ve lojistik süreçlerini daha verimli hale getirmek için belgeleri dijitalleşecek.
-Mevzuata Uyumluluk - Ticaret operasyonları boyunca gerçek zamanlı mevzuat uyumu ve riski tespiti sağlanacak.
-Uçtan Uça Çözüm - İhracattan ithalata kadar tüm süreci otomatikleştirirek tüm paydaşlar için kapsamlı bir çözüm sunulacal.</t>
-  </si>
-  <si>
-    <t>ISO 28000 TZ Güvenliği Yön. Sis. Belgesi</t>
-  </si>
-  <si>
-    <t>STB Dijital Dönüşüm Merkezi</t>
-  </si>
-  <si>
-    <t>AI Uygulamaları</t>
-  </si>
-  <si>
-    <t>TZ Süreçlerinde AI Kullanımı</t>
-  </si>
-  <si>
-    <t>KS2026-34</t>
-  </si>
-  <si>
-    <t>Tübitak 1711</t>
-  </si>
-  <si>
-    <t>KS2026-64</t>
-  </si>
-  <si>
-    <t>KS2026-39</t>
-  </si>
-  <si>
-    <t>KS2026-40</t>
-  </si>
-  <si>
-    <t>KS2026-38</t>
-  </si>
-  <si>
-    <t>KS2026-29</t>
-  </si>
-  <si>
-    <t>KS2026-32</t>
-  </si>
-  <si>
-    <t>KS2026-31</t>
-  </si>
-  <si>
-    <t>KS2026-37</t>
-  </si>
-  <si>
-    <t>KS2026-36</t>
-  </si>
-  <si>
-    <t>KS2026-33</t>
-  </si>
-  <si>
-    <t>KS2026-35</t>
-  </si>
-  <si>
-    <t>KS2026-24</t>
-  </si>
-  <si>
-    <t>KS2026-23</t>
-  </si>
-  <si>
-    <t>KS2026-27</t>
-  </si>
-  <si>
-    <t>KS2026-20</t>
-  </si>
-  <si>
-    <t>KS2026-21</t>
-  </si>
-  <si>
-    <t>KS2026-22</t>
-  </si>
-  <si>
-    <t>KS2026-19</t>
-  </si>
-  <si>
-    <t>KS2026-13</t>
-  </si>
-  <si>
-    <t>KS2026-25</t>
-  </si>
-  <si>
-    <t>KS2026-26</t>
-  </si>
-  <si>
-    <t>KS2026-17</t>
-  </si>
-  <si>
-    <t>KS2026-18</t>
-  </si>
-  <si>
-    <t>KKIM26-9</t>
-  </si>
-  <si>
-    <t>KS2026-16</t>
-  </si>
-  <si>
-    <t>KS2026-57</t>
-  </si>
-  <si>
-    <t>Otomasyon</t>
-  </si>
-  <si>
-    <t>Veri Analitiği</t>
-  </si>
-  <si>
-    <t>LLM ve Data Insights</t>
-  </si>
-  <si>
-    <t>Reçete Optimizasyonu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLAB MES Yapısının Kurulması </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperA MES Yapısının Kurulması </t>
-  </si>
-  <si>
-    <t>Yeni yatırımı yapılan System ve Sacmi kalite kontrol cihazlarının entegrasyonu başlatılacak. Gerekli kontrollerin tamamlanmasından sonra; Toplanan tüm makine verileri ile tekil karo bazında ileri analitik çalışmaları başlatılacak.​
-Yapay zekâ algoritmaları ile minimum fire ve maksimum verim sağlanacak.​
-Üretim hattı yöneticileri, dijital panellerden anlık KPI’ları görecek (verimlilik, kalite, fire oranı, OEE vb.).​</t>
+    <t>YK Masse, GR İkincil İşlemler Kurulumu</t>
+  </si>
+  <si>
+    <t>KB3, KB7 Kurulumu</t>
   </si>
   <si>
     <t>KB7, KB3  fabrikası iş analizi tamamlanmış olup backlog listesi tamamlanmıştır.​
@@ -992,503 +1291,54 @@
 Veri doğrulama işlemleri tamamlanmıştır (duruş ve fire), Kırmızı fire eşleşme doğrulaması devam ediyor​</t>
   </si>
   <si>
-    <t>KaleGo</t>
-  </si>
-  <si>
-    <t>Karayolu Gelişim</t>
-  </si>
-  <si>
-    <t>Diğer Modlarda Gelişim</t>
-  </si>
-  <si>
-    <t>Büyük Ebat Lojistiği</t>
-  </si>
-  <si>
-    <t>Kaydi Yapı</t>
-  </si>
-  <si>
-    <t>Saha Süreç ve Tesis Yönetimi</t>
-  </si>
-  <si>
-    <t>Teşhir Süreci</t>
-  </si>
-  <si>
-    <t>İthalat Süreci</t>
-  </si>
-  <si>
-    <t>Sevkiyat Süreci</t>
-  </si>
-  <si>
-    <t>Entegre Planlama Yapısı</t>
-  </si>
-  <si>
-    <t>S&amp;OE Süreci</t>
-  </si>
-  <si>
-    <t>Malzeme Depolama Süreci</t>
-  </si>
-  <si>
-    <t>Tedarikçi Gelişimi</t>
-  </si>
-  <si>
-    <t>KS2026-56</t>
-  </si>
-  <si>
-    <t>vSRM</t>
-  </si>
-  <si>
-    <t>Yetkinlik Gelişimi</t>
-  </si>
-  <si>
-    <t>Hizmet Seviyesi</t>
-  </si>
-  <si>
-    <t>S&amp;OP Tool</t>
-  </si>
-  <si>
-    <t>S&amp;OP Olgunluğu</t>
-  </si>
-  <si>
-    <t>Tahmin Yeteneği</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kampanya Verisi
-</t>
-  </si>
-  <si>
-    <t>Müşteri Temas
-Verisi</t>
-  </si>
-  <si>
-    <t>Teşhir Envanteri</t>
-  </si>
-  <si>
-    <t>Ürün Ana Verisi</t>
-  </si>
-  <si>
-    <t>Ürün Yaşam Döngüsü Verisi</t>
-  </si>
-  <si>
-    <t>Tahmin Dış Verisi</t>
-  </si>
-  <si>
-    <t>department order</t>
-  </si>
-  <si>
-    <t>function order</t>
-  </si>
-  <si>
-    <t>Ürünler Arası İlişki Tanımlarının Oluşturulması</t>
-  </si>
-  <si>
-    <t>Ürün İlişki Tanımları Aracının Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Kampanya Modül İhtiyaçlarının Belirlenmesi</t>
-  </si>
-  <si>
-    <t>Kampanya Modül Tasarımının Oluşturulması</t>
-  </si>
-  <si>
-    <t>Ürün Yaşam Döngüsü Bilgisinin Oluşturulması</t>
-  </si>
-  <si>
-    <t>Ürün ana veri yapısının incelenerek geliştirme/iyileştirme alanları ile hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Talep tahmin veri analitiği, SKU rasyonalizasyonu,  görünürlük, planlama stratejileri gibi pek çok çalışma için ürün ana veri yapısının iyileştirilmesi ihtiyacı ön koşul olarak bulunmaktadır.</t>
-  </si>
-  <si>
-    <t>Ana ebat tanımlarındaki eksikliklerin giderilmesi
-Faturalama için ambalaj tipi tanımlarının yapılması
-Piyasa kanalı tanımlarının revizyonu
-Üretim kontrol notu tanımlarındaki eksikliklerin giderilmesi
-Ürün hiyerarşisi uyumsuzluklarının tespiti ve düzeltilmesi
-Ürün hiyerarşisi tanımı yanlış olan kodların tespiti ve düzeltilmesi
-Gömme rezervuar ürün grubunda set kodlarının ayrıştırılması
-UP kodları için Marka bilgilerinin düzeltilmesi ve tamamlanması
-Orijin kodu bilgisinin düzenlenmesi ile ilgili çalışmaların başlatılması
-Ürün karakteristiklerinde yer alan kalite tanımı bilgilerinin düzenlenmesi</t>
-  </si>
-  <si>
-    <t>Palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
-Ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
-Ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - Mobilya
-Palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - SKM</t>
-  </si>
-  <si>
-    <t>Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-Vitrifiye
-Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-Mobilya
-Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-SKM 
-Farklı kalitedeki ürünlerin stok kodları arasında bağlantı oluşturulması</t>
-  </si>
-  <si>
-    <t>Ürün ana veri yapısında bulunan ambalaj bilgilerinin incelenerek hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Yükleme-rotalama optimizasyonu ve nakliye hesaplaması gibi pek çok çalışma için ürün ambalaj bilgilerinin tanımlanması ihtiyacı ön koşul olarak bulunmaktadır.</t>
-  </si>
-  <si>
-    <t>İlgili ürünlerin ve ilişkilerin belirlenmesi
-İlgili veri yapısının şirket içindeki kullanım şeklinin netleştirilmesi
-MRP tarafındaki kullanımının araştırılması
-Planlamadaki miktar bilgilerinde kullanılması
-Raporlamalardaki kullanım
-B2B'de öneri şeklinde sunulması
-Kalecore sayfasında öneri şeklinde sunulması
-Mevcut veri yapısının araştırılması (kataloglar ve fiyat listeleri gibi)
-İlişkilerin Tanımına dair ana veri yapısı çalışmasının yürütülmesi (IT ile)
-Gerekli tanımlamaların yapılması</t>
-  </si>
-  <si>
-    <t>"Ürünler Arası İlişki Tanımlarının Oluşturulması" projesi kapsamında oluşturulan verinin kurumsal olarak saklanması ve yönetimi için için yönetim aracı geliştirilmedi çalışmasıdır.</t>
-  </si>
-  <si>
-    <t>SF Teşhir Verisi Giriş Teknolojisinin Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>SF Temas Verisi Giriş Teknolojisinin Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Müşteri ziyaretlerinden SF üzerinde toplanan veriler, web crawling yöntemleriyle edinilen sektörel bilgiler ve GFK gibi dış kaynaklardan sağlanan veri setlerinin birlikte değerlendirilerek bir veri gölü yapısı oluşturulması çalışmasıdır. Konut istatistikleri, çıkarılan ruhsat sayıları, beyaz eşya satışları ve evlilik oranları gibi makro göstergelerle ilişkilendirilerek ileri analizler için altyapı hazırlanması.</t>
-  </si>
-  <si>
-    <t>Müşteri temsilcilerinin teşhir envanter bilgilerini daha hızlı ve pratik bir şekilde SF sistemine aktarabilmelerini sağlamak amacıyla yapılan çalışmadır.</t>
-  </si>
-  <si>
-    <t>Müşteri temsilcilerinin müşteri temas verilerini daha hızlı ve pratik bir şekilde SF sistemine aktarabilmelerini sağlamak amacıyla yapılan çalışmadır.</t>
-  </si>
-  <si>
-    <t>Kampanya süreçlerinin analizi, iş birimlerinden ihtiyaç toplanması ve hedeflenen kampanya yönetimi fonksiyonlarının belirlenmesi ile modül tasarım kriterlerinin oluşturulması çalışmasıdır.</t>
-  </si>
-  <si>
-    <t>"Kampanya Modül İhtiyaçlarının Belirlenmesi" proje kapsamında belirlenen ihtiyaç ve kriterlere uygun olarak kampanya yönetim modülünün oluşturulması ve/veya geliştirilmesi çalışmasıdır.</t>
-  </si>
-  <si>
-    <t>Ürün yaşam döngüsü takibine yönelik olarak windchill PLM akışında, talebin piyasa dağılımlı miktarsal ve tutarsal planı ve gerçekleşme durumu ve diğer ilgili bilgilerin eklenmesi çalışmasıdır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tahmin DFU Yapısının Güncellenmesi
-</t>
-  </si>
-  <si>
-    <t>Satış miktarlarındaki değişimler, palet konumu değişimleri ve tahmin doğruluk değerlerine göre DFU yapılarının güncellenme ihtiyacı bulunmaktadır. Bu güncellemelerde maliyet, fiyat, marka, üretim kaynağı-ticari, fabrika gibi unsurlar göz önünde bulundurulmaktadır. Bu proje ilgili ihtiyacı karşılamaya yönelik olarak DFU-SKU eşleşmesinin güncellenmesi içeren çalışmadır.</t>
-  </si>
-  <si>
-    <t>Satış verileri incelenerek DFU’ların etkinliğine ilişkin analizler oluşturuldu.
-Analizler sonucunda oluşturulan öneriler satış, kategori pazarlama ve planlama ekipleri ile paylaşıldı.
-Yapılan toplantılar ile kaldırılması, birleştirilmesi ya da yeni oluşturulması gereken DFU’lar belirlendi.
-Yeni DFU kodlarının SAP tanımları yapılarak eski DFU’lar kaldırıldı.
-SAP’de stok kodu ve yeni DFU eşleşmeleri tanımlandı.
-Yeni tanımlanan stok kodlarına ilişkin DFU tanımlarının güncel DFU’lar ile oluşturulması sağlanmaktadır.
-Periyodik olarak SAP’de tanımlı olan DFU’ların kontrolü ve tanımlanması sağlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Bu proje; değişen DFU yapıları doğrultusunda tahmin modelinin yeniden eğitilmesi ve mevcut tahmin uygulamasının yeni DFU’lar ile devreye alınması çalışmalarını kapsamaktadır.</t>
-  </si>
-  <si>
-    <t>Modelin eğitilmesine yönelik çalışma takvimi ve proje adımları belirlenmiştir.
-Modele beslenen dış verilere ait güncel değerler oluşturulmuştur.
-Model eğitiminin tamamlanması ile birlikte çıkan tahmin sonuçları incelenerek, tespit edilen hatalar doğrultusunda gerekli revizyonlar yaptırılmıştır.
-Sonuçların raporlanmasına ilişkin isterler belirlenerek piyasa ve DFU bazlı tahmin raporları oluşturulmuştur.
-Tahmin sonuçlarının düzenli olarak çalıştırılarak takip edilmektedir.
-Tahmin metrikleri hesaplanarak düzenli takip edilmektedir.
-SKU seviyesindeki sonuçlar planlama süreçlerinde kullanılmaktadır.</t>
-  </si>
-  <si>
-    <t>Yeni DFU Yapısı ile Modelin Eğitilmesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tahmin yetkinliğinin arttırılmasına yönelik olarak tahmin veri setinin değiştirilerek müşteri siparişi, fiyat, dış veriler, bayi satış verileri gibi bilgilerin kullanılarak yeni tahmin modelinin oluşturulmasına yönelik çalışmaları kapsamaktadır. </t>
-  </si>
-  <si>
-    <t>Tahmin modelinin oluşturulmasına yönelik kavramsal çalışmalar başlatılmıştır.
-Müşteri sipariş verilerine yönelik veri seti oluşturulmuştur.
-In-house talep tahmin çalışması başlatılmıştır.
-Model ve uygulamanın oluşturulmasına yönelik danışman firma ile proje takvimi ve adımlarının belirlenmesi devam etmektedir.</t>
-  </si>
-  <si>
-    <t>Modele beslenecek dış veriler belirlenecektir.
-Veri setinin analizi ve yeni tahmin modelinin tasarımı oluşturulacaktır. 
-Modelin eğitimi tamamlanarak sonuçlar değerlendirilecektir.
-Uygulama testleri ile uygulama devreye alınacaktır.</t>
-  </si>
-  <si>
-    <t>Tahminde Müşteri, Kampanya, Teşhir Bilgilerinin Kullanımı</t>
-  </si>
-  <si>
-    <t>Müşteri: Farklı müşteri eğilimlerini katmak üzere müşteri boyutunda satış organizasyonuna ilave dağıtım kanalı ve satış grubunun eklenmesi çalışmasıdır.
-Kampanya: Satış tahmin modeline kampanya etkisinin eklenmesi çalışmasıdır.
-Teşhir: Satış tahmin modeline bayi teşhir bilgisinin eklenmesi çalışmasıdır.</t>
-  </si>
-  <si>
-    <t>Genel Talep Tahmin Modelinin Oluşturulması</t>
-  </si>
-  <si>
-    <t>Piyasa büyüklügüne bağlı olarak genel talep tahminleme modelinin oluşturulması çalışmasıdır. Öncelikle ihtiyacın hangi seviyede olduğu belirlenecek ve sonrasında Türkiye ve/veya dünya için toplam bir talep tahmin modeli çalışması yürütülecektir.</t>
-  </si>
-  <si>
-    <t>Tahmin Fonksiyonunun Süreçlerde Kullanımı</t>
-  </si>
-  <si>
-    <t>Modelinin tekrar eğitilmesine yönelik çalışmalar tamamlanmıştır.
-Sonuçlarının raporlanmasına ilişkin isterler belirlenerek piyasa ve DFU bazlı raporlar oluşturulmuştur.
-Tahmin sonuçlarının S&amp;OP döngüsüne girdi olarak kullanılmasına ilişkin çalışmalar başlatılmıştır.
-Baz tahminler piyasalar ile paylaşılarak talep zenginleştirme çalışmaları yürütülmektedir.
-Tahmin sonuçları düzenli olarak takip edilmektedir.
-Tahmin doğruluğu metriklerinin belirlenmiştir. Düzenli olarak hesaplanarak takip edilmektedir.
-Baz tahmin, revize baz tahmin, revize tahmin, nihai tahmin sonuçlarının ve tahmin sapmalarının görüntülenmesine ilişkin Power BI raporlama dashboardu oluşturulmuştur.
-SKU seviyesinde tahmin sonuçlarının planlama süreçlerinde kullanılmaktadır.</t>
-  </si>
-  <si>
-    <t>Talep Optimizasyon Aracının Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Mevcut taleplerin karşılanmasının ötesinde, belirli müşteri-ürün gruplarına yönelik yüksek kar oluşturan çalışma şeklinin ortaya çıkarılmasını sağlayacak şekilde optimizasyon aracının geliştirilmesi çalışmasıdır. Araç hat yetenekleri ve talep kısıtlarına göre maksimum kar için talep planının oluşturulmasını sağlayacaktır.</t>
-  </si>
-  <si>
-    <t>Optimizasyon modelinin oluşturulması tamamlandı.
-Modelin çözümüne ilişkin python kodu geliştirildi.
-Veri girişi, veri export, optimizasyon ve raporlama özellikleri eklenerek komple bir web uygulaması çözümü oluşturuldu.
-Çözüm ve uygulama Kale Masters Doğrusal Programlama eğitimi kapsamında geliştirilmiştir.</t>
-  </si>
-  <si>
-    <t>S&amp;OP Talep Planlama Uyg. Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Talep tahmin uygulamasının çıktısını kullanarak tedarik planlama adımına girdi olacak ve mutabakat sağlanmış talep değerlerinin oluşturulmasını sağlayacak talep zenginleştirme ve mutabakat uygulamasının geliştirilmesi çalışmasıdır. Tahmin sonuçlarının girdi olarak alınabildiği, belirli hiyerarşilerde düzeltme yapılabildiği, belirli kişilerin üzerinde çalışabildiği ve veri girişi yapabildiği esnek bir ortam geliştirme çalışmasıdır. Odoo platformu üzerinde In-house olarak geliştirilmektedir.</t>
-  </si>
-  <si>
-    <t>S&amp;OP Finansallaştırma Uyg. Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>S&amp;OP süreci talep ve tedarik planlama adımlarından çıkan bilgilerin fiyat, maliyet, başta olmak üzere diğer finansal girdilerin kullanılarak tutarsal hale getirilmesi ve raporlanması çalışmasıdır. Buradan çıkan farklı senaryolar bazındaki finansalların değerlendirilmesi ile operasyonel planlara karar verilmesi sağlanacaktır. Bu çalışma In-house olarak planlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Kullanılan talep tahmin uygulaması, geliştirilmesi devam eden talep planlama uygulaması, geliştirilmesi planlanan finansallaştırma uygulaması çözümlerinin bir paket olarak birbirine bağlanmış bir ürün hale getirilmesi çalışmasıdır.
-In-house olarak ürünleştirme çalışmasından verim alınamaması durumunda yapılmış olan RFP çalışmasına istinaden ürün araştırılması yine bu çalışma kapsamındadır.</t>
-  </si>
-  <si>
-    <t>S&amp;OP Aracının Geliştirilmesi (In-House)</t>
-  </si>
-  <si>
-    <t>Beklenen Hizmet Sev. Tanımlanması</t>
-  </si>
-  <si>
-    <t>TZ süreçlerinin, beklenen hizmet seviyesini karşılayacak şekilde çalışabilmesi için müşteri-ürün boyutlarında farklılaşan beklenen hizmet seviyelerinin tanımlanması gerekmektedir. Bu proje ile müşteri-ürün boyutları bazında, belirlenmiş gruplar/kanallar için hizmet seviyelerinin tanımlanması amaçlamaktadır. Bu şekilde genel çalışma (standart hizmet) ve metrik takibinden, kategorize edilmiş ve tanımlanmış ihtiyaçların karşılandığı ve bunların ölçümü ile performans takibinin yapıldığı sisteme geçilebilecektir.</t>
-  </si>
-  <si>
-    <t>Hizmet için TZ Aks. Oluşturulması</t>
-  </si>
-  <si>
-    <t>Beklenen Hizmet Seviyelerinin Tanımlanması projesinde oluşturulan, kategorize edilmiş hizmet seviyesi tanımlarının, karşılanmasına yönelik olarak aksiyonların oluşturulduğu ve takibinin yapıldığı çalışmadır.</t>
-  </si>
-  <si>
-    <t>PI ların Oluşturulması ve Takibi</t>
-  </si>
-  <si>
-    <t>Hizmet için Tedarik Zinciri Aksiyonlarının Oluşturulması projesinde oluşturulan, aksiyonların performans sonuçlarının ölçümü ve takibine yönelik çalışmaların yürütüldüğü projedir.</t>
-  </si>
-  <si>
-    <t>Global Entegre Planlama Aracının İmplementasyonu</t>
-  </si>
-  <si>
-    <t>S&amp;OE süreci, onaylanmış S&amp;OP / Ana Üretim Planı çerçevesinde; kısa vadeli (günlük / haftalık) dönemde oluşan talep, stok ve sevkiyat sapmalarını hızlı kontrollü şekilde yönetmeyi amaçlayan, operasyonel bir karar alma sürecidir. Bu proje KS nin ihtiyaçlarına uygun S&amp;OE sürecinin geliştirilmesi ve tanımlanması çalışmasını içermektedir.</t>
-  </si>
-  <si>
-    <t>S&amp;OP toplantıları aylık olarak devam etmektedir. Toplantılarda stoklar, üretim planları, talep değişkenlikleri, üretim öncelikleri gibi bilgiler kontrol edilmektedir. 
-Süreç Kapsamının ve Zaman Ufku haftalık olarak belirlendi.
-Kritik karar konuları tamamlandı.
-Roller ve sorumluluklar netleştirildi. Paylaşılacak tablolar netleştirildi.
-Planlama olarak güncel tutulan tablolar üzerinden veri setleri oluşturuldu.
-Önceliklendirme ve Karar Kurallarının oluşturuldu.
-Toplantı yapısı katılımcılar ve periyotları belirlendi.
-KPI ve Başarı Göstergeleri S&amp;OP toplantılarında konuşulan aylık hedeflerin haftalık periyotlara bölünmüş hali olarak belirlendi. (Plana Uyum, Fazla Üretim vs.)</t>
-  </si>
-  <si>
-    <t>Pilot kapsamın netleştirilmesi
-S&amp;OE Toplantı Ritminin başlatılması (1 Mart itibariyle başlatılacaktır)
-Standart veri seti ile operasyonun yürütülmesi
-Önceliklendirme ve karar kurallarının uygulanması
-Aksiyon Takibi ve Disiplinin Sağlanması
-Eskalasyon Mekanizmasının İşletilmesi
-KPI takibi ve ilk etki ölçümü
-Geri Bildirim ve iyileştirme</t>
-  </si>
-  <si>
-    <t>Sipariş Önceliklendirme Optimizasyonu ve Çizelgeleme</t>
-  </si>
-  <si>
-    <t>S&amp;OP Aracının Geliştirilmesi (In-House) çalışmasında beklenen sonucun alınamaması durumunda hazırlanan RFP e göre global bir entegre planlama aracının tedariği ve şirkete implementasyonu çalışmasını içeren projedir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP sistemi içinde saklamalı sipariş, teyit-termin gibi şirkete özel olarak oluşturulmuş ve standart akışın dışına çıkan yaklaşımlar yerine aATP gibi (Advanced Available-to-Promise) standart çözümlerin kullanımına geçilmesi hedeflenmektedir. Bu çalışma kapsamında sipariş önceliklendirme için parametrelerin belirlenmesi, optimizasyon modelinin oluşturulması ve entegre planlama sürecine sipariş önceliklendirme fonksiyonunun entegrasyonu da hedeflenmektedir.
-</t>
-  </si>
-  <si>
-    <t>Sipariş önceliklendirme için parametrelerin belirlenmesi, optimizasyon modelinin oluşturulması ve entegre planlama sürecine sipariş önceliklendirme fonksiyonunun entegrasyonu hedeflenmektedir.</t>
-  </si>
-  <si>
-    <t>Envanter ve Planlama Str. Uygulanması</t>
-  </si>
-  <si>
-    <t>Planlama Str. Güncelleme Yazılımı Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Belirli veriler kullanılarak yapılan hesaplamalar doğrultusunda ve yine belirli kurallara göre olarak yapılan ürünlerinlerin planlama strateji gruplarının belirlenmesi sürecinin bir tool a aktarılarak otomatik olarak yapılması çalışmasıdır.</t>
-  </si>
-  <si>
-    <t>Ambalaj Mal. Depolamasının İyileştirilmesi</t>
-  </si>
-  <si>
-    <t>AGSW Uyg. İmplementasyonu</t>
-  </si>
-  <si>
-    <t>Mobilya Lojistik Süreçleri İmplementasyonu</t>
-  </si>
-  <si>
-    <t>Nakliye Hesaplama Modelinin İyileştirilmesi</t>
-  </si>
-  <si>
-    <t>Filo ve Spot Araç Kullanımı İyileştirilmesi</t>
-  </si>
-  <si>
-    <t>Sevkiyat Kapı ve Saha Yapısı İyileştirilmesi</t>
-  </si>
-  <si>
-    <t>Nakliyeci Atama ve Takip Uyg. Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Denizyolu Filo ve İş Hacminin Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Depo Stok Hareket Akışlarının Oluşturulması</t>
-  </si>
-  <si>
-    <t>SLAB Lojistik Yetkinliklerin Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Teşhir Süreci Yapılandırma ve Atölye Kurulumu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teknik SA kategorisinde teklifler, siparişler ihaleler dijital olarak SRM üzerinden toplanmaktadır. (3600+ işlem)
-Yeni cari tanımlarında vSRM dijital uygulaması ve BP entegrasyonu devreye alınmış ve 87 yeni cari kaydı vSRM üzerinden yapılmıştır.
-Satın alma ihalesinde açık artırma parametresinin uygulamaya dahil edilmesi.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satış ihalesi sürecinin SRM’ e tanımlanması. 
-SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır.
-</t>
-  </si>
-  <si>
-    <t>İhale Modülü ve SAP BP İmplementasyonu</t>
-  </si>
-  <si>
-    <t>DÖF Modülünün Devreye Alınması</t>
-  </si>
-  <si>
-    <t>Ambalaj kategorisinde Kalite Birimi tarafından aktif kullanılmaktadır.</t>
-  </si>
-  <si>
-    <t>Diğer SA kategorilerinde DÖF modülünün kullanılması yaygınlaştırılacaktır. Örnek Hammadde için Ar-Ge girdi kontrol kullanımı.
-Kategorilerde denetim kayıtlarının vSRM üzerinden yürütülmesi ve tedarikçiye iletilmesi.</t>
-  </si>
-  <si>
-    <t>Sipariş Modülü İyileştirme ve Yaygınlaştırma</t>
-  </si>
-  <si>
-    <t>Faz 1; Tedarikçi bazında kullanım (siparişlerin onayı ve irsaliye girişleri) oranlarının arttırılması ve süreç işlemlerin (SAS) iyileştirilmesi sağlanmıştır. 32 tedarikçinin % 58’ inde kullanıma geçilmiştir. 
-Teknik Satın alma kategorisinde hizmet alanında teklif ve siparişlerin oluşturulması %100 oranında devreye alınmıştır, stok kodlu alımlarda da kullanılmaya başlanmıştır.
-Bölgesel ve Merkezi Hizmet kategorisinde ilgili sipariş modulü eğitimi alınmıştır.
-Teknik hizmet iş kabullerinde VSRM üzerinden gerekli süreç tamamlanmıştır, 01.04.2026 tarihinde devreye alınmıştır.</t>
-  </si>
-  <si>
-    <t>Bölgesel Hizmet ve Merkezi Satın alma kategorilerinde sipariş modülü kullanıma başlanacaktır.
-Bölgesel Hizmet kategorisi için ilgili kullanıcılara (talep sahibi, tedarikçi) süreç hakkında bilgi verilecektir. Talepler vSRM üzerinden alınarak satın alma süreci başlatılacaktır.        
-vSRM dışı talep kabul edilmeyecektir. Taleplerin vSRM üzerinden alınması planlanmaktadır.
-vSRM kullanımı sipariş girişi sağlayan ambar birimlerine yaygınlaştırılacaktır.
-Siparişlerin hızlanması için vSRM üzerinden SAT açılması işlemlerinin otomatik olarak çalışması yapılmaktadır. Mayıs ayına kadar tamamlanması planlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Sevk Planı ve Müş. Stok Süreci İyileştirilmesi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tedarikçi Değerlendirme Sistemi yeniden kurgulandı. Performans kriterleri ve puanlama yapısı oluşturuldu.
-2025 yılı tedarikçi değerlendirmesi 2026 Ocak ayı içinde tamamlandı.
-Tedarikçi değerlendirme sonuçları iç müşteriler ve tedarikçiler  ile paylaşıldı.
-Tedarikçi değerlendirme süreci ITG firması tarafından örnek bir model gösterimiyle anlatıldı, KPI listesi paylaşıldı. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tedarikçi değerlendirme sürecinde kullanılabilecek vSRM sisteminde yer alan KPI listesi kontrolü ve sisteme entegre edilmesi. 
-</t>
-  </si>
-  <si>
-    <t>Tedarikçi Değerlendirme Sür. İyileştirilmesi</t>
-  </si>
-  <si>
-    <t>Tedarikçilerimizin verdiği teknik eğitimlerle hem kendi kullanıcımız hem de tedarikçimizin ürününün doğru kullanılması ile optimum sonuçlara ulaşılmaktadır.
-Ambalaj ve Tamamlayıcılar kategorisinde tedarikçilerimize açtığımız DÖF’ler ile ilgili malzeme geliştirmeleri yapılmakta ve bilgiler vSRM sistemi üzerinden kayda alınmaktadır.</t>
-  </si>
-  <si>
-    <t>DÖF yapısının vSRM modülü üzerinden Bölgesel ve Merkezi hizmet, Ambalaj ve Tamamlayıcılar, Hammadde ve Kimyasallar kategorisine de yaygınlaştırılması sağlanacaktır.
-Tedarikçi performans verilerinin vSRM (kalite, maliyet, teslimat, hizmet vb.) değerlendirilmesi.
-Yapılan tedarikçi değerlendirmeleri sonucunda tedarikçilerle paylaşılan sonuçlara istinaden gelişim alanlarının belirlenmesi. Örneğin termin anlamında düşük puan alan tedarikçilerin geliştirilmesi vs.</t>
-  </si>
-  <si>
-    <t>Tedarikçi Ağı Opt. ve Alt. Ted. Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Tedarikçi Benchmark çalışmaları yapılmıştır. 2 grup halinde farklı iki firma olan Sofra firması ve Dalgakıran firmaları satınalma yapısı olarak incelenmiştir. Sofra firmasından tedarikçi değerlendirme anlamında örnekler alınmıştır. 
-Çin pazarı tedarik ürünler satınalmasında Know how gelişimi için Trome firmasıyla aktif çalışmaya başlanılmıştır.</t>
-  </si>
-  <si>
-    <t>Maliyet yapıları ve fiyat kırılımları bilgisinin geliştirilmesi.
-Piyasa Emtialarının ve artış tahmin oranlarının bir bülten üzerinden takibinin yapılması ve geliştirilmesi.
-Kategori bazlı tedarikçilerin üretim hatlarının görüleceği ve teknik değerlendirilmesinin yapılabileceği ziyaret planlaması yapılacaktır.</t>
-  </si>
-  <si>
-    <t>FRM.GEN.SAT.031 form kodu ile Satın alma Fiyat Değişim Onay Formu oluşturulmuştur.
-İŞT.GEN.SAT.002 form kodu ile Satın alma Fiyat Değişim Onay Talimatı oluşturulmuştur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiyat Değişim Onay hiyerarşisinin SAP kurgusu Strateji birimiyle görüşülecektir. </t>
-  </si>
-  <si>
-    <t>Robot tarafından kayıt edilmesi planlanan tedarikçiler belirlenmiş, sisteme ……….. cari tanımlanmıştır.</t>
-  </si>
-  <si>
-    <t>Döviz bazlı faturaların RPA sürecine dahil edilmesi.
-Robot tarafından yapılan kayıtların miktarının artırılması.</t>
-  </si>
-  <si>
-    <t>Satın alma taleplerinin Teknik SA kategorisinde e-posta/telefon yerine SRM sistemi üzerinden alınıp yürütülmektedir.
-Teknik satınalma kategorisinde talepler teknik dokümanlar la birlikte SRM sistemi üzerinden alınmaya başlanmış ve tedarikçiye yine SRM sistemi üzerinden ihale, teklif toplama vb. şeklinde iletilmektedir.</t>
-  </si>
-  <si>
-    <t>SRM sistemi işlemlerinde Hizmet SAT’ larının talep sahibi onayı ile otomatik olarak SAP sisteminde yaratılması ve SRM sistemi ile entegre olması planlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Teknik hizmet alımlarında alınan hizmetin kontrolü E-flow sisteminde yer alan uygulama ile yapılmakta; talep sahipleri faturalara dijital onay vermektedir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stok kodlu ve hizmet siparişlerinde SAS onay sistemi kullanılmaktadır.
-Strateji tarafında SAS onay limitleri ve yetki tablosu belirlenmiştir. </t>
-  </si>
-  <si>
-    <t>SA Talebi Sistematiğinin İyileştirilmesi</t>
-  </si>
-  <si>
-    <t>Firma tarafından hizmet teslimi onayı
-Talep sahibi ve üst amir onayı
-Firmaya fatura düzenlenmesi için bilgi kaydı 
-Faturanın sistem tarafından ön kaydının yapılması</t>
-  </si>
-  <si>
-    <t>Granit Masse, Sır Üretim, Granit Kurulumu</t>
-  </si>
-  <si>
-    <t>KB3, KB7 Kurulumu</t>
-  </si>
-  <si>
-    <t>YK Masse, GR İkincil İşlemler Kurulumu</t>
+    <t xml:space="preserve">SLAB MES Yapısının Kurulması </t>
+  </si>
+  <si>
+    <t>Devam ediyor</t>
+  </si>
+  <si>
+    <t>Yeni yatırımı yapılan System ve Sacmi kalite kontrol cihazlarının entegrasyonu başlatılacak. Gerekli kontrollerin tamamlanmasından sonra; Toplanan tüm makine verileri ile tekil karo bazında ileri analitik çalışmaları başlatılacak.​
+Yapay zekâ algoritmaları ile minimum fire ve maksimum verim sağlanacak.​
+Üretim hattı yöneticileri, dijital panellerden anlık KPI’ları görecek (verimlilik, kalite, fire oranı, OEE vb.).​</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperA MES Yapısının Kurulması </t>
   </si>
   <si>
     <t>KSFX Yapısının Kurulması</t>
+  </si>
+  <si>
+    <t>KS2026-32</t>
+  </si>
+  <si>
+    <t>MES IOT Mobilya</t>
+  </si>
+  <si>
+    <t>Mobilya Üretimi MES Yapısının Kurulması</t>
+  </si>
+  <si>
+    <t>MES IOT Vitrifiye</t>
+  </si>
+  <si>
+    <t>Vitrifiye Üretimi MES Yapısının Kurulumu</t>
+  </si>
+  <si>
+    <t>KS2026-31</t>
+  </si>
+  <si>
+    <t>MES Uygulamaları</t>
+  </si>
+  <si>
+    <t>Fırın İzleme Sistemi</t>
+  </si>
+  <si>
+    <t>AI Destekli Fırın İzleme Sistemi</t>
+  </si>
+  <si>
+    <t>KS2026-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fırın verimliliğinin canlı takibi projesinin tamamlanmasından sonra Faz-2 olarak canlı takip sonuçlarının üretim sarf, reçete bilgisi ile optimize edilerek AI destekli izleme sisteminin kurulması hedeflenmektedir. </t>
   </si>
   <si>
     <t>Parkur içerisindeki tüm makinaların canlı takip verileri gcp de bulunmaktadır.​
@@ -1505,6 +1355,18 @@
 Üretim parametrelerinin kurulacak sisteme entegrasyonuyla Agentic AI modellemesi yapılarak fırının izlenmesi ve kontrolü sağlanacaktır.​</t>
   </si>
   <si>
+    <t>Otomasyon</t>
+  </si>
+  <si>
+    <t>Püskürtmeli Kurutucu Otomasyonu</t>
+  </si>
+  <si>
+    <t>KS2026-34</t>
+  </si>
+  <si>
+    <t>Canlı Rutubet Ölçümü ile Model kurularak Sprey kurutucu ısılarına müdahale eden robot geliştirilerek sprey çıkışı rutubetin sürekli stabil tutulması sağlanacaktır.</t>
+  </si>
+  <si>
     <t>Rutubet cihazının kurulumu ve PC bağlantıları tamamlandı​
 Üretilen farklı reçetelerdeki hammaddeler için cihaz kalibrasyonu ve ölçüm reçetesi oluşturulması tamamlandı​
 Veri doğrulama ve veri seti oluşturma tamamlandı.​
@@ -1519,6 +1381,15 @@
 Kurutma makine parametreleri ile rutubet ölçümü arasındaki gecikme zaman farkı hesaplanarak veri eşleşmesi yapılacaktır. ​</t>
   </si>
   <si>
+    <t>Masse ve Sır Stok Hareket İşlemleri</t>
+  </si>
+  <si>
+    <t>KS2026-33</t>
+  </si>
+  <si>
+    <t>Mevcutta yapılan parti bazlı ürün ve ürün ağacı takibinin tekil karo bazlı yapılması hedeflenmektedir.</t>
+  </si>
+  <si>
     <t>MES sistemi ile tekil karo bazlı takip yapılabilmektedir. ​
 Granit fabrikası ve granit masse üretimi arasında pilot çalışma planlanmıştır.​
 Tüketim datalarının SAP üzerinden anlık çıkışı için algoritma düzenlenmiştir. ​
@@ -1530,6 +1401,18 @@
 İş emrinin ürün ağacına göre çıkarılan fiili standart maaliyet oranı her bir karo çözünürlüğünde bakılarak trend analizi yapılacaktır. ​</t>
   </si>
   <si>
+    <t>Reçete Optimizasyonu</t>
+  </si>
+  <si>
+    <t>Granit Bünye Reçete Opt. Çalışması</t>
+  </si>
+  <si>
+    <t>KS2026-36</t>
+  </si>
+  <si>
+    <t>Masse ve sır için geçmiş üretim verilerinden öğrenen bir yapay zekâ sistemine dayanacaktır.    Modelin amacı deneme-yanılma sürecini ortadan kaldırmak, üretim verimliliğini artırmak, ürün kalitesinde sürdürülebilirliği garanti altına almak, hammadde kullanımında optimizasyon sağlamaktır.</t>
+  </si>
+  <si>
     <t>Gerekli olan tüm veriler MES sistemi içinde toplanmaya başlamıştır.​
 Modeli oluşturacak uygun veri seti büyüklüğü için tespit çalışmaları devam etmektedir.​
 Proje için üç konsorsiyum ile Horizon ön başvurusu yapılmış, sonuçları beklenmektedir.​</t>
@@ -1539,6 +1422,19 @@
 Reçete hammadde ve/veya oran değişimlerinin nihai ürüne etkisinin analizi yapılacak ​
 Üretim şartlarına uygun hammadde ihtiyacı öneri sistemi kurulacak​
 Projenin yazılım bütçesinin AB fonlarından karşılanması planlanmaktadır.​</t>
+  </si>
+  <si>
+    <t>Tübitak 1711</t>
+  </si>
+  <si>
+    <t>CWYF Uygulaması Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>KS2026-35</t>
+  </si>
+  <si>
+    <t>CeramIQ - Gerçek Zamanlı Üretim Verisi ve Akıllı Ajanları ile Desteklenen Endüstriyel Yapay Zekâ Modellerinin Geliştirilmesi ve Etkileşimli Karar Destek Asistanlarının Tasarımı
+Seramik üretim süreçlerinde (masse hazırlık, karo üretim ve fırın sonrası işlemler dahil) gerçek zamanlı üretim verilerinin toplanması, yapay zekâ tabanlı analitik modellerin geliştirilmesi ve etkileşimli karar destek asistanlarının kullanıma alınmasıyla; verimlilik, kalite, enerji optimizasyonu ve sürdürülebilirlik hedeflerini gerçekleştirmeyi amaçlamaktadır.</t>
   </si>
   <si>
     <t>Başvuru tamamlanmıştır. ​
@@ -1559,6 +1455,16 @@
 Sürdürülebilirlik &amp; Raporlama: Enerji ve hammadde tasarruflarının ölçülmesi, yönetim raporlarının hazırlanması.​</t>
   </si>
   <si>
+    <t>Veri Analitiği</t>
+  </si>
+  <si>
+    <t>Granit Kurutucu Verimlilik Optimizasyonu</t>
+  </si>
+  <si>
+    <t>Karonun kurutucu içinde görünürlüğünü sağlayarak tüm sepet ve raflarının aktif kullanımını sağlamak, verimliliğini ölçmek ve canlı izlemek için;
+Kurutuculardan toplanan operasyonel verilerin (sepet no, sepet id, tur bilgisi, çıkış sıcaklığı, doğalgaz sarfiyatı vb.) analitik yöntemlerle işlenmesi ve yapay zekâ destekli modeller kullanılarak  dikey kurutucunun her bir çevirimi için verimlilik artırımı ve enerji tasarrufu sağlanması.</t>
+  </si>
+  <si>
     <t>IoT sensörlerinden pres ve kurutucuya ait anlık veriler toplanmaktadır.​
 Makine parametreleri ile hat duruş bilgileri zaman etiketi üzerinden eşleştirilmiştir.​
 Dikey kurutucunun tüm raflarının aktif kullanımı için zaman serisi analizi tamamlanmıştır.​
@@ -1573,6 +1479,12 @@
 Kurutma yaşam döngüsü verileri ile kestirimci kalite çalışmaları</t>
   </si>
   <si>
+    <t>Masse  Verilerinin Granite Bağlanması</t>
+  </si>
+  <si>
+    <t>Masse hazırlık süreci ile karo üretim sürecini tek bir dijital izlenebilirlik zincirinde birleştirmek. Hammadde dozajından başlayıp, öğütme – kurutma – stoklama – presleme – sırlama – pişirim – fırın sonrası işlemler aşamalarına kadar tüm değer zincirini uçtan uca dijital olarak izlemek, veriye dayalı karar alma ve optimizasyon sağlamak.</t>
+  </si>
+  <si>
     <t>MES ve SAP entegrasyonu tamamlandı​
 IoT sensörleri ve SCADA sistemlerinden veri toplama süreci tamamlandı​
 Verinin depolanması ve veri kullanım senaryoları oluşturuldu​
@@ -1583,6 +1495,12 @@
 En çok yaşanan firelerin veri gölü içindeki sebep sonuç korelasyonları araştırılarak kök neden analizi yapılacak​
 Makine öğrenmesi ile oluşturulan modeller kullanılarak canlı makine parametreleri için kurallar tanımlanıp kestirimci kalite uyarıları hazırlanacak​
 Fırın çıkışında fire olacağı öngörülen karoların pişirim öncesi bertaraf edilerek ham kırık olarak geri kazanılması ​</t>
+  </si>
+  <si>
+    <t>Fırın Verimliliğinin Canlı Takibi</t>
+  </si>
+  <si>
+    <t>Seramik üretiminde en fazla enerji tüketimi bulunan pişirim sürecinin verimliliğinin sürekli olarak izlenmesi, olası verimlilik düşüklüklerinin bildirilmesi</t>
   </si>
   <si>
     <t>Fırın halı besleme veriminin çıkarılabilmesi için gerekli veriler toplanmıştır​
@@ -1598,6 +1516,12 @@
 KB7 yaygınlaştırması planlanacaktır.</t>
   </si>
   <si>
+    <t>Masse Boya Tahminleme Modeli</t>
+  </si>
+  <si>
+    <t>Mevcut sistemde ürün ağacına göre boya girilerek yapılan masse renklendirme işlemi yerine hazırlanan çamura uygun miktarda boya tahminlemesi modeli kurularak deneme miktarının azaltılması ve verimliliğin artırılması.</t>
+  </si>
+  <si>
     <t>Masse çamuru içerisine reçeteye göre boya girme işlemi yapılarak çamur renklendirilir. ​
 Renk ölçümü sonrasında tekrar müdahale edilerek hedefe ulaşılmaya çalışılmaktadır. ​
 Hammaddeler girdi kontrol şartlarını sağlasalar da renk performansları her partide farklı olabilmekte ve ürün ağacına uymamaktadır.</t>
@@ -1605,6 +1529,12 @@
   <si>
     <t>Girdi kontrol QM verileri ve MES sistemi laboratuvar kontrol verileri ile model geliştirilecektir. ​
 Hazırlanan çamura uygun boya ihtiyacının dinamik reçete ile tahminlenmesi için ileri analitik çalışması yapılacaktır.​</t>
+  </si>
+  <si>
+    <t>Bilya Performans Takibi</t>
+  </si>
+  <si>
+    <t>Değirmenlerde kullanılan bilya ve iç kaplama kaynaklı verimsizliklerin yapay zekâ destekli tahminlenmesi ve kestirimci bakım planı için çalışması.</t>
   </si>
   <si>
     <t>Öğütme öncesi tüm hammaddelerin QM verileri alınmıştır. ​
@@ -1620,6 +1550,19 @@
 Envanter takip ekranları ile değirmenlere yapılan bilya beslemeleri kaydedilecektir.​</t>
   </si>
   <si>
+    <t>Dijital Dönüşüm Merkezi</t>
+  </si>
+  <si>
+    <t>STB Dijital Dönüşüm Merkezi</t>
+  </si>
+  <si>
+    <t>STB DDM Başvuru Sürecinin Yürütülmesi</t>
+  </si>
+  <si>
+    <t>Dijital Dönüşüm Destek Programı ile teknolojik ürün ve çözümlerin işletme süreçlerine entegre edilmesi, işletmelerin üretim ve tedarik zinciri süreçlerinde verimliliklerinin artırılması, işletmelere küresel rekabette üstünlük kazandırılması ve Türkiye'nin teknolojik yetkinliğini yükselterek katma değerli ürünler üretilmesi amaçlanmaktadır.
+Kaleseramik olarak 5. Bölge teşviklerinden yararlanmak ve Dijital Dönüşüm Merkezi ünvanı alabilmek için başvuru yapılması planlanmıştır.</t>
+  </si>
+  <si>
     <t>Dijital olgunluk değerlendirmesi yapılmıştır.​
 Değerlendirme sonrası tüm birimler için gelişime açık noktalar belirlenmiştir​
 Dijital dönüşüm yol haritası hazırlanmıştır.​
@@ -1633,9 +1576,30 @@
 Gelişimi takip edebilmek için her yıl iç kaynaklar ile  olgunluk değerlendirmesi yapılacak ​</t>
   </si>
   <si>
+    <t>STB DDM Projelerinin Yürütülmesi</t>
+  </si>
+  <si>
+    <t>Dijital Dönüşüm Merkezi ünvanı alındıktan sonra ilgili projelerin yürütülmesi konusundaki proje yönetimi faaliyetlerini kapsamaktadır.</t>
+  </si>
+  <si>
     <t>3 yıllık yatırım projeksiyonu DDM üzerinden yönetilecek.​
 Merkez bünyesinde gösterilecek çalışanlar için bildiirm yapılacaktır.​
 2026 yılı sonu dijital olgunluk değerlendirilmesi tekrarlanacaktır.​</t>
+  </si>
+  <si>
+    <t>İş Zekası ve Görünürlük</t>
+  </si>
+  <si>
+    <t>Dijital İkiz</t>
+  </si>
+  <si>
+    <t>Dijital İkiz Çalışmasının Oluşturulması</t>
+  </si>
+  <si>
+    <t>KS2026-38</t>
+  </si>
+  <si>
+    <t>Fabrikanın fiziksel süreçlerini gerçek zamanlı veriyle beslenen sanal modeller aracılığıyla temsil edilmesi hedeflenmektedir. </t>
   </si>
   <si>
     <t>Microsoft Azure Digital Twins uygulaması ön çalışması tamamlanmıştır.​
@@ -1653,6 +1617,15 @@
 Çalışma in-house yönetilecektir.​</t>
   </si>
   <si>
+    <t>PowerBI Dashboard</t>
+  </si>
+  <si>
+    <t>Üretim Verileri PowerBI Aktarımları</t>
+  </si>
+  <si>
+    <t>Mühendislik birimi tarafından oluşturulan fabrikalara ait kalite, hata analizi, duruş raporlarının PowerBI üzerinden kod sistematiği içeren şekilde özelleştirilerek oluşturulması ve birimlerin bu konudaki yetkinliklerinin artırılması bu projenin çalışma konusunu oluşturmaktadır.</t>
+  </si>
+  <si>
     <t>Mühendislik tarafından oluşturulan fabrikalara ait kalite, hata analizi, duruş raporlarını içeren raporlar teslim alınarak, kod sistematiği kontrol edilmiş ve gerekli düzenlemeler yapılarak günlük takibi yapılmaktadır. ​
 Fabrika tüm raporları (hata, kalite, duruş)  güncel olarak takibi yapılıp yayımlanmaktadır.​
 Fabrika PowerBI raporlarının veri kaynağının değiştirilmiştir.​</t>
@@ -1661,6 +1634,12 @@
     <t>Farklı birimlerden gelen verilerin birleştirilerek ortak platformda görünürlüğü sağlanacaktır.​
 Raporlama arayüzleri revize edilecektir.​
 MES verileri işlenerek PowerBI a aktarılacaktır.​</t>
+  </si>
+  <si>
+    <t>Finans PowerBI Dashboard Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>Mali işler birimi tarafından talep edilen fagid Bütçe-Fiili raporu, günlük stok analiz raporu ve VSM maliyet raporu gibi çeşitli birimlerin ihtiyaç duyduğu raporların PowerBI üzerinden kod sistematiği içeren şekilde özelleştirilerek oluşturulması ve birimlerin bu konudaki yetkinliklerinin artırılması bu projenin çalışma konusunu oluşturmaktadır.</t>
   </si>
   <si>
     <t>Fagid Bütçe-Fiili raporu faaliyette olup gerçek zamanlı güncellenerek yayımlanmaktadır. ​
@@ -1671,6 +1650,12 @@
   <si>
     <t>Farklı birimlerden gelen verilerin birleştirilerek ortak platformda görünürlüğü sağlanacaktır.​
 Sürecin devam ettirilmesi için Mali İşler'den veri beklenmektedir.​</t>
+  </si>
+  <si>
+    <t>TZY PowerBI Dashboard Geliştirilmesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TZY Görünürlük Raporları ile üretim, stok, müşteri ve performans verilerinin bütünsel ve şeffaf bir şekilde izlenmesi, veriye dayalı karar alma süreçlerinin güçlendirilmesi ve her kategori için standart raporların hazırlanarak sürdürülebilir bir raporlama altyapısının oluşturulması hedeflenmektedir . Bu hedef doğrultusunda her kategori için kod sistematiği içeren PowerBI raporları oluşturulmaktadır. </t>
   </si>
   <si>
     <t>TZY - Bütçe -Fiili Üretim Raporu ​
@@ -1692,6 +1677,21 @@
 UYGULAMA KULLANILABİLİR HALE GETİRİLMİŞTİR.​</t>
   </si>
   <si>
+    <t>AI Uygulamaları</t>
+  </si>
+  <si>
+    <t>LLM ve Data Insights</t>
+  </si>
+  <si>
+    <t>Envanter Yön. AI Kullanım Fonk. Oluşturulması</t>
+  </si>
+  <si>
+    <t>KS2026-39</t>
+  </si>
+  <si>
+    <t>Kurumsal veri kaynaklarının (SAP, BW, v.b.) büyük dil modellerine bağlanarak anlık rapor ihtiyaçları ile veri analizi ve içgörülerin alınabildiği platformun oluşturulması/kullanılması çalışmasıdır. Seçili use case ler için geliştirilecektir. Malzeme, müşteri, ürün ağacı, iş planı, gibi veri yapılarındaki farklı alanlardaki bilgileri analiz ederek veri anomali tespitleri yapabilmek,  Ürün satış performansları, şirket ve bayilerimizdeki stok durumlarını analiz ederek ürünler için planlama ve envanter stratejilerini belirleyebilir öneriler sunmak için model geliştirilmesi planlanmaktadır.</t>
+  </si>
+  <si>
     <t>Stok, mal hareket, bayi stoğu, bayi satışı ve malzeme ana ver,ye ilişkin veri setleri hazırlanarak paylaşılmıştır.​
 POC için soru seti hazırlandı ve paylaşıldı.​
 Soru seti için hazırlanan modeller tedarikçi tarafından paylaşıldı ve Kale ekipleri ile birlikte değerlendirildi.​</t>
@@ -1702,29 +1702,36 @@
 Yapay zeka ajanları kullanımı için detaylı kullanım durumlarının oluşturulması.​</t>
   </si>
   <si>
+    <t>TZ Süreçlerinde AI Kullanımı</t>
+  </si>
+  <si>
+    <t>Genel AI Kullanım Fonksiyonları Oluşturulması</t>
+  </si>
+  <si>
+    <t>KS2026-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bu proje TZ süreçlerinde yapay zeka kullanımın yaklaşımını tanımlayan genel projeyi ifade etmektedir.  Veri analitiği dışında yapay zekanın kullanımına yönelik iki yaklaşım benimsenmiştir. İlki iş verilerinin büyük dil modellerine bağlanması ile bir ara yüz dahilinde hızlı raporlama ve içgörülerin alınmasıdır. Diğer ise kullanım durumu bazında yapay zeka ajanlarının iş süreçlerinde kullanılması ve çözümler oluşturulmasıdır. </t>
+  </si>
+  <si>
     <t>Her iki yaklaşım için örnek kullanım durumları belirlendi.​
 İş verilerinin büyük dil modeline bağlanması konusu için bir şirket ile gizlilik sözleşmesi yapıldı.​
 POC için çalışmalar devam ediyor.​</t>
   </si>
   <si>
+    <t>Genel Veri Analitiği Çalışmaları</t>
+  </si>
+  <si>
+    <t>KS2026-64</t>
+  </si>
+  <si>
+    <t>Bu proje kapsamında, Kaleseramik üretim ve yönetim ekosisteminde oluşan büyük hacimli operasyonel verilerin ileri veri analitiği, makine öğrenmesi ve yapay zekâ yöntemleriyle analiz edilmesi hedeflenmektedir.
+Amaç; mevcut verilerden öngörü üreten, karar destek sağlayan ve operasyonel verimlilik yaratan veri odaklı kullanım durumlarını sistematik olarak keşfetmek, önceliklendirmek ve iş değerine dönüştürmektir.</t>
+  </si>
+  <si>
     <t>Karar alma süreçleri sezgisel yaklaşımdan veri ve öngörü temelli yönetime taşınacak,​
 Dijital dönüşüm yol haritasındaki AI/ML ve dijital ikiz projeleri için ölçeklenebilir analitik bir temel oluşturulacak,​
 Üretim, kalite, bakım ve enerji ekiplerinin aynı veri dili üzerinden konuşabildiği ortak bir analitik çerçeve oluşturulacaktır.​</t>
-  </si>
-  <si>
-    <t>Finans PowerBI Dashboard Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>Envanter Yön. AI Kullanım Fonk. Oluşturulması</t>
-  </si>
-  <si>
-    <t>Kurumsal veri kaynaklarının (SAP, BW, v.b.) büyük dil modellerine bağlanarak anlık rapor ihtiyaçları ile veri analizi ve içgörülerin alınabildiği platformun oluşturulması/kullanılması çalışmasıdır. Seçili use case ler için geliştirilecektir. Malzeme, müşteri, ürün ağacı, iş planı, gibi veri yapılarındaki farklı alanlardaki bilgileri analiz ederek veri anomali tespitleri yapabilmek,  Ürün satış performansları, şirket ve bayilerimizdeki stok durumlarını analiz ederek ürünler için planlama ve envanter stratejilerini belirleyebilir öneriler sunmak için model geliştirilmesi planlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Genel AI Kullanım Fonksiyonları Oluşturulması</t>
-  </si>
-  <si>
-    <t>Genel Veri Analitiği Çalışmaları</t>
   </si>
 </sst>
 </file>
@@ -1734,7 +1741,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1771,6 +1778,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1799,7 +1812,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1838,6 +1851,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2185,83 +2201,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
   <dimension ref="A1:M95"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="2.83984375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="12.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.3125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15.3671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.1015625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.05078125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.47265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="90.3125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="71.47265625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="81.05078125" style="4" customWidth="1"/>
-    <col min="14" max="14" width="8.83984375" style="11" customWidth="1"/>
-    <col min="15" max="16384" width="8.83984375" style="11"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.28515625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.42578125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="90.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="71.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="81" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="11" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="9" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" s="9" customFormat="1" ht="22.15" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>176</v>
+        <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>275</v>
+        <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>177</v>
+        <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>178</v>
+        <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>179</v>
+        <v>5</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>180</v>
+        <v>7</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>182</v>
+        <v>9</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>185</v>
+        <v>10</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>183</v>
+        <v>11</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="144">
       <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C2" s="11">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="12">
@@ -2271,36 +2287,36 @@
         <v>46203</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>281</v>
+        <v>18</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>282</v>
+        <v>19</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="57.6">
       <c r="A3" s="10">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C3" s="11">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="12">
@@ -2310,36 +2326,36 @@
         <v>46234</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>283</v>
+        <v>23</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="144">
       <c r="A4" s="10">
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C4" s="11">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>276</v>
+        <v>25</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="12">
@@ -2349,39 +2365,39 @@
         <v>46265</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28.9">
       <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C5" s="11">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>277</v>
+        <v>29</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>238</v>
+        <v>30</v>
       </c>
       <c r="H5" s="12">
         <v>46204</v>
@@ -2390,218 +2406,218 @@
         <v>46326</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>287</v>
+        <v>32</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="57.6">
       <c r="A6" s="10">
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C6" s="11">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>273</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>290</v>
+        <v>37</v>
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" ht="28.9">
       <c r="A7" s="10">
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C7" s="11">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>270</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>288</v>
+        <v>39</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>291</v>
+        <v>40</v>
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" ht="28.9">
       <c r="A8" s="10">
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C8" s="11">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>269</v>
+        <v>41</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>289</v>
+        <v>42</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>292</v>
+        <v>43</v>
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" ht="28.9">
       <c r="A9" s="10">
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>268</v>
+        <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>278</v>
+        <v>45</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
       <c r="J9" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>293</v>
+        <v>46</v>
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13" ht="28.9">
       <c r="A10" s="10">
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C10" s="11">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>268</v>
+        <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>279</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>237</v>
+        <v>48</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>294</v>
+        <v>49</v>
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13" ht="28.9">
       <c r="A11" s="10">
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C11" s="11">
         <v>1</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>272</v>
+        <v>50</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>280</v>
+        <v>51</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>239</v>
+        <v>52</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="3" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>295</v>
+        <v>53</v>
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" ht="144">
       <c r="A12" s="10">
         <v>1</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C12" s="10">
         <v>2</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>296</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="12">
@@ -2611,36 +2627,36 @@
         <v>45930</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>297</v>
+        <v>58</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>298</v>
+        <v>59</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="129.6">
       <c r="A13" s="10">
         <v>1</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C13" s="10">
         <v>2</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>301</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="12">
@@ -2650,34 +2666,34 @@
         <v>46022</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>299</v>
+        <v>62</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>300</v>
+        <v>63</v>
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" ht="72">
       <c r="A14" s="10">
         <v>1</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C14" s="10">
         <v>2</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="12">
@@ -2687,100 +2703,100 @@
         <v>46203</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>302</v>
+        <v>65</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>303</v>
+        <v>66</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="57.6">
       <c r="A15" s="10">
         <v>1</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C15" s="10">
         <v>2</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>305</v>
+        <v>68</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
       <c r="J15" s="5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" ht="43.15">
       <c r="A16" s="10">
         <v>1</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C16" s="10">
         <v>2</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>307</v>
+        <v>72</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>308</v>
+        <v>74</v>
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:13" ht="172.9">
       <c r="A17" s="10">
         <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C17" s="10">
         <v>3</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="12">
@@ -2790,34 +2806,34 @@
         <v>46112</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:13" ht="129.6">
       <c r="A18" s="10">
         <v>1</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C18" s="10">
         <v>3</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="12">
@@ -2827,36 +2843,36 @@
         <v>46203</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="86.45">
       <c r="A19" s="10">
         <v>1</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C19" s="10">
         <v>3</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>311</v>
+        <v>84</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="12">
@@ -2866,37 +2882,37 @@
         <v>46112</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>312</v>
+        <v>85</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>313</v>
+        <v>86</v>
       </c>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:13" ht="72">
       <c r="A20" s="10">
         <v>1</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C20" s="10">
         <v>3</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>265</v>
+        <v>87</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>314</v>
+        <v>88</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>233</v>
+        <v>89</v>
       </c>
       <c r="H20" s="12">
         <v>46023</v>
@@ -2905,39 +2921,39 @@
         <v>46234</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>315</v>
+        <v>90</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="57.6">
       <c r="A21" s="10">
         <v>1</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C21" s="10">
         <v>3</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>265</v>
+        <v>87</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>316</v>
+        <v>93</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>234</v>
+        <v>94</v>
       </c>
       <c r="H21" s="12">
         <v>46174</v>
@@ -2946,31 +2962,31 @@
         <v>46295</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>317</v>
+        <v>95</v>
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:13" ht="28.9">
       <c r="A22" s="10">
         <v>1</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C22" s="10">
         <v>3</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>265</v>
+        <v>87</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="12">
@@ -2980,34 +2996,34 @@
         <v>46295</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:13" ht="57.6">
       <c r="A23" s="10">
         <v>1</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C23" s="10">
         <v>3</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>265</v>
+        <v>87</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>319</v>
+        <v>98</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="H23" s="12">
         <v>46327</v>
@@ -3016,31 +3032,31 @@
         <v>46387</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>318</v>
+        <v>100</v>
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:13" ht="100.9">
       <c r="A24" s="10">
         <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C24" s="10">
         <v>4</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>320</v>
+        <v>103</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="12">
@@ -3050,36 +3066,36 @@
         <v>46112</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="28.9">
       <c r="A25" s="10">
         <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C25" s="10">
         <v>4</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="12">
@@ -3089,34 +3105,34 @@
         <v>46203</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>323</v>
+        <v>108</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="28.9">
       <c r="A26" s="10">
         <v>1</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C26" s="10">
         <v>4</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>324</v>
+        <v>110</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="12">
@@ -3126,34 +3142,34 @@
         <v>46265</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>325</v>
+        <v>111</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="144">
       <c r="A27" s="10">
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C27" s="10">
         <v>1</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>258</v>
+        <v>115</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="12">
@@ -3163,33 +3179,33 @@
         <v>46112</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>327</v>
+        <v>117</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="115.15">
       <c r="A28" s="10">
         <v>2</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>258</v>
+        <v>115</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="12">
@@ -3199,100 +3215,100 @@
         <v>46203</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="28.9">
       <c r="A29" s="10">
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>326</v>
+        <v>123</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>227</v>
+        <v>99</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>331</v>
+        <v>124</v>
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:13" ht="28.9">
       <c r="A30" s="10">
         <v>2</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C30" s="10">
         <v>1</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>330</v>
+        <v>125</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>228</v>
+        <v>126</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
       <c r="J30" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>333</v>
+        <v>127</v>
       </c>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:13" ht="125.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:13" ht="125.1" customHeight="1">
       <c r="A31" s="10">
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>229</v>
+        <v>129</v>
       </c>
       <c r="H31" s="12">
         <v>46174</v>
@@ -3301,36 +3317,36 @@
         <v>46356</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>332</v>
+        <v>130</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="115.15">
       <c r="A32" s="10">
         <v>2</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>334</v>
+        <v>133</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="H32" s="12">
         <v>45839</v>
@@ -3339,68 +3355,68 @@
         <v>46112</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="43.15">
       <c r="A33" s="10">
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C33" s="10">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>335</v>
+        <v>137</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>231</v>
+        <v>138</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>336</v>
+        <v>139</v>
       </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:13" ht="316.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:13" ht="316.89999999999998">
       <c r="A34" s="10">
         <v>2</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C34" s="10">
         <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>232</v>
+        <v>141</v>
       </c>
       <c r="H34" s="12">
         <v>46023</v>
@@ -3409,33 +3425,33 @@
         <v>46203</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>9</v>
+        <v>142</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="132.30000000000001" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="132.4" customHeight="1">
       <c r="A35" s="10">
         <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C35" s="10">
         <v>2</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="12">
@@ -3445,33 +3461,33 @@
         <v>46295</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="113.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="113.1" customHeight="1">
       <c r="A36" s="10">
         <v>2</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C36" s="10">
         <v>2</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="12">
@@ -3481,33 +3497,33 @@
         <v>46142</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="172.9">
       <c r="A37" s="10">
         <v>2</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C37" s="10">
         <v>3</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>259</v>
+        <v>151</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>337</v>
+        <v>152</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="12">
@@ -3517,33 +3533,33 @@
         <v>46265</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>83</v>
+        <v>153</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="260.25">
       <c r="A38" s="10">
         <v>3</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="C38" s="10">
         <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>255</v>
+        <v>157</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>338</v>
+        <v>158</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="12">
@@ -3553,36 +3569,36 @@
         <v>46203</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>160</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="174">
       <c r="A39" s="10">
         <v>3</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="C39" s="10">
         <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>256</v>
+        <v>163</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="12">
@@ -3592,36 +3608,36 @@
         <v>46173</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>89</v>
+        <v>165</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>90</v>
+        <v>166</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="43.15">
       <c r="A40" s="10">
         <v>3</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="C40" s="10">
         <v>2</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>256</v>
+        <v>163</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="12">
@@ -3631,36 +3647,36 @@
         <v>46173</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="86.45">
       <c r="A41" s="10">
         <v>3</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="C41" s="10">
         <v>2</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>256</v>
+        <v>163</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>339</v>
+        <v>172</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="12">
@@ -3670,39 +3686,39 @@
         <v>46022</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>95</v>
+        <v>173</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="101.25">
       <c r="A42" s="10">
         <v>3</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>256</v>
+        <v>163</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="H42" s="12">
         <v>45778</v>
@@ -3711,75 +3727,75 @@
         <v>46203</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>49</v>
+        <v>178</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="144.75">
       <c r="A43" s="10">
         <v>3</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="C43" s="10">
         <v>3</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="12">
         <v>45992</v>
       </c>
       <c r="I43" s="12">
-        <v>46142</v>
+        <v>46170</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="129.6">
       <c r="A44" s="10">
         <v>4</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C44" s="10">
         <v>1</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>341</v>
+        <v>190</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="12">
@@ -3789,36 +3805,36 @@
         <v>46234</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="57.6">
       <c r="A45" s="10">
         <v>4</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C45" s="10">
         <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>340</v>
+        <v>194</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="12">
@@ -3828,36 +3844,36 @@
         <v>46265</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="57.6">
       <c r="A46" s="10">
         <v>4</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C46" s="10">
         <v>1</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="12">
@@ -3867,36 +3883,36 @@
         <v>46173</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="129.6">
       <c r="A47" s="10">
         <v>4</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C47" s="10">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>249</v>
+        <v>189</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="12">
@@ -3906,39 +3922,39 @@
         <v>46265</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="57.6">
       <c r="A48" s="10">
         <v>4</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>343</v>
+        <v>207</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="H48" s="12">
         <v>45962</v>
@@ -3947,36 +3963,36 @@
         <v>46356</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>123</v>
+        <v>210</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="86.45">
       <c r="A49" s="10">
         <v>4</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C49" s="10">
         <v>1</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>344</v>
+        <v>213</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="12">
@@ -3986,36 +4002,36 @@
         <v>46265</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="28.9">
       <c r="A50" s="10">
         <v>4</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C50" s="10">
         <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="12">
@@ -4025,36 +4041,36 @@
         <v>46295</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="86.45">
       <c r="A51" s="10">
         <v>4</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C51" s="10">
         <v>2</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>345</v>
+        <v>223</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="12">
@@ -4064,33 +4080,33 @@
         <v>46203</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>12</v>
+        <v>224</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="100.9">
       <c r="A52" s="10">
         <v>4</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C52" s="10">
         <v>2</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>133</v>
+        <v>227</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="12">
@@ -4100,36 +4116,36 @@
         <v>46265</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>13</v>
+        <v>228</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="57.6">
       <c r="A53" s="10">
         <v>4</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C53" s="10">
         <v>2</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>346</v>
+        <v>231</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="12">
@@ -4139,36 +4155,36 @@
         <v>46387</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="86.45">
       <c r="A54" s="10">
         <v>4</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C54" s="10">
         <v>2</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>342</v>
+        <v>236</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="12">
@@ -4178,36 +4194,36 @@
         <v>46326</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>14</v>
+        <v>237</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>120</v>
+        <v>238</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="115.15">
       <c r="A55" s="10">
         <v>4</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C55" s="10">
         <v>2</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="12">
@@ -4217,36 +4233,36 @@
         <v>46387</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>141</v>
+        <v>242</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="86.45">
       <c r="A56" s="10">
         <v>4</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="C56" s="10">
         <v>3</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>347</v>
+        <v>246</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="12">
@@ -4256,39 +4272,39 @@
         <v>46265</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>143</v>
+        <v>248</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="86.45">
       <c r="A57" s="10">
         <v>5</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C57" s="10">
         <v>1</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>350</v>
+        <v>253</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="H57" s="12">
         <v>45931</v>
@@ -4297,39 +4313,39 @@
         <v>46203</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>145</v>
+        <v>255</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>348</v>
+        <v>256</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="57.6">
       <c r="A58" s="10">
         <v>5</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C58" s="10">
         <v>1</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>351</v>
+        <v>258</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="H58" s="12">
         <v>45962</v>
@@ -4338,39 +4354,39 @@
         <v>46387</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>146</v>
+        <v>259</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>352</v>
+        <v>260</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="115.15">
       <c r="A59" s="10">
         <v>5</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C59" s="10">
         <v>1</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E59" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>354</v>
-      </c>
       <c r="G59" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="H59" s="12">
         <v>45931</v>
@@ -4379,39 +4395,39 @@
         <v>46203</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>147</v>
+        <v>263</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>355</v>
+        <v>264</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="86.45">
       <c r="A60" s="10">
         <v>5</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C60" s="10">
         <v>1</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>360</v>
+        <v>266</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="H60" s="12">
         <v>45931</v>
@@ -4420,36 +4436,36 @@
         <v>46295</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>148</v>
+        <v>267</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>358</v>
+        <v>268</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="72">
       <c r="A61" s="10">
         <v>5</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C61" s="10">
         <v>2</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>31</v>
+        <v>270</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>32</v>
+        <v>272</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="12">
@@ -4459,36 +4475,36 @@
         <v>46387</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>149</v>
+        <v>273</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>361</v>
+        <v>274</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="115.15">
       <c r="A62" s="10">
         <v>5</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C62" s="10">
         <v>2</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>31</v>
+        <v>270</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>363</v>
+        <v>276</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="12">
@@ -4498,31 +4514,31 @@
         <v>46387</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>150</v>
+        <v>277</v>
       </c>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:13" ht="72">
       <c r="A63" s="10">
         <v>5</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C63" s="10">
         <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>33</v>
+        <v>278</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="12">
@@ -4532,36 +4548,36 @@
         <v>46356</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>10</v>
+        <v>281</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>364</v>
+        <v>282</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="28.9">
       <c r="A64" s="10">
         <v>5</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C64" s="10">
         <v>3</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>33</v>
+        <v>278</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>151</v>
+        <v>284</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="12">
@@ -4571,36 +4587,36 @@
         <v>46203</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>152</v>
+        <v>285</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>366</v>
+        <v>286</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="43.15">
       <c r="A65" s="10">
         <v>5</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C65" s="10">
         <v>4</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>190</v>
+        <v>289</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="12">
@@ -4610,36 +4626,36 @@
         <v>46326</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>156</v>
+        <v>290</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="72">
       <c r="A66" s="10">
         <v>5</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C66" s="10">
         <v>4</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>374</v>
+        <v>293</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="12">
@@ -4649,36 +4665,36 @@
         <v>46356</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>153</v>
+        <v>294</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>370</v>
+        <v>295</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="57.6">
       <c r="A67" s="10">
         <v>5</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C67" s="10">
         <v>4</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>189</v>
+        <v>297</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="12">
@@ -4688,36 +4704,36 @@
         <v>46234</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>154</v>
+        <v>298</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>372</v>
+        <v>299</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="43.15">
       <c r="A68" s="10">
         <v>5</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C68" s="10">
         <v>4</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>35</v>
+        <v>301</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="12">
@@ -4727,36 +4743,36 @@
         <v>46112</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>155</v>
+        <v>302</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="43.15">
       <c r="A69" s="10">
         <v>6</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C69" s="10">
         <v>1</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>158</v>
+        <v>306</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>376</v>
+        <v>307</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>218</v>
+        <v>308</v>
       </c>
       <c r="H69" s="12">
         <v>45778</v>
@@ -4765,34 +4781,34 @@
         <v>45869</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="M69" s="1"/>
     </row>
-    <row r="70" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:13" ht="43.15">
       <c r="A70" s="10">
         <v>6</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C70" s="10">
         <v>1</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>158</v>
+        <v>306</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>378</v>
+        <v>310</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>218</v>
+        <v>308</v>
       </c>
       <c r="H70" s="12">
         <v>45931</v>
@@ -4801,34 +4817,34 @@
         <v>46053</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="M70" s="1"/>
     </row>
-    <row r="71" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:13" ht="129.6">
       <c r="A71" s="10">
         <v>6</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C71" s="10">
         <v>1</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>158</v>
+        <v>306</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>377</v>
+        <v>311</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>218</v>
+        <v>308</v>
       </c>
       <c r="H71" s="12">
         <v>45931</v>
@@ -4837,37 +4853,37 @@
         <v>46112</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="M71" s="1"/>
     </row>
-    <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:13" ht="72">
       <c r="A72" s="10">
         <v>6</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>158</v>
+        <v>306</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>218</v>
+        <v>308</v>
       </c>
       <c r="H72" s="12">
         <v>46023</v>
@@ -4876,36 +4892,36 @@
         <v>46387</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="72">
       <c r="A73" s="10">
         <v>6</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C73" s="10">
         <v>1</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>158</v>
+        <v>306</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>245</v>
+        <v>316</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>218</v>
+        <v>308</v>
       </c>
       <c r="H73" s="12">
         <v>46023</v>
@@ -4914,126 +4930,126 @@
         <v>46387</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="28.9">
       <c r="A74" s="10">
         <v>6</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C74" s="10">
         <v>1</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>158</v>
+        <v>306</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>379</v>
+        <v>317</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>219</v>
+        <v>318</v>
       </c>
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
       <c r="J74" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K74" s="5"/>
       <c r="L74" s="4"/>
     </row>
-    <row r="75" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:13" ht="28.9">
       <c r="A75" s="10">
         <v>6</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C75" s="10">
         <v>1</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>161</v>
+        <v>319</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>41</v>
+        <v>320</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>219</v>
+        <v>318</v>
       </c>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K75" s="5"/>
       <c r="L75" s="4"/>
     </row>
-    <row r="76" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:13" ht="28.9">
       <c r="A76" s="10">
         <v>6</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C76" s="10">
         <v>1</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>6</v>
+        <v>305</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>160</v>
+        <v>321</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>201</v>
+        <v>322</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>220</v>
+        <v>323</v>
       </c>
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
       <c r="J76" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K76" s="5"/>
       <c r="L76" s="4"/>
     </row>
-    <row r="77" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:13" ht="115.15">
       <c r="A77" s="10">
         <v>6</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C77" s="10">
         <v>2</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>46</v>
+        <v>325</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>205</v>
+        <v>326</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>221</v>
+        <v>327</v>
       </c>
       <c r="H77" s="12">
         <v>46204</v>
@@ -5042,39 +5058,39 @@
         <v>46387</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>170</v>
+        <v>328</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="129.6">
       <c r="A78" s="10">
         <v>6</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C78" s="10">
         <v>2</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>240</v>
+        <v>331</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>45</v>
+        <v>332</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="H78" s="12">
         <v>46023</v>
@@ -5083,39 +5099,39 @@
         <v>46142</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>167</v>
+        <v>334</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>382</v>
+        <v>335</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="86.45">
       <c r="A79" s="10">
         <v>6</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C79" s="10">
         <v>2</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>240</v>
+        <v>331</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>203</v>
+        <v>337</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>223</v>
+        <v>338</v>
       </c>
       <c r="H79" s="12">
         <v>45992</v>
@@ -5124,39 +5140,39 @@
         <v>46142</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>168</v>
+        <v>339</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>384</v>
+        <v>340</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="57.6">
       <c r="A80" s="10">
         <v>6</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C80" s="10">
         <v>2</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>243</v>
+        <v>342</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>204</v>
+        <v>343</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>222</v>
+        <v>344</v>
       </c>
       <c r="H80" s="12">
         <v>46023</v>
@@ -5165,39 +5181,39 @@
         <v>46387</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>169</v>
+        <v>345</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>386</v>
+        <v>346</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="158.44999999999999">
       <c r="A81" s="10">
         <v>6</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C81" s="10">
         <v>2</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>213</v>
+        <v>348</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>171</v>
+        <v>349</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>224</v>
+        <v>350</v>
       </c>
       <c r="H81" s="12">
         <v>46023</v>
@@ -5206,39 +5222,39 @@
         <v>46357</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>16</v>
+        <v>351</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>388</v>
+        <v>352</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="100.9">
       <c r="A82" s="10">
         <v>6</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>241</v>
+        <v>354</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>191</v>
+        <v>355</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="H82" s="12">
         <v>45931</v>
@@ -5247,39 +5263,39 @@
         <v>46053</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>162</v>
+        <v>356</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="115.15">
       <c r="A83" s="10">
         <v>6</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C83" s="10">
         <v>2</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>241</v>
+        <v>354</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>202</v>
+        <v>359</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="H83" s="12">
         <v>46023</v>
@@ -5288,39 +5304,39 @@
         <v>46112</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>163</v>
+        <v>360</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="158.44999999999999">
       <c r="A84" s="10">
         <v>6</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C84" s="10">
         <v>2</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>241</v>
+        <v>354</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>42</v>
+        <v>363</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="H84" s="12">
         <v>46023</v>
@@ -5329,39 +5345,39 @@
         <v>46203</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>164</v>
+        <v>364</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="57.6">
       <c r="A85" s="10">
         <v>6</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C85" s="10">
         <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>241</v>
+        <v>354</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>43</v>
+        <v>367</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="H85" s="12">
         <v>46174</v>
@@ -5370,39 +5386,39 @@
         <v>46295</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>165</v>
+        <v>368</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="86.45">
       <c r="A86" s="10">
         <v>6</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C86" s="10">
         <v>2</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>241</v>
+        <v>354</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>44</v>
+        <v>371</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="H86" s="12">
         <v>46023</v>
@@ -5411,36 +5427,36 @@
         <v>46142</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>166</v>
+        <v>372</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="86.45">
       <c r="A87" s="10">
         <v>6</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C87" s="10">
         <v>3</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>8</v>
+        <v>375</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>209</v>
+        <v>376</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>192</v>
+        <v>377</v>
       </c>
       <c r="G87" s="3"/>
       <c r="H87" s="12">
@@ -5450,36 +5466,36 @@
         <v>46157</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>17</v>
+        <v>378</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="43.15">
       <c r="A88" s="10">
         <v>6</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C88" s="10">
         <v>3</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>8</v>
+        <v>375</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>209</v>
+        <v>376</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>193</v>
+        <v>381</v>
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="12">
@@ -5489,37 +5505,37 @@
         <v>46387</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>18</v>
+        <v>382</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="100.9">
       <c r="A89" s="10">
         <v>6</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C89" s="10">
         <v>4</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>47</v>
+        <v>384</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>48</v>
+        <v>385</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>196</v>
+        <v>386</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>217</v>
+        <v>387</v>
       </c>
       <c r="H89" s="12">
         <v>46023</v>
@@ -5528,36 +5544,36 @@
         <v>46357</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>174</v>
+        <v>388</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="72">
       <c r="A90" s="10">
         <v>6</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C90" s="10">
         <v>4</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>47</v>
+        <v>384</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>206</v>
+        <v>392</v>
       </c>
       <c r="G90" s="3"/>
       <c r="H90" s="12">
@@ -5567,36 +5583,36 @@
         <v>46082</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>173</v>
+        <v>393</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="57.6">
       <c r="A91" s="10">
         <v>6</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C91" s="10">
         <v>4</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>47</v>
+        <v>384</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="12">
@@ -5606,36 +5622,36 @@
         <v>46112</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>172</v>
+        <v>397</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="129.6">
       <c r="A92" s="10">
         <v>6</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C92" s="10">
         <v>4</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>47</v>
+        <v>384</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>194</v>
+        <v>391</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>195</v>
+        <v>400</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="12">
@@ -5645,39 +5661,39 @@
         <v>46112</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>19</v>
+        <v>401</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="72">
       <c r="A93" s="10">
         <v>6</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C93" s="10">
         <v>5</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>210</v>
+        <v>404</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>242</v>
+        <v>405</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>215</v>
+        <v>407</v>
       </c>
       <c r="H93" s="12">
         <v>46023</v>
@@ -5686,39 +5702,39 @@
         <v>46295</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="57.6">
       <c r="A94" s="10">
         <v>6</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C94" s="10">
         <v>5</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>210</v>
+        <v>404</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>211</v>
+        <v>411</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>216</v>
+        <v>413</v>
       </c>
       <c r="H94" s="12">
         <v>46023</v>
@@ -5727,39 +5743,39 @@
         <v>46266</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>20</v>
+        <v>414</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="72">
       <c r="A95" s="10">
         <v>6</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="C95" s="10">
         <v>5</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>210</v>
+        <v>404</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>241</v>
+        <v>354</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>214</v>
+        <v>417</v>
       </c>
       <c r="H95" s="12">
         <v>46023</v>
@@ -5768,14 +5784,14 @@
         <v>46357</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>175</v>
+        <v>418</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emretasci\antigravity\scm-project-portal\dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/TZY Gelişim Planı/Gelişim Planı/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{257BABEA-FDF5-43DC-8E2D-61D4597C19B1}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FBE20DC-4C54-4524-8BDD-570D5A33A3B3}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects Data" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="423">
   <si>
     <t>department order</t>
   </si>
@@ -99,22 +99,26 @@
     <t>Ürün ana veri yapısının incelenerek geliştirme/iyileştirme alanları ile hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Talep tahmin veri analitiği, SKU rasyonalizasyonu,  görünürlük, planlama stratejileri gibi pek çok çalışma için ürün ana veri yapısının iyileştirilmesi ihtiyacı ön koşul olarak bulunmaktadır.</t>
   </si>
   <si>
-    <t>Ana ebat tanımlarındaki eksikliklerin giderilmesi
-Faturalama için ambalaj tipi tanımlarının yapılması
-Piyasa kanalı tanımlarının revizyonu
-Üretim kontrol notu tanımlarındaki eksikliklerin giderilmesi
-Ürün hiyerarşisi uyumsuzluklarının tespiti ve düzeltilmesi
-Ürün hiyerarşisi tanımı yanlış olan kodların tespiti ve düzeltilmesi
-Gömme rezervuar ürün grubunda set kodlarının ayrıştırılması
-UP kodları için Marka bilgilerinin düzeltilmesi ve tamamlanması
-Orijin kodu bilgisinin düzenlenmesi ile ilgili çalışmaların başlatılması
-Ürün karakteristiklerinde yer alan kalite tanımı bilgilerinin düzenlenmesi</t>
-  </si>
-  <si>
-    <t>Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-Vitrifiye
-Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-Mobilya
-Ürün hiyerarşisi bazında ürün bilgilerinin kontrolü-SKM 
-Farklı kalitedeki ürünlerin stok kodları arasında bağlantı oluşturulması</t>
+    <t>Ürün bilgilerinin ve karakteristik tanımlarının düzenli takibi ve kontrolü için Ürün Dashboard çalışması tamamlanmıştır.
+Haftalık toplantılar ile ürün bilgilerindeki eksiklikler tespit edilmekte ve çalışmalar yapılmaktadır.
+Bölüm KPI'larına Ürün Ana Veri İyileştirme Endeksi eklenmiştir.
+Faturalama için ambalaj tipi tanımları takip edilmekte ve eksiklikler giderilmektedir.
+Piyasa kanalı tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+Üretim kontrol notu takip edilmekte ve eksiklikler giderilmektedir.
+Ürün hiyerarşisi uyumsuzluklarının tespit edilmekte ve düzeltilmektedir.
+Ürün hiyerarşisi tanımı yanlış olan kodların tespit edilmekte ve düzeltilmektedir.
+Gömme rezervuar ürün grubunda set kodlarının ayrıştırılmıştır.
+Marka tanımları takip edilmekte ve eksiklikler giderilmektedir.
+Kalite tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.</t>
+  </si>
+  <si>
+    <t>Orijin kodu bilgisinin düzenlenmesi ile ilgili çalışmaların başlatılması
+Farklı kalitedeki ürünlerin stok kodları arasında bağlantı oluşturulması
+SKM CTDA Eksikliklerinin Giderilmesi
+Vitrifiye Renk Tanımı Eksikliklerinin Giderilmesi
+SKM Ebat Eksikliklerinin Giderilmesi ve Bilgi Kontrolü
+SKM Kısa Kod Eksikliklerinin Giderilmesi ve Bilgi Kontrolü
+Planlama stratejilerinin tanımlarının revizyonu yapılmıştır. Kod bazlı tanımlamaların yapılması</t>
   </si>
   <si>
     <t>Ürün Ambalaj Bilgilerinin Tanımlanması</t>
@@ -284,10 +288,11 @@
     <t>Tahmin modelinin oluşturulmasına yönelik kavramsal çalışmalar başlatılmıştır.
 Müşteri sipariş verilerine yönelik veri seti oluşturulmuştur.
 In-house talep tahmin çalışması başlatılmıştır.
-Model ve uygulamanın oluşturulmasına yönelik danışman firma ile proje takvimi ve adımlarının belirlenmesi devam etmektedir.</t>
-  </si>
-  <si>
-    <t>Modele beslenecek dış veriler belirlenecektir.
+Model ve uygulamanın oluşturulmasına yönelik danışman firma ile proje takvimi ve adımlarının belirlenmesi devam etmektedir.
+Modele beslenecek dış veriler belirlenmiştir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 Veri setinin analizi ve yeni tahmin modelinin tasarımı oluşturulacaktır. 
 Modelin eğitimi tamamlanarak sonuçlar değerlendirilecektir.
 Uygulama testleri ile uygulama devreye alınacaktır.</t>
@@ -368,6 +373,9 @@
 Çözüm ve uygulama Kale Masters Doğrusal Programlama eğitimi kapsamında geliştirilmiştir.</t>
   </si>
   <si>
+    <t>Optimizasyon için gerekli veriler oluşturularak POC çalışması yürütülecektir.</t>
+  </si>
+  <si>
     <t>S&amp;OP Tool</t>
   </si>
   <si>
@@ -384,10 +392,13 @@
 Yazılım ve KS ekibi kavramsal tasarım üzerinde mutabakat sağlamıştır.
 İş akış dokümanı oluşturulmuştur ve IT ekibine iletilmiştir.
 IT tarafından platform kararı verilmiştir.
-Proje planı ve backloglar oluşturulmuştur. (agile proje yönetimi)</t>
-  </si>
-  <si>
-    <t>Proje takvimine uygun olarak aksiyon takibi ve test çalışmaları yürütülecektir.</t>
+Proje planı ve backloglar oluşturulmuştur. (agile proje yönetimi)
+Sprint-1 kapsamında sistemsel düzenlemeler yapılmıştır. 
+Sprint-2 kapsamında senaryo oluşturma, excel ile veri yükleme, verilerin raporlanması  ve yetki düzenlemeleri  yapılmıştır.</t>
+  </si>
+  <si>
+    <t>Proje takvimine uygun olarak aksiyon takibi ve test çalışmaları yürütülecektir.
+Sprint-3 kapsamında DFU bazlı revizyonların yapılması, katsayı ile revizyonların yapılması, iş akışının durumunun gösterilmesi ve kullanıcı bazlı testler yapılacaktır.</t>
   </si>
   <si>
     <t>S&amp;OP Finansallaştırma Uyg. Geliştirilmesi</t>
@@ -486,14 +497,14 @@
     <t>Bu proje kapsamında; tanımlanan Sales &amp; Operations Execution (S&amp;OE) süreci, belirlenen kapsam, roller, veri setleri ve karar kuralları doğrultusunda operasyonel olarak devreye alınacaktır. Amaç; onaylanmış S&amp;OP ve ana üretim planları çerçevesinde, kısa vadede (günlük / haftalık) oluşan talep, üretim, stok ve sevkiyat sapmalarını standart bir toplantı ritmi ve veri seti ile yönetmek, alınan kararların sahada fiilen uygulanmasını ve takibini sağlamaktır.</t>
   </si>
   <si>
-    <t>Pilot kapsamın netleştirilmesi
-S&amp;OE Toplantı Ritminin başlatılması (1 Mart itibariyle başlatılacaktır)
-Standart veri seti ile operasyonun yürütülmesi
-Önceliklendirme ve karar kurallarının uygulanması
-Aksiyon Takibi ve Disiplinin Sağlanması
-Eskalasyon Mekanizmasının İşletilmesi
-KPI takibi ve ilk etki ölçümü
-Geri Bildirim ve iyileştirme</t>
+    <t>S&amp;OE Toplantı Ritminin başlatılması (1 Nisan itibariyle başlatılmıştır.)
+Pilot kapsam netleştirildi.
+Standart veri seti ile operasyonun yürütülmesi sağlandı.
+Önceliklendirme ve karar kurallarının uygulanmasına başlandı.
+Eskalasyon Mekanizması işletilmektedir.
+KPI takibi ve ilk etki ölçümü ( Üretim toplantısında takip edilmektedir.)
+- Geri Bildirim ve iyileştirmelerin alınması devam etmektedir.
+- Toplantı saati ve günü konusunda değişiklikler olabilir.</t>
   </si>
   <si>
     <t>Entegre Planlama Yapısı</t>
@@ -524,12 +535,13 @@
 </t>
   </si>
   <si>
-    <t>Siparişler satış ekibi tarafından sisteme girilmektedir ancak öncelik kriterleri net tanımlı değildir.
-“En çok ısrar eden müşteri” gibi subjektif kriterler ön plana çıkmakta, bu da adaletsizliğe yol açmaktadır.
-Kritik müşteriler ve yüksek kârlı siparişler bazen geri planda kalabilmektedir.
-Üretim hattında kapasite kullanımı, bazen düşük önemdeki siparişlere ayrılarak kârlılık ve müşteri memnuniyeti potansiyeli zayıflamaktadır.
-SAP sisteminde şirkete özel oluşturulmuş saklama, teyit sistemi gibi yapılar kullanılmaktadır.
-Mevcut Durum Analizi: Son 6-12 aylık sipariş ve üretim verilerinin incelenmesi. Müşteri tipolojisi, sipariş kârlılık dağılımı ve teslimat performansı analizi.
+    <t>- Siparişler satış ekibi tarafından sisteme girilmektedir ancak öncelik kriterleri net tanımlı değildir.
+- “En çok ısrar eden müşteri” gibi subjektif kriterler ön plana çıkmakta, bu da adaletsizliğe yol açmaktadır.
+- Kritik müşteriler ve yüksek kârlı siparişler bazen geri planda kalabilmektedir.
+- Üretim hattında kapasite kullanımı, bazen düşük önemdeki siparişlere ayrılarak kârlılık ve müşteri memnuniyeti potansiyeli zayıflamaktadır.
+- SAP sisteminde şirkete özel oluşturulmuş saklama, teyit sistemi gibi yapılar kullanılmaktadır.
+Mevcut Durum Analizi: Son 6-12 aylık sipariş ve üretim verilerinin incelenmesi. 
+Müşteri tipolojisi, sipariş kârlılık dağılımı ve teslimat performansı analizi.
 Önceliklendirme Kriterlerinin Belirlenmesi: İstek tarihi (zaman faktörü), Müşteri önem derecesi (A-B-C müşteri sınıflaması), Sipariş toplam brüt kârı, (Opsiyonel) Stratejik müşteri/ürün önceliği
 Sıralama Algoritmasının Geliştirilmesi: Kriterlere ağırlık puanları atanması, (ör. %40 istek tarihi, %30 müşteri önemi, %30 brüt kâr), ERP üzerinde siparişlerin otomatik skorlanması.
 Pilot Çalışma: Belirli bir ürün hattında yeni sistemin test edilmesi., Sonuçların müşteri memnuniyeti ve kârlılık açısından ölçülmesi.
@@ -548,11 +560,11 @@
     <t>Tüm ürün gruplarında beklenen müşteri hizmet seviyelerini sağlamak ve stok seviyelerini optimize etmek  amacıyla ürünlerin üretim periyot ve stok seviyelerinin belirlenmesi ve bu kurallara uygun şekilde yönetilmesi yaklaşımıdır. Tanımlı hizmet seviyelerini sağlamak, üretim verimliliğini artırmak (setup maliyetleri) ve doğru bir stok yönetimi yapabilmek için planlama sürecinde, planlama stratejileri yapısının devreye alınması bu proje kapsamında sağlanacaktır.</t>
   </si>
   <si>
-    <t>SKM, Banyo, Vitrifiye ürün grupları için gerekli veriler hazırlanarak Planlama Stratejileri belirlenmiştir.
-Belirlenen stratejiler pazarlama ve satış ile paylaşılmıştır.
-Stok seviyelerinin takibi yapılarak azaltılmasına yönelik hedeflerin belirlenmesi ve uygulamaya alınması
-MTO-APB ürün gruplarında yer alan özel müşteriler için yapılan ESM altı üretimlerde yaklaşımın nasıl olacağına karar verilecek. 
-Pazarlama ve Satış ile mutabık kalındıktan sonra sistemsel tanımlamaların yapılması,</t>
+    <t>- SKM, Banyo, Vitrifiye ürün grupları için gerekli veriler hazırlanarak Planlama Stratejileri belirlenmiştir.
+- Belirlenen stratejiler pazarlama ve satış ile paylaşılmıştır.
+- Stok seviyelerinin takibi yapılarak azaltılmasına yönelik hedeflerin belirlenmesi ve uygulamaya alınması
+MTO-APB ürün gruplarında yer alan özel müşteriler için yapılan ESM altı üretimlerde yaklaşımın nasıl olacağına karar verilmiştir. 
+- Pazarlama ve Satış ile mutabık kalındıktan sonra sistemsel tanımlamalar yapıldı.</t>
   </si>
   <si>
     <t>Planlama Str. Güncelleme Yazılımı Geliştirilmesi</t>
@@ -570,32 +582,34 @@
     <t>KS2026-13</t>
   </si>
   <si>
-    <t>Bu çalışma ile planlama sürecine şirket içindeki bilgilere ilave olarak, bayi ağımızdaki KS ürünleri satış ve stok bilgilerinin de eklenerek planlama sürecinin etkinliğinin artırılması hedeflenmektedir.</t>
-  </si>
-  <si>
-    <t>Mevcut durumda KBY verileri üretim planlama ve stok yönetimine bir girdi sağlamamaktadır.
-Nihai pazar talepleri belirlenememektedir, talep görünürlüğü düşük seviyededir.
-Satış siparişleri baz alınarak üretim yapıldığında, bayi deposunda zaten stok olsa bile fabrika tekrar üretim yapmaktadır. Bu durum talep şişirmesine (artificial demand) yol açmaktadır. Gerçekte tüketim düşükken üretimin yüksek planlanmasına neden olmaktadır.
-Fabrika ve bayi depolarında çifte stok oluşmaktadır bu da finansman yükü, yüksek stok taşıma maliyeti ve olası değer kayıplarına (moda/renk/serilerde eskime) neden olmaktadır.
-Bayide stok fazlası olmasına rağmen müşteriye ulaşmayan ürünler nedeniyle yanlış planlama kaynaklı eksiklik yaşanabilir. Diğer yandan düşük talebi olan ürünlerde stok yığılır, bayi nakit döngüsü bozulabilir. 
-KBY lerin yaptıkları fiili satışlar üzerinden oluşturulacak stok seviyeleri belirlenip, Çekme Sistemiyle birlikte 2 farklı seviye ve kontrol mekanizması oluşturulabilir. 
-Fabrika Depolarındaki DFU bazlı stok seviyelerinde düşüş yaşanır.
-Bu sayede hem satış verileri hem de pazarın gerçek tüketim hızı görülebilir, “fazla sipariş – düşük tüketim” dengesizlikleri önlenir.
-Stokların görünürlüğü sayesinde üretim planı daha proaktif yapılır.
-Stok Optimizasyonu sağlanır. Hem fabrika hem de bayi depoları birlikte değerlendirildiğinde, toplam stok seviyeleri optimumda tutulur.
-Gereksiz üretim ve depolama maliyetleri azalır, nakit akışı iyileşir.
-Bayilerin doğru ürünü bulundurması, müşteri memnuniyetini arttırır.</t>
+    <t>Bu çalışma ile planlama sürecine şirket içindeki bilgilere ilave olarak, bayi ağımızdaki KS ürünleri satış ve stok bilgilerinin de eklenerek planlama sürecinin etkinliğinin artırılması hedeflenmektedir.
+- Mevcut durumda KBY verileri üretim planlama ve stok yönetimine bir girdi sağlamamaktadır.
+- Nihai pazar talepleri belirlenememektedir, talep görünürlüğü düşük seviyededir.
+- Satış siparişleri baz alınarak üretim yapıldığında, bayi deposunda zaten stok olsa bile fabrika tekrar üretim yapmaktadır. Bu durum talep şişirmesine (artificial demand) yol açmaktadır. Gerçekte tüketim düşükken üretimin yüksek planlanmasına neden olmaktadır.
+- Fabrika ve bayi depolarında çifte stok oluşmaktadır bu da finansman yükü, yüksek stok taşıma maliyeti ve olası değer kayıplarına (moda/renk/serilerde eskime) neden olmaktadır.
+- Bayide stok fazlası olmasına rağmen müşteriye ulaşmayan ürünler nedeniyle yanlış planlama kaynaklı eksiklik yaşanabilir. Diğer yandan düşük talebi olan ürünlerde stok yığılır, bayi nakit döngüsü bozulabilir. 
+- KBY lerin yaptıkları fiili satışlar üzerinden oluşturulacak stok seviyeleri belirlenip, Çekme Sistemiyle birlikte 2 farklı seviye ve kontrol mekanizması oluşturulabilir. 
+- Fabrika Depolarındaki DFU bazlı stok seviyelerinde düşüş yaşanır.
+- Bu sayede hem satış verileri hem de pazarın gerçek tüketim hızı görülebilir, “fazla sipariş – düşük tüketim” dengesizlikleri önlenir.
+- Stokların görünürlüğü sayesinde üretim planı daha proaktif yapılır.
+- Stok Optimizasyonu sağlanır. Hem fabrika hem de bayi depoları birlikte değerlendirildiğinde, toplam stok seviyeleri optimumda tutulur.
+- Gereksiz üretim ve depolama maliyetleri azalır, nakit akışı iyileşir.
+- Bayilerin doğru ürünü bulundurması, müşteri memnuniyetini arttırır.</t>
+  </si>
+  <si>
+    <t>- Bayi stoklarının sistemden çekilip takip edilmesi, talep ve planlama yönetimine girdi oluşturması sağlanacaktır.
+- Bayi stoklarının güncel doğruluğunun kontrol edilmesi gerekmektedir.
+- Bayi stok ve satışları değerlendirilip, bayi ve bölge bazlı analizler hazırlanacaktır.</t>
   </si>
   <si>
     <t xml:space="preserve">SSG Ürün Grubu Postponement Uygulaması </t>
   </si>
   <si>
-    <t>Ürünün üretim veya dağıtım sürecinde son aşamalarını müşteri talebi kesinleşene kadar erteleyerek hem maliyet avantajı hem de talep esnekliği kazandırmak.</t>
-  </si>
-  <si>
-    <t>Stoğa ya da siparişe üretim yaptığımız tüm ürünlerde kutu, yardımcı malzemeler (taharet musluğu, kullanım kılavuzu, S kada vs.) seramik parçalar ile birlikte stoklanmaktadır. Bu da;
+    <t>Postponement, ürünün üretim veya dağıtım sürecinde son aşamalarını müşteri talebi kesinleşene kadar erteleyerek hem maliyet avantajı hem de talep esnekliği kazandırmak için uygulanan bir stok yönetim şeklidir.
+Stoğa ya da siparişe üretim yaptığımız tüm ürünlerde kutu, yardımcı malzemeler (taharet musluğu, kullanım kılavuzu, S kada vs.) seramik parçalar ile birlikte stoklanmaktadır. Bu da;
 Yüksek Stok Maliyeti
 Stok Fazlası ve Hurda Riski
+Kutu değişim ve elleçleme maliyetleri
 Esneklik Kaybı
 Kapitalin Bağlanması (Nakit akışa olumsuz etki)
 Lojistik Zorlukları gibi zorluklara neden olmaktadır. 
@@ -609,22 +623,40 @@
     Müşteri yakınında sonlandırma (Ürünün son haline sevke en yakın zamanda getirme)</t>
   </si>
   <si>
+    <t>- Tüm mamullerin ürün ağaçları incelendi ve ürün ağacındaki seramik harici yardımcı malzemeler belirlendi. Adetsel ve tutarsal analizleri yapıldı.
+- Açık sahada stoklanan kutulu mamullerin geçtiğimiz döneme dair (yıllık) yeniden elleçleme maliyetleri çıkartıldı.
+- Mamul sevk miktarlarına göre projeye dahil olacak ürünlerin yardımcı malzemelerinin, malzeme depo ve kalite ayrımda tutulması gereken stok seviyeleri belirlendi.
+- Mamul ürünlerin yardımcı malzeme olmadan stoklanması için alternatif stoklama yöntemi için kafes tip aparatlar incelendi.Maliyet ve kullanım şekline göre alternatifler oluşturuldu.</t>
+  </si>
+  <si>
+    <t>- Mamul ambarda sevk miktarlarına uygun olacak şekilde U-Tipi paketleme alanı oluşturulacaktır.
+- Sevk miktarlarına göre işgücü, ekipman ihtiyacı ve atölye tasarımı çalışılacaktır.</t>
+  </si>
+  <si>
     <t>MİP Sürecinin Geliştirilmesi</t>
   </si>
   <si>
     <t>Şirketin üretim süreçlerinde kullanılan Malzeme İhtiyaç Planlaması (MRP) sisteminin mevcut yapısını analiz ederek daha etkin, esnek ve verimli bir planlama mekanizması oluşturmayı amaçlamaktadır. Proje kapsamında; talep tahminleri, stok seviyeleri, satın alma siparişleri ve üretim planları arasındaki entegrasyonun güçlendirilmesi hedeflenmektedir. Böylece, doğru malzemenin doğru zamanda ve doğru miktarda temin edilmesi sağlanarak maliyetlerin azaltılması, stok devir hızının artırılması ve müşteri teslim sürelerinin iyileştirilmesi planlanmaktadır.</t>
   </si>
   <si>
-    <t>İlgili gruptaki malzemeler için talebe dayalı bir tedarik sistemi uygulanmaktadır. Satınalma talepleri manuel olarak oluşturulmaktadır. 
+    <t xml:space="preserve">İlgili gruptaki malzemeler için talebe dayalı bir tedarik sistemi uygulanmaktadır. Satınalma talepleri manuel olarak oluşturulmaktadır. 
 Üretim Malzemeleri için müşteri siparişleri ve üretim programları incelenmekte ve satınalma talepleri manuel olarak oluşturulmaktadır. Sistemin oluşturduğu SAT belgeleri kullanılmamaktadır. 
 Malzemelerin gruplanması:
-Gruplar bazında tedarik planlama yaklaşımlarının belirlenmesi
+Gruplar bazında tedarik planlama yaklaşımlarının belirlenmiştir
 Mevcut MRP süreçlerinin detaylı analizi yapılacak, güçlü ve zayıf yönler belirlenmiştir.
 Talep tahmini, güvenlik stoğu, lot büyüklüğü ve sipariş periyotlarının daha etkin yönetilmesi için yeni yöntemler geliştirilmiştir.
 KPI’lar (stok devir hızı, stok doğruluk oranı, müşteri teslim performansı vb.) üzerinden ölçülebilir iyileştirmeler hedeflenmiştir. 
-ERP/MRP yazılımında ihtiyaç duyulan iyileştirmeler ve otomasyonlar tanımlanacaktır.
-Satın alma, üretim planlama ve depo yönetimi arasındaki koordinasyon artırılacaktır.
-İşletme malzemeleri görsel arşiv (SKU Kimlik Kartı) çalışmaları devam etmektedir. İlgili stoklu malzemelerin %50 sinin görselleştirme çalışmaları tamamlanmıştır. Bu çalışmanın devamında AI destekli ürün yönlendirme çalışmaları devam etmektedir.</t>
+</t>
+  </si>
+  <si>
+    <t>- ERP/MRP yazılımında ihtiyaç duyulan iyileştirmeler ve otomasyonlar tanımlanacaktır.
+- Satın alma, üretim planlama ve depo yönetimi arasındaki koordinasyon artırılacaktır.
+- İşletme malzemeleri görsel arşiv (SKU Kimlik Kartı) çalışmaları devam etmektedir. İlgili stoklu malzemelerin %50 sinin görselleştirme çalışmaları tamamlanmıştır. Bu çalışmanın devamında AI destekli ürün yönlendirme çalışmaları devam etmektedir.
+- KS01 &amp; KS02 MLZ Türlerüne ait SKU ların %30 u için Emniyet stokları tanımlanmıştır.
+- MİP sürecnin iyileştirmesine hizmet edecek, geçmiş tarihli açık rezervasyonlar kapatılmıştır. Takip edimektedir.
+- MİP süreci açık SAS &amp; açık SAT lar raporlanarak haftalık geçmiş tarihli olanların kapatılması için aksiyonlar alınmaktadır.
+- Malzeme &amp; Aramamül kodlarına ait ABC &amp; XYZ gruplamaları aylık olarak revize edilerek takip edilmektedir.
+-Güvenlik stokları, dinamik olarak frekans tüketim, max,min tüketim verilerini içeren bir hesaplama geliştirilmiştir.</t>
   </si>
   <si>
     <t>Malzeme Depo Yönetimi</t>
@@ -1741,7 +1773,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1784,6 +1816,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1812,7 +1850,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1855,6 +1893,9 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2208,13 +2249,14 @@
     <col min="3" max="3" width="2.28515625" style="10" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.42578125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" style="13" customWidth="1"/>
     <col min="10" max="10" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="90.28515625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="71.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="81" style="4" customWidth="1"/>
+    <col min="11" max="11" width="62.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="90.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="51.85546875" style="4" customWidth="1"/>
     <col min="14" max="14" width="8.85546875" style="11" customWidth="1"/>
     <col min="15" max="16384" width="8.85546875" style="11"/>
   </cols>
@@ -2260,7 +2302,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="144">
+    <row r="2" spans="1:13" ht="245.25">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -2600,7 +2642,7 @@
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="144">
+    <row r="12" spans="1:13" ht="158.44999999999999">
       <c r="A12" s="10">
         <v>1</v>
       </c>
@@ -2676,7 +2718,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="72">
+    <row r="14" spans="1:13" ht="86.45">
       <c r="A14" s="10">
         <v>1</v>
       </c>
@@ -2779,7 +2821,7 @@
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:13" ht="172.9">
+    <row r="17" spans="1:13" ht="201.6">
       <c r="A17" s="10">
         <v>1</v>
       </c>
@@ -2890,9 +2932,11 @@
       <c r="L19" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="1:13" ht="72">
+      <c r="M19" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="115.5">
       <c r="A20" s="10">
         <v>1</v>
       </c>
@@ -2906,13 +2950,13 @@
         <v>75</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20" s="12">
         <v>46023</v>
@@ -2924,13 +2968,13 @@
         <v>17</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="57.6">
@@ -2947,13 +2991,13 @@
         <v>75</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H21" s="12">
         <v>46174</v>
@@ -2965,11 +3009,11 @@
         <v>31</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:13" ht="28.9">
+    <row r="22" spans="1:13" ht="43.15">
       <c r="A22" s="10">
         <v>1</v>
       </c>
@@ -2983,10 +3027,10 @@
         <v>75</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="12">
@@ -2999,11 +3043,11 @@
         <v>31</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:13" ht="57.6">
+    <row r="23" spans="1:13" ht="72">
       <c r="A23" s="10">
         <v>1</v>
       </c>
@@ -3017,13 +3061,13 @@
         <v>75</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H23" s="12">
         <v>46327</v>
@@ -3035,7 +3079,7 @@
         <v>31</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L23" s="4"/>
     </row>
@@ -3050,13 +3094,13 @@
         <v>4</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="12">
@@ -3069,13 +3113,13 @@
         <v>17</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="28.9">
@@ -3089,13 +3133,13 @@
         <v>4</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="12">
@@ -3108,11 +3152,11 @@
         <v>31</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="28.9">
@@ -3126,13 +3170,13 @@
         <v>4</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="12">
@@ -3145,11 +3189,11 @@
         <v>31</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="144">
@@ -3157,19 +3201,19 @@
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C27" s="10">
         <v>1</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="12">
@@ -3182,30 +3226,30 @@
         <v>57</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="115.15">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="115.5">
       <c r="A28" s="10">
         <v>2</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="12">
@@ -3215,36 +3259,37 @@
         <v>46203</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="28.9">
+        <v>122</v>
+      </c>
+      <c r="M28" s="1"/>
+    </row>
+    <row r="29" spans="1:13" ht="57.75">
       <c r="A29" s="10">
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C29" s="10">
         <v>1</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
@@ -3252,31 +3297,31 @@
         <v>70</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:13" ht="28.9">
+    <row r="30" spans="1:13" ht="57.75">
       <c r="A30" s="10">
         <v>2</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C30" s="10">
         <v>1</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
@@ -3284,7 +3329,7 @@
         <v>70</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L30" s="4"/>
     </row>
@@ -3293,22 +3338,22 @@
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31" s="10">
         <v>1</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H31" s="12">
         <v>46174</v>
@@ -3320,33 +3365,33 @@
         <v>31</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L31" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="115.15">
+      <c r="M31" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="130.5">
       <c r="A32" s="10">
         <v>2</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H32" s="12">
         <v>45839</v>
@@ -3358,33 +3403,33 @@
         <v>57</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="43.15">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="64.5" customHeight="1">
       <c r="A33" s="10">
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C33" s="10">
         <v>2</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
@@ -3392,31 +3437,31 @@
         <v>70</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:13" ht="316.89999999999998">
+    <row r="34" spans="1:13" ht="186" customHeight="1">
       <c r="A34" s="10">
         <v>2</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C34" s="10">
         <v>2</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H34" s="12">
         <v>46023</v>
@@ -3428,10 +3473,10 @@
         <v>17</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="L34" s="1" t="s">
         <v>143</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="132.4" customHeight="1">
@@ -3439,19 +3484,19 @@
         <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C35" s="10">
         <v>2</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="12">
@@ -3461,33 +3506,36 @@
         <v>46295</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="113.1" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="256.5" customHeight="1">
       <c r="A36" s="10">
         <v>2</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C36" s="10">
         <v>2</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="12">
@@ -3500,30 +3548,33 @@
         <v>17</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="172.9">
+        <v>150</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="174">
       <c r="A37" s="10">
         <v>2</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C37" s="10">
         <v>3</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="12">
@@ -3536,30 +3587,30 @@
         <v>17</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="260.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="332.25">
       <c r="A38" s="10">
         <v>3</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C38" s="10">
         <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="12">
@@ -3572,33 +3623,33 @@
         <v>17</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M38" s="14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="174">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="172.9">
       <c r="A39" s="10">
         <v>3</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C39" s="10">
         <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="12">
@@ -3611,13 +3662,13 @@
         <v>17</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="43.15">
@@ -3625,19 +3676,19 @@
         <v>3</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C40" s="10">
         <v>2</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="12">
@@ -3650,13 +3701,13 @@
         <v>17</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="86.45">
@@ -3664,19 +3715,19 @@
         <v>3</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C41" s="10">
         <v>2</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="12">
@@ -3689,36 +3740,36 @@
         <v>57</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="101.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="100.9">
       <c r="A42" s="10">
         <v>3</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H42" s="12">
         <v>45778</v>
@@ -3730,33 +3781,33 @@
         <v>17</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="144.75">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="144">
       <c r="A43" s="10">
         <v>3</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C43" s="10">
         <v>3</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="12">
@@ -3769,13 +3820,13 @@
         <v>17</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="129.6">
@@ -3783,19 +3834,19 @@
         <v>4</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C44" s="10">
         <v>1</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="12">
@@ -3808,13 +3859,13 @@
         <v>17</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="57.6">
@@ -3822,19 +3873,19 @@
         <v>4</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C45" s="10">
         <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="12">
@@ -3847,13 +3898,13 @@
         <v>17</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="57.6">
@@ -3861,19 +3912,19 @@
         <v>4</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C46" s="10">
         <v>1</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="12">
@@ -3886,13 +3937,13 @@
         <v>17</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="129.6">
@@ -3900,19 +3951,19 @@
         <v>4</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C47" s="10">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="12">
@@ -3925,13 +3976,13 @@
         <v>17</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="57.6">
@@ -3939,22 +3990,22 @@
         <v>4</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H48" s="12">
         <v>45962</v>
@@ -3966,13 +4017,13 @@
         <v>17</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="86.45">
@@ -3980,19 +4031,19 @@
         <v>4</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C49" s="10">
         <v>1</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="12">
@@ -4005,33 +4056,33 @@
         <v>17</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="28.9">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="43.15">
       <c r="A50" s="10">
         <v>4</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C50" s="10">
         <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="12">
@@ -4044,13 +4095,13 @@
         <v>17</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="86.45">
@@ -4058,19 +4109,19 @@
         <v>4</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C51" s="10">
         <v>2</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="12">
@@ -4083,30 +4134,30 @@
         <v>57</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="100.9">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="115.15">
       <c r="A52" s="10">
         <v>4</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C52" s="10">
         <v>2</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="12">
@@ -4119,13 +4170,13 @@
         <v>17</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="57.6">
@@ -4133,19 +4184,19 @@
         <v>4</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C53" s="10">
         <v>2</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="12">
@@ -4158,33 +4209,33 @@
         <v>17</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="86.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="100.9">
       <c r="A54" s="10">
         <v>4</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C54" s="10">
         <v>2</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="12">
@@ -4197,13 +4248,13 @@
         <v>17</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="115.15">
@@ -4211,19 +4262,19 @@
         <v>4</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C55" s="10">
         <v>2</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="12">
@@ -4236,13 +4287,13 @@
         <v>17</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="86.45">
@@ -4250,19 +4301,19 @@
         <v>4</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C56" s="10">
         <v>3</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="12">
@@ -4275,13 +4326,13 @@
         <v>17</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="86.45">
@@ -4289,22 +4340,22 @@
         <v>5</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C57" s="10">
         <v>1</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H57" s="12">
         <v>45931</v>
@@ -4316,13 +4367,13 @@
         <v>17</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="57.6">
@@ -4330,22 +4381,22 @@
         <v>5</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C58" s="10">
         <v>1</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H58" s="12">
         <v>45962</v>
@@ -4357,13 +4408,13 @@
         <v>17</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="115.15">
@@ -4371,22 +4422,22 @@
         <v>5</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C59" s="10">
         <v>1</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H59" s="12">
         <v>45931</v>
@@ -4398,13 +4449,13 @@
         <v>17</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="86.45">
@@ -4412,22 +4463,22 @@
         <v>5</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C60" s="10">
         <v>1</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H60" s="12">
         <v>45931</v>
@@ -4439,33 +4490,33 @@
         <v>17</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="72">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="86.45">
       <c r="A61" s="10">
         <v>5</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C61" s="10">
         <v>2</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="12">
@@ -4478,13 +4529,13 @@
         <v>17</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="115.15">
@@ -4492,19 +4543,19 @@
         <v>5</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C62" s="10">
         <v>2</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="12">
@@ -4517,7 +4568,7 @@
         <v>31</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="L62" s="4"/>
     </row>
@@ -4526,19 +4577,19 @@
         <v>5</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C63" s="10">
         <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="12">
@@ -4551,13 +4602,13 @@
         <v>17</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="28.9">
@@ -4565,19 +4616,19 @@
         <v>5</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C64" s="10">
         <v>3</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="12">
@@ -4590,13 +4641,13 @@
         <v>17</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="43.15">
@@ -4604,19 +4655,19 @@
         <v>5</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C65" s="10">
         <v>4</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="12">
@@ -4629,13 +4680,13 @@
         <v>17</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="72">
@@ -4643,19 +4694,19 @@
         <v>5</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C66" s="10">
         <v>4</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="12">
@@ -4668,13 +4719,13 @@
         <v>17</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="57.6">
@@ -4682,19 +4733,19 @@
         <v>5</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C67" s="10">
         <v>4</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="12">
@@ -4707,13 +4758,13 @@
         <v>17</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="43.15">
@@ -4721,19 +4772,19 @@
         <v>5</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C68" s="10">
         <v>4</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="12">
@@ -4746,10 +4797,10 @@
         <v>57</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="43.15">
@@ -4757,22 +4808,22 @@
         <v>6</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C69" s="10">
         <v>1</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H69" s="12">
         <v>45778</v>
@@ -4784,7 +4835,7 @@
         <v>57</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M69" s="1"/>
     </row>
@@ -4793,22 +4844,22 @@
         <v>6</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C70" s="10">
         <v>1</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H70" s="12">
         <v>45931</v>
@@ -4820,7 +4871,7 @@
         <v>57</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M70" s="1"/>
     </row>
@@ -4829,22 +4880,22 @@
         <v>6</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C71" s="10">
         <v>1</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F71" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G71" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="H71" s="12">
         <v>45931</v>
@@ -4856,34 +4907,34 @@
         <v>57</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M71" s="1"/>
     </row>
-    <row r="72" spans="1:13" ht="72">
+    <row r="72" spans="1:13" ht="86.45">
       <c r="A72" s="10">
         <v>6</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H72" s="12">
         <v>46023</v>
@@ -4892,36 +4943,36 @@
         <v>46387</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="72">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="86.45">
       <c r="A73" s="10">
         <v>6</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C73" s="10">
         <v>1</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H73" s="12">
         <v>46023</v>
@@ -4930,13 +4981,13 @@
         <v>46387</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="28.9">
@@ -4944,22 +4995,22 @@
         <v>6</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C74" s="10">
         <v>1</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H74" s="12"/>
       <c r="I74" s="12"/>
@@ -4974,22 +5025,22 @@
         <v>6</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C75" s="10">
         <v>1</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
@@ -5004,22 +5055,22 @@
         <v>6</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C76" s="10">
         <v>1</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H76" s="12"/>
       <c r="I76" s="12"/>
@@ -5029,27 +5080,27 @@
       <c r="K76" s="5"/>
       <c r="L76" s="4"/>
     </row>
-    <row r="77" spans="1:13" ht="115.15">
+    <row r="77" spans="1:13" ht="129.6">
       <c r="A77" s="10">
         <v>6</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C77" s="10">
         <v>2</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="H77" s="12">
         <v>46204</v>
@@ -5061,36 +5112,36 @@
         <v>31</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="129.6">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="144">
       <c r="A78" s="10">
         <v>6</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C78" s="10">
         <v>2</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H78" s="12">
         <v>46023</v>
@@ -5099,16 +5150,16 @@
         <v>46142</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="86.45">
@@ -5116,22 +5167,22 @@
         <v>6</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C79" s="10">
         <v>2</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H79" s="12">
         <v>45992</v>
@@ -5140,16 +5191,16 @@
         <v>46142</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="57.6">
@@ -5157,22 +5208,22 @@
         <v>6</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C80" s="10">
         <v>2</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H80" s="12">
         <v>46023</v>
@@ -5181,39 +5232,39 @@
         <v>46387</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="158.44999999999999">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="172.9">
       <c r="A81" s="10">
         <v>6</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C81" s="10">
         <v>2</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="H81" s="12">
         <v>46023</v>
@@ -5222,39 +5273,39 @@
         <v>46357</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="100.9">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="115.15">
       <c r="A82" s="10">
         <v>6</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H82" s="12">
         <v>45931</v>
@@ -5266,13 +5317,13 @@
         <v>57</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="115.15">
@@ -5280,22 +5331,22 @@
         <v>6</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C83" s="10">
         <v>2</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H83" s="12">
         <v>46023</v>
@@ -5304,39 +5355,39 @@
         <v>46112</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M83" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="158.44999999999999">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="172.9">
       <c r="A84" s="10">
         <v>6</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C84" s="10">
         <v>2</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H84" s="12">
         <v>46023</v>
@@ -5345,16 +5396,16 @@
         <v>46203</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="57.6">
@@ -5362,22 +5413,22 @@
         <v>6</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C85" s="10">
         <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H85" s="12">
         <v>46174</v>
@@ -5389,13 +5440,13 @@
         <v>31</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="86.45">
@@ -5403,22 +5454,22 @@
         <v>6</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C86" s="10">
         <v>2</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H86" s="12">
         <v>46023</v>
@@ -5427,16 +5478,16 @@
         <v>46142</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="86.45">
@@ -5444,19 +5495,19 @@
         <v>6</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C87" s="10">
         <v>3</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G87" s="3"/>
       <c r="H87" s="12">
@@ -5466,16 +5517,16 @@
         <v>46157</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="43.15">
@@ -5483,19 +5534,19 @@
         <v>6</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C88" s="10">
         <v>3</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="12">
@@ -5508,11 +5559,11 @@
         <v>31</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="100.9">
@@ -5520,22 +5571,22 @@
         <v>6</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C89" s="10">
         <v>4</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="H89" s="12">
         <v>46023</v>
@@ -5544,16 +5595,16 @@
         <v>46357</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="90" spans="1:13" ht="72">
@@ -5561,19 +5612,19 @@
         <v>6</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C90" s="10">
         <v>4</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G90" s="3"/>
       <c r="H90" s="12">
@@ -5586,33 +5637,33 @@
         <v>57</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="57.6">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="86.45">
       <c r="A91" s="10">
         <v>6</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C91" s="10">
         <v>4</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="12">
@@ -5625,13 +5676,13 @@
         <v>57</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="129.6">
@@ -5639,19 +5690,19 @@
         <v>6</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C92" s="10">
         <v>4</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="12">
@@ -5661,39 +5712,39 @@
         <v>46112</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="72">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="86.45">
       <c r="A93" s="10">
         <v>6</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C93" s="10">
         <v>5</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H93" s="12">
         <v>46023</v>
@@ -5702,16 +5753,16 @@
         <v>46295</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="57.6">
@@ -5719,22 +5770,22 @@
         <v>6</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C94" s="10">
         <v>5</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="H94" s="12">
         <v>46023</v>
@@ -5743,16 +5794,16 @@
         <v>46266</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="72">
@@ -5760,22 +5811,22 @@
         <v>6</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C95" s="10">
         <v>5</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="H95" s="12">
         <v>46023</v>
@@ -5784,14 +5835,14 @@
         <v>46357</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/TZY Gelişim Planı/Gelişim Planı/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FBE20DC-4C54-4524-8BDD-570D5A33A3B3}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3317ACA9-28EE-4A77-B1A9-F3A1433A344E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects Data" sheetId="31" r:id="rId1"/>
@@ -650,6 +650,7 @@
   </si>
   <si>
     <t>- ERP/MRP yazılımında ihtiyaç duyulan iyileştirmeler ve otomasyonlar tanımlanacaktır.
+- Ürün ağaçlarının haftalık olarak mail atılmasına yönelik aksiyon planlanmıştır.(SAP-Mail)
 - Satın alma, üretim planlama ve depo yönetimi arasındaki koordinasyon artırılacaktır.
 - İşletme malzemeleri görsel arşiv (SKU Kimlik Kartı) çalışmaları devam etmektedir. İlgili stoklu malzemelerin %50 sinin görselleştirme çalışmaları tamamlanmıştır. Bu çalışmanın devamında AI destekli ürün yönlendirme çalışmaları devam etmektedir.
 - KS01 &amp; KS02 MLZ Türlerüne ait SKU ların %30 u için Emniyet stokları tanımlanmıştır.
@@ -685,6 +686,10 @@
 KPI Takibi ve Süreç Stabilizasyonu devam etmektedir.</t>
   </si>
   <si>
+    <t>Ambalaj malzemeleri için mevcut fiziksel depolama alanı yetersiz kalmaktadır. Artan hacim ve çeşitlilik dikkate alınarak, daha verimli yerleşim ve ilave alan ihtiyacının değerlendirilmesine ihtiyaç vardır.
+KPI Set;  Stok doğruluğu, Malzeme bulunurluk,Hat besleme, Yetersizlik, 180+% , Adresleme şeklinde yapılandırılmaya çalışılıyor.</t>
+  </si>
+  <si>
     <t>Lojistik</t>
   </si>
   <si>
@@ -710,14 +715,14 @@
 Entegrasyon ve Geliştirme Başlangıcı
 Kale SAP sistemindeki GTIP bilgilerinin kontrol edildi. Eksiklikler tamamlandı.
 GTİP akışları karşılıklı olarak test edildi.
-İthalat Süreci Kavramsal çalışması tamamlandı.</t>
+İthalat Süreci Kavramsal çalışması tamamlandı.
+MM03’teki GTIP tanımlarının girişi tamamlandı.</t>
   </si>
   <si>
     <t xml:space="preserve">
 VPN Bağlantı ve KEQ sistemine kullanıcı bağlantı. (Merkezi gümrükleme uçtan uca ihracat-ithalat süreci için)
 Geliştirme adımı, kavramsal onayı sonrası, geliştirme yönlendirmesi Kale tarafından yapıldıktan sonra başlayacak.
 OGİ İşlemler Menusü, kullanım dokumanı gibi, SAP'deki kurgunun kullanıcı dokumanı hazırlanacak.
-MM03’teki GTIP tanımlarının girişi incelenecek.
 SAP’te VL31N ile oluşturulan Alınan Teslimatların, gümrük sistemine otomatik olarak aktarılması
 *Her bir Alınan Teslimat kaydı, gümrük tarafında ayrı bir dosya olarak ele alınacaktır.
 Gümrük sistemi üzerindeki statü bilgilerinin, SAP’ye geri akması
@@ -779,10 +784,8 @@
 İyi uygulamaların tüm lokasyonlara uygulanması​ adına karar alındı.
 Organizasyonel yapının değiştirilmesi​ için proje ekibi kuruldu.
 Mevcut yapıya alternatifler çalışıldı, en uygun model belirlendi.
-IK-Üst Yönetim değerlendirmesi adına nihai model sunuldu.</t>
-  </si>
-  <si>
-    <t>Bandırma süreçleri noktalı olarak Sipariş Karşılama ve Lojistik ekibine bağlandı.
+IK-Üst Yönetim değerlendirmesi adına nihai model sunuldu.
+Bandırma süreçleri noktalı olarak Sipariş Karşılama ve Lojistik ekibine bağlandı.
 SAP TM üzerinden süreçler izlenmeye başlandı.</t>
   </si>
   <si>
@@ -805,7 +808,34 @@
     <t>MDP ile palet, paket dönüşümüne çözüm alternatifleri için geri bildirim yapıldı. Dönüş bekleniyor.
 MDP Vitra benchmark için geri bildirim bekleniyor.
 Optiyol sadece rota optimizasyonu desteği verdiğinden mevcut durumda askıya alındı.
-MDP’ye alternatif olarak Golive firması ile görüşülecek.</t>
+Kuralların tanımlanacak:
+Araç doluluk alt limiti
+Yüklerin kaç gün bekleyebileceği
+Aynı araçta hangi yüklerin birlikte/birlikte olamayacağı
+Öncelik, ceza–puan mekanizmaları
+Tedarikçi çözümlerinin karşılaştırılması yapılacak:
+Optiyol, SAP TM (MDP Grup / GoLive) çözümleri için km–maliyet bazlı objektif mukayese tablosu oluşturulacak.
+Optimizasyon algoritmasının anlaşılması:
+Yüklerin hangi kurala göre seçildiği
+Tek paletin ne zaman sevk edildiği
+Ceza/ödül sisteminin nasıl çalıştığı
+Firmalarla net şekilde sorgulanacak.
+SAP TM paketleme süreci hazırlığı:
+Paketleme fonksiyonunun süreçte devreye alınması görüşülecek.
+İstifleme, üst üste yükleme, kamyon içi yerleşim kurallarının ana veriye girilmesi devam ediyor.
+Ana veri doğruluğu ve eksiklerin tamamlanması:
+Ürün ölçüleri, ambalaj, istif faktörü
+Araç kapasite, hacim ve fiziksel kısıtlar
+Lokasyon enlem–boylam bilgileri
+POC yaklaşımının standardize edilmesi:
+Aynı veri seti ve aynı kurallar ile tüm firmalardan tekrar POC sonucu alınacak.
+Süreç iyileştirme aksiyonları:
+TM’ye gönderme (SV) adımının manuel olmaktan çıkarılacak (RPA / otomasyon)
+Optimizasyon havuzunun genişletilecek.
+Operasyonel karar noktalarının gözden geçirilmesi:
+Teslimat oluşturma aşamasında verilen kararların optimizasyonu kısıtlayıp kısıtlamadığı değerlendirilecek.
+Uyarı / ikaz sistemi kurgusu:
+YZ Yanımda projesi kapsamında sapma, doluluk, bekleme süresi gibi konularda uyarı mekanizmaları tasarlanacak.</t>
   </si>
   <si>
     <t>Kalite Belgesi</t>
@@ -822,7 +852,7 @@
   <si>
     <t>Danışmanlık, eğitim ve belgelendirme için teklif toplandı.​
 Altı firma ile görüşme yapıldı. Teklifler alındı.​
-Teklifler ve içerik değerlendirildi.​vBelgelendirme firmasına karar verirdi, sözleşme aşamasına geçildi.​vSözleşme tamamlandı.​
+Teklifler ve içerik değerlendirildi. Belgelendirme firmasına karar verirdi, sözleşme aşamasına geçildi.​vSözleşme tamamlandı.​
 GAP analizi ve standart gereklilikleri bir çalıştay ile gözden geçirildi.
 ​Proje takvimi netleştirildi.​
 Bölümler arası bilgilendirme ve görevlendirme yapıldı.
@@ -1814,13 +1844,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1850,7 +1880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1891,11 +1921,14 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2302,7 +2335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="245.25">
+    <row r="2" spans="1:13" ht="244.9">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -2642,7 +2675,7 @@
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="158.44999999999999">
+    <row r="12" spans="1:13" ht="144">
       <c r="A12" s="10">
         <v>1</v>
       </c>
@@ -2821,7 +2854,7 @@
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:13" ht="201.6">
+    <row r="17" spans="1:13" ht="172.9">
       <c r="A17" s="10">
         <v>1</v>
       </c>
@@ -2936,7 +2969,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="115.5">
+    <row r="20" spans="1:13" ht="115.15">
       <c r="A20" s="10">
         <v>1</v>
       </c>
@@ -3013,7 +3046,7 @@
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:13" ht="43.15">
+    <row r="22" spans="1:13" ht="28.9">
       <c r="A22" s="10">
         <v>1</v>
       </c>
@@ -3047,7 +3080,7 @@
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:13" ht="72">
+    <row r="23" spans="1:13" ht="57.6">
       <c r="A23" s="10">
         <v>1</v>
       </c>
@@ -3232,7 +3265,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="115.5">
+    <row r="28" spans="1:13" ht="115.15">
       <c r="A28" s="10">
         <v>2</v>
       </c>
@@ -3269,7 +3302,7 @@
       </c>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" ht="57.75">
+    <row r="29" spans="1:13" ht="28.9">
       <c r="A29" s="10">
         <v>2</v>
       </c>
@@ -3301,7 +3334,7 @@
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:13" ht="57.75">
+    <row r="30" spans="1:13" ht="28.9">
       <c r="A30" s="10">
         <v>2</v>
       </c>
@@ -3367,11 +3400,11 @@
       <c r="K31" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="M31" s="14" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="130.5">
+    <row r="32" spans="1:13" ht="129.6">
       <c r="A32" s="10">
         <v>2</v>
       </c>
@@ -3518,7 +3551,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="256.5" customHeight="1">
+    <row r="36" spans="1:13" ht="314.25" customHeight="1">
       <c r="A36" s="10">
         <v>2</v>
       </c>
@@ -3550,14 +3583,14 @@
       <c r="K36" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="L36" s="14" t="s">
+      <c r="L36" s="2" t="s">
         <v>151</v>
       </c>
       <c r="M36" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="174">
+    <row r="37" spans="1:13" ht="187.5" customHeight="1">
       <c r="A37" s="10">
         <v>2</v>
       </c>
@@ -3592,25 +3625,28 @@
       <c r="L37" s="1" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="332.25">
+      <c r="M37" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="318">
       <c r="A38" s="10">
         <v>3</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C38" s="10">
         <v>1</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="12">
@@ -3623,33 +3659,33 @@
         <v>17</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="M38" s="14" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="172.9">
+      <c r="M38" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="158.44999999999999">
       <c r="A39" s="10">
         <v>3</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C39" s="10">
         <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="12">
@@ -3662,13 +3698,13 @@
         <v>17</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="43.15">
@@ -3676,19 +3712,19 @@
         <v>3</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C40" s="10">
         <v>2</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="12">
@@ -3701,33 +3737,33 @@
         <v>17</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="86.45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="115.5">
       <c r="A41" s="10">
         <v>3</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C41" s="10">
         <v>2</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="12">
@@ -3740,30 +3776,28 @@
         <v>57</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="M41" s="1" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="100.9">
+      <c r="M41" s="1"/>
+    </row>
+    <row r="42" spans="1:13" ht="409.6">
       <c r="A42" s="10">
         <v>3</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>179</v>
@@ -3795,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C43" s="10">
         <v>3</v>
@@ -4065,7 +4099,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="43.15">
+    <row r="50" spans="1:13" ht="28.9">
       <c r="A50" s="10">
         <v>4</v>
       </c>
@@ -4140,7 +4174,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="115.15">
+    <row r="52" spans="1:13" ht="100.9">
       <c r="A52" s="10">
         <v>4</v>
       </c>
@@ -4218,7 +4252,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="100.9">
+    <row r="54" spans="1:13" ht="86.45">
       <c r="A54" s="10">
         <v>4</v>
       </c>
@@ -4499,7 +4533,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="86.45">
+    <row r="61" spans="1:13" ht="72">
       <c r="A61" s="10">
         <v>5</v>
       </c>
@@ -4914,7 +4948,7 @@
       </c>
       <c r="M71" s="1"/>
     </row>
-    <row r="72" spans="1:13" ht="86.45">
+    <row r="72" spans="1:13" ht="72">
       <c r="A72" s="10">
         <v>6</v>
       </c>
@@ -4952,7 +4986,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="86.45">
+    <row r="73" spans="1:13" ht="72">
       <c r="A73" s="10">
         <v>6</v>
       </c>
@@ -5080,7 +5114,7 @@
       <c r="K76" s="5"/>
       <c r="L76" s="4"/>
     </row>
-    <row r="77" spans="1:13" ht="129.6">
+    <row r="77" spans="1:13" ht="115.15">
       <c r="A77" s="10">
         <v>6</v>
       </c>
@@ -5121,7 +5155,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="144">
+    <row r="78" spans="1:13" ht="129.6">
       <c r="A78" s="10">
         <v>6</v>
       </c>
@@ -5244,7 +5278,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="172.9">
+    <row r="81" spans="1:13" ht="158.44999999999999">
       <c r="A81" s="10">
         <v>6</v>
       </c>
@@ -5285,7 +5319,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="115.15">
+    <row r="82" spans="1:13" ht="100.9">
       <c r="A82" s="10">
         <v>6</v>
       </c>
@@ -5367,7 +5401,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="172.9">
+    <row r="84" spans="1:13" ht="158.44999999999999">
       <c r="A84" s="10">
         <v>6</v>
       </c>
@@ -5646,7 +5680,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="86.45">
+    <row r="91" spans="1:13" ht="57.6">
       <c r="A91" s="10">
         <v>6</v>
       </c>
@@ -5724,7 +5758,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="86.45">
+    <row r="93" spans="1:13" ht="72">
       <c r="A93" s="10">
         <v>6</v>
       </c>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/TZY Gelişim Planı/Gelişim Planı/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3317ACA9-28EE-4A77-B1A9-F3A1433A344E}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DCA5802-ED84-44BF-8474-FE4E0183729C}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects Data" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="436">
   <si>
     <t>department order</t>
   </si>
@@ -639,25 +639,20 @@
     <t>Şirketin üretim süreçlerinde kullanılan Malzeme İhtiyaç Planlaması (MRP) sisteminin mevcut yapısını analiz ederek daha etkin, esnek ve verimli bir planlama mekanizması oluşturmayı amaçlamaktadır. Proje kapsamında; talep tahminleri, stok seviyeleri, satın alma siparişleri ve üretim planları arasındaki entegrasyonun güçlendirilmesi hedeflenmektedir. Böylece, doğru malzemenin doğru zamanda ve doğru miktarda temin edilmesi sağlanarak maliyetlerin azaltılması, stok devir hızının artırılması ve müşteri teslim sürelerinin iyileştirilmesi planlanmaktadır.</t>
   </si>
   <si>
-    <t xml:space="preserve">İlgili gruptaki malzemeler için talebe dayalı bir tedarik sistemi uygulanmaktadır. Satınalma talepleri manuel olarak oluşturulmaktadır. 
-Üretim Malzemeleri için müşteri siparişleri ve üretim programları incelenmekte ve satınalma talepleri manuel olarak oluşturulmaktadır. Sistemin oluşturduğu SAT belgeleri kullanılmamaktadır. 
-Malzemelerin gruplanması:
-Gruplar bazında tedarik planlama yaklaşımlarının belirlenmiştir
-Mevcut MRP süreçlerinin detaylı analizi yapılacak, güçlü ve zayıf yönler belirlenmiştir.
-Talep tahmini, güvenlik stoğu, lot büyüklüğü ve sipariş periyotlarının daha etkin yönetilmesi için yeni yöntemler geliştirilmiştir.
+    <t xml:space="preserve">
 KPI’lar (stok devir hızı, stok doğruluk oranı, müşteri teslim performansı vb.) üzerinden ölçülebilir iyileştirmeler hedeflenmiştir. 
+KS01 &amp; KS02 malzeme türlerine ait SKU’ların %30’u için emniyet stok seviyeleri tanımlanmış olup, kapsamın genişletilmesine yönelik çalışmalar devam etmektedir.
+MİP sürecinin sağlıklı çalışmasını desteklemek amacıyla geçmiş tarihli açık rezervasyonlar kapatılmış, süreç düzenli olarak izlenmektedir.
+Açık SAS ve SAT’lar haftalık raporlanmakta, geçmiş kayıtlar için aksiyon alınmaktadır.
+Malzeme ve aramamül kodları için ABC &amp; XYZ sınıflandırmaları aylık olarak güncellenmektedir.
+Emniyet stokları; tüketim frekansı ve min–max değerlere göre dinamik olarak hesaplanmaktadır.
 </t>
   </si>
   <si>
-    <t>- ERP/MRP yazılımında ihtiyaç duyulan iyileştirmeler ve otomasyonlar tanımlanacaktır.
-- Ürün ağaçlarının haftalık olarak mail atılmasına yönelik aksiyon planlanmıştır.(SAP-Mail)
-- Satın alma, üretim planlama ve depo yönetimi arasındaki koordinasyon artırılacaktır.
-- İşletme malzemeleri görsel arşiv (SKU Kimlik Kartı) çalışmaları devam etmektedir. İlgili stoklu malzemelerin %50 sinin görselleştirme çalışmaları tamamlanmıştır. Bu çalışmanın devamında AI destekli ürün yönlendirme çalışmaları devam etmektedir.
-- KS01 &amp; KS02 MLZ Türlerüne ait SKU ların %30 u için Emniyet stokları tanımlanmıştır.
-- MİP sürecnin iyileştirmesine hizmet edecek, geçmiş tarihli açık rezervasyonlar kapatılmıştır. Takip edimektedir.
-- MİP süreci açık SAS &amp; açık SAT lar raporlanarak haftalık geçmiş tarihli olanların kapatılması için aksiyonlar alınmaktadır.
-- Malzeme &amp; Aramamül kodlarına ait ABC &amp; XYZ gruplamaları aylık olarak revize edilerek takip edilmektedir.
--Güvenlik stokları, dinamik olarak frekans tüketim, max,min tüketim verilerini içeren bir hesaplama geliştirilmiştir.</t>
+    <t xml:space="preserve">ERP/MRP yazılımında ihtiyaç duyulan iyileştirmeler ve otomasyonlar tanımlanacaktır.
+Ürün ağaçlarının haftalık olarak mail atılmasına yönelik aksiyon planlanmıştır.(SAP-Mail)
+Satın alma, üretim planlama ve depo yönetimi arasındaki koordinasyon artırılacaktır.
+</t>
   </si>
   <si>
     <t>Malzeme Depo Yönetimi</t>
@@ -688,6 +683,82 @@
   <si>
     <t>Ambalaj malzemeleri için mevcut fiziksel depolama alanı yetersiz kalmaktadır. Artan hacim ve çeşitlilik dikkate alınarak, daha verimli yerleşim ve ilave alan ihtiyacının değerlendirilmesine ihtiyaç vardır.
 KPI Set;  Stok doğruluğu, Malzeme bulunurluk,Hat besleme, Yetersizlik, 180+% , Adresleme şeklinde yapılandırılmaya çalışılıyor.</t>
+  </si>
+  <si>
+    <t>Stok Verimliliği ve Yaşlı Stok Yönetimi Geliştirme</t>
+  </si>
+  <si>
+    <t>Bu proje; işletme genelindeki stok yapısının daha etkin, sürdürülebilir ve yönetilebilir hale getirilmesini amaçlamaktadır. Özellikle 180+ yaşlı stokların azaltılması, stok hareketliliğinin artırılması ve atıl malzeme oluşumunun önlenmesine odaklanılacaktır.
+Proje kapsamında; stok yaş analizleri, tüketim hareketleri, satın alma davranışları, emniyet stokları, açık SAT/SAS süreçleri ve malzeme kullanım alışkanlıkları düzenli olarak değerlendirilecektir. Ayrıca kullanılmayan veya düşük hareketli malzemeler için kullanım, transfer, iade, satış ve bertaraf alternatifleri analiz edilerek aksiyon planları oluşturulacaktır.</t>
+  </si>
+  <si>
+    <t>Power BI 180+ yaşlı stoklara ait düzenli yaş analiz raporları oluşturulmuş ve aylık takip yapısı devreye alınmıştır.
+Malzeme bazlı son tüketim, son satın alma ve hareket analizleri için SAP 'de Stok Etkinlik Raporu tasarlanmıştır.
+Kullanımı olmayan ve düşük hareketli malzemeler için aksiyon takip listeleri oluşturulmuştur.
+Açık SAT ve SAS süreçleri analiz edilerek geçmiş tarihli kayıtların kapatılması için takip mekanizması kurulmuştur.
+Emniyet stokları belirli malzeme grupları için tanımlanmış ve düzenli takip edilmeye başlanmıştır.
+Stok bölünmesine neden olan mükerrer malzeme kodları için inceleme çalışmaları yapılmıştır.
+Belirli malzeme gruplarında kullanılmayan kodların pasiflenmesi sağlanmıştır.
+Yaşlı stokların kullanım, transfer, iade, satış ve bertaraf süreçleri için ilgili ekiplerle aksiyon çalışmaları başlatılmıştır.
+ABC &amp; XYZ analizleri revize edilerek stok önceliklendirme yapısı güncellenmiştir.</t>
+  </si>
+  <si>
+    <t>Düşük hareketli ve atıl stoklar için aksiyon yönetim sürecinin standardize edilmesi.
+Açık SAT ve SAS süreçleri için otomatik takip ve uyarı mekanizmasının geliştirilmesi.
+Yaşlı stoklar için satış, iade ve bertaraf süreçlerinin hızlandırılması.
+Satın alma süreçlerinde ihtiyaç fazlası stok oluşumunu önleyecek kontrol yapılarının geliştirilmesi
+Depo ve planlama ekipleri için stok verimliliği odaklı süreç eğitimlerinin gerçekleştirilmesi.</t>
+  </si>
+  <si>
+    <t>Akıllı Görsel Eşleştirme ile Stok Optimizasyonu</t>
+  </si>
+  <si>
+    <t>İşletmede kullanılan malzemelere ait görsellerin dijital bir arşiv altında toplanarak envanter yönetim süreçlerine entegre edilmesini amaçlamaktadır. Görsel arama ve akıllı eşleştirme teknolojileri sayesinde, benzer ve mükerrer malzeme kodlarının tespiti, doğru malzeme seçiminin desteklenmesi ve stok yapısının sadeleştirilmesi hedeflenmektedir.
+Proje kapsamında; malzemelerin görsel kimliklendirilmesi, merkezi bir veri yapısında yönetilmesi ve ilgili sistemlerle entegre edilmesi sağlanarak, stok doğruluğu artırılacak, satın alma ve planlama süreçleri daha etkin hale getirilecek ve gereksiz stok oluşumu azaltılacaktır.</t>
+  </si>
+  <si>
+    <t>Görsel arşiv altyapısı oluşturulmuş ve merkezi veri yapısı kurulmuştur.
+İşletme malzemelerine ait ~2500 görsel dijital ortama aktarılmıştır. ( Stoklu  SKU lar için %62 tamamlanmıştır)
+Görseller, ilgili malzeme kodları ile eşleştirilerek standart bir isimlendirme yapısı oluşturulmuştur.
+Görsel çekim, arşivleme ve güncelleme süreçlerine yönelik standartlar belirlenmiştir.
+Görsel arama ve benzer ürün eşleştirme (SKUMATCH) uygulaması devreye alınmıştır.
+Referans görsel veri seti oluşturularak sistemin öğrenme altyapısı hazırlanmıştır.
+Uygulamanın kullanımına yönelik ilk bilgilendirme ve tanıtım çalışmaları gerçekleştirilmiştir.</t>
+  </si>
+  <si>
+    <t>Görsel arşivin SAP malzeme kartları ile entegrasyonunun sağlanması
+SKUMATCH uygulamasının tüm ilgili ekiplerde aktif kullanımının yaygınlaştırılması
+Arama sonuçlarına stok miktarı ve lokasyon bilgilerinin eklenmesi
+Yeni malzeme girişlerinde zorunlu görsel ekleme kuralının devreye alınması
+Görsel arşivin haftalık / aylık periyotlarla düzenli güncellenmesi
+Benzer ve mükerrer malzeme kodlarının sistematik olarak tespit edilmesi ve aksiyon planlarının oluşturulması
+180+ stoklar için görsel eşleştirme destekli satış / iade / alternatif kullanım çalışmalarının başlatılması
+Mobil kullanım (telefon/tablet) altyapısının geliştirilmesi
+Kullanım performansı ve fayda analizine yönelik raporlama ve KPI yapısının oluşturulması
+Kullanıcı eğitimleri ve saha adaptasyon sürecinin tamamlanması
+Görsel kalite standardının artırılması (arka plan, açı, çözünürlük vb.)</t>
+  </si>
+  <si>
+    <t>Malzeme Kod Yapısının Sadeleştirilmesi ve Atıl Kod Yönetimi</t>
+  </si>
+  <si>
+    <t>Bu proje, işletmede kullanılan malzeme kod yapısının sadeleştirilmesi ve daha etkin yönetilmesini amaçlamaktadır. Mevcut sistemde yer alan kullanılmayan, mükerrer veya düşük hareketli malzeme kodlarının tespit edilerek yönetilebilir hale getirilmesi hedeflenmektedir.
+Proje kapsamında; aktif ve pasif malzeme kodları ayrıştırılacak, gereksiz kodların azaltılması sağlanacak ve yeni kod açılış süreçleri kontrol altına alınacaktır. Böylece stok yapısı daha şeffaf hale gelecek, planlama ve satın alma süreçleri daha sağlıklı veri üzerinden yürütülecek ve gereksiz stok oluşumunun önüne geçilecektir.</t>
+  </si>
+  <si>
+    <t>KS02 malzeme türleri için detaylı analiz çalışması gerçekleştirilmiştir
+İlgili malzeme kodları için SAT, SAS, kod yaşı ve hareket analizleri yapılmıştır
+Son tüketim ve hareket verilerine göre kullanılmayan hareketsiz kodlar tespit edilmiştir
+KS02 kapsamında yapılan analizler ile yaklaşık 3000 atıl malzeme kodu sistemden ayrıştırılmıştır.
+Analiz kapsamında 2025–2026 yıllarında açılan yeni kodlar hariç tutulmuştur</t>
+  </si>
+  <si>
+    <t>Mükerrer ve benzer malzeme kodları ana veri seviyesinde gözden geçirilerek birleştirilecektir
+Yeni malzeme kodu açılış süreci belirli kurallar ve onay mekanizması ile kontrollü hale getirilecektir
+Tüm organizasyonda kullanılmak üzere standart bir kod isimlendirme yapısı oluşturulacaktır
+Görsel arşiv (SKUMATCH) ile malzeme ana veri süreci entegre edilerek doğru kod seçimi desteklenecektir
+Malzeme ana veri kalitesi belirli KPI’lar ile düzenli olarak izlenecek ve raporlanacaktır
+Belirli periyotlarda (aylık/çeyreklik) ana veri temizlik ve kontrol süreci işletilecektir</t>
   </si>
   <si>
     <t>Lojistik</t>
@@ -1145,15 +1216,87 @@
     <t>E-İhale faaliyetlerinin dijital, şeffaf, izlenebilir ve standart bir yapıya kavuşturulması amaçlanmaktadır. İhale planlama, teklif toplama, değerlendirme, onay ve raporlama süreçlerinin sistem üzerinden yönetilmesi, manuel ve e-posta bazlı süreçlerin ortadan kaldırılması hedeflenmektedir.</t>
   </si>
   <si>
-    <t xml:space="preserve">Teknik SA kategorisinde teklifler, siparişler ihaleler dijital olarak SRM üzerinden toplanmaktadır. (3600+ işlem)
-Yeni cari tanımlarında vSRM dijital uygulaması ve BP entegrasyonu devreye alınmış ve 87 yeni cari kaydı vSRM üzerinden yapılmıştır.
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Teknik SA kategorisinde teklifler, siparişler ihaleler dijital olarak SRM üzerinden toplanmaktadır. (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">4400+ işlem)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Yeni cari tanımlarında vSRM dijital uygulaması ve BP entegrasyonu devreye alınmış ve </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>105</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> yeni cari kaydı vSRM üzerinden yapılmıştır.
 Satın alma ihalesinde açık artırma parametresinin uygulamaya dahil edilmesi.
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satış ihalesi sürecinin SRM’ e tanımlanması. 
-SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır.
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır, eğitimler ilgili kategorilere verilmiş ve teklif toplama denemelerine geçilmiştir. Bölgesel SA (5 işlem yapıldı) ve Merkezi SA (2 işlem yapıldı) kategorileri ilk denemelerini yapmıştır. Hammadde SA da firmalara vSRM üzerinden teklife çıkılacak bilgisi yayınlanmıştır.
 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Satış ihalesi sürecinin SRM’ e tanımlanması. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır.
+</t>
+    </r>
   </si>
   <si>
     <t>DÖF Modülünün Devreye Alınması</t>
@@ -1162,11 +1305,55 @@
     <t>Tedarikçi kaynaklı uygunsuzluklar, denetim bulguları, performans düşüşleri ve şikâyetler sonucunda başlatılan Düzeltici ve Önleyici Faaliyet (DÖF) süreçlerinin SRM sistemi üzerinden dijital, izlenebilir ve standart bir yapıya kavuşturulması amaçlanmaktadır. DÖF açma, takip etme, aksiyonların izlenmesi ve kapanış süreçlerinin manuel ve dağınık yöntemler yerine tek bir merkezi sistem üzerinden yönetilmesi hedeflenmektedir.</t>
   </si>
   <si>
-    <t>Ambalaj kategorisinde Kalite Birimi tarafından aktif kullanılmaktadır.</t>
-  </si>
-  <si>
-    <t>Diğer SA kategorilerinde DÖF modülünün kullanılması yaygınlaştırılacaktır. Örnek Hammadde için Ar-Ge girdi kontrol kullanımı.
-Kategorilerde denetim kayıtlarının vSRM üzerinden yürütülmesi ve tedarikçiye iletilmesi.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ambalaj kategorisinde Kalite Birimi tarafından aktif kullanılmaktadır.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hammadde kategorsinde girdi kontrolde DÖF uygulaması için eğitimler verilmiştir.İlk örnek Sibelco firması üzerinden gelen uygun olmayan red için yapılmaktadır.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Diğer SA kategorilerinde DÖF modülünün kullanılması yaygınlaştırılacaktır. Örnek Hammadde için Ar-Ge girdi kontrol kullanımı.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kategorilerde denetim kayıtlarının vSRM üzerinden yürütülmesi ve tedarikçiye iletilmesi.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Diğer kategorilerin DÖF kullanımına geçilecek.</t>
+    </r>
   </si>
   <si>
     <t>Sipariş Modülü İyileştirme ve Yaygınlaştırma</t>
@@ -1175,17 +1362,43 @@
     <t>SRM Sipariş Modülünün kullanım etkinliğini artırmak, mevcut kullanım problemlerini gidermek ve satın alma–tedarikçi süreçleri arasında daha hızlı, hatasız ve izlenebilir bir sipariş yönetimi sağlamak amaçlanmaktadır.</t>
   </si>
   <si>
-    <t>Faz 1; Tedarikçi bazında kullanım (siparişlerin onayı ve irsaliye girişleri) oranlarının arttırılması ve süreç işlemlerin (SAS) iyileştirilmesi sağlanmıştır. 32 tedarikçinin % 58’ inde kullanıma geçilmiştir. 
+    <t xml:space="preserve">Faz 1; Tedarikçi bazında kullanım (siparişlerin onayı ve irsaliye girişleri) oranlarının arttırılması ve süreç işlemlerin (SAS) iyileştirilmesi sağlanmıştır. 32 tedarikçinin % 58’ inde kullanıma geçilmiştir. 
 Teknik Satın alma kategorisinde hizmet alanında teklif ve siparişlerin oluşturulması %100 oranında devreye alınmıştır, stok kodlu alımlarda da kullanılmaya başlanmıştır.
 Bölgesel ve Merkezi Hizmet kategorisinde ilgili sipariş modulü eğitimi alınmıştır.
-Teknik hizmet iş kabullerinde VSRM üzerinden gerekli süreç tamamlanmıştır, 01.04.2026 tarihinde devreye alınmıştır.</t>
-  </si>
-  <si>
-    <t>Bölgesel Hizmet ve Merkezi Satın alma kategorilerinde sipariş modülü kullanıma başlanacaktır.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Bölgesel Hizmet ve Merkezi Satın alma kategorilerinde sipariş modülü kullanıma başlanacaktır.
 Bölgesel Hizmet kategorisi için ilgili kullanıcılara (talep sahibi, tedarikçi) süreç hakkında bilgi verilecektir. Talepler vSRM üzerinden alınarak satın alma süreci başlatılacaktır.        
 vSRM dışı talep kabul edilmeyecektir. Taleplerin vSRM üzerinden alınması planlanmaktadır.
 vSRM kullanımı sipariş girişi sağlayan ambar birimlerine yaygınlaştırılacaktır.
-Siparişlerin hızlanması için vSRM üzerinden SAT açılması işlemlerinin otomatik olarak çalışması yapılmaktadır. Mayıs ayına kadar tamamlanması planlanmaktadır.</t>
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Siparişlerin hızlanması için vSRM üzerinden SAT açılması işlemlerinin otomatik olarak çalışması yapılmaktadır. Haziran ayına kadar tamamlanması planlanmaktadır</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. (Üzerinde çalışılıyor.)</t>
+    </r>
   </si>
   <si>
     <t>Tedarikçi Değerlendirme Sür. İyileştirilmesi</t>
@@ -1216,8 +1429,25 @@
     <t>Mevcut tedarikçilerin performans, kalite, maliyet, teslimat, sürdürülebilirlik ve uyum kriterleri doğrultusunda geliştirilmesini sağlamak; tedarik zincirinin genel verimliliğini ve sürekliliğini artırmak amaçlanmaktadır. Tedarikçi performansının sistematik olarak izlenmesi, gelişim alanlarının belirlenmesi ve bu alanlara yönelik yapılandırılmış geliştirme planlarının hayata geçirilmesi hedeflenmektedir.</t>
   </si>
   <si>
-    <t>Tedarikçilerimizin verdiği teknik eğitimlerle hem kendi kullanıcımız hem de tedarikçimizin ürününün doğru kullanılması ile optimum sonuçlara ulaşılmaktadır.
-Ambalaj ve Tamamlayıcılar kategorisinde tedarikçilerimize açtığımız DÖF’ler ile ilgili malzeme geliştirmeleri yapılmakta ve bilgiler vSRM sistemi üzerinden kayda alınmaktadır.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tedarikçilerimizin verdiği teknik eğitimlerle hem kendi kullanıcımız hem de tedarikçimizin ürününün doğru kullanılması ile optimum sonuçlara ulaşılmaktadır.
+Ambalaj ve Tamamlayıcılar kategorisinde tedarikçilerimize açtığımız DÖF’ler ile ilgili malzeme geliştirmeleri yapılmakta ve bilgiler vSRM sistemi üzerinden kayda alınmaktadır. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tedarikçilerimizin kullanıcılara verdiği eğitimler devam etmektedir. 2. etap pnömatik sistem eğitimleri verilmiştir.</t>
+    </r>
   </si>
   <si>
     <t>DÖF yapısının vSRM modülü üzerinden Bölgesel ve Merkezi hizmet, Ambalaj ve Tamamlayıcılar, Hammadde ve Kimyasallar kategorisine de yaygınlaştırılması sağlanacaktır.
@@ -1245,8 +1475,25 @@
     <t xml:space="preserve">Belirli bir geliştirme planına bağlı olarak önceliklendirilen kategori, malzeme ve hizmet gruplarında en iyi uygulamaları öğrenmek, yetkinlikleri geliştirmek ve grup için kırılımlı maliyet yapısının sistematik veri olarak elde edilmesini de sağlayacak faaliyetleri içeren çalışmadır. </t>
   </si>
   <si>
-    <t>Tedarikçi Benchmark çalışmaları yapılmıştır. 2 grup halinde farklı iki firma olan Sofra firması ve Dalgakıran firmaları satınalma yapısı olarak incelenmiştir. Sofra firmasından tedarikçi değerlendirme anlamında örnekler alınmıştır. 
-Çin pazarı tedarik ürünler satınalmasında Know how gelişimi için Trome firmasıyla aktif çalışmaya başlanılmıştır.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tedarikçi Benchmark çalışmaları yapılmıştır. 2 grup halinde farklı iki firma olan Sofra firması ve Dalgakıran firmaları satınalma yapısı olarak incelenmiştir. Sofra firmasından tedarikçi değerlendirme anlamında örnekler alınmıştır. 
+Çin pazarı tedarik ürünler satınalmasında Know how gelişimi için Trome firmasıyla aktif çalışmaya başlanılmıştır. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Personel Servis tedarikçimiz Gürsel firması ile know-how geliştirme anlamında deneyim paylaşım toplantısı yapıldı, içerik olarak firmanın temel hedefi olarak taşıyacağı kişiyi zamanında, güvenli şekilde ulaştırma ve bunu yaparken çok sade bir yapıda yönetim yapıldığı bizim ekibe aktarılmıştır.</t>
+    </r>
   </si>
   <si>
     <t>Maliyet yapıları ve fiyat kırılımları bilgisinin geliştirilmesi.
@@ -1276,7 +1523,33 @@
     <t>Fatura kayıt süreçlerinde gerçekleştirilen manuel, tekrarlayan ve zaman alan işlemlerin Robotik Proses Otomasyonu (RPA) ile otomatikleştirilerek; işlem sürelerinin kısaltılması, hata oranlarının azaltılması ve satın alma/mali işler süreçlerinde verimliliğin artırılması amaçlanmaktadır.</t>
   </si>
   <si>
-    <t>Robot tarafından kayıt edilmesi planlanan tedarikçiler belirlenmiş, sisteme ……….. cari tanımlanmıştır.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Robot tarafından kayıt edilmesi planlanan tedarikçiler belirlenmiş, sisteme </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">99 cari </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tanımlanmıştır.</t>
+    </r>
   </si>
   <si>
     <t>Döviz bazlı faturaların RPA sürecine dahil edilmesi.
@@ -1289,8 +1562,34 @@
     <t>Satın alma taleplerinin standart, doğru, eksiksiz ve izlenebilir şekilde oluşturulmasını sağlamak; satın alma süreçlerinde yaşanan gecikmeleri, tekrarları ve hatalı talepleri azaltmak amaçlanmaktadır.</t>
   </si>
   <si>
-    <t>Satın alma taleplerinin Teknik SA kategorisinde e-posta/telefon yerine SRM sistemi üzerinden alınıp yürütülmektedir.
-Teknik satınalma kategorisinde talepler teknik dokümanlar la birlikte SRM sistemi üzerinden alınmaya başlanmış ve tedarikçiye yine SRM sistemi üzerinden ihale, teklif toplama vb. şeklinde iletilmektedir.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Satın alma taleplerinin Teknik SA kategorisinde e-posta/telefon yerine SRM sistemi üzerinden alınıp yürütülmektedir.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> % 100 Hizmette geçildi.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Teknik satınalma kategorisinde talepler teknik dokümanlar la birlikte SRM sistemi üzerinden alınmaya başlanmış ve tedarikçiye yine SRM sistemi üzerinden ihale, teklif toplama vb. şeklinde iletilmektedir.</t>
+    </r>
   </si>
   <si>
     <t>SRM sistemi işlemlerinde Hizmet SAT’ larının talep sahibi onayı ile otomatik olarak SAP sisteminde yaratılması ve SRM sistemi ile entegre olması planlanmaktadır.</t>
@@ -1302,12 +1601,28 @@
     <t>Teknik hizmetlerin (bakım, onarım, montaj, mühendislik, servis vb.) sözleşme, teknik şartname ve kalite beklentilerine uygunluğunun sistematik, standart ve izlenebilir şekilde kontrol sürecinin SRM sisteminde yapılması amaçlanmaktadır.</t>
   </si>
   <si>
-    <t>Teknik hizmet alımlarında alınan hizmetin kontrolü E-flow sisteminde yer alan uygulama ile yapılmakta; talep sahipleri faturalara dijital onay vermektedir.</t>
-  </si>
-  <si>
-    <t>Firma tarafından hizmet teslimi onayı
-Talep sahibi ve üst amir onayı
-Firmaya fatura düzenlenmesi için bilgi kaydı 
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Teknik hizmet alımlarında alınan hizmetin kontrolü E-flow sisteminde yer alan uygulama ile yapılmakta; talep sahipleri faturalara dijital onay vermektedir. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Teknik hizmet iş kabullerinde VSRM üzerinden gerekli süreç tamamlanmıştır, 01.04.2026 tarihinde devreye alınmıştır. Firma tarafından hizmet teslimi onayı
+Talep sahibi ve üst amir onayı</t>
+    </r>
+  </si>
+  <si>
+    <t>Firmaya fatura düzenlenmesi için bilgi kaydı 
 Faturanın sistem tarafından ön kaydının yapılması</t>
   </si>
   <si>
@@ -1795,6 +2110,9 @@
 Dijital dönüşüm yol haritasındaki AI/ML ve dijital ikiz projeleri için ölçeklenebilir analitik bir temel oluşturulacak,​
 Üretim, kalite, bakım ve enerji ekiplerinin aynı veri dili üzerinden konuşabildiği ortak bir analitik çerçeve oluşturulacaktır.​</t>
   </si>
+  <si>
+    <t>Görsel Arşiv Çalışması</t>
+  </si>
 </sst>
 </file>
 
@@ -1803,7 +2121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1844,9 +2162,28 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
@@ -1880,7 +2217,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1927,7 +2264,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2274,7 +2620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
@@ -2335,7 +2681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="244.9">
+    <row r="2" spans="1:13" ht="174">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -2374,7 +2720,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="57.6">
+    <row r="3" spans="1:13" ht="72.599999999999994">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -2413,7 +2759,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="144">
+    <row r="4" spans="1:13" ht="188.45">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -2452,7 +2798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="28.9">
+    <row r="5" spans="1:13" ht="43.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -2491,7 +2837,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="57.6">
+    <row r="6" spans="1:13" ht="87">
       <c r="A6" s="10">
         <v>1</v>
       </c>
@@ -2521,7 +2867,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="28.9">
+    <row r="7" spans="1:13" ht="43.5">
       <c r="A7" s="10">
         <v>1</v>
       </c>
@@ -2551,7 +2897,7 @@
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="28.9">
+    <row r="8" spans="1:13" ht="43.5">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -2581,7 +2927,7 @@
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="28.9">
+    <row r="9" spans="1:13" ht="43.5">
       <c r="A9" s="10">
         <v>1</v>
       </c>
@@ -2611,7 +2957,7 @@
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="28.9">
+    <row r="10" spans="1:13" ht="43.5">
       <c r="A10" s="10">
         <v>1</v>
       </c>
@@ -2643,7 +2989,7 @@
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="28.9">
+    <row r="11" spans="1:13" ht="43.5">
       <c r="A11" s="10">
         <v>1</v>
       </c>
@@ -2675,7 +3021,7 @@
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="144">
+    <row r="12" spans="1:13" ht="101.45">
       <c r="A12" s="10">
         <v>1</v>
       </c>
@@ -2714,7 +3060,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="129.6">
+    <row r="13" spans="1:13" ht="116.1">
       <c r="A13" s="10">
         <v>1</v>
       </c>
@@ -2751,7 +3097,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="86.45">
+    <row r="14" spans="1:13" ht="87">
       <c r="A14" s="10">
         <v>1</v>
       </c>
@@ -2790,7 +3136,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="57.6">
+    <row r="15" spans="1:13" ht="87">
       <c r="A15" s="10">
         <v>1</v>
       </c>
@@ -2822,7 +3168,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="43.15">
+    <row r="16" spans="1:13" ht="57.95">
       <c r="A16" s="10">
         <v>1</v>
       </c>
@@ -2854,7 +3200,7 @@
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:13" ht="172.9">
+    <row r="17" spans="1:13" ht="130.5">
       <c r="A17" s="10">
         <v>1</v>
       </c>
@@ -2891,7 +3237,7 @@
       </c>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="129.6">
+    <row r="18" spans="1:13" ht="116.1">
       <c r="A18" s="10">
         <v>1</v>
       </c>
@@ -2930,7 +3276,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="86.45">
+    <row r="19" spans="1:13" ht="72.599999999999994">
       <c r="A19" s="10">
         <v>1</v>
       </c>
@@ -2969,7 +3315,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="115.15">
+    <row r="20" spans="1:13" ht="116.1">
       <c r="A20" s="10">
         <v>1</v>
       </c>
@@ -3010,7 +3356,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="57.6">
+    <row r="21" spans="1:13" ht="72.599999999999994">
       <c r="A21" s="10">
         <v>1</v>
       </c>
@@ -3046,7 +3392,7 @@
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:13" ht="28.9">
+    <row r="22" spans="1:13" ht="43.5">
       <c r="A22" s="10">
         <v>1</v>
       </c>
@@ -3080,7 +3426,7 @@
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:13" ht="57.6">
+    <row r="23" spans="1:13" ht="101.45">
       <c r="A23" s="10">
         <v>1</v>
       </c>
@@ -3116,7 +3462,7 @@
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:13" ht="100.9">
+    <row r="24" spans="1:13" ht="116.1">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -3155,7 +3501,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="28.9">
+    <row r="25" spans="1:13" ht="43.5">
       <c r="A25" s="10">
         <v>1</v>
       </c>
@@ -3192,7 +3538,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="28.9">
+    <row r="26" spans="1:13" ht="43.5">
       <c r="A26" s="10">
         <v>1</v>
       </c>
@@ -3229,7 +3575,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="144">
+    <row r="27" spans="1:13" ht="144.94999999999999">
       <c r="A27" s="10">
         <v>2</v>
       </c>
@@ -3265,7 +3611,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="115.15">
+    <row r="28" spans="1:13" ht="116.1">
       <c r="A28" s="10">
         <v>2</v>
       </c>
@@ -3302,7 +3648,7 @@
       </c>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" ht="28.9">
+    <row r="29" spans="1:13" ht="43.5">
       <c r="A29" s="10">
         <v>2</v>
       </c>
@@ -3334,7 +3680,7 @@
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:13" ht="28.9">
+    <row r="30" spans="1:13" ht="43.5">
       <c r="A30" s="10">
         <v>2</v>
       </c>
@@ -3404,7 +3750,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="129.6">
+    <row r="32" spans="1:13" ht="101.45">
       <c r="A32" s="10">
         <v>2</v>
       </c>
@@ -3629,187 +3975,185 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="318">
+    <row r="38" spans="1:13" ht="187.5" customHeight="1">
       <c r="A38" s="10">
+        <v>2</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="10">
         <v>3</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="D38" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="C38" s="10">
-        <v>1</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="12">
-        <v>45839</v>
+        <v>46023</v>
       </c>
       <c r="I38" s="12">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="M38" s="16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="158.44999999999999">
+        <v>160</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="187.5" customHeight="1">
       <c r="A39" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C39" s="10">
         <v>2</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="12">
-        <v>45809</v>
+        <v>45901</v>
       </c>
       <c r="I39" s="12">
-        <v>46173</v>
+        <v>46387</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="43.15">
+        <v>164</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="M39" s="14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="187.5" customHeight="1">
       <c r="A40" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C40" s="10">
         <v>2</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="E40" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="12">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="I40" s="12">
-        <v>46173</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>46387</v>
+      </c>
+      <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="115.5">
+        <v>168</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="318">
       <c r="A41" s="10">
         <v>3</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C41" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="12">
-        <v>45962</v>
+        <v>45839</v>
       </c>
       <c r="I41" s="12">
-        <v>46022</v>
+        <v>46203</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K41" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="M41" s="1"/>
-    </row>
-    <row r="42" spans="1:13" ht="409.6">
+    </row>
+    <row r="42" spans="1:13" ht="144.75">
       <c r="A42" s="10">
         <v>3</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G42" s="3" t="s">
         <v>180</v>
       </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="12">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="I42" s="12">
-        <v>46203</v>
+        <v>46173</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>17</v>
@@ -3817,194 +4161,194 @@
       <c r="K42" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="L42" s="14" t="s">
         <v>182</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="144">
+    <row r="43" spans="1:13" ht="72.75">
       <c r="A43" s="10">
         <v>3</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="C43" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="12">
-        <v>45992</v>
+        <v>46113</v>
       </c>
       <c r="I43" s="12">
-        <v>46170</v>
+        <v>46173</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K43" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="M43" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L43" s="1" t="s">
+    </row>
+    <row r="44" spans="1:13" ht="115.5">
+      <c r="A44" s="10">
+        <v>3</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="10">
+        <v>2</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="129.6">
-      <c r="A44" s="10">
-        <v>4</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C44" s="10">
-        <v>1</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="12">
-        <v>45870</v>
+        <v>45962</v>
       </c>
       <c r="I44" s="12">
-        <v>46234</v>
+        <v>46022</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="57.6">
+        <v>189</v>
+      </c>
+      <c r="L44" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="M44" s="1"/>
+    </row>
+    <row r="45" spans="1:13" ht="409.6">
       <c r="A45" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="C45" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="G45" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G45" s="3"/>
       <c r="H45" s="12">
-        <v>45962</v>
+        <v>45778</v>
       </c>
       <c r="I45" s="12">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K45" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L45" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="144.75">
+      <c r="A46" s="10">
+        <v>3</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" s="10">
+        <v>3</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="57.6">
-      <c r="A46" s="10">
-        <v>4</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C46" s="10">
-        <v>1</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="12">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I46" s="12">
-        <v>46173</v>
+        <v>46170</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
+      </c>
+      <c r="L46" s="14" t="s">
+        <v>200</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="129.6">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="87">
       <c r="A47" s="10">
         <v>4</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C47" s="10">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>205</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="12">
-        <v>45931</v>
+        <v>45870</v>
       </c>
       <c r="I47" s="12">
-        <v>46265</v>
+        <v>46234</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>17</v>
@@ -4012,190 +4356,193 @@
       <c r="K47" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="L47" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="M47" s="4" t="s">
+      <c r="M47" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="57.6">
+    <row r="48" spans="1:13" ht="101.25">
       <c r="A48" s="10">
         <v>4</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C48" s="10">
         <v>1</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>211</v>
-      </c>
+      <c r="G48" s="3"/>
       <c r="H48" s="12">
         <v>45962</v>
       </c>
       <c r="I48" s="12">
-        <v>46356</v>
+        <v>46265</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K48" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="L48" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="M48" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="86.45">
+    </row>
+    <row r="49" spans="1:13" ht="87">
       <c r="A49" s="10">
         <v>4</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C49" s="10">
         <v>1</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="12">
-        <v>45962</v>
+        <v>46023</v>
       </c>
       <c r="I49" s="12">
-        <v>46265</v>
+        <v>46173</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
+      </c>
+      <c r="L49" s="14" t="s">
+        <v>215</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="28.9">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="130.5">
       <c r="A50" s="10">
         <v>4</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C50" s="10">
         <v>1</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I50" s="12">
-        <v>46295</v>
+        <v>46265</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="86.45">
+        <v>218</v>
+      </c>
+      <c r="L50" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="57.95">
       <c r="A51" s="10">
         <v>4</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C51" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H51" s="12">
+        <v>45962</v>
+      </c>
+      <c r="I51" s="12">
+        <v>46356</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="L51" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="M51" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G51" s="3"/>
-      <c r="H51" s="12">
-        <v>45931</v>
-      </c>
-      <c r="I51" s="12">
-        <v>46203</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="100.9">
+    </row>
+    <row r="52" spans="1:13" ht="87">
       <c r="A52" s="10">
         <v>4</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C52" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="12">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I52" s="12">
         <v>46265</v>
@@ -4204,236 +4551,229 @@
         <v>17</v>
       </c>
       <c r="K52" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="M52" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="57.6">
+    </row>
+    <row r="53" spans="1:13" ht="43.5">
       <c r="A53" s="10">
         <v>4</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C53" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="12">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="I53" s="12">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K53" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="M53" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="86.45">
+    </row>
+    <row r="54" spans="1:13" ht="72.599999999999994">
       <c r="A54" s="10">
         <v>4</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C54" s="10">
         <v>2</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E54" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="12">
-        <v>45809</v>
+        <v>45931</v>
       </c>
       <c r="I54" s="12">
-        <v>46326</v>
+        <v>46203</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="K54" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="L54" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="L54" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="115.15">
+    </row>
+    <row r="55" spans="1:13" ht="101.45">
       <c r="A55" s="10">
         <v>4</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C55" s="10">
         <v>2</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="12">
-        <v>45992</v>
+        <v>45931</v>
       </c>
       <c r="I55" s="12">
-        <v>46387</v>
+        <v>46265</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K55" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L55" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="L55" s="1" t="s">
+      <c r="M55" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="M55" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="86.45">
+    </row>
+    <row r="56" spans="1:13" ht="87">
       <c r="A56" s="10">
         <v>4</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C56" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="12">
         <v>45931</v>
       </c>
       <c r="I56" s="12">
-        <v>46265</v>
+        <v>46387</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K56" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="130.5">
+      <c r="A57" s="10">
+        <v>4</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C57" s="10">
+        <v>2</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="F57" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="M56" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="86.45">
-      <c r="A57" s="10">
-        <v>5</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C57" s="10">
-        <v>1</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>257</v>
-      </c>
+      <c r="G57" s="3"/>
       <c r="H57" s="12">
-        <v>45931</v>
+        <v>45809</v>
       </c>
       <c r="I57" s="12">
-        <v>46203</v>
+        <v>46326</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="57.6">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="130.5">
       <c r="A58" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="C58" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="E58" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>257</v>
-      </c>
+      <c r="G58" s="3"/>
       <c r="H58" s="12">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I58" s="12">
         <v>46387</v>
@@ -4442,83 +4782,81 @@
         <v>17</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="L58" s="4" t="s">
-        <v>263</v>
+        <v>256</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="115.15">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="101.45">
       <c r="A59" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>253</v>
+        <v>202</v>
       </c>
       <c r="C59" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>257</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="G59" s="3"/>
       <c r="H59" s="12">
         <v>45931</v>
       </c>
       <c r="I59" s="12">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="86.45">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="94.5" customHeight="1">
       <c r="A60" s="10">
         <v>5</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C60" s="10">
         <v>1</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F60" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G60" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="H60" s="12">
         <v>45931</v>
       </c>
       <c r="I60" s="12">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>17</v>
@@ -4526,35 +4864,37 @@
       <c r="K60" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="L60" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M60" s="17" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="72">
+    <row r="61" spans="1:13" ht="101.25">
       <c r="A61" s="10">
         <v>5</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C61" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="G61" s="3"/>
+      <c r="G61" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="H61" s="12">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I61" s="12">
         <v>46387</v>
@@ -4563,113 +4903,122 @@
         <v>17</v>
       </c>
       <c r="K61" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="M61" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="L61" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="115.15">
+    </row>
+    <row r="62" spans="1:13" ht="188.25">
       <c r="A62" s="10">
         <v>5</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C62" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="F62" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="H62" s="12">
+        <v>45931</v>
+      </c>
+      <c r="I62" s="12">
+        <v>46203</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="L62" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="G62" s="3"/>
-      <c r="H62" s="12">
-        <v>46174</v>
-      </c>
-      <c r="I62" s="12">
-        <v>46387</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K62" s="3" t="s">
+      <c r="M62" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="L62" s="4"/>
-    </row>
-    <row r="63" spans="1:13" ht="72">
+    </row>
+    <row r="63" spans="1:13" ht="72.75">
       <c r="A63" s="10">
         <v>5</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C63" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="G63" s="3"/>
+      <c r="G63" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="H63" s="12">
-        <v>46054</v>
+        <v>45931</v>
       </c>
       <c r="I63" s="12">
-        <v>46356</v>
+        <v>46295</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K63" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="M63" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="L63" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="28.9">
+    </row>
+    <row r="64" spans="1:13" ht="130.5">
       <c r="A64" s="10">
         <v>5</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C64" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>287</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I64" s="12">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>17</v>
@@ -4677,74 +5026,69 @@
       <c r="K64" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="L64" s="1" t="s">
+      <c r="L64" s="16" t="s">
         <v>289</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="43.15">
+    <row r="65" spans="1:13" ht="159.6">
       <c r="A65" s="10">
         <v>5</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C65" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>292</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="12">
-        <v>45962</v>
+        <v>46174</v>
       </c>
       <c r="I65" s="12">
-        <v>46326</v>
+        <v>46387</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="72">
+        <v>292</v>
+      </c>
+      <c r="L65" s="4"/>
+    </row>
+    <row r="66" spans="1:13" ht="101.25">
       <c r="A66" s="10">
         <v>5</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C66" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>13</v>
+        <v>294</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="12">
-        <v>46113</v>
+        <v>46054</v>
       </c>
       <c r="I66" s="12">
         <v>46356</v>
@@ -4753,184 +5097,191 @@
         <v>17</v>
       </c>
       <c r="K66" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="L66" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="L66" s="1" t="s">
+      <c r="M66" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="M66" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="57.6">
+    </row>
+    <row r="67" spans="1:13" ht="43.5">
       <c r="A67" s="10">
         <v>5</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C67" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>13</v>
+        <v>294</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="12">
         <v>46023</v>
       </c>
       <c r="I67" s="12">
-        <v>46234</v>
+        <v>46203</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="K67" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="L67" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="L67" s="1" t="s">
+      <c r="M67" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="M67" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="43.15">
+    </row>
+    <row r="68" spans="1:13" ht="72.75">
       <c r="A68" s="10">
         <v>5</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C68" s="10">
         <v>4</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>13</v>
+        <v>237</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>304</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="12">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I68" s="12">
-        <v>46112</v>
+        <v>46326</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="L68" s="16" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" ht="43.15">
+      <c r="M68" s="19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="57.75">
       <c r="A69" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="C69" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D69" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="G69" s="3"/>
+      <c r="H69" s="12">
+        <v>46113</v>
+      </c>
+      <c r="I69" s="12">
+        <v>46356</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="L69" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="M69" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H69" s="12">
-        <v>45778</v>
-      </c>
-      <c r="I69" s="12">
-        <v>45869</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K69" s="3" t="s">
+    </row>
+    <row r="70" spans="1:13" ht="57.75">
+      <c r="A70" s="10">
+        <v>5</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C70" s="10">
+        <v>4</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="M69" s="1"/>
-    </row>
-    <row r="70" spans="1:13" ht="43.15">
-      <c r="A70" s="10">
-        <v>6</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C70" s="10">
-        <v>1</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F70" s="3" t="s">
+      <c r="G70" s="3"/>
+      <c r="H70" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I70" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="H70" s="12">
-        <v>45931</v>
-      </c>
-      <c r="I70" s="12">
-        <v>46053</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="M70" s="1"/>
-    </row>
-    <row r="71" spans="1:13" ht="129.6">
+      <c r="L70" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="43.5">
       <c r="A71" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="C71" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>309</v>
+        <v>13</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>311</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="G71" s="3"/>
       <c r="H71" s="12">
         <v>45931</v>
       </c>
@@ -4941,232 +5292,241 @@
         <v>57</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="M71" s="1"/>
-    </row>
-    <row r="72" spans="1:13" ht="72">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="72.599999999999994">
       <c r="A72" s="10">
         <v>6</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C72" s="10">
         <v>1</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H72" s="12">
-        <v>46023</v>
+        <v>45778</v>
       </c>
       <c r="I72" s="12">
-        <v>46387</v>
+        <v>45869</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>317</v>
+        <v>57</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="M72" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="72">
+        <v>324</v>
+      </c>
+      <c r="M72" s="1"/>
+    </row>
+    <row r="73" spans="1:13" ht="72.599999999999994">
       <c r="A73" s="10">
         <v>6</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C73" s="10">
         <v>1</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H73" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I73" s="12">
-        <v>46387</v>
+        <v>46053</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>317</v>
+        <v>57</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="M73" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="28.9">
+        <v>324</v>
+      </c>
+      <c r="M73" s="1"/>
+    </row>
+    <row r="74" spans="1:13" ht="116.1">
       <c r="A74" s="10">
         <v>6</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C74" s="10">
         <v>1</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H74" s="12"/>
-      <c r="I74" s="12"/>
+        <v>323</v>
+      </c>
+      <c r="H74" s="12">
+        <v>45931</v>
+      </c>
+      <c r="I74" s="12">
+        <v>46112</v>
+      </c>
       <c r="J74" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K74" s="5"/>
-      <c r="L74" s="4"/>
-    </row>
-    <row r="75" spans="1:13" ht="28.9">
+        <v>57</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="M74" s="1"/>
+    </row>
+    <row r="75" spans="1:13" ht="116.1">
       <c r="A75" s="10">
         <v>6</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C75" s="10">
         <v>1</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F75" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G75" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G75" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="H75" s="12"/>
-      <c r="I75" s="12"/>
+      <c r="H75" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I75" s="12">
+        <v>46387</v>
+      </c>
       <c r="J75" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K75" s="5"/>
-      <c r="L75" s="4"/>
-    </row>
-    <row r="76" spans="1:13" ht="28.9">
+        <v>329</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="116.1">
       <c r="A76" s="10">
         <v>6</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C76" s="10">
         <v>1</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="E76" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H76" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I76" s="12">
+        <v>46387</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K76" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K76" s="5"/>
-      <c r="L76" s="4"/>
-    </row>
-    <row r="77" spans="1:13" ht="115.15">
+      <c r="M76" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="29.1">
       <c r="A77" s="10">
         <v>6</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C77" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="H77" s="12">
-        <v>46204</v>
-      </c>
-      <c r="I77" s="12">
-        <v>46387</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
       <c r="J77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="M77" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="129.6">
+        <v>70</v>
+      </c>
+      <c r="K77" s="5"/>
+      <c r="L77" s="4"/>
+    </row>
+    <row r="78" spans="1:13" ht="29.1">
       <c r="A78" s="10">
         <v>6</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C78" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>334</v>
@@ -5175,344 +5535,322 @@
         <v>335</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="H78" s="12">
-        <v>46023</v>
-      </c>
-      <c r="I78" s="12">
-        <v>46142</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
       <c r="J78" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="86.45">
+        <v>70</v>
+      </c>
+      <c r="K78" s="5"/>
+      <c r="L78" s="4"/>
+    </row>
+    <row r="79" spans="1:13" ht="29.1">
       <c r="A79" s="10">
         <v>6</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C79" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="H79" s="12">
-        <v>45992</v>
-      </c>
-      <c r="I79" s="12">
-        <v>46142</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
       <c r="J79" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="57.6">
+        <v>70</v>
+      </c>
+      <c r="K79" s="5"/>
+      <c r="L79" s="4"/>
+    </row>
+    <row r="80" spans="1:13" ht="116.1">
       <c r="A80" s="10">
         <v>6</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C80" s="10">
         <v>2</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="H80" s="12">
-        <v>46023</v>
+        <v>46204</v>
       </c>
       <c r="I80" s="12">
         <v>46387</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>317</v>
+        <v>31</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="158.44999999999999">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="116.1">
       <c r="A81" s="10">
         <v>6</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C81" s="10">
         <v>2</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="H81" s="12">
         <v>46023</v>
       </c>
       <c r="I81" s="12">
-        <v>46357</v>
+        <v>46142</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="100.9">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="101.45">
       <c r="A82" s="10">
         <v>6</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C82" s="10">
         <v>2</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="H82" s="12">
-        <v>45931</v>
+        <v>45992</v>
       </c>
       <c r="I82" s="12">
-        <v>46053</v>
+        <v>46142</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>57</v>
+        <v>329</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="115.15">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="116.1">
       <c r="A83" s="10">
         <v>6</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C83" s="10">
         <v>2</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>357</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="H83" s="12">
         <v>46023</v>
       </c>
       <c r="I83" s="12">
-        <v>46112</v>
+        <v>46387</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="M83" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="158.44999999999999">
+        <v>361</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="217.5">
       <c r="A84" s="10">
         <v>6</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C84" s="10">
         <v>2</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="H84" s="12">
         <v>46023</v>
       </c>
       <c r="I84" s="12">
-        <v>46203</v>
+        <v>46357</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="K84" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="L84" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="L84" s="1" t="s">
+      <c r="M84" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="57.6">
+    </row>
+    <row r="85" spans="1:13" ht="101.45">
       <c r="A85" s="10">
         <v>6</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C85" s="10">
         <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>370</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="H85" s="12">
-        <v>46174</v>
+        <v>45931</v>
       </c>
       <c r="I85" s="12">
-        <v>46295</v>
+        <v>46053</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="K85" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="L85" s="1" t="s">
+      <c r="L85" s="2" t="s">
         <v>372</v>
       </c>
       <c r="M85" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="86.45">
+    <row r="86" spans="1:13" ht="130.5">
       <c r="A86" s="10">
         <v>6</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C86" s="10">
         <v>2</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>374</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="H86" s="12">
         <v>46023</v>
       </c>
       <c r="I86" s="12">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>375</v>
@@ -5520,370 +5858,513 @@
       <c r="L86" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="M86" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="86.45">
+    <row r="87" spans="1:13" ht="130.5">
       <c r="A87" s="10">
         <v>6</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C87" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F87" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="G87" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H87" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I87" s="12">
+        <v>46203</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K87" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="L87" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="12">
-        <v>45931</v>
-      </c>
-      <c r="I87" s="12">
-        <v>46157</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="K87" s="3" t="s">
+      <c r="M87" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="L87" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="M87" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="43.15">
+    </row>
+    <row r="88" spans="1:13" ht="57.95">
       <c r="A88" s="10">
         <v>6</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C88" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="G88" s="3"/>
+        <v>382</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="H88" s="12">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="I88" s="12">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="J88" s="3" t="s">
         <v>31</v>
       </c>
       <c r="K88" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="M88" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="L88" s="4"/>
-      <c r="M88" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="100.9">
+    </row>
+    <row r="89" spans="1:13" ht="144.94999999999999">
       <c r="A89" s="10">
         <v>6</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C89" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>387</v>
+        <v>339</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="H89" s="12">
         <v>46023</v>
       </c>
       <c r="I89" s="12">
-        <v>46357</v>
+        <v>46142</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="72">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="101.45">
       <c r="A90" s="10">
         <v>6</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C90" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G90" s="3"/>
       <c r="H90" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I90" s="12">
-        <v>46082</v>
+        <v>46157</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>57</v>
+        <v>329</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="57.6">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="72.599999999999994">
       <c r="A91" s="10">
         <v>6</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C91" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="12">
-        <v>45901</v>
+        <v>46173</v>
       </c>
       <c r="I91" s="12">
-        <v>46112</v>
+        <v>46387</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>401</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="L91" s="4"/>
       <c r="M91" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="129.6">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="130.5">
       <c r="A92" s="10">
         <v>6</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C92" s="10">
         <v>4</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F92" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="H92" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I92" s="12">
+        <v>46357</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K92" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="12">
-        <v>45901</v>
-      </c>
-      <c r="I92" s="12">
-        <v>46112</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="K92" s="3" t="s">
+      <c r="L92" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="L92" s="2" t="s">
+      <c r="M92" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="M92" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="72">
+    </row>
+    <row r="93" spans="1:13" ht="57.95">
       <c r="A93" s="10">
         <v>6</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C93" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D93" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="F93" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>410</v>
-      </c>
+      <c r="G93" s="3"/>
       <c r="H93" s="12">
         <v>46023</v>
       </c>
       <c r="I93" s="12">
-        <v>46295</v>
+        <v>46082</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>317</v>
+        <v>57</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="57.6">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="72.599999999999994">
       <c r="A94" s="10">
         <v>6</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C94" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="E94" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G94" s="3"/>
+      <c r="H94" s="12">
+        <v>45901</v>
+      </c>
+      <c r="I94" s="12">
+        <v>46112</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="M94" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="H94" s="12">
-        <v>46023</v>
-      </c>
-      <c r="I94" s="12">
-        <v>46266</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="M94" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="72">
+    </row>
+    <row r="95" spans="1:13" ht="130.5">
       <c r="A95" s="10">
         <v>6</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C95" s="10">
+        <v>4</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="12">
+        <v>45901</v>
+      </c>
+      <c r="I95" s="12">
+        <v>46112</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="116.1">
+      <c r="A96" s="10">
+        <v>6</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C96" s="10">
         <v>5</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="F95" s="3" t="s">
+      <c r="D96" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="E96" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="H95" s="12">
+      <c r="F96" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H96" s="12">
         <v>46023</v>
       </c>
-      <c r="I95" s="12">
+      <c r="I96" s="12">
+        <v>46295</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="87">
+      <c r="A97" s="10">
+        <v>6</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C97" s="10">
+        <v>5</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="H97" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I97" s="12">
+        <v>46266</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="101.45">
+      <c r="A98" s="10">
+        <v>6</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C98" s="10">
+        <v>5</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="H98" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I98" s="12">
         <v>46357</v>
       </c>
-      <c r="J95" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="L95" s="4"/>
-      <c r="M95" s="2" t="s">
-        <v>422</v>
+      <c r="J98" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="L98" s="4"/>
+      <c r="M98" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="29.1">
+      <c r="A99" s="10">
+        <v>2</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C99" s="10">
+        <v>2</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>435</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M95">
-    <sortCondition ref="A9:A95"/>
-    <sortCondition ref="C9:C95"/>
-    <sortCondition ref="E9:E95"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M98">
+    <sortCondition ref="A9:A98"/>
+    <sortCondition ref="C9:C98"/>
+    <sortCondition ref="E9:E98"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/TZY Gelişim Planı/Gelişim Planı/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DCA5802-ED84-44BF-8474-FE4E0183729C}"/>
+  <xr:revisionPtr revIDLastSave="461" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1097A4-8374-47F8-A1BD-3AADB94BCC89}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects Data" sheetId="31" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects Data'!$A$2:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects Data'!$A$1:$M$101</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="438">
   <si>
     <t>department order</t>
   </si>
@@ -639,19 +639,26 @@
     <t>Şirketin üretim süreçlerinde kullanılan Malzeme İhtiyaç Planlaması (MRP) sisteminin mevcut yapısını analiz ederek daha etkin, esnek ve verimli bir planlama mekanizması oluşturmayı amaçlamaktadır. Proje kapsamında; talep tahminleri, stok seviyeleri, satın alma siparişleri ve üretim planları arasındaki entegrasyonun güçlendirilmesi hedeflenmektedir. Böylece, doğru malzemenin doğru zamanda ve doğru miktarda temin edilmesi sağlanarak maliyetlerin azaltılması, stok devir hızının artırılması ve müşteri teslim sürelerinin iyileştirilmesi planlanmaktadır.</t>
   </si>
   <si>
-    <t xml:space="preserve">
+    <t xml:space="preserve">MRP üzerinden oluşan ihtiyaç sinyalleri düzenli olarak analiz edilerek satınalma ve tedarik planlama süreçlerinde aktif olarak kullanılmaktadır.
+Sistem tarafından oluşan SAT kayıtları; stok yapısı, tüketim hareketleri, açık siparişler ve üretim planı ile birlikte değerlendirilerek aksiyona dönüştürülmektedir.
 KPI’lar (stok devir hızı, stok doğruluk oranı, müşteri teslim performansı vb.) üzerinden ölçülebilir iyileştirmeler hedeflenmiştir. 
 KS01 &amp; KS02 malzeme türlerine ait SKU’ların %30’u için emniyet stok seviyeleri tanımlanmış olup, kapsamın genişletilmesine yönelik çalışmalar devam etmektedir.
 MİP sürecinin sağlıklı çalışmasını desteklemek amacıyla geçmiş tarihli açık rezervasyonlar kapatılmış, süreç düzenli olarak izlenmektedir.
 Açık SAS ve SAT’lar haftalık raporlanmakta, geçmiş kayıtlar için aksiyon alınmaktadır.
 Malzeme ve aramamül kodları için ABC &amp; XYZ sınıflandırmaları aylık olarak güncellenmektedir.
 Emniyet stokları; tüketim frekansı ve min–max değerlere göre dinamik olarak hesaplanmaktadır.
+180+ stok yaşına sahip malzemeler için kırılım analizleri hazırlanmış ve düzenli takip yapısı oluşturulmuştur.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ERP/MRP yazılımında ihtiyaç duyulan iyileştirmeler ve otomasyonlar tanımlanacaktır.
+    <t xml:space="preserve">
+MRP doğruluğunu ve planlama etkinliğini artırmak amacıyla; Genel İşletme Malz.Grubunda Bilgisayar &amp; Ofis, Gıda ve Temizlik malzemeleri, Üretim Malz.Grubunda Boyalar, Teknik İşletme grubunda ise Metal Sarf malzemeleri özelinde iyileştirme çalışmaları planlanmıştır.
+Belirlenen malzeme gruplarında tüketim yapısı, stok hareketleri ve ihtiyaç oluşum süreçleri analiz edilerek MRP etkinliğinin artırılması hedeflenmektedir.
+İlgili malzeme gruplarında ihtiyaç planlama yapısının geliştirilmesi ve sistemsel sinyal kalitesinin artırılmasına yönelik çalışmalar yürütülecektir.
+Stok tutarı ile tüketim ilişkisi değerlendirilerek yeterlilik seviyelerinin daha etkin yönetilmesine yönelik çalışmalar planlanmıştır.
+Dinamik tüketim verilerine göre çalışan emniyet stoğu ve min–max yönetim yapısının oluşturulması hedeflenmiştir.
 Ürün ağaçlarının haftalık olarak mail atılmasına yönelik aksiyon planlanmıştır.(SAP-Mail)
-Satın alma, üretim planlama ve depo yönetimi arasındaki koordinasyon artırılacaktır.
+Satınalma, Üretim Planlama ve Depo süreçleri arasındaki bilgi akışının daha hızlı ve sürdürülebilir hale getirilmesi hedeflenmiştir.
 </t>
   </si>
   <si>
@@ -669,7 +676,9 @@
 Proje kapsamında; ambalaj malzemelerinin depolama alanları, yerleşim düzeni, stok takibi ve hat besleme yöntemleri detaylı olarak analiz edilerek; alan kullanımını optimize eden, malzeme bulunurluğunu artıran ve üretim akışını kesintiye uğratmayacak bir depo yapısı tasarlanacaktır.</t>
   </si>
   <si>
-    <t>Üretimde kullanılan ambalaj malzemeleri ihtiyaçları aylık üretim planları incelenerek tespit edilmektedir. Kullanılan malzemelerin sıklığına göre belirlenen bazı ambalaj malzemeleri oluşturulan stok seviyeleriyle stok kontrolü yapılmaktadır. 
+    <t>Ambalaj malzemeleri kutular grubu için  hareket yapılarına göre ayrıştırılarak 16 farklı raf alanı tanımlanmış ve depolama düzeni yeniden yapılandırılmıştır.
+Raflarda bulunan malzemeler Mobil App ile entegre edilerek anlık erişim ve takip yapısı oluşturulmuş, sistem operasyon ihtiyaçlarına göre revize edilmektedir.
+Üretimde kullanılan ambalaj malzemeleri ihtiyaçları aylık üretim planları incelenerek tespit edilmektedir. Kullanılan malzemelerin sıklığına göre belirlenen bazı ambalaj malzemeleri oluşturulan stok seviyeleriyle stok kontrolü yapılmaktadır. 
 Mevcut Durum Analizi (As-Is) yapılmıştır.
 Ambalaj Malzemelerinin Sınıflandırılması tamamlanmıştır.
 Hedef Depo Yerleşim ve Alan Optimizasyonu tamamlanmıştır.
@@ -1221,6 +1230,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Teknik SA kategorisinde teklifler, siparişler ihaleler dijital olarak SRM üzerinden toplanmaktadır. (</t>
@@ -1230,6 +1240,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">4400+ işlem)
@@ -1240,6 +1251,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Yeni cari tanımlarında vSRM dijital uygulaması ve BP entegrasyonu devreye alınmış ve </t>
@@ -1249,6 +1261,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>105</t>
@@ -1258,6 +1271,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> yeni cari kaydı vSRM üzerinden yapılmıştır.
@@ -1269,6 +1283,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır, eğitimler ilgili kategorilere verilmiş ve teklif toplama denemelerine geçilmiştir. Bölgesel SA (5 işlem yapıldı) ve Merkezi SA (2 işlem yapıldı) kategorileri ilk denemelerini yapmıştır. Hammadde SA da firmalara vSRM üzerinden teklife çıkılacak bilgisi yayınlanmıştır.
@@ -1281,6 +1296,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Satış ihalesi sürecinin SRM’ e tanımlanması. 
@@ -1292,6 +1308,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">SA diğer kategorileri için de RFQ çalışmaları başlatılmıştır.
@@ -1310,6 +1327,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Ambalaj kategorisinde Kalite Birimi tarafından aktif kullanılmaktadır.</t>
@@ -1319,6 +1337,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Hammadde kategorsinde girdi kontrolde DÖF uygulaması için eğitimler verilmiştir.İlk örnek Sibelco firması üzerinden gelen uygun olmayan red için yapılmaktadır.</t>
@@ -1331,6 +1350,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Diğer SA kategorilerinde DÖF modülünün kullanılması yaygınlaştırılacaktır. Örnek Hammadde için Ar-Ge girdi kontrol kullanımı.
@@ -1341,6 +1361,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Kategorilerde denetim kayıtlarının vSRM üzerinden yürütülmesi ve tedarikçiye iletilmesi.</t>
@@ -1350,6 +1371,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Diğer kategorilerin DÖF kullanımına geçilecek.</t>
@@ -1373,6 +1395,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Bölgesel Hizmet ve Merkezi Satın alma kategorilerinde sipariş modülü kullanıma başlanacaktır.
@@ -1386,6 +1409,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Siparişlerin hızlanması için vSRM üzerinden SAT açılması işlemlerinin otomatik olarak çalışması yapılmaktadır. Haziran ayına kadar tamamlanması planlanmaktadır</t>
@@ -1395,6 +1419,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>. (Üzerinde çalışılıyor.)</t>
@@ -1434,6 +1459,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Tedarikçilerimizin verdiği teknik eğitimlerle hem kendi kullanıcımız hem de tedarikçimizin ürününün doğru kullanılması ile optimum sonuçlara ulaşılmaktadır.
@@ -1444,6 +1470,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Tedarikçilerimizin kullanıcılara verdiği eğitimler devam etmektedir. 2. etap pnömatik sistem eğitimleri verilmiştir.</t>
@@ -1480,6 +1507,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Tedarikçi Benchmark çalışmaları yapılmıştır. 2 grup halinde farklı iki firma olan Sofra firması ve Dalgakıran firmaları satınalma yapısı olarak incelenmiştir. Sofra firmasından tedarikçi değerlendirme anlamında örnekler alınmıştır. 
@@ -1490,6 +1518,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Personel Servis tedarikçimiz Gürsel firması ile know-how geliştirme anlamında deneyim paylaşım toplantısı yapıldı, içerik olarak firmanın temel hedefi olarak taşıyacağı kişiyi zamanında, güvenli şekilde ulaştırma ve bunu yaparken çok sade bir yapıda yönetim yapıldığı bizim ekibe aktarılmıştır.</t>
@@ -1528,6 +1557,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Robot tarafından kayıt edilmesi planlanan tedarikçiler belirlenmiş, sisteme </t>
@@ -1537,6 +1567,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">99 cari </t>
@@ -1546,6 +1577,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>tanımlanmıştır.</t>
@@ -1567,6 +1599,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Satın alma taleplerinin Teknik SA kategorisinde e-posta/telefon yerine SRM sistemi üzerinden alınıp yürütülmektedir.</t>
@@ -1576,6 +1609,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> % 100 Hizmette geçildi.
@@ -1586,19 +1620,11 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Teknik satınalma kategorisinde talepler teknik dokümanlar la birlikte SRM sistemi üzerinden alınmaya başlanmış ve tedarikçiye yine SRM sistemi üzerinden ihale, teklif toplama vb. şeklinde iletilmektedir.</t>
     </r>
-  </si>
-  <si>
-    <t>SRM sistemi işlemlerinde Hizmet SAT’ larının talep sahibi onayı ile otomatik olarak SAP sisteminde yaratılması ve SRM sistemi ile entegre olması planlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Teknik Hizmet Alınan Hizmetin Kontrolü</t>
-  </si>
-  <si>
-    <t>Teknik hizmetlerin (bakım, onarım, montaj, mühendislik, servis vb.) sözleşme, teknik şartname ve kalite beklentilerine uygunluğunun sistematik, standart ve izlenebilir şekilde kontrol sürecinin SRM sisteminde yapılması amaçlanmaktadır.</t>
   </si>
   <si>
     <r>
@@ -1606,6 +1632,35 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SRM sistemi işlemlerinde Hizmet SAT’ larının talep sahibi onayı ile otomatik olarak SAP sisteminde yaratılması ve SRM sistemi ile entegre olması planlanmaktadır.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> SAS onaylarında onay formuna içine onaylayıcının bilgileri göreceği örnek ihale dosyası , teklifler vs. bilgilerin eklenmesi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Teknik Hizmet Alınan Hizmetin Kontrolü</t>
+  </si>
+  <si>
+    <t>Teknik hizmetlerin (bakım, onarım, montaj, mühendislik, servis vb.) sözleşme, teknik şartname ve kalite beklentilerine uygunluğunun sistematik, standart ve izlenebilir şekilde kontrol sürecinin SRM sisteminde yapılması amaçlanmaktadır.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Teknik hizmet alımlarında alınan hizmetin kontrolü E-flow sisteminde yer alan uygulama ile yapılmakta; talep sahipleri faturalara dijital onay vermektedir. </t>
@@ -1615,6 +1670,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Teknik hizmet iş kabullerinde VSRM üzerinden gerekli süreç tamamlanmıştır, 01.04.2026 tarihinde devreye alınmıştır. Firma tarafından hizmet teslimi onayı
@@ -1654,24 +1710,63 @@
     <t>Bu proje, Kaleseramik SKM üretim süreçlerini uçtan uca dijitalleştirerek, tekil ürün bazında gerçek zamanlı veri akışına dayalı akıllı üretim yönetimi ve yapay zekâ destekli karar destek sistemleri kurmayı hedeflemektedir. Amaç; kaliteyi artırmak, verimliliği yükseltmek, maliyetleri azaltmak ve müşteri memnuniyetini güçlendirmektir.</t>
   </si>
   <si>
-    <t>YK Masse, GR İkincil İşlemler Kurulumu</t>
-  </si>
-  <si>
-    <t>KB3, KB7 Kurulumu</t>
-  </si>
-  <si>
-    <t>KB7, KB3  fabrikası iş analizi tamamlanmış olup backlog listesi tamamlanmıştır.​
-Saha çalışmaları tamamlanmıştır. Fırın çıkışına kadar olan sürecin yazılımı tamamlanmış olup testleri başlatılmış, kabul süreci devam etmektedir. ​
+    <t>YK Masse Dijital Dönüşüm</t>
+  </si>
+  <si>
+    <t>Sürecin yazılımı tamamlanmıştır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saha Scada entegrasyonları yapılacaktır.
+IOT, Gateway tedarik süreci başlatılmıştır.
+Step Teknoloji tarafından yapılacak tersine mühendislik çalışmaları haziran başı itibariyle başlatılacaktır. </t>
+  </si>
+  <si>
+    <t>GR İkincil İşlemler Kurulumu</t>
+  </si>
+  <si>
+    <t>Yazılım tamamlanmıştır.
+Donanım tedariği tamamlandı.
+Kalibre - Planar, Ambalaj-Stacker verileri alındı ve MES entegrasyonu tamamlandı.</t>
+  </si>
+  <si>
+    <t>Parlatma kareleme makineleri için veri mühendisliği çalışmaları devam etmektedir.
+Stok takip entegrasyon çalışmaları devam etmektedir.
+Kesme nedeniyle izlenebilirlik kaybı için çözüm geliştirilecektir.</t>
+  </si>
+  <si>
+    <t>KB7 Kurulumu</t>
+  </si>
+  <si>
+    <t>Devam ediyor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KB7 fabrikası iş analizi tamamlanmış olup backlog listesi tamamlanmıştır.​
+Saha çalışmaları tamamlanmıştır. Fırın çıkışına kadar olan sürecin yazılımı tamamlanmıştır. ​
 KB7 fabrikası fırın sonrası 2. işlemler için saha veri çalışmaları, tersine mühendislik çalışmaları tamamlanmıştır. ​
 Fırın çıkışı sonrası MES yazılımı tamamlanmıştır.​
-Kalite ayrım hata giriş ekranı ve ambalaj makinesi senkronizasyonu devam etmektedir.​
-Veri doğrulama işlemleri tamamlanmıştır (duruş ve fire), Kırmızı fire eşleşme doğrulaması devam ediyor​</t>
+Kalite ayrım hata giriş ekranı ve ambalaj makinesi senkronizasyonu tamamlanmıştır.
+Veri doğrulama işlemleri tamamlanmıştır (duruş ve fire).
+</t>
+  </si>
+  <si>
+    <t>Kırmızı fire eşleşme doğrulaması devam ediyor​. 
+Yeni alınan otomatik kalite ayrım makinesinin verilerinin alınacak ve barkod eşleştirmesi yapılacaktır.
+Fırın üst parlatma hattı eski olduğu için çalışma yapılmamış , 2027 yatırımı ile yenilenecek hatta yapılacaktır.</t>
+  </si>
+  <si>
+    <t>KB3 Kurulumu</t>
+  </si>
+  <si>
+    <t>KB3  fabrikası iş analizi tamamlanmış olup backlog listesi tamamlanmıştır.​
+Saha çalışmaları tamamlanmıştır.
+KB3 fabrikası makineleri için  saha veri çalışmaları, tersine mühendislik teklifleri onaylanmıştır.
+KB7 ile olan parkur farklılıkları analizi tamamlanmıştır.</t>
   </si>
   <si>
     <t xml:space="preserve">SLAB MES Yapısının Kurulması </t>
   </si>
   <si>
-    <t>Devam ediyor</t>
+    <t>Kavramsal tasarımları tamamlanmıştır.</t>
   </si>
   <si>
     <t>Yeni yatırımı yapılan System ve Sacmi kalite kontrol cihazlarının entegrasyonu başlatılacak. Gerekli kontrollerin tamamlanmasından sonra; Toplanan tüm makine verileri ile tekil karo bazında ileri analitik çalışmaları başlatılacak.​
@@ -1706,175 +1801,13 @@
     <t>MES Uygulamaları</t>
   </si>
   <si>
-    <t>Fırın İzleme Sistemi</t>
-  </si>
-  <si>
-    <t>AI Destekli Fırın İzleme Sistemi</t>
-  </si>
-  <si>
-    <t>KS2026-37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fırın verimliliğinin canlı takibi projesinin tamamlanmasından sonra Faz-2 olarak canlı takip sonuçlarının üretim sarf, reçete bilgisi ile optimize edilerek AI destekli izleme sisteminin kurulması hedeflenmektedir. </t>
-  </si>
-  <si>
-    <t>Parkur içerisindeki tüm makinaların canlı takip verileri gcp de bulunmaktadır.​
-Hat duruşları sahada bulunan kamera ve fotosel çiftleri ile otomatik tespit edilebilmektedir.​
-Envanter bilgileri ile mevcutta bulunan tüm kalıp ve set bilgileri tekil karo bazlı takip edilmektedir.​
-Fırın halı besleme veriminin çıkarılabilmesi için gerekli veriler toplanmaya başlamıştır.​
-Pres envanter sayfası üzerinden üretimi yapılan ürünün ebadı(60x120, 61x121)​
-Fırın kontrol panosu üzerinden fırın devir süresi​
-Barkod takip üzerinden fırına aktif giren üretimin tespiti​</t>
-  </si>
-  <si>
-    <t>Fırın halı besleme oranının canlı takibi ve verimlilik düşüşü (fırın devrinde ürün ağacından sapma, aralıklı besleme, vb) durumlarında erken uyarı sistemi kurulması​
-Fırın besleme sisteminin operatör kontrolünden çıkarılarak 24 saat canlı izlenmesi sağlanacak.​
-Üretim parametrelerinin kurulacak sisteme entegrasyonuyla Agentic AI modellemesi yapılarak fırının izlenmesi ve kontrolü sağlanacaktır.​</t>
-  </si>
-  <si>
-    <t>Otomasyon</t>
-  </si>
-  <si>
-    <t>Püskürtmeli Kurutucu Otomasyonu</t>
+    <t>Veri Analitiği</t>
+  </si>
+  <si>
+    <t>Fırın Verimliliğinin Canlı Takibi Faz-1</t>
   </si>
   <si>
     <t>KS2026-34</t>
-  </si>
-  <si>
-    <t>Canlı Rutubet Ölçümü ile Model kurularak Sprey kurutucu ısılarına müdahale eden robot geliştirilerek sprey çıkışı rutubetin sürekli stabil tutulması sağlanacaktır.</t>
-  </si>
-  <si>
-    <t>Rutubet cihazının kurulumu ve PC bağlantıları tamamlandı​
-Üretilen farklı reçetelerdeki hammaddeler için cihaz kalibrasyonu ve ölçüm reçetesi oluşturulması tamamlandı​
-Veri doğrulama ve veri seti oluşturma tamamlandı.​
-MES sistemi ile sprey kurutucu makine parametreleri toplandı.​
-Sprey dryer ve rutubet ölçüm cihazı arasındaki gecikme farkı hesaplandı.​
-Sprey dryer da önemli parametrelerin belirlenmesi için analiz çalışması yapıldı.​
-Canlı rutubet takibi ile canlı makine verileri arasındaki korelasyon için veri analitiği çalışmaları yapılarak model oluşturulmuştur. Modelin doğruluğu sahada test edilecektir.​</t>
-  </si>
-  <si>
-    <t>Oluşturulan modelin canlı veri üzerinden testleri yapılarak güvenilirlik kontrolü yapılacak.​
-Model saha entegrasyonu yapılacak.​
-Kurutma makine parametreleri ile rutubet ölçümü arasındaki gecikme zaman farkı hesaplanarak veri eşleşmesi yapılacaktır. ​</t>
-  </si>
-  <si>
-    <t>Masse ve Sır Stok Hareket İşlemleri</t>
-  </si>
-  <si>
-    <t>KS2026-33</t>
-  </si>
-  <si>
-    <t>Mevcutta yapılan parti bazlı ürün ve ürün ağacı takibinin tekil karo bazlı yapılması hedeflenmektedir.</t>
-  </si>
-  <si>
-    <t>MES sistemi ile tekil karo bazlı takip yapılabilmektedir. ​
-Granit fabrikası ve granit masse üretimi arasında pilot çalışma planlanmıştır.​
-Tüketim datalarının SAP üzerinden anlık çıkışı için algoritma düzenlenmiştir. ​
-Dijital tartım ünitelerine takılan IOT cihazları SCADA akışını bozduğundan dolayı yeni çalışma yapılması planlanmıştır.​</t>
-  </si>
-  <si>
-    <t>Her bir karonun tüm yaşam döngüsü bilindiğinden canlı makine verileri ile ürün ağacı kıyaslaması yapılacaktır.​
-Karo üretiminde kullanılan masse, sır, doğalgaz, elektrik, işçilik vb. veriler canlı ve otomatik sarf edilecektir.​
-İş emrinin ürün ağacına göre çıkarılan fiili standart maaliyet oranı her bir karo çözünürlüğünde bakılarak trend analizi yapılacaktır. ​</t>
-  </si>
-  <si>
-    <t>Reçete Optimizasyonu</t>
-  </si>
-  <si>
-    <t>Granit Bünye Reçete Opt. Çalışması</t>
-  </si>
-  <si>
-    <t>KS2026-36</t>
-  </si>
-  <si>
-    <t>Masse ve sır için geçmiş üretim verilerinden öğrenen bir yapay zekâ sistemine dayanacaktır.    Modelin amacı deneme-yanılma sürecini ortadan kaldırmak, üretim verimliliğini artırmak, ürün kalitesinde sürdürülebilirliği garanti altına almak, hammadde kullanımında optimizasyon sağlamaktır.</t>
-  </si>
-  <si>
-    <t>Gerekli olan tüm veriler MES sistemi içinde toplanmaya başlamıştır.​
-Modeli oluşturacak uygun veri seti büyüklüğü için tespit çalışmaları devam etmektedir.​
-Proje için üç konsorsiyum ile Horizon ön başvurusu yapılmış, sonuçları beklenmektedir.​</t>
-  </si>
-  <si>
-    <t>Nihai ürün kalite kontrol verileri ile tüm girdilerin korelasyonu sağlanacak​
-Reçete hammadde ve/veya oran değişimlerinin nihai ürüne etkisinin analizi yapılacak ​
-Üretim şartlarına uygun hammadde ihtiyacı öneri sistemi kurulacak​
-Projenin yazılım bütçesinin AB fonlarından karşılanması planlanmaktadır.​</t>
-  </si>
-  <si>
-    <t>Tübitak 1711</t>
-  </si>
-  <si>
-    <t>CWYF Uygulaması Geliştirilmesi</t>
-  </si>
-  <si>
-    <t>KS2026-35</t>
-  </si>
-  <si>
-    <t>CeramIQ - Gerçek Zamanlı Üretim Verisi ve Akıllı Ajanları ile Desteklenen Endüstriyel Yapay Zekâ Modellerinin Geliştirilmesi ve Etkileşimli Karar Destek Asistanlarının Tasarımı
-Seramik üretim süreçlerinde (masse hazırlık, karo üretim ve fırın sonrası işlemler dahil) gerçek zamanlı üretim verilerinin toplanması, yapay zekâ tabanlı analitik modellerin geliştirilmesi ve etkileşimli karar destek asistanlarının kullanıma alınmasıyla; verimlilik, kalite, enerji optimizasyonu ve sürdürülebilirlik hedeflerini gerçekleştirmeyi amaçlamaktadır.</t>
-  </si>
-  <si>
-    <t>Başvuru tamamlanmıştır. ​
-Amaç: Kaleseramik üretim hatlarında dijital dönüşüm ile uçtan uca izlenebilirlik ve karar destek sistemleri kurmak.​
-Yenilik: IoT tabanlı veri toplama, yapay zekâ modelleri ve akıllı dijital asistanların üretim kararlarını desteklemesi.​
-Kapsam: Hammadde dozajlama, değirmenler, kurutucular, presler, fırınlar ve son işlem hatlarında veri analitiği uygulamaları.​
-Katkı: Firelerin ve plansız duruşların azaltılması, kalite tutarlılığının artması, enerji tüketiminde düşüş ve çevresel sürdürülebilirlik.​
-Başvurumuz onaylanmıştır.​
-Proje Kick-Off u yapılmış, çalışmalar başlatılmıştır.​</t>
-  </si>
-  <si>
-    <t>Veri Toplama Altyapısı: IoT sensörleri, SCADA/MES entegrasyonu ile anlık veri akışının sağlanması.​
-Veri Ambarı ve Analitik: Toplanan verilerin merkezi platformda saklanması, temizlenmesi ve analize hazır hale getirilmesi.​
-Model Geliştirme: Makine öğrenmesi ve yapay zekâ algoritmaları ile kalite, enerji ve bakım tahminleme modellerinin geliştirilmesi.​
-Karar Destek Asistanı: Operatörler ve yöneticiler için etkileşimli dijital asistan ve dashboard’ların tasarımı.​
-Pilot Uygulama: Seçilen hatlarda (ör. masse değirmenleri ve kurutucular) test ve validasyon çalışmaları.​
-Yaygınlaştırma: Tüm üretim tesislerine entegrasyon, ERP sistemleri ile bütünleşme.​
-Sürdürülebilirlik &amp; Raporlama: Enerji ve hammadde tasarruflarının ölçülmesi, yönetim raporlarının hazırlanması.​</t>
-  </si>
-  <si>
-    <t>Veri Analitiği</t>
-  </si>
-  <si>
-    <t>Granit Kurutucu Verimlilik Optimizasyonu</t>
-  </si>
-  <si>
-    <t>Karonun kurutucu içinde görünürlüğünü sağlayarak tüm sepet ve raflarının aktif kullanımını sağlamak, verimliliğini ölçmek ve canlı izlemek için;
-Kurutuculardan toplanan operasyonel verilerin (sepet no, sepet id, tur bilgisi, çıkış sıcaklığı, doğalgaz sarfiyatı vb.) analitik yöntemlerle işlenmesi ve yapay zekâ destekli modeller kullanılarak  dikey kurutucunun her bir çevirimi için verimlilik artırımı ve enerji tasarrufu sağlanması.</t>
-  </si>
-  <si>
-    <t>IoT sensörlerinden pres ve kurutucuya ait anlık veriler toplanmaktadır.​
-Makine parametreleri ile hat duruş bilgileri zaman etiketi üzerinden eşleştirilmiştir.​
-Dikey kurutucunun tüm raflarının aktif kullanımı için zaman serisi analizi tamamlanmıştır.​
-Veri görselleştirme dashboard’ları geliştirilmiştir​
-Rapor her gün süreç sahipleri ile paylaşılmaktadır.​
-OEE (Overall Equipment Effectiveness) artışı gerçekleşmiştir​
-Enerji tüketimi %3 azalma sağlanmıştır​</t>
-  </si>
-  <si>
-    <t>Makine öğrenmesi tabanlı tahminleme (enerji tüketimi, duruş, fire riski, verimlilik)​
-Kurutma bilgileri ile Faz-2 olarak fire korelasyonu çalışması yapılacaktır.​
-Kurutma yaşam döngüsü verileri ile kestirimci kalite çalışmaları</t>
-  </si>
-  <si>
-    <t>Masse  Verilerinin Granite Bağlanması</t>
-  </si>
-  <si>
-    <t>Masse hazırlık süreci ile karo üretim sürecini tek bir dijital izlenebilirlik zincirinde birleştirmek. Hammadde dozajından başlayıp, öğütme – kurutma – stoklama – presleme – sırlama – pişirim – fırın sonrası işlemler aşamalarına kadar tüm değer zincirini uçtan uca dijital olarak izlemek, veriye dayalı karar alma ve optimizasyon sağlamak.</t>
-  </si>
-  <si>
-    <t>MES ve SAP entegrasyonu tamamlandı​
-IoT sensörleri ve SCADA sistemlerinden veri toplama süreci tamamlandı​
-Verinin depolanması ve veri kullanım senaryoları oluşturuldu​
-Gerçek zamanlı dashboard’lar (enerji, kalite, fire, OEE) oluşturuldu​</t>
-  </si>
-  <si>
-    <t>Reçete ve tüm (Masse+Üretim) proses parametreleri ile ürün kalitesi arasındaki korelasyon analizi yapılacak​
-En çok yaşanan firelerin veri gölü içindeki sebep sonuç korelasyonları araştırılarak kök neden analizi yapılacak​
-Makine öğrenmesi ile oluşturulan modeller kullanılarak canlı makine parametreleri için kurallar tanımlanıp kestirimci kalite uyarıları hazırlanacak​
-Fırın çıkışında fire olacağı öngörülen karoların pişirim öncesi bertaraf edilerek ham kırık olarak geri kazanılması ​</t>
-  </si>
-  <si>
-    <t>Fırın Verimliliğinin Canlı Takibi</t>
   </si>
   <si>
     <t>Seramik üretiminde en fazla enerji tüketimi bulunan pişirim sürecinin verimliliğinin sürekli olarak izlenmesi, olası verimlilik düşüklüklerinin bildirilmesi</t>
@@ -1888,9 +1821,165 @@
 Duruş ve boşluklu besleme kaynaklı kapasite kayıpları ölçülerek günlük olarak raprolanmaya başlandı.​</t>
   </si>
   <si>
-    <t>Farklı üretimlerde farklı fırın rejimleri kod içerisine eklenerek dinamik kontrol geliştirilecektir.​
-Fırın besleme sisteminin operatör kontrolünden çıkarılarak 24 saat canlı izlenmesi sağlanacaktır​
+    <t>Faz-2'de ;
+Kurulan algoritma otomatikleştirilecektir.
+​Proje çıktısı her gün PDF halinde ilgililerle paylaşılacaktır.
 KB7 yaygınlaştırması planlanacaktır.</t>
+  </si>
+  <si>
+    <t>Fırın İzleme Sistemi</t>
+  </si>
+  <si>
+    <t>AI Destekli Fırın İzleme Sistemi</t>
+  </si>
+  <si>
+    <t>KS2026-37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fırın verimliliğinin canlı takibi projesinin tamamlanmasından sonra Faz-2 olarak canlı takip sonuçlarının AI destekli izleme sisteminin kurulması hedeflenmektedir. </t>
+  </si>
+  <si>
+    <t>Faz-1 tamamlanmıştır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faz-1 ile elde edilen sonuç, günlük halı besleme verimi olarak 24 saatte bir paylaşılacaktır. 
+Fırın halı besleme oranının canlı takibi ve verimlilik düşüşü (fırın devrinde ürün ağacından sapma, aralıklı besleme, vb) durumlarında erken uyarı sistemi kurulacaktır.
+</t>
+  </si>
+  <si>
+    <t>Otomasyon</t>
+  </si>
+  <si>
+    <t>Püskürtmeli Kurutucu Otomasyonu</t>
+  </si>
+  <si>
+    <t>Canlı Rutubet Ölçümü ile Model kurularak Sprey kurutucu ısılarına müdahale eden robot geliştirilerek sprey çıkışı rutubetin sürekli stabil tutulması sağlanacaktır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutubet cihazının kurulumu ve PC bağlantıları tamamlandı​
+Üretilen farklı reçetelerdeki hammaddeler için cihaz kalibrasyonu ve ölçüm reçetesi oluşturulması tamamlandı​
+Veri doğrulama ve veri seti oluşturma tamamlandı.​
+MES sistemi ile sprey kurutucu makine parametreleri toplandı.​
+Sprey dryer ve rutubet ölçüm cihazı arasındaki gecikme farkı hesaplandı.​
+Sprey dryer da önemli parametrelerin belirlenmesi için analiz çalışması yapıldı.​
+Canlı rutubet takibi ile canlı makine verileri arasındaki korelasyon için veri analitiği çalışmaları yapılarak model oluşturulmuştur. 
+Modelin doğruluğu sahada test edilecektir.​ Kurutma makine parametreleri ile rutubet ölçümü arasındaki gecikme zaman farkı hesaplanarak veri eşleşmesi yapılacaktır. </t>
+  </si>
+  <si>
+    <t>Masse ve Sır Stok Hareket İşlemleri</t>
+  </si>
+  <si>
+    <t>KS2026-33</t>
+  </si>
+  <si>
+    <t>Mevcutta yapılan parti bazlı ürün ve ürün ağacı takibinin tekil karo bazlı yapılması hedeflenmektedir.</t>
+  </si>
+  <si>
+    <t>MES sistemi ile tekil karo bazlı takip yapılabilmektedir. ​
+Granit fabrikası ve granit masse üretimi arasında pilot çalışma planlanmıştır.​
+Tüketim datalarının SAP üzerinden anlık çıkışı için algoritma düzenlenmiştir. ​
+Dijital tartım ünitelerine takılan IOT cihazları SCADA akışını bozduğundan dolayı yeni çalışma yapılması planlanmıştır.​</t>
+  </si>
+  <si>
+    <t>Her bir karonun tüm yaşam döngüsü bilindiğinden canlı makine verileri ile ürün ağacı kıyaslaması yapılacaktır.​
+Karo üretiminde kullanılan masse, sır, doğalgaz, elektrik, işçilik vb. veriler canlı ve otomatik sarf edilecektir.​
+İş emrinin ürün ağacına göre çıkarılan fiili standart maaliyet oranı her bir karo çözünürlüğünde bakılarak trend analizi yapılacaktır. ​</t>
+  </si>
+  <si>
+    <t>Reçete Optimizasyonu</t>
+  </si>
+  <si>
+    <t>Granit Bünye Reçete Opt. Çalışması</t>
+  </si>
+  <si>
+    <t>KS2026-36</t>
+  </si>
+  <si>
+    <t>Masse ve sır için geçmiş üretim verilerinden öğrenen bir yapay zekâ sistemine dayanacaktır.    Modelin amacı deneme-yanılma sürecini ortadan kaldırmak, üretim verimliliğini artırmak, ürün kalitesinde sürdürülebilirliği garanti altına almak, hammadde kullanımında optimizasyon sağlamaktır.</t>
+  </si>
+  <si>
+    <t>Gerekli olan tüm veriler MES sistemi içinde toplanmaya başlamıştır.​
+Modeli oluşturacak uygun veri seti büyüklüğü için tespit çalışmaları devam etmektedir.​
+Proje için üç konsorsiyum ile Horizon ön başvurusu yapılmış, sonuçları beklenmektedir.​</t>
+  </si>
+  <si>
+    <t>Nihai ürün kalite kontrol verileri ile tüm girdilerin korelasyonu sağlanacak​tır.
+Reçete hammadde ve/veya oran değişimlerinin nihai ürüne etkisinin analizi yapılacaktır.
+Üretim şartlarına uygun hammadde ihtiyacı öneri sistemi kurulacaktır.​
+Projenin yazılım bütçesinin AB fonlarından karşılanması planlanmaktadır.​</t>
+  </si>
+  <si>
+    <t>Tübitak 1711</t>
+  </si>
+  <si>
+    <t>CWYF Uygulaması Geliştirilmesi</t>
+  </si>
+  <si>
+    <t>KS2026-35</t>
+  </si>
+  <si>
+    <t>CeramIQ - Gerçek Zamanlı Üretim Verisi ve Akıllı Ajanları ile Desteklenen Endüstriyel Yapay Zekâ Modellerinin Geliştirilmesi ve Etkileşimli Karar Destek Asistanlarının Tasarımı
+Seramik üretim süreçlerinde (masse hazırlık, karo üretim ve fırın sonrası işlemler dahil) gerçek zamanlı üretim verilerinin toplanması, yapay zekâ tabanlı analitik modellerin geliştirilmesi ve etkileşimli karar destek asistanlarının kullanıma alınmasıyla; verimlilik, kalite, enerji optimizasyonu ve sürdürülebilirlik hedeflerini gerçekleştirmeyi amaçlamaktadır.</t>
+  </si>
+  <si>
+    <t>​Başvuru tamamlanmıştır. ​
+Başvurumuz onaylanmıştır.​
+Proje Kick-Off'u yapılmış, çalışmalar Medipol Üniversitesi ile işbirliği halinde yürütülmektedir.</t>
+  </si>
+  <si>
+    <t>IoT sensörleri, SCADA/MES entegrasyonu ile anlık veri akışının sağlanması.​
+Toplanan verilerin merkezi platformda saklanması, temizlenmesi ve analize hazır hale getirilmesi.​
+Makine öğrenmesi ve yapay zekâ algoritmaları ile kalite, enerji ve bakım tahminleme modellerinin geliştirilmesi.​
+Operatörler ve yöneticiler için etkileşimli dijital asistan ve dashboard’ların tasarımı.​
+Seçilen hatlarda (ör. masse değirmenleri ve kurutucular) test ve validasyon çalışmaları.​
+Tüm üretim tesislerine entegrasyon, ERP sistemleri ile bütünleşme.​
+Enerji ve hammadde tasarruflarının ölçülmesi, yönetim raporlarının hazırlanması.​</t>
+  </si>
+  <si>
+    <t>Granit Kurutucu Verimlilik Optimizasyonu Faz-1</t>
+  </si>
+  <si>
+    <t>Karonun kurutucu içinde görünürlüğünü sağlayarak tüm sepet ve raflarının aktif kullanımını sağlamak, verimliliğini ölçmek ve canlı izlemek için;
+Kurutuculardan toplanan operasyonel verilerin (sepet no, sepet id, tur bilgisi, çıkış sıcaklığı, doğalgaz sarfiyatı vb.) analitik yöntemlerle işlenmesi ve yapay zekâ destekli modeller kullanılarak  dikey kurutucunun her bir çevirimi için verimlilik artırımı ve enerji tasarrufu sağlanması.</t>
+  </si>
+  <si>
+    <t>IoT sensörlerinden pres ve kurutucuya ait anlık veriler toplanmaktadır.​
+Makine parametreleri ile hat duruş bilgileri zaman etiketi üzerinden eşleştirilmiştir.​
+Dikey kurutucunun tüm raflarının aktif kullanımı için zaman serisi analizi tamamlanmıştır.​
+Veri görselleştirme dashboard’ları geliştirilmiştir​.
+Rapor her gün süreç sahipleri ile paylaşılmaktadır.​
+OEE (Overall Equipment Effectiveness) artışı gerçekleşmiştir​.
+Enerji tüketimi %3 azalma sağlanmıştır​.</t>
+  </si>
+  <si>
+    <t>Granit Kurutucu Verimlilik Optimizasyonu Faz-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doğalgaz ve duruş verileri Faz-1 algoritma yapısına eklenmiştir. 
+Projenin Faz-1 aşamasında hesaplanan tur sayısının ve verimliliğinin ham kırığa etkisi analiz aşamasına dahil edilmiştir.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nihai sonucun dashboardları revize edilecektir. 
+</t>
+  </si>
+  <si>
+    <t>Masse  Verilerinin Granite Bağlanması</t>
+  </si>
+  <si>
+    <t>Masse hazırlık süreci ile karo üretim sürecini tek bir dijital izlenebilirlik zincirinde birleştirmek. Hammadde dozajından başlayıp, öğütme – kurutma – stoklama – presleme – sırlama – pişirim – fırın sonrası işlemler aşamalarına kadar tüm değer zincirini uçtan uca dijital olarak izlemek, veriye dayalı karar alma ve optimizasyon sağlamak.</t>
+  </si>
+  <si>
+    <t>MES ve SAP entegrasyonu tamamlandı​.
+IoT sensörleri ve SCADA sistemlerinden veri toplama süreci tamamlandı​.
+Verinin depolanması ve veri kullanım senaryoları oluşturuldu​.
+Gerçek zamanlı dashboard’lar (enerji, kalite, fire, OEE) oluşturuldu​.</t>
+  </si>
+  <si>
+    <t>Reçete ve tüm (Masse+Üretim) proses parametreleri ile ürün kalitesi arasındaki korelasyon analizi yapılacak​tır.
+En çok yaşanan firelerin veri gölü içindeki sebep sonuç korelasyonları araştırılarak kök neden analizi yapılacak​tır.
+Makine öğrenmesi ile oluşturulan modeller kullanılarak canlı makine parametreleri için kurallar tanımlanıp kestirimci kalite uyarıları hazırlanacak​tır.
+Fırın çıkışında fire olacağı öngörülen karoların pişirim öncesi bertaraf edilerek ham kırık olarak geri kazanılması ​sağlanacaktır.</t>
   </si>
   <si>
     <t>Masse Boya Tahminleme Modeli</t>
@@ -1927,6 +2016,18 @@
 Envanter takip ekranları ile değirmenlere yapılan bilya beslemeleri kaydedilecektir.​</t>
   </si>
   <si>
+    <t>Fırın Rulo Bakım Tahminlemesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fırın rulo sağlığı  ve tahrik sistemi canlı takibi yapılacak
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fırının her bir modülü için set ve actual hız değerleri alınacak.
+Bu verilerin trend analizleri izlenerek makine öğrenmesi yapılacaktır.
+</t>
+  </si>
+  <si>
     <t>Dijital Dönüşüm Merkezi</t>
   </si>
   <si>
@@ -1979,19 +2080,20 @@
     <t>Fabrikanın fiziksel süreçlerini gerçek zamanlı veriyle beslenen sanal modeller aracılığıyla temsil edilmesi hedeflenmektedir. </t>
   </si>
   <si>
-    <t>Microsoft Azure Digital Twins uygulaması ön çalışması tamamlanmıştır.​
+    <t xml:space="preserve">Microsoft Azure Digital Twins uygulaması ön çalışması tamamlanmıştır.​
 Görselleştirme yöntemleri olarak Microsoft 3D Scenes ve simülasyon için Unity araştırılmıştır.​
 Fabrika hatlarının taslağı çıkarılmıştır (DrawIO uyglaması)​
-Fabrka grafik tasarımının Part-1 tamamlanmıştır (Blender 3D)​
-Mic. Azure üzerinde makinelerin parametreleri ile beraber iş akış modelinin sinir ağları oluşturulmuştur.​</t>
-  </si>
-  <si>
-    <t>Sahadan alınan sensör dataları ile varlık dataları uyumlu hale getirilecektir.​
-Soğuk veri akışı simüle edilecektir.​
+Fabrika grafik tasarımının Part-1 tamamlanmıştır. (Blender 3D)​
+Mic. Azure üzerinde makinelerin parametreleri ile beraber iş akış modelinin sinir ağları oluşturulmuştur.​
+Sahadan alınan sensör dataları ile varlık dataları uyumlu hale getirilmiştir.​
+Microsoft Azure ile lokal kod uygulamaları arasında bağlantı kurulmuştur ve sağlıklı kod çıktısı gözlenmiştir. </t>
+  </si>
+  <si>
+    <t>Soğuk veri akışı simüle edilecektir.​
 Canlı veriye geçiş çalışmaları başlatılacaktır (HOLDING IT)​
 Fabrika hatlarındaki değişikliklerin tahminleneceği mantık katmanı eklenecektir.​
 Olası arızaları önceden tahmin edilecek ve bakım planları otomatik olarak optimize edilecektir.​
-Çalışma in-house yönetilecektir.​</t>
+Sahadan alınan sensör dataları ile varlık dataları uyumlu hale getirilecektir.​</t>
   </si>
   <si>
     <t>PowerBI Dashboard</t>
@@ -2006,11 +2108,6 @@
     <t>Mühendislik tarafından oluşturulan fabrikalara ait kalite, hata analizi, duruş raporlarını içeren raporlar teslim alınarak, kod sistematiği kontrol edilmiş ve gerekli düzenlemeler yapılarak günlük takibi yapılmaktadır. ​
 Fabrika tüm raporları (hata, kalite, duruş)  güncel olarak takibi yapılıp yayımlanmaktadır.​
 Fabrika PowerBI raporlarının veri kaynağının değiştirilmiştir.​</t>
-  </si>
-  <si>
-    <t>Farklı birimlerden gelen verilerin birleştirilerek ortak platformda görünürlüğü sağlanacaktır.​
-Raporlama arayüzleri revize edilecektir.​
-MES verileri işlenerek PowerBI a aktarılacaktır.​</t>
   </si>
   <si>
     <t>Finans PowerBI Dashboard Geliştirilmesi</t>
@@ -2025,33 +2122,28 @@
 Mali işlerin ihtiyaçlarına yönelik raporların alt yapısı oluşturulmuştur. ​</t>
   </si>
   <si>
-    <t>Farklı birimlerden gelen verilerin birleştirilerek ortak platformda görünürlüğü sağlanacaktır.​
-Sürecin devam ettirilmesi için Mali İşler'den veri beklenmektedir.​</t>
-  </si>
-  <si>
     <t>TZY PowerBI Dashboard Geliştirilmesi</t>
   </si>
   <si>
     <t xml:space="preserve">TZY Görünürlük Raporları ile üretim, stok, müşteri ve performans verilerinin bütünsel ve şeffaf bir şekilde izlenmesi, veriye dayalı karar alma süreçlerinin güçlendirilmesi ve her kategori için standart raporların hazırlanarak sürdürülebilir bir raporlama altyapısının oluşturulması hedeflenmektedir . Bu hedef doğrultusunda her kategori için kod sistematiği içeren PowerBI raporları oluşturulmaktadır. </t>
   </si>
   <si>
-    <t>TZY - Bütçe -Fiili Üretim Raporu ​
-KKO ve Teyitsiz siparişler raporu oluşturulmuştur​
+    <t xml:space="preserve">TZY - Bütçe -Fiili Üretim Raporu oluşturulmuştur.
+KKO ve Teyitsiz siparişler raporu oluşturulmuştur​.
 Fabrika doluluk raporu oluşturulmuştur.​
-TZY - Performans Göstergeleri Raporu ​
-TZY - Müşteri Raporu ​
-TZY - Envanter Yönetimi ​
-TZY - Ürün Raporu ​
-Talep Yönetimi Raporu tamamlandı​
-Inbound lojistik ve Outbound lojistik raporu​</t>
-  </si>
-  <si>
-    <t>Satın alma raporu ​
-Proje yönetimi raporu​
-Sipariş Yönetimi Raporu​
-KN raporu ​
-Tüm TZY raporlarının tek bir platformda toplanması tamamlanmış, veri girişi beklenmektedir.​
-UYGULAMA KULLANILABİLİR HALE GETİRİLMİŞTİR.​</t>
+TZY - Performans Göstergeleri Raporu ​oluşturulmuştur.
+TZY - Müşteri Raporu ​oluşturulmuştur.
+TZY - Envanter Yönetimi ​oluşturulmuştur.
+TZY - Ürün Raporu ​oluşturulmuştur.
+Talep Yönetimi Raporu oluşturulmuştur.
+Inbound lojistik ve Outbound lojistik raporu​ oluşturulmuştur.
+Proje yönetimi raporu​ oluşturulmuştur.
+Uygulama kullanılabilir hale getirilmiştir. </t>
+  </si>
+  <si>
+    <t>KN raporu oluşturulacaktır.
+Satın alma raporu oluşturulacaktır.
+Sipariş yönetimi raporu oluşturulacaktır.</t>
   </si>
   <si>
     <t>AI Uygulamaları</t>
@@ -2060,58 +2152,41 @@
     <t>LLM ve Data Insights</t>
   </si>
   <si>
-    <t>Envanter Yön. AI Kullanım Fonk. Oluşturulması</t>
-  </si>
-  <si>
-    <t>KS2026-39</t>
-  </si>
-  <si>
-    <t>Kurumsal veri kaynaklarının (SAP, BW, v.b.) büyük dil modellerine bağlanarak anlık rapor ihtiyaçları ile veri analizi ve içgörülerin alınabildiği platformun oluşturulması/kullanılması çalışmasıdır. Seçili use case ler için geliştirilecektir. Malzeme, müşteri, ürün ağacı, iş planı, gibi veri yapılarındaki farklı alanlardaki bilgileri analiz ederek veri anomali tespitleri yapabilmek,  Ürün satış performansları, şirket ve bayilerimizdeki stok durumlarını analiz ederek ürünler için planlama ve envanter stratejilerini belirleyebilir öneriler sunmak için model geliştirilmesi planlanmaktadır.</t>
-  </si>
-  <si>
-    <t>Stok, mal hareket, bayi stoğu, bayi satışı ve malzeme ana ver,ye ilişkin veri setleri hazırlanarak paylaşılmıştır.​
-POC için soru seti hazırlandı ve paylaşıldı.​
-Soru seti için hazırlanan modeller tedarikçi tarafından paylaşıldı ve Kale ekipleri ile birlikte değerlendirildi.​</t>
-  </si>
-  <si>
-    <t>POC nin tamamlanması ve sonuçların analiz edilmesi.​
-POC sonrası belirli bir plan dahilinde gerçek kullanıma geçiş.​
-Yapay zeka ajanları kullanımı için detaylı kullanım durumlarının oluşturulması.​</t>
-  </si>
-  <si>
-    <t>TZ Süreçlerinde AI Kullanımı</t>
-  </si>
-  <si>
-    <t>Genel AI Kullanım Fonksiyonları Oluşturulması</t>
-  </si>
-  <si>
-    <t>KS2026-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bu proje TZ süreçlerinde yapay zeka kullanımın yaklaşımını tanımlayan genel projeyi ifade etmektedir.  Veri analitiği dışında yapay zekanın kullanımına yönelik iki yaklaşım benimsenmiştir. İlki iş verilerinin büyük dil modellerine bağlanması ile bir ara yüz dahilinde hızlı raporlama ve içgörülerin alınmasıdır. Diğer ise kullanım durumu bazında yapay zeka ajanlarının iş süreçlerinde kullanılması ve çözümler oluşturulmasıdır. </t>
-  </si>
-  <si>
-    <t>Her iki yaklaşım için örnek kullanım durumları belirlendi.​
-İş verilerinin büyük dil modeline bağlanması konusu için bir şirket ile gizlilik sözleşmesi yapıldı.​
-POC için çalışmalar devam ediyor.​</t>
-  </si>
-  <si>
-    <t>Genel Veri Analitiği Çalışmaları</t>
-  </si>
-  <si>
-    <t>KS2026-64</t>
-  </si>
-  <si>
-    <t>Bu proje kapsamında, Kaleseramik üretim ve yönetim ekosisteminde oluşan büyük hacimli operasyonel verilerin ileri veri analitiği, makine öğrenmesi ve yapay zekâ yöntemleriyle analiz edilmesi hedeflenmektedir.
-Amaç; mevcut verilerden öngörü üreten, karar destek sağlayan ve operasyonel verimlilik yaratan veri odaklı kullanım durumlarını sistematik olarak keşfetmek, önceliklendirmek ve iş değerine dönüştürmektir.</t>
-  </si>
-  <si>
-    <t>Karar alma süreçleri sezgisel yaklaşımdan veri ve öngörü temelli yönetime taşınacak,​
-Dijital dönüşüm yol haritasındaki AI/ML ve dijital ikiz projeleri için ölçeklenebilir analitik bir temel oluşturulacak,​
-Üretim, kalite, bakım ve enerji ekiplerinin aynı veri dili üzerinden konuşabildiği ortak bir analitik çerçeve oluşturulacaktır.​</t>
-  </si>
-  <si>
-    <t>Görsel Arşiv Çalışması</t>
+    <t>KALE IQ (Stok ve Envanter Zekası Girişimi)</t>
+  </si>
+  <si>
+    <t>KaleIQ, işletmelerin stoklarını doğru zamanda, doğru miktarda ve minimum maliyetle yönetmesini sağlayan akıllı stok yönetim asistanıdır. Sistem; ERP, BW, KBY ve diğer veri kaynaklarından aldığı canlı ve geçmiş dönem verilerini, gelişmiş yapay zeka yetenekleriyle harmanlayan, kullanıcıların verilerle doğal dilde konuşmasına olanak tanıyan, akıllı ikaz-uyarı ve otomatik karar destek mekanizmalarıyla çalışan veriye dayalı bir operasyonel izleme ve analiz platformudur.
+Projenin genel amacı, operasyonel stok yönetimini geleneksel raporlama yapısından çıkararak, yapay zeka destekli, proaktif ve etkileşimli bir karar destek mekanizmasına dönüştürmektir. Proje, şirket içindeki karmaşık envanter verilerini, satış geçmişini, bayi stok-satış ve teşhir bilgilerini LLM ve RAG mimarisiyle işleyerek, kullanıcıların sistemle doğal dilde iletişim kurmasının önünü açar. Bu sayede, kritik stok uyarılarının otomatik olarak üretilmesi, sku bazında aksiyon önerileri ve müşteriye özel dinamik teklif taslaklarının oluşturulması hedeflenmektedir. Nihai hedef, veriyi sadece izlemek değil; operasyonel verimliliği artıran, hızlı ve "sezgisel" içgörüler sunan akıllı bir iş akışı ekosistemi yaratmaktır.</t>
+  </si>
+  <si>
+    <t>Kısa Vadeli Hedefler
+Kullanıcılarının, veri ve analizlere hızla ulaşmasını sağlamak
+Haftalık ve aylık olarak hazırlanan manuel rapor ve analizlerin hazırlanma süresini kısaltmak/ortadan kaldırmak
+Sistemden alınan veriler ile YZ içgörüleri arasında tam uyum ile, karar vericilerin güvenle kullanabileceği bir "tek gerçek kaynak" platformu oluşturmak
+Kritik stok seviyeleri, oluşacak SDD, yaşlı stok, atıl stok gibi konularda otomatik ikaz-uyarı sistemine geçmek
+Uzun Vadeli Hedefler
+Atıl stok miktarını azaltmak ve optimum stok seviyelerini koruyarak, şirketin işletme sermayesi verimliliğini ve stok devir hızını artırmak
+Sistemin sadece veri sunan bir araçtan, bayi ve müşteri özelinde "en uygun fiyat ve paket" tekliflerini otomatik öneren aktif bir satış yardımcısına dönüşmesini sağlamak
+Kategori Pazarlama tarafından yürütülen ürün yönetimi sürecine girdi ve öneriler sağlamak.
+KALE IQ modelini diğer iş birimlerine ölçekleyerek, şirketin "Yapay Zeka Destekli Yönetim" vizyonuna öncülük etmek.</t>
+  </si>
+  <si>
+    <t>KALE IQ (Stok ve Envanter Zekası Girişimi) - B2B iyileştirme</t>
+  </si>
+  <si>
+    <t>KaleIQ - B2B İyileştirme, KS mağazalarının ve KS bayilerinin nihai müşteri satışlarında kullanabilecekleri bir satış destek sistemidir. Veri kaynağı olarak sistemdeki tüm stok (KS + tüm bayi stokları) bilgilerini kullanacaktır. Stok ve diğer ilave ana veriler ile müşteri ile satış temsilcisi arasındaki iletişim etkileşimin artırılması ve müşteri deneyiminin iyileştirilmesi hedeflenmektedir.
+Proje, bu sistemin kurulmasına yönelik olara KALE IQ altyapısı üzerinde yapılandırılacaktır.
+Projenin genel amacı, müşteri temsilcisi ile müşteri arasındaki iletişim ve etkileşimi artırarak müşterinin satış esnasındaki deneyimini iyileştirmek ve satış hacmini yükseltmektir.</t>
+  </si>
+  <si>
+    <t>Kısa Vadeli Hedefler
+KS mağazalarının kullanımını sağlamak
+KS satış ekibinin kullanımını sağlamak
+Uzun Vadeli Hedefler
+Bayi satış ekibinin kullanımını sağlamak
+Satış hacmini artırmak
+Müşteri deneyimini iyileştirmek
+Kategori Pazarlama tarafından yürütülen ürün yönetimi sürecine girdi ve öneriler sağlamak. (nihai müşteri talepleri)</t>
   </si>
 </sst>
 </file>
@@ -2121,7 +2196,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2166,20 +2241,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2187,6 +2251,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2217,7 +2282,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2264,16 +2329,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2620,27 +2676,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
-  <dimension ref="A1:M99"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="A1:M101"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.28515625" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83984375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.26171875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.26171875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="15.41796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.15625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.26171875" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" style="13" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="13" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="62.42578125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="90.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="51.85546875" style="4" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="11" customWidth="1"/>
-    <col min="15" max="16384" width="8.85546875" style="11"/>
+    <col min="8" max="8" width="11.15625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="11.26171875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="12.41796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="62.41796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="90.41796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="51.83984375" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.83984375" style="11" customWidth="1"/>
+    <col min="15" max="16384" width="8.83984375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="9" customFormat="1" ht="22.15" customHeight="1">
+    <row r="1" spans="1:13" s="9" customFormat="1" ht="45.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2681,7 +2737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="174">
+    <row r="2" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -2720,7 +2776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="72.599999999999994">
+    <row r="3" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -2759,7 +2815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="188.45">
+    <row r="4" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -2798,7 +2854,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="43.5">
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -2837,7 +2893,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="87">
+    <row r="6" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="10">
         <v>1</v>
       </c>
@@ -2867,7 +2923,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="43.5">
+    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="10">
         <v>1</v>
       </c>
@@ -2897,7 +2953,7 @@
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="43.5">
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -2927,7 +2983,7 @@
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="43.5">
+    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="10">
         <v>1</v>
       </c>
@@ -2957,7 +3013,7 @@
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="43.5">
+    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="10">
         <v>1</v>
       </c>
@@ -2989,7 +3045,7 @@
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="43.5">
+    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="10">
         <v>1</v>
       </c>
@@ -3021,7 +3077,7 @@
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="101.45">
+    <row r="12" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="10">
         <v>1</v>
       </c>
@@ -3060,7 +3116,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="116.1">
+    <row r="13" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="10">
         <v>1</v>
       </c>
@@ -3097,7 +3153,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="87">
+    <row r="14" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="10">
         <v>1</v>
       </c>
@@ -3136,7 +3192,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="87">
+    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="10">
         <v>1</v>
       </c>
@@ -3168,7 +3224,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="57.95">
+    <row r="16" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="10">
         <v>1</v>
       </c>
@@ -3200,7 +3256,7 @@
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:13" ht="130.5">
+    <row r="17" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="10">
         <v>1</v>
       </c>
@@ -3237,7 +3293,7 @@
       </c>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="116.1">
+    <row r="18" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="10">
         <v>1</v>
       </c>
@@ -3276,7 +3332,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="72.599999999999994">
+    <row r="19" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="10">
         <v>1</v>
       </c>
@@ -3315,7 +3371,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="116.1">
+    <row r="20" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="10">
         <v>1</v>
       </c>
@@ -3356,7 +3412,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="72.599999999999994">
+    <row r="21" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="10">
         <v>1</v>
       </c>
@@ -3392,7 +3448,7 @@
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:13" ht="43.5">
+    <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="10">
         <v>1</v>
       </c>
@@ -3426,7 +3482,7 @@
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:13" ht="101.45">
+    <row r="23" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="10">
         <v>1</v>
       </c>
@@ -3462,7 +3518,7 @@
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:13" ht="116.1">
+    <row r="24" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -3501,7 +3557,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="43.5">
+    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="10">
         <v>1</v>
       </c>
@@ -3538,7 +3594,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="43.5">
+    <row r="26" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="10">
         <v>1</v>
       </c>
@@ -3575,7 +3631,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="144.94999999999999">
+    <row r="27" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="10">
         <v>2</v>
       </c>
@@ -3611,7 +3667,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="116.1">
+    <row r="28" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="10">
         <v>2</v>
       </c>
@@ -3648,7 +3704,7 @@
       </c>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" ht="43.5">
+    <row r="29" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="10">
         <v>2</v>
       </c>
@@ -3680,7 +3736,7 @@
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:13" ht="43.5">
+    <row r="30" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="10">
         <v>2</v>
       </c>
@@ -3712,7 +3768,7 @@
       </c>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:13" ht="125.1" customHeight="1">
+    <row r="31" spans="1:13" ht="125.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="10">
         <v>2</v>
       </c>
@@ -3750,7 +3806,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="101.45">
+    <row r="32" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="10">
         <v>2</v>
       </c>
@@ -3788,7 +3844,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="64.5" customHeight="1">
+    <row r="33" spans="1:13" ht="64.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="10">
         <v>2</v>
       </c>
@@ -3820,7 +3876,7 @@
       </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:13" ht="186" customHeight="1">
+    <row r="34" spans="1:13" ht="186" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="10">
         <v>2</v>
       </c>
@@ -3858,7 +3914,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="132.4" customHeight="1">
+    <row r="35" spans="1:13" ht="132.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="10">
         <v>2</v>
       </c>
@@ -3897,7 +3953,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="314.25" customHeight="1">
+    <row r="36" spans="1:13" ht="314.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="10">
         <v>2</v>
       </c>
@@ -3936,7 +3992,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="187.5" customHeight="1">
+    <row r="37" spans="1:13" ht="187.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="10">
         <v>2</v>
       </c>
@@ -3975,7 +4031,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="187.5" customHeight="1">
+    <row r="38" spans="1:13" ht="187.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="10">
         <v>2</v>
       </c>
@@ -3999,7 +4055,7 @@
         <v>46023</v>
       </c>
       <c r="I38" s="12">
-        <v>46265</v>
+        <v>46387</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>17</v>
@@ -4007,14 +4063,14 @@
       <c r="K38" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="L38" s="14" t="s">
+      <c r="L38" s="1" t="s">
         <v>161</v>
       </c>
       <c r="M38" s="14" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="187.5" customHeight="1">
+    <row r="39" spans="1:13" ht="187.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -4046,14 +4102,14 @@
       <c r="K39" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="L39" s="14" t="s">
+      <c r="L39" s="1" t="s">
         <v>165</v>
       </c>
       <c r="M39" s="14" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="187.5" customHeight="1">
+    <row r="40" spans="1:13" ht="187.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="10">
         <v>2</v>
       </c>
@@ -4083,14 +4139,14 @@
       <c r="K40" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="L40" s="14" t="s">
+      <c r="L40" s="1" t="s">
         <v>169</v>
       </c>
       <c r="M40" s="14" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="318">
+    <row r="41" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="10">
         <v>3</v>
       </c>
@@ -4122,14 +4178,14 @@
       <c r="K41" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L41" s="14" t="s">
+      <c r="L41" s="1" t="s">
         <v>176</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="144.75">
+    <row r="42" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="10">
         <v>3</v>
       </c>
@@ -4161,14 +4217,14 @@
       <c r="K42" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="L42" s="14" t="s">
+      <c r="L42" s="1" t="s">
         <v>182</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="72.75">
+    <row r="43" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="10">
         <v>3</v>
       </c>
@@ -4200,14 +4256,14 @@
       <c r="K43" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="L43" s="18" t="s">
+      <c r="L43" s="4" t="s">
         <v>186</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="115.5">
+    <row r="44" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="10">
         <v>3</v>
       </c>
@@ -4239,12 +4295,12 @@
       <c r="K44" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="L44" s="14" t="s">
+      <c r="L44" s="1" t="s">
         <v>190</v>
       </c>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:13" ht="409.6">
+    <row r="45" spans="1:13" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="10">
         <v>3</v>
       </c>
@@ -4278,14 +4334,14 @@
       <c r="K45" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L45" s="14" t="s">
+      <c r="L45" s="1" t="s">
         <v>194</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="144.75">
+    <row r="46" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="10">
         <v>3</v>
       </c>
@@ -4317,14 +4373,14 @@
       <c r="K46" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="L46" s="14" t="s">
+      <c r="L46" s="1" t="s">
         <v>200</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="87">
+    <row r="47" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="10">
         <v>4</v>
       </c>
@@ -4356,14 +4412,14 @@
       <c r="K47" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="L47" s="14" t="s">
+      <c r="L47" s="1" t="s">
         <v>207</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="101.25">
+    <row r="48" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="10">
         <v>4</v>
       </c>
@@ -4395,14 +4451,14 @@
       <c r="K48" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="L48" s="14" t="s">
+      <c r="L48" s="1" t="s">
         <v>211</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="87">
+    <row r="49" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="10">
         <v>4</v>
       </c>
@@ -4434,14 +4490,14 @@
       <c r="K49" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="L49" s="14" t="s">
+      <c r="L49" s="1" t="s">
         <v>215</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="130.5">
+    <row r="50" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="10">
         <v>4</v>
       </c>
@@ -4473,14 +4529,14 @@
       <c r="K50" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="L50" s="14" t="s">
+      <c r="L50" s="1" t="s">
         <v>219</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="57.95">
+    <row r="51" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="10">
         <v>4</v>
       </c>
@@ -4521,7 +4577,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="87">
+    <row r="52" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="10">
         <v>4</v>
       </c>
@@ -4560,7 +4616,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="43.5">
+    <row r="53" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="10">
         <v>4</v>
       </c>
@@ -4599,7 +4655,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="72.599999999999994">
+    <row r="54" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="10">
         <v>4</v>
       </c>
@@ -4635,7 +4691,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="101.45">
+    <row r="55" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="10">
         <v>4</v>
       </c>
@@ -4674,7 +4730,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="87">
+    <row r="56" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="10">
         <v>4</v>
       </c>
@@ -4713,7 +4769,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="130.5">
+    <row r="57" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="10">
         <v>4</v>
       </c>
@@ -4752,7 +4808,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="130.5">
+    <row r="58" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="10">
         <v>4</v>
       </c>
@@ -4791,7 +4847,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="101.45">
+    <row r="59" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="10">
         <v>4</v>
       </c>
@@ -4830,7 +4886,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="94.5" customHeight="1">
+    <row r="60" spans="1:13" ht="94.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="10">
         <v>5</v>
       </c>
@@ -4864,14 +4920,14 @@
       <c r="K60" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="L60" s="16" t="s">
+      <c r="L60" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="M60" s="17" t="s">
+      <c r="M60" s="2" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="101.25">
+    <row r="61" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="10">
         <v>5</v>
       </c>
@@ -4905,14 +4961,14 @@
       <c r="K61" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="L61" s="16" t="s">
+      <c r="L61" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="M61" s="17" t="s">
+      <c r="M61" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="188.25">
+    <row r="62" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="10">
         <v>5</v>
       </c>
@@ -4946,14 +5002,14 @@
       <c r="K62" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="L62" s="16" t="s">
+      <c r="L62" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="M62" s="17" t="s">
+      <c r="M62" s="2" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="72.75">
+    <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="10">
         <v>5</v>
       </c>
@@ -4994,7 +5050,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="130.5">
+    <row r="64" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="10">
         <v>5</v>
       </c>
@@ -5026,14 +5082,14 @@
       <c r="K64" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="L64" s="16" t="s">
+      <c r="L64" s="1" t="s">
         <v>289</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="159.6">
+    <row r="65" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="10">
         <v>5</v>
       </c>
@@ -5067,7 +5123,7 @@
       </c>
       <c r="L65" s="4"/>
     </row>
-    <row r="66" spans="1:13" ht="101.25">
+    <row r="66" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="10">
         <v>5</v>
       </c>
@@ -5099,14 +5155,14 @@
       <c r="K66" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="L66" s="16" t="s">
+      <c r="L66" s="1" t="s">
         <v>297</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="43.5">
+    <row r="67" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="10">
         <v>5</v>
       </c>
@@ -5141,11 +5197,11 @@
       <c r="L67" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="M67" s="1" t="s">
+      <c r="M67" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="72.75">
+    <row r="68" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="10">
         <v>5</v>
       </c>
@@ -5177,14 +5233,14 @@
       <c r="K68" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="L68" s="16" t="s">
+      <c r="L68" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="M68" s="19" t="s">
+      <c r="M68" s="16" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="57.75">
+    <row r="69" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="10">
         <v>5</v>
       </c>
@@ -5216,14 +5272,14 @@
       <c r="K69" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="L69" s="16" t="s">
+      <c r="L69" s="1" t="s">
         <v>310</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="57.75">
+    <row r="70" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="10">
         <v>5</v>
       </c>
@@ -5255,14 +5311,14 @@
       <c r="K70" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="L70" s="16" t="s">
+      <c r="L70" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="M70" s="16" t="s">
+      <c r="M70" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="43.5">
+    <row r="71" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="10">
         <v>5</v>
       </c>
@@ -5298,7 +5354,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="72.599999999999994">
+    <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="10">
         <v>6</v>
       </c>
@@ -5334,7 +5390,7 @@
       </c>
       <c r="M72" s="1"/>
     </row>
-    <row r="73" spans="1:13" ht="72.599999999999994">
+    <row r="73" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="10">
         <v>6</v>
       </c>
@@ -5360,17 +5416,22 @@
         <v>45931</v>
       </c>
       <c r="I73" s="12">
-        <v>46053</v>
+        <v>46295</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="M73" s="1"/>
-    </row>
-    <row r="74" spans="1:13" ht="116.1">
+      <c r="L73" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="10">
         <v>6</v>
       </c>
@@ -5387,7 +5448,7 @@
         <v>321</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>323</v>
@@ -5396,20 +5457,22 @@
         <v>45931</v>
       </c>
       <c r="I74" s="12">
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>324</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="M74" s="1"/>
-    </row>
-    <row r="75" spans="1:13" ht="116.1">
+        <v>329</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="10">
         <v>6</v>
       </c>
@@ -5426,28 +5489,31 @@
         <v>321</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>323</v>
       </c>
       <c r="H75" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I75" s="12">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K75" s="3" t="s">
         <v>324</v>
       </c>
+      <c r="L75" s="1" t="s">
+        <v>333</v>
+      </c>
       <c r="M75" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="116.1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="10">
         <v>6</v>
       </c>
@@ -5464,28 +5530,29 @@
         <v>321</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>323</v>
       </c>
       <c r="H76" s="12">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I76" s="12">
         <v>46387</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="M76" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="29.1">
+      <c r="L76" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="M76" s="1"/>
+    </row>
+    <row r="77" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="10">
         <v>6</v>
       </c>
@@ -5502,20 +5569,31 @@
         <v>321</v>
       </c>
       <c r="F77" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H77" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I77" s="12">
+        <v>46387</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H77" s="12"/>
-      <c r="I77" s="12"/>
-      <c r="J77" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K77" s="5"/>
-      <c r="L77" s="4"/>
-    </row>
-    <row r="78" spans="1:13" ht="29.1">
+      <c r="K77" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="10">
         <v>6</v>
       </c>
@@ -5529,23 +5607,34 @@
         <v>320</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H78" s="12"/>
-      <c r="I78" s="12"/>
+        <v>323</v>
+      </c>
+      <c r="H78" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I78" s="12">
+        <v>46387</v>
+      </c>
       <c r="J78" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K78" s="5"/>
-      <c r="L78" s="4"/>
-    </row>
-    <row r="79" spans="1:13" ht="29.1">
+        <v>332</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="10">
         <v>6</v>
       </c>
@@ -5559,13 +5648,13 @@
         <v>320</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
@@ -5575,7 +5664,7 @@
       <c r="K79" s="5"/>
       <c r="L79" s="4"/>
     </row>
-    <row r="80" spans="1:13" ht="116.1">
+    <row r="80" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="10">
         <v>6</v>
       </c>
@@ -5583,40 +5672,29 @@
         <v>319</v>
       </c>
       <c r="C80" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="H80" s="12">
-        <v>46204</v>
-      </c>
-      <c r="I80" s="12">
-        <v>46387</v>
-      </c>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
       <c r="J80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="116.1">
+        <v>70</v>
+      </c>
+      <c r="K80" s="5"/>
+      <c r="L80" s="4"/>
+    </row>
+    <row r="81" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="10">
         <v>6</v>
       </c>
@@ -5624,40 +5702,29 @@
         <v>319</v>
       </c>
       <c r="C81" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="E81" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F81" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="G81" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H81" s="12">
-        <v>46023</v>
-      </c>
-      <c r="I81" s="12">
-        <v>46142</v>
-      </c>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
       <c r="J81" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="101.45">
+        <v>70</v>
+      </c>
+      <c r="K81" s="5"/>
+      <c r="L81" s="4"/>
+    </row>
+    <row r="82" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="10">
         <v>6</v>
       </c>
@@ -5668,37 +5735,37 @@
         <v>2</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F82" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H82" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I82" s="12">
+        <v>46203</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K82" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="L82" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="H82" s="12">
-        <v>45992</v>
-      </c>
-      <c r="I82" s="12">
-        <v>46142</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="K82" s="3" t="s">
+      <c r="M82" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="L82" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="116.1">
+    </row>
+    <row r="83" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="10">
         <v>6</v>
       </c>
@@ -5709,37 +5776,37 @@
         <v>2</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E83" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G83" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>359</v>
-      </c>
       <c r="H83" s="12">
-        <v>46023</v>
+        <v>46204</v>
       </c>
       <c r="I83" s="12">
         <v>46387</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K83" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="M83" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="L83" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="217.5">
+    </row>
+    <row r="84" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="10">
         <v>6</v>
       </c>
@@ -5750,37 +5817,35 @@
         <v>2</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="H84" s="12">
         <v>46023</v>
       </c>
       <c r="I84" s="12">
-        <v>46357</v>
+        <v>46142</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>329</v>
+        <v>70</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="101.45">
+        <v>364</v>
+      </c>
+      <c r="M84" s="2"/>
+    </row>
+    <row r="85" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="10">
         <v>6</v>
       </c>
@@ -5791,37 +5856,37 @@
         <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E85" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="H85" s="12">
+        <v>45992</v>
+      </c>
+      <c r="I85" s="12">
+        <v>46142</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="M85" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H85" s="12">
-        <v>45931</v>
-      </c>
-      <c r="I85" s="12">
-        <v>46053</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="130.5">
+    </row>
+    <row r="86" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="10">
         <v>6</v>
       </c>
@@ -5832,37 +5897,37 @@
         <v>2</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="H86" s="12">
         <v>46023</v>
       </c>
       <c r="I86" s="12">
-        <v>46112</v>
+        <v>46387</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K86" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="M86" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="L86" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="130.5">
+    </row>
+    <row r="87" spans="1:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="10">
         <v>6</v>
       </c>
@@ -5873,37 +5938,37 @@
         <v>2</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F87" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G87" s="3" t="s">
         <v>378</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="H87" s="12">
         <v>46023</v>
       </c>
       <c r="I87" s="12">
-        <v>46203</v>
+        <v>46357</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K87" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="L87" s="1" t="s">
+      <c r="L87" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="M87" s="1" t="s">
+      <c r="M87" s="2" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="57.95">
+    <row r="88" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="10">
         <v>6</v>
       </c>
@@ -5914,37 +5979,35 @@
         <v>2</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>382</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="H88" s="12">
-        <v>46174</v>
+        <v>45931</v>
       </c>
       <c r="I88" s="12">
-        <v>46295</v>
+        <v>46053</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="L88" s="1" t="s">
+      <c r="L88" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="M88" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="144.94999999999999">
+      <c r="M88" s="2"/>
+    </row>
+    <row r="89" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="10">
         <v>6</v>
       </c>
@@ -5955,37 +6018,37 @@
         <v>2</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="F89" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H89" s="12">
+        <v>45931</v>
+      </c>
+      <c r="I89" s="12">
+        <v>46203</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="L89" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H89" s="12">
-        <v>46023</v>
-      </c>
-      <c r="I89" s="12">
-        <v>46142</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="K89" s="3" t="s">
+      <c r="M89" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="L89" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="M89" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="101.45">
+    </row>
+    <row r="90" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="10">
         <v>6</v>
       </c>
@@ -5993,38 +6056,40 @@
         <v>319</v>
       </c>
       <c r="C90" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H90" s="12">
+        <v>46023</v>
+      </c>
+      <c r="I90" s="12">
+        <v>46203</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="L90" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="M90" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="G90" s="3"/>
-      <c r="H90" s="12">
-        <v>45931</v>
-      </c>
-      <c r="I90" s="12">
-        <v>46157</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="M90" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="72.599999999999994">
+    </row>
+    <row r="91" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="10">
         <v>6</v>
       </c>
@@ -6032,36 +6097,40 @@
         <v>319</v>
       </c>
       <c r="C91" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>390</v>
+        <v>348</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>391</v>
+        <v>349</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="G91" s="3"/>
+        <v>392</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="H91" s="12">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="I91" s="12">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>31</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="L91" s="4"/>
+        <v>393</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>394</v>
+      </c>
       <c r="M91" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="130.5">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="10">
         <v>6</v>
       </c>
@@ -6069,40 +6138,40 @@
         <v>319</v>
       </c>
       <c r="C92" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>399</v>
+        <v>348</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>400</v>
+        <v>349</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>402</v>
+        <v>351</v>
       </c>
       <c r="H92" s="12">
         <v>46023</v>
       </c>
       <c r="I92" s="12">
-        <v>46357</v>
+        <v>46264</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="57.95">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="10">
         <v>6</v>
       </c>
@@ -6110,38 +6179,38 @@
         <v>319</v>
       </c>
       <c r="C93" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>399</v>
+        <v>348</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>406</v>
+        <v>349</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G93" s="3"/>
+        <v>400</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="H93" s="12">
-        <v>46023</v>
+        <v>46174</v>
       </c>
       <c r="I93" s="12">
-        <v>46082</v>
+        <v>46264</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>409</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="L93" s="2"/>
       <c r="M93" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="72.599999999999994">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="10">
         <v>6</v>
       </c>
@@ -6149,38 +6218,38 @@
         <v>319</v>
       </c>
       <c r="C94" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="G94" s="3"/>
       <c r="H94" s="12">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="I94" s="12">
-        <v>46112</v>
+        <v>46157</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>57</v>
+        <v>332</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="130.5">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="10">
         <v>6</v>
       </c>
@@ -6188,38 +6257,36 @@
         <v>319</v>
       </c>
       <c r="C95" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="G95" s="3"/>
       <c r="H95" s="12">
-        <v>45901</v>
+        <v>46173</v>
       </c>
       <c r="I95" s="12">
-        <v>46112</v>
+        <v>46387</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>329</v>
+        <v>31</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>417</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="L95" s="4"/>
       <c r="M95" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="116.1">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="10">
         <v>6</v>
       </c>
@@ -6227,40 +6294,40 @@
         <v>319</v>
       </c>
       <c r="C96" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="H96" s="12">
         <v>46023</v>
       </c>
       <c r="I96" s="12">
-        <v>46295</v>
+        <v>46357</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="87">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="10">
         <v>6</v>
       </c>
@@ -6268,40 +6335,36 @@
         <v>319</v>
       </c>
       <c r="C97" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D97" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>426</v>
-      </c>
       <c r="F97" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>428</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="G97" s="3"/>
       <c r="H97" s="12">
         <v>46023</v>
       </c>
       <c r="I97" s="12">
-        <v>46266</v>
+        <v>46082</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>329</v>
+        <v>57</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="101.45">
+        <v>422</v>
+      </c>
+      <c r="M97" s="2"/>
+    </row>
+    <row r="98" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="10">
         <v>6</v>
       </c>
@@ -6309,62 +6372,153 @@
         <v>319</v>
       </c>
       <c r="C98" s="10">
+        <v>4</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="G98" s="3"/>
+      <c r="H98" s="12">
+        <v>45901</v>
+      </c>
+      <c r="I98" s="12">
+        <v>46112</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="M98" s="2"/>
+    </row>
+    <row r="99" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="10">
+        <v>6</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C99" s="10">
+        <v>4</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="G99" s="3"/>
+      <c r="H99" s="12">
+        <v>45901</v>
+      </c>
+      <c r="I99" s="12">
+        <v>46112</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="10">
+        <v>6</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C100" s="10">
         <v>5</v>
       </c>
-      <c r="D98" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="F98" s="3" t="s">
+      <c r="D100" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="E100" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="F100" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="H98" s="12">
-        <v>46023</v>
-      </c>
-      <c r="I98" s="12">
-        <v>46357</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="K98" s="3" t="s">
+      <c r="G100" s="3"/>
+      <c r="H100" s="12">
+        <v>46174</v>
+      </c>
+      <c r="I100" s="12">
+        <v>46295</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K100" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="L98" s="4"/>
-      <c r="M98" s="2" t="s">
+      <c r="L100" s="2"/>
+      <c r="M100" s="2" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="29.1">
-      <c r="A99" s="10">
-        <v>2</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C99" s="10">
-        <v>2</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F99" s="3" t="s">
+    <row r="101" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="10">
+        <v>6</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C101" s="10">
+        <v>5</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>435</v>
       </c>
+      <c r="G101" s="3"/>
+      <c r="H101" s="12">
+        <v>46235</v>
+      </c>
+      <c r="I101" s="12">
+        <v>46356</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2" t="s">
+        <v>437</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M98">
-    <sortCondition ref="A9:A98"/>
-    <sortCondition ref="C9:C98"/>
-    <sortCondition ref="E9:E98"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M101">
+    <sortCondition ref="A9:A101"/>
+    <sortCondition ref="C9:C101"/>
+    <sortCondition ref="E9:E101"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/TZY Gelişim Planı/Gelişim Planı/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="461" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1097A4-8374-47F8-A1BD-3AADB94BCC89}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE69C9E3-9F7A-4ED7-8630-F580BA23A6DA}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="525" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="560" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects Data" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="442">
   <si>
     <t>department order</t>
   </si>
@@ -102,14 +102,16 @@
     <t>Ürün bilgilerinin ve karakteristik tanımlarının düzenli takibi ve kontrolü için Ürün Dashboard çalışması tamamlanmıştır.
 Haftalık toplantılar ile ürün bilgilerindeki eksiklikler tespit edilmekte ve çalışmalar yapılmaktadır.
 Bölüm KPI'larına Ürün Ana Veri İyileştirme Endeksi eklenmiştir.
-Faturalama için ambalaj tipi tanımları takip edilmekte ve eksiklikler giderilmektedir.
 Piyasa kanalı tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+Kalite tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+Planlama stratejilerinin tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+DFU tanımları takip edilmekte ve eksiklikler giderilmektedir.
 Üretim kontrol notu takip edilmekte ve eksiklikler giderilmektedir.
-Ürün hiyerarşisi uyumsuzluklarının tespit edilmekte ve düzeltilmektedir.
-Ürün hiyerarşisi tanımı yanlış olan kodların tespit edilmekte ve düzeltilmektedir.
-Gömme rezervuar ürün grubunda set kodlarının ayrıştırılmıştır.
+Ürün hiyerarşisi uyumsuzlukları tespit edilmekte ve düzeltilmektedir.
+Ürün hiyerarşisi tanımı yanlış olan kodlar tespit edilmekte ve düzeltilmektedir.
+Gömme rezervuar ürün grubunda set kodları ayrıştırılmıştır.
 Marka tanımları takip edilmekte ve eksiklikler giderilmektedir.
-Kalite tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.</t>
+Faturalama için ambalaj tipi tanımları takip edilmekte ve eksiklikler giderilmektedir.</t>
   </si>
   <si>
     <t>Orijin kodu bilgisinin düzenlenmesi ile ilgili çalışmaların başlatılması
@@ -118,7 +120,7 @@
 Vitrifiye Renk Tanımı Eksikliklerinin Giderilmesi
 SKM Ebat Eksikliklerinin Giderilmesi ve Bilgi Kontrolü
 SKM Kısa Kod Eksikliklerinin Giderilmesi ve Bilgi Kontrolü
-Planlama stratejilerinin tanımlarının revizyonu yapılmıştır. Kod bazlı tanımlamaların yapılması</t>
+Mükerrer açılan kodların tespiti ve düzenlenmesi</t>
   </si>
   <si>
     <t>Ürün Ambalaj Bilgilerinin Tanımlanması</t>
@@ -133,8 +135,10 @@
 Palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi - SKM</t>
   </si>
   <si>
-    <t>Ürün ve palet kg bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
-Palet içi miktar bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye</t>
+    <t>Ürün ve palet kg bilgilerinin kontrolü ve eksikliklerin giderilmesi - SKM (numune kodlar)
+Ürün ve palet kg bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
+Palet içi miktar bilgilerinin kontrolü ve eksikliklerin giderilmesi - Vitrifiye
+Palet içi miktar bilgilerinin kontrolü ve eksikliklerin giderilmesi - Tedarik Ürünler</t>
   </si>
   <si>
     <t>Ürünler Arası İlişki Tanımlarının Oluşturulması</t>
@@ -143,18 +147,18 @@
     <t>Birbirleri ile satış ve fonksiyonellik açısından bağı bulunun ancak mevcutta ürün ağacı, pack, vb. bir veri yapısında bu ilişkisi tanımlanmamış olan ürünlerin ilgili veri yapısının kurumsal veri olarak yapılandırılması çalışmasıdır.</t>
   </si>
   <si>
-    <t>Örnek veri yapısının oluşturularak IT ile paylaşılması</t>
-  </si>
-  <si>
-    <t>İlgili ürünlerin ve ilişkilerin belirlenmesi
-İlgili veri yapısının şirket içindeki kullanım şeklinin netleştirilmesi
-MRP tarafındaki kullanımının araştırılması
-Planlamadaki miktar bilgilerinde kullanılması
-Raporlamalardaki kullanım
+    <t xml:space="preserve">Örnek veri yapısı oluşturularak IT ile paylaşılmıştır.
+Kavramsal tasarım dokümanı oluşturularak IT ile paylaşılmıştır. 
+</t>
+  </si>
+  <si>
+    <t>İlgili veri yapısının şirket içindeki kullanım şeklinin netleştirilmesi
+PP modülü için MRP kullanımının araştırılması
+Raporlama olarak kullanımının sağlanması
 B2B'de öneri şeklinde sunulması
 Kalecore sayfasında öneri şeklinde sunulması
 Mevcut veri yapısının araştırılması (kataloglar ve fiyat listeleri gibi)
-İlişkilerin Tanımına dair ana veri yapısı çalışmasının yürütülmesi (IT ile)
+İlişki kurulacak ürünlerin ve ilişki yapısının belirlenmesi
 Gerekli tanımlamaların yapılması</t>
   </si>
   <si>
@@ -167,10 +171,10 @@
     <t>Başlamadı</t>
   </si>
   <si>
-    <t>"Ürünler Arası İlişki Tanımlarının Oluşturulması" projesi kapsamında oluşturulan verinin kurumsal olarak saklanması ve yönetimi için için yönetim aracı geliştirilmedi çalışmasıdır.</t>
-  </si>
-  <si>
-    <t>İlişki Verileri Yönetim Aracının Oluşturulması</t>
+    <t>"Ürünler Arası İlişki Tanımlarının Oluşturulması" projesi kapsamında oluşturulan verinin kurumsal olarak saklanması ve yönetimi için yönetim aracı geliştirilmesi çalışmasıdır.</t>
+  </si>
+  <si>
+    <t>Yönetim aracı belirlendikten sonra ilişkilerin tanımına dair ana veri çalışmalarının yürütülmesi</t>
   </si>
   <si>
     <t>Tahmin Dış Verisi</t>
@@ -288,7 +292,7 @@
     <t>Tahmin modelinin oluşturulmasına yönelik kavramsal çalışmalar başlatılmıştır.
 Müşteri sipariş verilerine yönelik veri seti oluşturulmuştur.
 In-house talep tahmin çalışması başlatılmıştır.
-Model ve uygulamanın oluşturulmasına yönelik danışman firma ile proje takvimi ve adımlarının belirlenmesi devam etmektedir.
+Model ve uygulamanın oluşturulmasına yönelik danışman firma ile proje takvimi ve adımları belirlenmiştir.
 Modele beslenecek dış veriler belirlenmiştir.</t>
   </si>
   <si>
@@ -353,12 +357,14 @@
 Aylık S&amp;OP takvimine uygun bir şekilde toplantılar gerçekleştirilerek S&amp;OP kültürünün yayılımı sağlanmıştır. 
 Toplantı gündeminin standartlaştırılması sağlanmıştır.
 Toplantı sunumları ve tutanakları düzenli bir şekilde paylaşılmaktadır.
-Karar, aksiyon ve sorumluluk takibi yapısının kurulmuştur.
-Fabrika kapalılıkları, ÇKG ve büyük tutarlı ticari alım konuları gündeme getirilerek kritik kararların verilmesi sağlanmıştır.
+Karar, aksiyon ve sorumluluk takibi yapısı kurulmuştur.
+Fabrika kapalılıkları, ÇKG ve büyük tutarlı ticari alım konuları gündeme getirilerek kritik kararların verilmesi sağlanmaktadır.
 Standart rapor setlerinin oluşturulmuştur.</t>
   </si>
   <si>
-    <t>Finansallaştırma adımının eklenmesi ile birlikte S&amp;OP döngüsünün tamamlanması</t>
+    <t>Satış ve üretim planlama ile mutabakat toplantılarının standartlaştırılması
+Nihai tahmin sonucu üretim ve stok miktarlarının oluşturularak standart raporların hazırlanması
+Finansallaştırma adımının eklenmesi ile birlikte S&amp;OP döngüsünün tamamlanması</t>
   </si>
   <si>
     <t>Talep Optimizasyon Aracının Geliştirilmesi</t>
@@ -388,17 +394,20 @@
     <t>Talep tahmin uygulamasının çıktısını kullanarak tedarik planlama adımına girdi olacak ve mutabakat sağlanmış talep değerlerinin oluşturulmasını sağlayacak talep zenginleştirme ve mutabakat uygulamasının geliştirilmesi çalışmasıdır. Tahmin sonuçlarının girdi olarak alınabildiği, belirli hiyerarşilerde düzeltme yapılabildiği, belirli kişilerin üzerinde çalışabildiği ve veri girişi yapabildiği esnek bir ortam geliştirme çalışmasıdır. Odoo platformu üzerinde In-house olarak geliştirilmektedir.</t>
   </si>
   <si>
-    <t>İstekler belirlenerek kavramsal tasarım dokümanı IT birimine iletilmiştir.
-Yazılım ve KS ekibi kavramsal tasarım üzerinde mutabakat sağlamıştır.
-İş akış dokümanı oluşturulmuştur ve IT ekibine iletilmiştir.
+    <t>İstekler belirlenerek kavramsal tasarım dokümanı IT birimine iletilerek mutabakat sağlamıştır.
+İş akış dokümanı oluşturulmuştur.
 IT tarafından platform kararı verilmiştir.
 Proje planı ve backloglar oluşturulmuştur. (agile proje yönetimi)
 Sprint-1 kapsamında sistemsel düzenlemeler yapılmıştır. 
-Sprint-2 kapsamında senaryo oluşturma, excel ile veri yükleme, verilerin raporlanması  ve yetki düzenlemeleri  yapılmıştır.</t>
-  </si>
-  <si>
-    <t>Proje takvimine uygun olarak aksiyon takibi ve test çalışmaları yürütülecektir.
-Sprint-3 kapsamında DFU bazlı revizyonların yapılması, katsayı ile revizyonların yapılması, iş akışının durumunun gösterilmesi ve kullanıcı bazlı testler yapılacaktır.</t>
+Sprint-2 kapsamında senaryo ve rollerin oluşturulması, excel ile verilerin yüklenmesi/raporlanması ve rol bazlı yetki düzenlemeleri  yapılmıştır.
+Sprint-3 kapsamında DFU bazlı revizyonlar, katsayı ile revizyonlar ve iş akış durumunun gösterilmesi yapılmıştır.
+Sprint-4 kapsamında kullanıcı bazlı test ortamına erişim, iş akışının onaylanması ve yürütülmesi, değişiklik takibinin yapılması ve dönem bazlı kilitleme yapılmıştır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proje takvimine uygun olarak aksiyon takibi ve test çalışmaları yürütülecektir.
+Sprint-5 kapsamında çalışmalar devam etmektedir. 
+Toplam 8 sprint ile proje tamamlanacaktır.
+</t>
   </si>
   <si>
     <t>S&amp;OP Finansallaştırma Uyg. Geliştirilmesi</t>
@@ -755,11 +764,13 @@
 Proje kapsamında; aktif ve pasif malzeme kodları ayrıştırılacak, gereksiz kodların azaltılması sağlanacak ve yeni kod açılış süreçleri kontrol altına alınacaktır. Böylece stok yapısı daha şeffaf hale gelecek, planlama ve satın alma süreçleri daha sağlıklı veri üzerinden yürütülecek ve gereksiz stok oluşumunun önüne geçilecektir.</t>
   </si>
   <si>
-    <t>KS02 malzeme türleri için detaylı analiz çalışması gerçekleştirilmiştir
+    <t xml:space="preserve">KS02 malzeme türleri için detaylı analiz çalışması gerçekleştirilmiştir
 İlgili malzeme kodları için SAT, SAS, kod yaşı ve hareket analizleri yapılmıştır
 Son tüketim ve hareket verilerine göre kullanılmayan hareketsiz kodlar tespit edilmiştir
 KS02 kapsamında yapılan analizler ile yaklaşık 3000 atıl malzeme kodu sistemden ayrıştırılmıştır.
-Analiz kapsamında 2025–2026 yıllarında açılan yeni kodlar hariç tutulmuştur</t>
+Analiz kapsamında 2025–2026 yıllarında açılan yeni kodlar hariç tutulmuştur.
+3 Aylık periyotlarda ana veri temizlik ve kontrol süreci planlanmıştır.
+</t>
   </si>
   <si>
     <t>Mükerrer ve benzer malzeme kodları ana veri seviyesinde gözden geçirilerek birleştirilecektir
@@ -767,7 +778,7 @@
 Tüm organizasyonda kullanılmak üzere standart bir kod isimlendirme yapısı oluşturulacaktır
 Görsel arşiv (SKUMATCH) ile malzeme ana veri süreci entegre edilerek doğru kod seçimi desteklenecektir
 Malzeme ana veri kalitesi belirli KPI’lar ile düzenli olarak izlenecek ve raporlanacaktır
-Belirli periyotlarda (aylık/çeyreklik) ana veri temizlik ve kontrol süreci işletilecektir</t>
+Kod talep süreçlerinin standart hale getirilmesi için prosedür/talimat dokümanının hazırlanarak devreye alınacaktır.</t>
   </si>
   <si>
     <t>Lojistik</t>
@@ -847,7 +858,8 @@
     <t>SLA kapsamında müşteri ve KS gerekliliklerini, kurallarını, uygulama esaslarının tanımlandığı metnin güncel ihtiyaçlara göre gözden geçirilmesi, uygulanmayan kuralların kaldırılması, uygulanması gerekenlerin eklenmesi, anlaşılır ve sade bir dille metnin tekrar hazırlanması.</t>
   </si>
   <si>
-    <t>2026 yılı ön hazırlıkları yapıldı. Üst yönetim takvimine istinaden 2026 Mayıs ayına ilk toplantı organize edildi.</t>
+    <t>2026 yılı ön hazırlıkları yapıldı. Üst yönetim takvimine istinaden 2026 Mayıs ayına ilk toplantı organize edildi.
+Satış ve müşteri talepleri alındı. TZY değerlendirmesi devam ediyor.</t>
   </si>
   <si>
     <t>TZY, satış ve diğer satış sürecine dahil birimlerin SLA'yı arttırmak amacı ile önerileri değerlendirilerek kural setine dönüştürülecek ve müşterilere duyurusu yapılacak.</t>
@@ -937,7 +949,9 @@
 ​Proje takvimi netleştirildi.​
 Bölümler arası bilgilendirme ve görevlendirme yapıldı.
 Sistem kurulumu ve uygulanmas için alınacak aksiyonlar belirlendi.
-Bağlam ve İlgili Taraflar Analizi 16 Nisan'da başladı. Belgelendirme firması yönlendirmesi ile haftalık güncellemeler yapılıyor.</t>
+Bağlam ve İlgili Taraflar Analizi 16 Nisan'da başladı. Belgelendirme firması yönlendirmesi ile haftalık güncellemeler yapılıyor.
+22 Mayıs tarihinde el kitabı ve ek dokümanlar hazırlandı.
+4 Haziran'da nihai kontroller yapılarak belgelendirme ay sonuna kadar tamamlanacak.</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -1713,12 +1727,14 @@
     <t>YK Masse Dijital Dönüşüm</t>
   </si>
   <si>
-    <t>Sürecin yazılımı tamamlanmıştır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saha Scada entegrasyonları yapılacaktır.
-IOT, Gateway tedarik süreci başlatılmıştır.
-Step Teknoloji tarafından yapılacak tersine mühendislik çalışmaları haziran başı itibariyle başlatılacaktır. </t>
+    <t>Sürecin yazılımı tamamlanmıştır.
+IOT tedariği yapılmıştır. Pano montajları başlatılmıştır.
+Gr&amp;Sfx Masse ile farklılıkların iş maddeleri çıkarılmıştır.</t>
+  </si>
+  <si>
+    <t>Saha Scada entegrasyonları yapılacaktır.
+Gateway tedarik süreci başlatılmıştır.
+Step Teknoloji tarafından yapılacak tersine mühendislik çalışmaları haziran başı itibariyle başlatılmıştır.</t>
   </si>
   <si>
     <t>GR İkincil İşlemler Kurulumu</t>
@@ -1731,7 +1747,8 @@
   <si>
     <t>Parlatma kareleme makineleri için veri mühendisliği çalışmaları devam etmektedir.
 Stok takip entegrasyon çalışmaları devam etmektedir.
-Kesme nedeniyle izlenebilirlik kaybı için çözüm geliştirilecektir.</t>
+Kesme nedeniyle izlenebilirlik kaybı için çözüm geliştirilecektir.
+Donanım ve pano montajları devam etmektedir.</t>
   </si>
   <si>
     <t>KB7 Kurulumu</t>
@@ -1740,8 +1757,8 @@
     <t>Devam ediyor</t>
   </si>
   <si>
-    <t xml:space="preserve">KB7 fabrikası iş analizi tamamlanmış olup backlog listesi tamamlanmıştır.​
-Saha çalışmaları tamamlanmıştır. Fırın çıkışına kadar olan sürecin yazılımı tamamlanmıştır. ​
+    <t xml:space="preserve">KB7 fabrikası iş analizi tamamlanmış olup backlog listesi oluşturulmuştur.
+Saha çalışmaları ve fırın çıkışına kadar olan sürecin yazılımı tamamlanmıştır. ​
 KB7 fabrikası fırın sonrası 2. işlemler için saha veri çalışmaları, tersine mühendislik çalışmaları tamamlanmıştır. ​
 Fırın çıkışı sonrası MES yazılımı tamamlanmıştır.​
 Kalite ayrım hata giriş ekranı ve ambalaj makinesi senkronizasyonu tamamlanmıştır.
@@ -1750,6 +1767,7 @@
   </si>
   <si>
     <t>Kırmızı fire eşleşme doğrulaması devam ediyor​. 
+İkincil işlemler yazılımı ve donanımı tamamlanmış, kullanıcı testleri devam etmektedir.
 Yeni alınan otomatik kalite ayrım makinesinin verilerinin alınacak ve barkod eşleştirmesi yapılacaktır.
 Fırın üst parlatma hattı eski olduğu için çalışma yapılmamış , 2027 yatırımı ile yenilenecek hatta yapılacaktır.</t>
   </si>
@@ -1757,24 +1775,36 @@
     <t>KB3 Kurulumu</t>
   </si>
   <si>
-    <t>KB3  fabrikası iş analizi tamamlanmış olup backlog listesi tamamlanmıştır.​
+    <t>KB3  fabrikası iş analizi tamamlanmış olup backlog listesi oluşturulmuştur.
 Saha çalışmaları tamamlanmıştır.
 KB3 fabrikası makineleri için  saha veri çalışmaları, tersine mühendislik teklifleri onaylanmıştır.
 KB7 ile olan parkur farklılıkları analizi tamamlanmıştır.</t>
   </si>
   <si>
+    <t>Donanım tedariği ile birlikte pano ve montaj çalışmaları başlatılacaktır.
+Granit ve KB7'den  farklı olan makine parkuru için tersine mühendislik çalışmaları başlatılacaktır. (PLC ve Scada)
+Yeni yatırıma göre makine entegrasyonu sağlanacaktır.(Yeni yatırım kararı netleşmedi)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SLAB MES Yapısının Kurulması </t>
   </si>
   <si>
-    <t>Kavramsal tasarımları tamamlanmıştır.</t>
+    <t>Kavramsal tasarımları tamamlanmıştır.
+Backlog maddeleri oluşturulmaya başlanmıştır.</t>
+  </si>
+  <si>
+    <t>Yeni yatırımı yapılan System ve Sacmi kalite kontrol cihazlarının entegrasyonu başlatılacak. Gerekli kontrollerin tamamlanmasından sonra; Toplanan tüm makine verileri ile tekil karo bazında ileri analitik çalışmaları başlatılacak.​
+Yapay zekâ algoritmaları ile minimum fire ve maksimum verim sağlanacak.​
+Üretim hattı yöneticileri, dijital panellerden anlık KPI’ları görecek (verimlilik, kalite, fire oranı, OEE vb.).​
+Hypermate ile Kale99 entegrasyon çalışmaları başlatılacaktır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperA MES Yapısının Kurulması </t>
   </si>
   <si>
     <t>Yeni yatırımı yapılan System ve Sacmi kalite kontrol cihazlarının entegrasyonu başlatılacak. Gerekli kontrollerin tamamlanmasından sonra; Toplanan tüm makine verileri ile tekil karo bazında ileri analitik çalışmaları başlatılacak.​
 Yapay zekâ algoritmaları ile minimum fire ve maksimum verim sağlanacak.​
 Üretim hattı yöneticileri, dijital panellerden anlık KPI’ları görecek (verimlilik, kalite, fire oranı, OEE vb.).​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperA MES Yapısının Kurulması </t>
   </si>
   <si>
     <t>KSFX Yapısının Kurulması</t>
@@ -1842,7 +1872,8 @@
     <t>Faz-1 tamamlanmıştır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Faz-1 ile elde edilen sonuç, günlük halı besleme verimi olarak 24 saatte bir paylaşılacaktır. 
+    <t xml:space="preserve">Holding IT birimleri tarafından yönetilen entegrasyon çalışmaları beklenmektedir ( Gecikme 3 hafta).
+Faz-1 ile elde edilen sonuç, günlük halı besleme verimi olarak 24 saatte bir paylaşılacaktır. (Entegrasyon sonrası yapılacaktır).
 Fırın halı besleme oranının canlı takibi ve verimlilik düşüşü (fırın devrinde ürün ağacından sapma, aralıklı besleme, vb) durumlarında erken uyarı sistemi kurulacaktır.
 </t>
   </si>
@@ -1856,14 +1887,15 @@
     <t>Canlı Rutubet Ölçümü ile Model kurularak Sprey kurutucu ısılarına müdahale eden robot geliştirilerek sprey çıkışı rutubetin sürekli stabil tutulması sağlanacaktır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rutubet cihazının kurulumu ve PC bağlantıları tamamlandı​
+    <t>Rutubet cihazının kurulumu ve PC bağlantıları tamamlandı​
 Üretilen farklı reçetelerdeki hammaddeler için cihaz kalibrasyonu ve ölçüm reçetesi oluşturulması tamamlandı​
 Veri doğrulama ve veri seti oluşturma tamamlandı.​
 MES sistemi ile sprey kurutucu makine parametreleri toplandı.​
 Sprey dryer ve rutubet ölçüm cihazı arasındaki gecikme farkı hesaplandı.​
 Sprey dryer da önemli parametrelerin belirlenmesi için analiz çalışması yapıldı.​
 Canlı rutubet takibi ile canlı makine verileri arasındaki korelasyon için veri analitiği çalışmaları yapılarak model oluşturulmuştur. 
-Modelin doğruluğu sahada test edilecektir.​ Kurutma makine parametreleri ile rutubet ölçümü arasındaki gecikme zaman farkı hesaplanarak veri eşleşmesi yapılacaktır. </t>
+Modelin doğruluğu sahada test edilecektir.​ Kurutma makine parametreleri ile rutubet ölçümü arasındaki gecikme zaman farkı hesaplanarak veri eşleşmesi yapılacaktır. 
+Sensörlerde actual yerine set değerler alındığı için anlamlı bir sonuç çıkarılamayacak olup proje iptal edilmiştir.</t>
   </si>
   <si>
     <t>Masse ve Sır Stok Hareket İşlemleri</t>
@@ -1875,15 +1907,18 @@
     <t>Mevcutta yapılan parti bazlı ürün ve ürün ağacı takibinin tekil karo bazlı yapılması hedeflenmektedir.</t>
   </si>
   <si>
-    <t>MES sistemi ile tekil karo bazlı takip yapılabilmektedir. ​
+    <t xml:space="preserve">MES sistemi ile tekil karo bazlı takip yapılabilmektedir. ​
 Granit fabrikası ve granit masse üretimi arasında pilot çalışma planlanmıştır.​
 Tüketim datalarının SAP üzerinden anlık çıkışı için algoritma düzenlenmiştir. ​
-Dijital tartım ünitelerine takılan IOT cihazları SCADA akışını bozduğundan dolayı yeni çalışma yapılması planlanmıştır.​</t>
-  </si>
-  <si>
-    <t>Her bir karonun tüm yaşam döngüsü bilindiğinden canlı makine verileri ile ürün ağacı kıyaslaması yapılacaktır.​
+İş emrinin ürün ağacına göre çıkarılan fiili standart maaliyet oranı her bir karo çözünürlüğünde bakılarak trend analizi yapılmıştır.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Her bir karonun tüm yaşam döngüsü bilindiğinden canlı makine verileri ile ürün ağacı kıyaslaması yapılacaktır.​
 Karo üretiminde kullanılan masse, sır, doğalgaz, elektrik, işçilik vb. veriler canlı ve otomatik sarf edilecektir.​
-İş emrinin ürün ağacına göre çıkarılan fiili standart maaliyet oranı her bir karo çözünürlüğünde bakılarak trend analizi yapılacaktır. ​</t>
+Dijital tartım ünitelerine takılan IOT cihazları SCADA akışını bozduğundan dolayı yeni çalışma yapılması planlanmıştır.​
+Canlı stok hareketlerinin izlenebilmesi  ve sürecin uçtan uca takibi için Ardıç tarafından yeni bir yazılım yapılacak ve Kale99 MES'e entegre edilecektir.
+</t>
   </si>
   <si>
     <t>Reçete Optimizasyonu</t>
@@ -1900,7 +1935,8 @@
   <si>
     <t>Gerekli olan tüm veriler MES sistemi içinde toplanmaya başlamıştır.​
 Modeli oluşturacak uygun veri seti büyüklüğü için tespit çalışmaları devam etmektedir.​
-Proje için üç konsorsiyum ile Horizon ön başvurusu yapılmış, sonuçları beklenmektedir.​</t>
+Proje için üç konsorsiyum ile Horizon ön başvurusu yapılmış, sonuçları beklenmektedir.​
+Aynı bilgiler kullanılarak demo çalışması için Argelog.AI ile anlaşma yapılmıştır, sonuçları beklenmektedir.</t>
   </si>
   <si>
     <t>Nihai ürün kalite kontrol verileri ile tüm girdilerin korelasyonu sağlanacak​tır.
@@ -1924,7 +1960,8 @@
   <si>
     <t>​Başvuru tamamlanmıştır. ​
 Başvurumuz onaylanmıştır.​
-Proje Kick-Off'u yapılmış, çalışmalar Medipol Üniversitesi ile işbirliği halinde yürütülmektedir.</t>
+Proje Kick-Off'u yapılmış, çalışmalar Medipol Üniversitesi ile işbirliği halinde yürütülmektedir.
+2. Dönem sonu hakem görüşmesi tamamlanmış olup proje akışı plana göre devam etmektedir(Ekim sonu itibariyle ilk versiyonu kullanıma açılacaktır).</t>
   </si>
   <si>
     <t>IoT sensörleri, SCADA/MES entegrasyonu ile anlık veri akışının sağlanması.​
@@ -1961,6 +1998,7 @@
   </si>
   <si>
     <t xml:space="preserve">Nihai sonucun dashboardları revize edilecektir. 
+Faz-1 proje sonuçları her gün ilgili kişilere paylaşılacaktır. İlgili çalışmalar Holding IT birimleri tarafından yapılacak ve teslim edilecektir.
 </t>
   </si>
   <si>
@@ -2007,11 +2045,11 @@
 Kullanılan reçeteler ile hangi hammaddeden ne oranda kullanıldığı mevcuttur.​
 Değirmenin dönme süresi bilinmektedir.​
 Değirmene ek müdahale verileri alınmıştır.​
-Laboratuvar ölçümleri ile ek tur öncesi ve sonrası kabakum miktarı bilinmektedir.​</t>
-  </si>
-  <si>
-    <t>Fabrikalar içerisinde çalışan tüm makinaların yaptıkları her öğütme döngüsü sonrası birbirleri ile kıyaslamalı data seti oluşturulacaktır.​
-Farklı değirmenlere giren farklı reçetelerin çıktıları toplanarak dinamik work index çıkarılabilmekte ve kıyaslamalı olarak değirmen verimine ulaşılacaktır.​
+Laboratuvar ölçümleri ile ek tur öncesi ve sonrası kabakum miktarı bilinmektedir.​
+Fabrikalar içerisinde çalışan tüm makinaların yaptıkları her öğütme döngüsü sonrası birbirleri ile kıyaslamalı data seti oluşturuldu.</t>
+  </si>
+  <si>
+    <t>Farklı değirmenlere giren farklı reçetelerin çıktıları toplanarak dinamik work index çıkarılabilmekte ve kıyaslamalı olarak değirmen verimine ulaşılacaktır.​
 Sürekli izlenen verimde azalma tespit edildiğinde alarm oluşturulabilecektir.​
 Envanter takip ekranları ile değirmenlere yapılan bilya beslemeleri kaydedilecektir.​</t>
   </si>
@@ -2023,8 +2061,19 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Fırının her bir modülü için set ve actual hız değerleri alınacak.
-Bu verilerin trend analizleri izlenerek makine öğrenmesi yapılacaktır.
+    <t xml:space="preserve">Veri ön işleme tamamlanmıştır.
+Sensör sapmaları tespit edilmiş ve normal çalışma bantlarının alt ve üst sınırları  tespit edilmiştir.
+Duruşlar ve bant çalışma hızları tek tablo üzerinde birleştirilmiştir.
+Rolelerin çalışma zamanları birbirleriyle hizalandırılmış ve normal çalışma rejminin dışında kalan alanlar tespit edilmiştir. 
+Bantların çalışma hızları zaman dilimlerine bölünüp detaylandırılarak sebep analizine hazır hale getirilmiştir.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bantların çalışma rejimlerindeki anomaliler izlenecek ve tespiti yapılacaktır.
+Bu anomaliler olması en olası sebepler ile ilişkilendirilecek ve korelasyon çalışması yapılacaktır.
+Sebepler belirlendikten sonra röleler için verilebilecek ön alarm durumları tespit edilecektir.
+Rölelerin bakımına sebebiyet veren durumlar analiz edilecek ve alarm sistemi ile önüne geçilmeye çalışılacaktır.
+Bantların trend analizleri izlenerek makine öğrenmesi yapılacaktır.
 </t>
   </si>
   <si>
@@ -2060,9 +2109,14 @@
     <t>Dijital Dönüşüm Merkezi ünvanı alındıktan sonra ilgili projelerin yürütülmesi konusundaki proje yönetimi faaliyetlerini kapsamaktadır.</t>
   </si>
   <si>
-    <t>3 yıllık yatırım projeksiyonu DDM üzerinden yönetilecek.​
+    <t>Haziranın ilk haftası için toplantı planlanmıştır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haziranın dördüncü haftası itibari ile proje planı STB platformuna yüklenecektir.
+3 yıllık yatırım projeksiyonu DDM üzerinden yönetilecek.​
 Merkez bünyesinde gösterilecek çalışanlar için bildiirm yapılacaktır.​
-2026 yılı sonu dijital olgunluk değerlendirilmesi tekrarlanacaktır.​</t>
+2026 yılı sonu dijital olgunluk değerlendirilmesi tekrarlanacaktır.​
+</t>
   </si>
   <si>
     <t>İş Zekası ve Görünürlük</t>
@@ -2086,14 +2140,15 @@
 Fabrika grafik tasarımının Part-1 tamamlanmıştır. (Blender 3D)​
 Mic. Azure üzerinde makinelerin parametreleri ile beraber iş akış modelinin sinir ağları oluşturulmuştur.​
 Sahadan alınan sensör dataları ile varlık dataları uyumlu hale getirilmiştir.​
+Sahadan alınan sensör dataları ile varlık dataları uyumlu hale getirilmiştir.
 Microsoft Azure ile lokal kod uygulamaları arasında bağlantı kurulmuştur ve sağlıklı kod çıktısı gözlenmiştir. </t>
   </si>
   <si>
-    <t>Soğuk veri akışı simüle edilecektir.​
-Canlı veriye geçiş çalışmaları başlatılacaktır (HOLDING IT)​
+    <t xml:space="preserve">Soğuk veri akışı simüle edilecektir.​
+Canlı veriye geçiş çalışmaları başlatılacaktır (HOLDING IT kararına göre veri kaynağı için kullanılacak yöntem belirlenecektir.)​
 Fabrika hatlarındaki değişikliklerin tahminleneceği mantık katmanı eklenecektir.​
 Olası arızaları önceden tahmin edilecek ve bakım planları otomatik olarak optimize edilecektir.​
-Sahadan alınan sensör dataları ile varlık dataları uyumlu hale getirilecektir.​</t>
+</t>
   </si>
   <si>
     <t>PowerBI Dashboard</t>
@@ -2141,9 +2196,9 @@
 Uygulama kullanılabilir hale getirilmiştir. </t>
   </si>
   <si>
-    <t>KN raporu oluşturulacaktır.
-Satın alma raporu oluşturulacaktır.
-Sipariş yönetimi raporu oluşturulacaktır.</t>
+    <t>KN raporu oluşturulacaktır. (KN yönetim ekibinden bilgi beklenmektedir.)
+Satın alma raporu oluşturulacaktır. (Satın alma birimlerinden bilgi beklenmektedir.)
+Sipariş yönetimi raporu oluşturulacaktır. (Sipariş yönetimi birimlerinden bilgi beklenmektedir.)</t>
   </si>
   <si>
     <t>AI Uygulamaları</t>
@@ -2196,7 +2251,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2282,7 +2337,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2331,6 +2386,9 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2677,26 +2735,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
   <dimension ref="A1:M101"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="2.83984375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="12.26171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.26171875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="15.41796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.26171875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.15625" style="13" customWidth="1"/>
-    <col min="9" max="9" width="11.26171875" style="13" customWidth="1"/>
-    <col min="10" max="10" width="12.41796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="62.41796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="90.41796875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="51.83984375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="8.83984375" style="11" customWidth="1"/>
-    <col min="15" max="16384" width="8.83984375" style="11"/>
+    <col min="8" max="8" width="11.140625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" style="13" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="62.42578125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="89.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="63.28515625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="11" customWidth="1"/>
+    <col min="15" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="9" customFormat="1" ht="45.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" s="9" customFormat="1" ht="45.95" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2737,7 +2795,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:13" ht="217.15" customHeight="1">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -2776,7 +2834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:13" ht="87">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -2815,7 +2873,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:13" ht="123" customHeight="1">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -2854,7 +2912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:13" ht="43.5">
       <c r="A5" s="10">
         <v>1</v>
       </c>
@@ -2889,11 +2947,11 @@
         <v>32</v>
       </c>
       <c r="L5" s="4"/>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:13" ht="87">
       <c r="A6" s="10">
         <v>1</v>
       </c>
@@ -2923,7 +2981,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:13" ht="43.5">
       <c r="A7" s="10">
         <v>1</v>
       </c>
@@ -2953,7 +3011,7 @@
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:13" ht="43.5">
       <c r="A8" s="10">
         <v>1</v>
       </c>
@@ -2983,7 +3041,7 @@
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:13" ht="43.5">
       <c r="A9" s="10">
         <v>1</v>
       </c>
@@ -3013,7 +3071,7 @@
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:13" ht="43.5">
       <c r="A10" s="10">
         <v>1</v>
       </c>
@@ -3045,7 +3103,7 @@
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:13" ht="43.5">
       <c r="A11" s="10">
         <v>1</v>
       </c>
@@ -3077,7 +3135,7 @@
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:13" ht="101.45">
       <c r="A12" s="10">
         <v>1</v>
       </c>
@@ -3116,7 +3174,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:13" ht="116.1">
       <c r="A13" s="10">
         <v>1</v>
       </c>
@@ -3153,7 +3211,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:13" ht="76.150000000000006" customHeight="1">
       <c r="A14" s="10">
         <v>1</v>
       </c>
@@ -3174,10 +3232,10 @@
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="12">
-        <v>46054</v>
+        <v>46174</v>
       </c>
       <c r="I14" s="12">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>17</v>
@@ -3192,7 +3250,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:13" ht="87">
       <c r="A15" s="10">
         <v>1</v>
       </c>
@@ -3224,7 +3282,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:13" ht="57.95">
       <c r="A16" s="10">
         <v>1</v>
       </c>
@@ -3256,7 +3314,7 @@
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:13" ht="130.5">
       <c r="A17" s="10">
         <v>1</v>
       </c>
@@ -3293,7 +3351,7 @@
       </c>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:13" ht="116.1">
       <c r="A18" s="10">
         <v>1</v>
       </c>
@@ -3332,7 +3390,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:13" ht="72.599999999999994">
       <c r="A19" s="10">
         <v>1</v>
       </c>
@@ -3371,7 +3429,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:13" ht="160.15" customHeight="1">
       <c r="A20" s="10">
         <v>1</v>
       </c>
@@ -3412,7 +3470,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:13" ht="72.599999999999994">
       <c r="A21" s="10">
         <v>1</v>
       </c>
@@ -3448,7 +3506,7 @@
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:13" ht="43.5">
       <c r="A22" s="10">
         <v>1</v>
       </c>
@@ -3482,7 +3540,7 @@
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:13" ht="101.45">
       <c r="A23" s="10">
         <v>1</v>
       </c>
@@ -3518,7 +3576,7 @@
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:13" ht="116.1">
       <c r="A24" s="10">
         <v>1</v>
       </c>
@@ -3557,7 +3615,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:13" ht="43.5">
       <c r="A25" s="10">
         <v>1</v>
       </c>
@@ -3594,7 +3652,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:13" ht="43.5">
       <c r="A26" s="10">
         <v>1</v>
       </c>
@@ -3631,7 +3689,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:13" ht="144.94999999999999">
       <c r="A27" s="10">
         <v>2</v>
       </c>
@@ -3667,7 +3725,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:13" ht="116.1">
       <c r="A28" s="10">
         <v>2</v>
       </c>
@@ -3704,7 +3762,7 @@
       </c>
       <c r="M28" s="1"/>
     </row>
-    <row r="29" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:13" ht="43.5">
       <c r="A29" s="10">
         <v>2</v>
       </c>
@@ -3736,7 +3794,7 @@
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:13" ht="43.5">
       <c r="A30" s="10">
         <v>2</v>
       </c>
@@ -3768,7 +3826,7 @@
       </c>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:13" ht="125.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:13" ht="125.1" customHeight="1">
       <c r="A31" s="10">
         <v>2</v>
       </c>
@@ -3806,7 +3864,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:13" ht="101.45">
       <c r="A32" s="10">
         <v>2</v>
       </c>
@@ -3844,7 +3902,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="64.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:13" ht="64.5" customHeight="1">
       <c r="A33" s="10">
         <v>2</v>
       </c>
@@ -3876,7 +3934,7 @@
       </c>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" spans="1:13" ht="186" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:13" ht="186" customHeight="1">
       <c r="A34" s="10">
         <v>2</v>
       </c>
@@ -3914,7 +3972,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="132.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:13" ht="132.4" customHeight="1">
       <c r="A35" s="10">
         <v>2</v>
       </c>
@@ -3953,7 +4011,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="314.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:13" ht="314.25" customHeight="1">
       <c r="A36" s="10">
         <v>2</v>
       </c>
@@ -3992,7 +4050,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="187.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:13" ht="187.5" customHeight="1">
       <c r="A37" s="10">
         <v>2</v>
       </c>
@@ -4031,7 +4089,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="187.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:13" ht="187.5" customHeight="1">
       <c r="A38" s="10">
         <v>2</v>
       </c>
@@ -4070,7 +4128,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="187.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:13" ht="187.5" customHeight="1">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -4109,7 +4167,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="187.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:13" ht="187.5" customHeight="1">
       <c r="A40" s="10">
         <v>2</v>
       </c>
@@ -4135,7 +4193,9 @@
       <c r="I40" s="12">
         <v>46387</v>
       </c>
-      <c r="J40" s="3"/>
+      <c r="J40" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="K40" s="3" t="s">
         <v>168</v>
       </c>
@@ -4146,7 +4206,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:13" ht="275.45">
       <c r="A41" s="10">
         <v>3</v>
       </c>
@@ -4185,7 +4245,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:13" ht="144.94999999999999">
       <c r="A42" s="10">
         <v>3</v>
       </c>
@@ -4224,7 +4284,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:13" ht="57.95">
       <c r="A43" s="10">
         <v>3</v>
       </c>
@@ -4248,7 +4308,7 @@
         <v>46113</v>
       </c>
       <c r="I43" s="12">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>17</v>
@@ -4256,14 +4316,14 @@
       <c r="K43" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="L43" s="4" t="s">
+      <c r="L43" s="1" t="s">
         <v>186</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:13" ht="116.1">
       <c r="A44" s="10">
         <v>3</v>
       </c>
@@ -4300,7 +4360,7 @@
       </c>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:13" ht="409.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:13" ht="409.5">
       <c r="A45" s="10">
         <v>3</v>
       </c>
@@ -4326,7 +4386,7 @@
         <v>45778</v>
       </c>
       <c r="I45" s="12">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>17</v>
@@ -4341,7 +4401,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:13" ht="174">
       <c r="A46" s="10">
         <v>3</v>
       </c>
@@ -4365,7 +4425,7 @@
         <v>45992</v>
       </c>
       <c r="I46" s="12">
-        <v>46170</v>
+        <v>46203</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>17</v>
@@ -4380,7 +4440,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:13" ht="87">
       <c r="A47" s="10">
         <v>4</v>
       </c>
@@ -4419,7 +4479,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:13" ht="72.599999999999994">
       <c r="A48" s="10">
         <v>4</v>
       </c>
@@ -4458,7 +4518,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:13" ht="57.95">
       <c r="A49" s="10">
         <v>4</v>
       </c>
@@ -4497,7 +4557,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:13" ht="130.5">
       <c r="A50" s="10">
         <v>4</v>
       </c>
@@ -4536,7 +4596,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:13" ht="57.95">
       <c r="A51" s="10">
         <v>4</v>
       </c>
@@ -4577,7 +4637,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:13" ht="87">
       <c r="A52" s="10">
         <v>4</v>
       </c>
@@ -4616,7 +4676,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:13" ht="43.5">
       <c r="A53" s="10">
         <v>4</v>
       </c>
@@ -4655,7 +4715,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:13" ht="72.599999999999994">
       <c r="A54" s="10">
         <v>4</v>
       </c>
@@ -4691,7 +4751,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:13" ht="101.45">
       <c r="A55" s="10">
         <v>4</v>
       </c>
@@ -4730,7 +4790,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:13" ht="87">
       <c r="A56" s="10">
         <v>4</v>
       </c>
@@ -4769,7 +4829,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:13" ht="101.45">
       <c r="A57" s="10">
         <v>4</v>
       </c>
@@ -4808,7 +4868,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:13" ht="101.45">
       <c r="A58" s="10">
         <v>4</v>
       </c>
@@ -4847,7 +4907,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:13" ht="87">
       <c r="A59" s="10">
         <v>4</v>
       </c>
@@ -4886,7 +4946,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="94.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:13" ht="94.5" customHeight="1">
       <c r="A60" s="10">
         <v>5</v>
       </c>
@@ -4927,7 +4987,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:13" ht="87">
       <c r="A61" s="10">
         <v>5</v>
       </c>
@@ -4968,7 +5028,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:13" ht="159.6">
       <c r="A62" s="10">
         <v>5</v>
       </c>
@@ -5009,7 +5069,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:13" ht="72.599999999999994">
       <c r="A63" s="10">
         <v>5</v>
       </c>
@@ -5050,7 +5110,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:13" ht="116.1">
       <c r="A64" s="10">
         <v>5</v>
       </c>
@@ -5089,7 +5149,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:13" ht="159.6">
       <c r="A65" s="10">
         <v>5</v>
       </c>
@@ -5123,7 +5183,7 @@
       </c>
       <c r="L65" s="4"/>
     </row>
-    <row r="66" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:13" ht="101.45">
       <c r="A66" s="10">
         <v>5</v>
       </c>
@@ -5162,7 +5222,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:13" ht="43.5">
       <c r="A67" s="10">
         <v>5</v>
       </c>
@@ -5201,7 +5261,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:13" ht="57.95">
       <c r="A68" s="10">
         <v>5</v>
       </c>
@@ -5240,7 +5300,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:13" ht="57.95">
       <c r="A69" s="10">
         <v>5</v>
       </c>
@@ -5279,7 +5339,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:13" ht="57.95">
       <c r="A70" s="10">
         <v>5</v>
       </c>
@@ -5318,7 +5378,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:13" ht="43.5">
       <c r="A71" s="10">
         <v>5</v>
       </c>
@@ -5354,7 +5414,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:13" ht="72.599999999999994">
       <c r="A72" s="10">
         <v>6</v>
       </c>
@@ -5390,7 +5450,7 @@
       </c>
       <c r="M72" s="1"/>
     </row>
-    <row r="73" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:13" ht="72.599999999999994">
       <c r="A73" s="10">
         <v>6</v>
       </c>
@@ -5431,7 +5491,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:13" ht="72.599999999999994">
       <c r="A74" s="10">
         <v>6</v>
       </c>
@@ -5472,7 +5532,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:13" ht="116.1">
       <c r="A75" s="10">
         <v>6</v>
       </c>
@@ -5513,7 +5573,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:13" ht="72.599999999999994">
       <c r="A76" s="10">
         <v>6</v>
       </c>
@@ -5550,9 +5610,11 @@
       <c r="L76" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="M76" s="1"/>
-    </row>
-    <row r="77" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="M76" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="116.1">
       <c r="A77" s="10">
         <v>6</v>
       </c>
@@ -5569,7 +5631,7 @@
         <v>321</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>323</v>
@@ -5587,13 +5649,13 @@
         <v>324</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="101.45">
       <c r="A78" s="10">
         <v>6</v>
       </c>
@@ -5610,7 +5672,7 @@
         <v>321</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>323</v>
@@ -5628,13 +5690,13 @@
         <v>324</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="29.1">
       <c r="A79" s="10">
         <v>6</v>
       </c>
@@ -5651,10 +5713,10 @@
         <v>321</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H79" s="12"/>
       <c r="I79" s="12"/>
@@ -5664,7 +5726,7 @@
       <c r="K79" s="5"/>
       <c r="L79" s="4"/>
     </row>
-    <row r="80" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:13" ht="29.1">
       <c r="A80" s="10">
         <v>6</v>
       </c>
@@ -5678,13 +5740,13 @@
         <v>320</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F80" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G80" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
@@ -5694,7 +5756,7 @@
       <c r="K80" s="5"/>
       <c r="L80" s="4"/>
     </row>
-    <row r="81" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:13" ht="29.1">
       <c r="A81" s="10">
         <v>6</v>
       </c>
@@ -5708,13 +5770,13 @@
         <v>320</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H81" s="12"/>
       <c r="I81" s="12"/>
@@ -5724,7 +5786,7 @@
       <c r="K81" s="5"/>
       <c r="L81" s="4"/>
     </row>
-    <row r="82" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:13" ht="144.94999999999999">
       <c r="A82" s="10">
         <v>6</v>
       </c>
@@ -5735,16 +5797,16 @@
         <v>2</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H82" s="12">
         <v>46023</v>
@@ -5756,16 +5818,16 @@
         <v>57</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="116.1">
       <c r="A83" s="10">
         <v>6</v>
       </c>
@@ -5776,16 +5838,16 @@
         <v>2</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H83" s="12">
         <v>46204</v>
@@ -5797,16 +5859,16 @@
         <v>332</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="188.45">
       <c r="A84" s="10">
         <v>6</v>
       </c>
@@ -5817,16 +5879,16 @@
         <v>2</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H84" s="12">
         <v>46023</v>
@@ -5838,14 +5900,14 @@
         <v>70</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M84" s="2"/>
     </row>
-    <row r="85" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:13" ht="130.5">
       <c r="A85" s="10">
         <v>6</v>
       </c>
@@ -5856,16 +5918,16 @@
         <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H85" s="12">
         <v>45992</v>
@@ -5877,16 +5939,16 @@
         <v>332</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="72.599999999999994">
       <c r="A86" s="10">
         <v>6</v>
       </c>
@@ -5897,16 +5959,16 @@
         <v>2</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H86" s="12">
         <v>46023</v>
@@ -5918,16 +5980,16 @@
         <v>332</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="174">
       <c r="A87" s="10">
         <v>6</v>
       </c>
@@ -5938,16 +6000,16 @@
         <v>2</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H87" s="12">
         <v>46023</v>
@@ -5959,16 +6021,16 @@
         <v>332</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="101.45">
       <c r="A88" s="10">
         <v>6</v>
       </c>
@@ -5979,16 +6041,16 @@
         <v>2</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H88" s="12">
         <v>45931</v>
@@ -6000,14 +6062,14 @@
         <v>57</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:13" ht="87">
       <c r="A89" s="10">
         <v>6</v>
       </c>
@@ -6018,16 +6080,16 @@
         <v>2</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H89" s="12">
         <v>45931</v>
@@ -6039,16 +6101,16 @@
         <v>332</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="130.5">
       <c r="A90" s="10">
         <v>6</v>
       </c>
@@ -6059,16 +6121,16 @@
         <v>2</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H90" s="12">
         <v>46023</v>
@@ -6080,16 +6142,16 @@
         <v>332</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="57.95">
       <c r="A91" s="10">
         <v>6</v>
       </c>
@@ -6100,16 +6162,16 @@
         <v>2</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H91" s="12">
         <v>46174</v>
@@ -6118,19 +6180,19 @@
         <v>46295</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="101.45">
       <c r="A92" s="10">
         <v>6</v>
       </c>
@@ -6141,16 +6203,16 @@
         <v>2</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H92" s="12">
         <v>46023</v>
@@ -6162,16 +6224,16 @@
         <v>332</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="144.94999999999999">
       <c r="A93" s="10">
         <v>6</v>
       </c>
@@ -6182,16 +6244,16 @@
         <v>2</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H93" s="12">
         <v>46174</v>
@@ -6200,17 +6262,19 @@
         <v>46264</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="L93" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>404</v>
+      </c>
       <c r="M93" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="101.45">
       <c r="A94" s="10">
         <v>6</v>
       </c>
@@ -6221,13 +6285,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G94" s="3"/>
       <c r="H94" s="12">
@@ -6240,16 +6304,16 @@
         <v>332</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="87">
       <c r="A95" s="10">
         <v>6</v>
       </c>
@@ -6260,13 +6324,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G95" s="3"/>
       <c r="H95" s="12">
@@ -6276,17 +6340,19 @@
         <v>46387</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="L95" s="4"/>
+        <v>413</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>414</v>
+      </c>
       <c r="M95" s="2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="116.1">
       <c r="A96" s="10">
         <v>6</v>
       </c>
@@ -6297,16 +6363,16 @@
         <v>4</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="H96" s="12">
         <v>46023</v>
@@ -6318,16 +6384,16 @@
         <v>332</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="57.95">
       <c r="A97" s="10">
         <v>6</v>
       </c>
@@ -6338,13 +6404,13 @@
         <v>4</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="12">
@@ -6357,14 +6423,14 @@
         <v>57</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M97" s="2"/>
     </row>
-    <row r="98" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:13" ht="72.599999999999994">
       <c r="A98" s="10">
         <v>6</v>
       </c>
@@ -6375,13 +6441,13 @@
         <v>4</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="12">
@@ -6394,14 +6460,14 @@
         <v>57</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M98" s="2"/>
     </row>
-    <row r="99" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:13" ht="159.6">
       <c r="A99" s="10">
         <v>6</v>
       </c>
@@ -6412,13 +6478,13 @@
         <v>4</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="12">
@@ -6431,16 +6497,16 @@
         <v>332</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="324.60000000000002" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="324.60000000000002" customHeight="1">
       <c r="A100" s="10">
         <v>6</v>
       </c>
@@ -6451,13 +6517,13 @@
         <v>5</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="12">
@@ -6470,14 +6536,14 @@
         <v>31</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="159.6">
       <c r="A101" s="10">
         <v>6</v>
       </c>
@@ -6488,13 +6554,13 @@
         <v>5</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="12">
@@ -6507,14 +6573,15 @@
         <v>31</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M101" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M101">
     <sortCondition ref="A9:A101"/>
     <sortCondition ref="C9:C101"/>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/TZY Gelişim Planı/Gelişim Planı/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="918" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78521750-1F31-4D9D-92B9-5B4B924D2C19}"/>
+  <xr:revisionPtr revIDLastSave="947" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6A5F3BB-9B0E-4E7D-834F-2F73CA41D0C2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="560" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects Data'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects Data'!$A$1:$M$109</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -743,25 +743,28 @@
   </si>
   <si>
     <t xml:space="preserve">MRP üzerinden oluşan ihtiyaç sinyalleri düzenli olarak analiz edilerek satınalma ve tedarik planlama süreçlerinde aktif olarak kullanılmaktadır.
-Sistem tarafından oluşan SAT kayıtları; stok yapısı, tüketim hareketleri, açık siparişler ve üretim planı ile birlikte değerlendirilerek aksiyona dönüştürülmektedir.
-KPI’lar (stok devir hızı, stok doğruluk oranı, müşteri teslim performansı vb.) üzerinden ölçülebilir iyileştirmeler sağlanmıştır.
-KS01 &amp; KS02 malzeme türlerine ait SKU’ların %30’u için emniyet stok seviyeleri tanımlanmıştır. Kapsamın genişletilmesine yönelik çalışmalar devam etmektedir.
-MİP sürecinin sağlıklı çalışmasını desteklemek amacıyla geçmiş tarihli açık rezervasyonlar kapatılmış, süreç düzenli olarak izlenmektedir.
-Açık SAS ve SAT’lar haftalık raporlanmakta, geçmiş kayıtlar için aksiyon alınmaktadır.
-Malzeme ve aramamül kodları için ABC &amp; XYZ sınıflandırmaları aylık olarak güncellenmektedir.
-Emniyet stokları; tüketim frekansı ve min–max değerlere göre dinamik olarak hesaplanmaktadır.
+Sistem tarafından oluşan SAT kayıtları; mevcut stok, tüketim hareketleri, açık siparişler ve üretim planı birlikte değerlendirilerek aksiyona dönüştürülmektedir.
+Açık SAS ve SAT kayıtları haftalık olarak raporlanmakta, geçmiş tarihli kayıtlar için gerekli aksiyonlar alınmaktadır.
+MİP sürecinin sağlıklı çalışmasını desteklemek amacıyla geçmiş tarihli açık rezervasyonlar kapatılmış ve düzenli kontrol yapısı oluşturulmuştur.
+Malzeme ve aramamül kodları için ABC &amp; XYZ sınıflandırmaları oluşturulmuş ve aylık güncelleme süreci devreye alınmıştır.
+KS01 &amp; KS02 kapsamındaki SKU’ların yaklaşık %30’u için emniyet stok seviyeleri tanımlanmıştır.
+Emniyet stoğu çalışmalarında tüketim frekansı ile min–max değerlerin dikkate alındığı dinamik hesaplama yaklaşımı oluşturulmuştur.
 180+ stok yaşına sahip malzemeler için kırılım analizleri hazırlanmış ve düzenli takip yapısı oluşturulmuştur.
-MRP doğruluğunu ve planlama etkinliğini artırmak amacıyla; Genel İşletme Malz.Grubunda Bilgisayar &amp; Ofis, Gıda ve Temizlik malzemeleri, Üretim Malz.Grubunda Boyalar, Teknik İşletme grubunda ise Metal Sarf malzemeleri özelinde iyileştirme çalışmaları planlanmıştır.
-Belirlenen malzeme gruplarında tüketim yapısı, stok hareketleri ve ihtiyaç oluşum süreçleri analiz edilerek MRP etkinliğinin artırılması hedeflenmektedir.
-İlgili malzeme gruplarında ihtiyaç planlama yapısının geliştirilmesi ve sistemsel sinyal kalitesinin artırılmasına yönelik çalışmalar sistematik olarak gerçekleştirilmektedir.
-Stok tutarı ile tüketim ilişkisi değerlendirilerek yeterlilik seviyelerinin daha etkin yönetilmesine yönelik çalışmalar planlanmıştır.
-Dinamik tüketim verilerine göre çalışan emniyet stoğu ve min–max yönetim yapısının oluşturulması hedeflenmiştir.
+Stok tutarı ile tüketim ilişkisini izlemeye yönelik analizler yapılarak stok yeterlilik seviyelerinin görünürlüğü artırılmıştır.
+MRP etkinliğini artırmak amacıyla öncelikli malzeme grupları belirlenmiş; Bilgisayar &amp; Ofis, Gıda, Temizlik, Boyalar ve Metal Sarf malzemelerinde tüketim, stok hareketleri ve ihtiyaç oluşum süreçleri analiz edilmeye başlanmıştır.
+MİP sürecinin performansı; stok devir hızı, stok doğruluğu, stok yaşlandırma ve teslimat performansı gibi KPI’lar üzerinden takip edilmektedir.
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Ürün ağaçlarının haftalık olarak mail atılmasına yönelik aksiyon planlanmıştır.(SAP-Mail)
-Satınalma, Üretim Planlama ve Depo süreçleri arasındaki bilgi akışının daha hızlı ve sürdürülebilir hale getirilmesi hedeflenmiştir.
-</t>
+    <t>KS01 &amp; KS02 kapsamında emniyet stoğu tanımlanan SKU oranının artırılması ve uygulamanın daha geniş malzeme gruplarına yaygınlaştırılması.
+Dinamik emniyet stoğu ve min–max yönetim yapısının standartlaştırılarak sistemsel hale getirilmesi.
+Belirlenen öncelikli malzeme gruplarında yapılan analizler doğrultusunda MRP parametrelerinin ve ihtiyaç oluşturma yapısının iyileştirilmesi.
+MRP sinyal kalitesini artırmak amacıyla tüketim frekansı, geçmiş tüketim, stok seviyesi ve ihtiyaç yapısının daha etkin şekilde sisteme dahil edilmesi.
+Stok tutarı ile tüketim ilişkisine göre optimum stok / yeterlilik seviyelerinin malzeme grubu bazında belirlenmesi.
+Ürün ağaçlarının haftalık olarak otomatik mail ile paylaşılmasına yönelik SAP-Mail yapısının devreye alınması.
+Satınalma, Üretim Planlama ve Depo süreçleri arasındaki bilgi akışının hızlandırılması ve sürdürülebilir bir takip mekanizmasının oluşturulması.
+MRP, stok, açık sipariş ve üretim planı bilgilerinin mümkün olduğunca tek bir izleme ve karar destek yapısında birleştirilmesi.
+MRP iyileştirmelerinin etkisinin; stok seviyesi, stok devir hızı, 180+ stok, açık SAT/SAS ve hizmet seviyesi KPI’ları üzerinden düzenli olarak ölçülmesi.</t>
   </si>
   <si>
     <t>SAP QM Kapsamında SKT Uyarı ve FIFO Kontrol Projesi</t>
@@ -858,26 +861,27 @@
 Proje kapsamında; malzemelerin görsel kimliklendirilmesi, merkezi bir veri yapısında yönetilmesi ve ilgili sistemlerle entegre edilmesi sağlanarak, stok doğruluğu artırılacak, satın alma ve planlama süreçleri daha etkin hale getirilecek ve gereksiz stok oluşumu azaltılacaktır.</t>
   </si>
   <si>
-    <t>Görsel arşiv altyapısı oluşturulmuş ve merkezi veri yapısı kurulmuştur.
-İşletme malzemelerine ait ~2500 görsel dijital ortama aktarılmıştır. ( Stoklu  SKU lar için %62 tamamlanmıştır)
-Görseller, ilgili malzeme kodları ile eşleştirilerek standart bir isimlendirme yapısı oluşturulmuştur.
-Görsel çekim, arşivleme ve güncelleme süreçlerine yönelik standartlar belirlenmiştir.
-Görsel arama ve benzer ürün eşleştirme (SKUMATCH) uygulaması devreye alınmıştır.
-Referans görsel veri seti oluşturularak sistemin öğrenme altyapısı hazırlanmıştır.
-Uygulamanın kullanımına yönelik ilk bilgilendirme ve tanıtım çalışmaları gerçekleştirilmiştir.
-Yeni malzeme girişlerinde zorunlu görsel ekleme kuralının devreye alınması
-Benzer ve mükerrer malzeme kodlarının sistematik olarak tespit edilmesi ve aksiyon planlarının oluşturulması konusu devam etmektedir.</t>
-  </si>
-  <si>
-    <t>Görsel arşivin SAP malzeme kartları ile entegrasyonunun sağlanması
-SKUMATCH uygulamasının tüm ilgili ekiplerde aktif kullanımının yaygınlaştırılması
-Arama sonuçlarına stok miktarı ve lokasyon bilgilerinin eklenmesi
-Görsel arşivin haftalık / aylık periyotlarla düzenli güncellenmesi
-180+ stoklar için görsel eşleştirme destekli satış / iade / alternatif kullanım çalışmalarının başlatılması
-Mobil kullanım (telefon/tablet) altyapısının geliştirilmesi
-Kullanım performansı ve fayda analizine yönelik raporlama ve KPI yapısının oluşturulması
-Kullanıcı eğitimleri ve saha adaptasyon sürecinin tamamlanması
-Görsel kalite standardının artırılması (arka plan, açı, çözünürlük vb.)</t>
+    <t>Referans görsel veri tabanı oluşturuldu ve genişletildi. Başlangıçta yaklaşık 2.088 görsel ile oluşturulan havuz, yaklaşık 3.309 görsel seviyesine çıkarıldı.
+Yüklenen görsellerin mevcut malzeme referanslarıyla karşılaştırılarak en yakın sonuçların kullanıcıya sunulması sağlandı.
+Uygulama kurumsal erişime açıldı. SKU MATCH AI, PortaKale → Kaleseramik → Yapay Zeka Uygulamaları üzerinden kullanıcıların erişimine sunuldu.
+Kullanımı ve kullanıcı adaptasyonunu ölçmek amacıyla raporlama altyapısı oluşturuldu.
+Mükerrer ve atıl malzeme kodlarının tespitine yönelik çalışma gerçekleştirildi. Yaklaşık 600 mükerrer/atıl kod üzerinde temizlik ve değerlendirme çalışması yapıldı.
+180+ stokların azaltılmasına katkı sağlandı. Projenin ilk dört aylık döneminde ilgili SKU’larda yaklaşık %12 iyileşme elde edildi.
+Yaygınlaştırma çalışmaları kapsamında tanıtım videosu hazırlandı ve yemekhane ekranlarında yayınlanmaya başlandı.
+Projenin geliştirme yol haritası oluşturuldu. Raporlama, mobil kullanım, stok/ambar entegrasyonu ve yönetim fonksiyonlarını kapsayan sonraki fazlar tanımlandı.</t>
+  </si>
+  <si>
+    <t>Malzeme tanımlarının sisteme eklenmesi: Görsel eşleşme sonuçlarının malzeme adı ve açıklamasıyla desteklenmesi.
+Malzeme barkodlarının eklenmesi: Barkod üzerinden hızlı doğrulama ve malzeme erişiminin sağlanması.
+360° ürün/video görsellerinin kullanılması: Malzemenin farklı açılardan tanınabilirliğinin ve eşleşme doğruluğunun artırılması.
+Görsel veri tabanının genişletilmesi: Referans görsel sayısının artırılarak daha fazla malzemenin kapsama alınması.
+Mobil kullanımın geliştirilmesi: Depo ve saha çalışanlarının telefon/tablet üzerinden doğrudan fotoğraf ile arama yapabilmesi.
+Stok ve ambar bilgilerinin entegrasyonu: Eşleşen malzemenin mevcut stok miktarı ve depo/lokasyon bilgisinin gösterilmesi.
+Eşleşme doğruluğunun geliştirilmesi: Kullanıcı geri bildirimleri ve kullanım verileri üzerinden AI modelinin iyileştirilmesi.
+Kullanım raporlarının geliştirilmesi: Kullanıcı, arama, eşleşme ve kullanım sıklığı bazında KPI takibinin yapılması.
+Mükerrer kod kontrolünün sürece entegre edilmesi: Yeni kod açılışı öncesinde SKU MATCH AI üzerinden mevcut malzeme kontrolünün standart hale getirilmesi.
+Yönetim/Admin ekranının geliştirilmesi: Yeni görsel ekleme, eşleşme kontrolü ve benzerlik eşiği gibi parametrelerin yönetilebilmesi.
+Yaygınlaştırma çalışmalarının sürdürülmesi: Kullanıcı iletişimi, kısa eğitimler ve saha kullanımının artırılmasına yönelik çalışmaların devam ettirilmesi.</t>
   </si>
   <si>
     <t>Malzeme Kod Çeşitlerinin Azaltılması ve Atıl Kod Yönetimi</t>
@@ -901,7 +905,8 @@
   <si>
     <t>Görsel arşiv (SKUMATCH) ile malzeme ana veri süreci entegre edilerek doğru kod seçimi desteklenecektir
 Malzeme ana veri kalitesi belirli KPI’lar ile düzenli olarak izlenecek ve raporlanacaktır
-Kod talep süreçlerinin standart hale getirilmesi için prosedür/talimat dokümanının hazırlanarak devreye alınacaktır.</t>
+Kod talep süreçlerinin standart hale getirilmesi için prosedür/talimat dokümanının hazırlanarak devreye alınacaktır.
+Kod talep yönetiminin SAP tarafına alınması ile ilgili IT talep hızlandırılmaya çalışılacak.</t>
   </si>
   <si>
     <t>Lojistik</t>
@@ -3929,7 +3934,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="150">
+    <row r="27" spans="1:13" ht="150" hidden="1">
       <c r="A27" s="8">
         <v>2</v>
       </c>
@@ -3965,7 +3970,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="120">
+    <row r="28" spans="1:13" ht="120" hidden="1">
       <c r="A28" s="8">
         <v>2</v>
       </c>
@@ -4002,7 +4007,7 @@
       </c>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" spans="1:13" ht="60">
+    <row r="29" spans="1:13" ht="60" hidden="1">
       <c r="A29" s="8">
         <v>2</v>
       </c>
@@ -4034,7 +4039,7 @@
       </c>
       <c r="L29" s="13"/>
     </row>
-    <row r="30" spans="1:13" ht="60">
+    <row r="30" spans="1:13" ht="60" hidden="1">
       <c r="A30" s="8">
         <v>2</v>
       </c>
@@ -4066,7 +4071,7 @@
       </c>
       <c r="L30" s="13"/>
     </row>
-    <row r="31" spans="1:13" ht="390">
+    <row r="31" spans="1:13" ht="390" hidden="1">
       <c r="A31" s="8">
         <v>2</v>
       </c>
@@ -4104,7 +4109,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="144.75">
+    <row r="32" spans="1:13" ht="144.75" hidden="1">
       <c r="A32" s="8">
         <v>2</v>
       </c>
@@ -4131,7 +4136,7 @@
         <v>46356</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>134</v>
@@ -4143,7 +4148,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="87">
+    <row r="33" spans="1:13" ht="87" hidden="1">
       <c r="A33" s="8">
         <v>2</v>
       </c>
@@ -4180,7 +4185,7 @@
       </c>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:13" ht="159">
+    <row r="34" spans="1:13" ht="159" hidden="1">
       <c r="A34" s="8">
         <v>2</v>
       </c>
@@ -4441,7 +4446,7 @@
       </c>
       <c r="M40" s="11"/>
     </row>
-    <row r="41" spans="1:13" ht="405">
+    <row r="41" spans="1:13" ht="346.5">
       <c r="A41" s="8">
         <v>2</v>
       </c>
@@ -4519,7 +4524,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="217.5">
+    <row r="43" spans="1:13" ht="217.5" hidden="1">
       <c r="A43" s="8">
         <v>2</v>
       </c>
@@ -4597,7 +4602,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="174">
+    <row r="45" spans="1:13" ht="346.5">
       <c r="A45" s="8">
         <v>2</v>
       </c>
@@ -4675,7 +4680,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="300" hidden="1">
+    <row r="47" spans="1:13" ht="274.5" hidden="1">
       <c r="A47" s="8">
         <v>3</v>
       </c>
@@ -4714,7 +4719,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="165" hidden="1">
+    <row r="48" spans="1:13" ht="144.75" hidden="1">
       <c r="A48" s="8">
         <v>3</v>
       </c>
@@ -4753,7 +4758,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="75" hidden="1">
+    <row r="49" spans="1:13" ht="72.75" hidden="1">
       <c r="A49" s="8">
         <v>3</v>
       </c>
@@ -4792,7 +4797,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="120" hidden="1">
+    <row r="50" spans="1:13" ht="115.5" hidden="1">
       <c r="A50" s="8">
         <v>3</v>
       </c>
@@ -4829,7 +4834,7 @@
       </c>
       <c r="M50" s="11"/>
     </row>
-    <row r="51" spans="1:13" ht="409.5" hidden="1">
+    <row r="51" spans="1:13" ht="409.6" hidden="1">
       <c r="A51" s="8">
         <v>3</v>
       </c>
@@ -4870,7 +4875,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="180" hidden="1">
+    <row r="52" spans="1:13" ht="174" hidden="1">
       <c r="A52" s="8">
         <v>3</v>
       </c>
@@ -4909,7 +4914,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="86.45" hidden="1">
+    <row r="53" spans="1:13" ht="87" hidden="1">
       <c r="A53" s="8">
         <v>4</v>
       </c>
@@ -4987,7 +4992,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="72" hidden="1">
+    <row r="55" spans="1:13" ht="72.75" hidden="1">
       <c r="A55" s="8">
         <v>4</v>
       </c>
@@ -7124,10 +7129,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N109" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
+  <autoFilter ref="A1:M109" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
     <filterColumn colId="1">
       <filters>
         <filter val="Planlama"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Envanter Yönetimi"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/dataset/SCM Project Portal Data.xlsx
+++ b/dataset/SCM Project Portal Data.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kale365-my.sharepoint.com/personal/emretasci_kale_com_tr/Documents/TZY Gelişim Planı/Gelişim Planı/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emretasci\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="947" documentId="13_ncr:1_{9D892197-6089-456B-88D9-758A624E5DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6A5F3BB-9B0E-4E7D-834F-2F73CA41D0C2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE6B70A-9B11-42B3-94D7-910658530805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="560" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="18192" windowHeight="11472" tabRatio="560" xr2:uid="{ECFC6BE2-ED5C-4CA8-B0E4-B56B8A9FC05E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects Data" sheetId="31" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects Data'!$A$1:$M$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects Data'!$A$1:$M$111</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="475">
   <si>
     <t>department order</t>
   </si>
@@ -99,46 +99,10 @@
     <t>Ürün ana veri yapısının incelenerek geliştirme/iyileştirme alanları ile hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Talep tahmin veri analitiği, SKU rasyonalizasyonu,  görünürlük, planlama stratejileri gibi pek çok çalışma için ürün ana veri yapısının iyileştirilmesi ihtiyacı ön koşul olarak bulunmaktadır.</t>
   </si>
   <si>
-    <t>Ürün bilgilerinin ve karakteristik tanımlarının düzenli takibi ve kontrolü için power BI'da Ürün Dashboard çalışması tamamlanmıştır.
-Haftalık toplantılar ile ürün bilgilerindeki eksiklikler tespit edilmekte ve çalışmalar yapılmaktadır.
-Bölüm KPI'larına Ürün Ana Veri İyileştirme Endeksi eklenmiştir.
-Piyasa kanalı tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
-Kalite tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
-Planlama stratejileri tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
-DFU tanımları takip edilmekte ve eksiklikler giderilmektedir.
-Üretim kontrol notu takip edilmekte ve eksiklikler giderilmektedir.
-Ürün hiyerarşisi uyumsuzlukları tespit edilmekte ve düzeltilmektedir.
-Ürün hiyerarşisi tanımı yanlış olan kodlar tespit edilmekte ve düzeltilmektedir.
-Gömme rezervuar ürün grubunda set kodları ayrıştırılmıştır.
-Marka tanımları takip edilmekte ve eksiklikler giderilmektedir.
-Faturalama için ambalaj tipi tanımları takip edilmekte ve eksiklikler giderilmektedir.</t>
-  </si>
-  <si>
-    <t>Orijin kodu bilgisinin düzenlenmesine yönelik çalışmalar devam etmektedir.
-SKM CTDA eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
-SKM Ebat eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
-SKM Kısa Kod eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
-Vitrifiye Renk tanımı eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
-Mükerrer açılan kodların tespiti ve düzenlenmesine yönelik çalışmalar devam etmektedir.
-Farklı kalitedeki ürünlerin stok kodları arasında bağlantı oluşturulacaktır.</t>
-  </si>
-  <si>
     <t>Ürün Ambalaj Bilgilerinin Tanımlanması</t>
   </si>
   <si>
     <t>Ürün ana veri yapısında bulunan ambalaj bilgilerinin incelenerek hata ve/veya eksikliklerin tespit edilmesi ve bunların iyileştirilmesi, hataların giderilmesi faaliyetlerini içeren çalışmadır. Yükleme-rotalama optimizasyonu ve nakliye hesaplaması gibi pek çok çalışma için ürün ambalaj bilgilerinin tanımlanması ihtiyacı ön koşul olarak bulunmaktadır.</t>
-  </si>
-  <si>
-    <t>Vitrifiye ürün grubu için palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
-Vitrifiye ürün grubu için ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
-Mobilya ürün grubu için ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
-SKM ürün grubu için palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.</t>
-  </si>
-  <si>
-    <t>SKM ürün grubu için (numune kodlar) ürün ve palet kg bilgileri kontrol edilerek eksiklikler giderilecektir.
-Vitrifiye ürün grubu için ürün ve palet kg bilgileri kontrol edilerek eksiklikler giderilecektir.
-Vitrifiye ürün grubu için palet içi miktar bilgileri kontrol edilerek eksiklikler giderilecektir.
-Tedarik ürün grupları için palet içi miktar bilgileri kontrol edilerek eksiklikler giderilecektir.</t>
   </si>
   <si>
     <t>Ürünler Arası İlişki Tanımlarının Oluşturulması</t>
@@ -289,19 +253,6 @@
     <t xml:space="preserve">Tahmin yetkinliğinin arttırılmasına yönelik olarak tahmin veri setinin değiştirilerek müşteri siparişi, fiyat, dış veriler, bayi satış verileri gibi bilgilerin kullanılarak yeni tahmin modelinin oluşturulmasına yönelik çalışmaları kapsamaktadır. </t>
   </si>
   <si>
-    <t>Tahmin modelinin oluşturulmasına yönelik kavramsal çalışmalar başlatılmıştır.
-Müşteri sipariş verilerine yönelik veri seti oluşturulmuştur.
-In-house talep tahmin çalışması başlatılmıştır.
-Model ve uygulamanın oluşturulmasına yönelik danışman firma ile proje takvimi ve adımları belirlenmiştir.
-Modele beslenecek dış veriler belirlenmiştir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Veri setinin analizi ve yeni tahmin modelinin tasarımı oluşturulacaktır. 
-Modelin eğitimi tamamlanarak sonuçlar değerlendirilecektir.
-Uygulama testleri ile uygulama devreye alınacaktır.</t>
-  </si>
-  <si>
     <t>Tahminde Müşteri, Kampanya, Teşhir Bilgilerinin Kullanımı</t>
   </si>
   <si>
@@ -392,22 +343,6 @@
   </si>
   <si>
     <t>Talep tahmin uygulamasının çıktısını kullanarak tedarik planlama adımına girdi olacak ve mutabakat sağlanmış talep değerlerinin oluşturulmasını sağlayacak talep zenginleştirme ve mutabakat uygulamasının geliştirilmesi çalışmasıdır. Tahmin sonuçlarının girdi olarak alınabildiği, belirli hiyerarşilerde düzeltme yapılabildiği, belirli kişilerin üzerinde çalışabildiği ve veri girişi yapabildiği esnek bir ortam geliştirme çalışmasıdır. Odoo platformu üzerinde In-house olarak geliştirilmektedir.</t>
-  </si>
-  <si>
-    <t>İstekler belirlenerek kavramsal tasarım dokümanı IT birimine iletilerek mutabakat sağlamıştır.
-İş akış dokümanı oluşturulmuştur.
-IT tarafından platform kararı verilmiştir.
-Proje planı ve backloglar oluşturulmuştur. (agile proje yönetimi)
-Sprint-1 kapsamında sistemsel düzenlemeler yapılmıştır. 
-Sprint-2 kapsamında senaryo ve rollerin oluşturulması, excel ile verilerin yüklenmesi/raporlanması ve rol bazlı yetki düzenlemeleri  yapılmıştır.
-Sprint-3 kapsamında DFU bazlı revizyonlar, katsayı ile revizyonlar ve iş akış durumunun gösterilmesi yapılmıştır.
-Sprint-4 kapsamında kullanıcı bazlı test ortamına erişim, iş akışının onaylanması ve yürütülmesi, değişiklik takibinin yapılması ve dönem bazlı kilitleme yapılmıştır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proje takvimine uygun olarak aksiyon takibi ve test çalışmaları yürütülecektir.
-Sprint-5 kapsamında çalışmalar devam etmektedir. 
-Toplam 8 sprint ile proje tamamlanacaktır.
-</t>
   </si>
   <si>
     <t>S&amp;OP Finansallaştırma Uyg. Geliştirilmesi</t>
@@ -615,6 +550,33 @@
 Anlık takip ekranlarının geliştirilmesi
 Gecikme uyarıları
 OEM sipariş bazlı takip için standart veri yapısı oluşturuldu.</t>
+  </si>
+  <si>
+    <t>MTS Tip Ürünler İçin Max Stok Seviye Kontrol RPA</t>
+  </si>
+  <si>
+    <t>30/11/2026</t>
+  </si>
+  <si>
+    <t>Üretim Planlama süreçlerinde MTS ürünlerin stok seviyeleri belirlenen maksimum stok limitlerinin üzerine çıkabilmektedir. Bu durum fazla üretim, gereksiz stok maliyeti, depo alanı kaybı ve işletme sermayesinin verimsiz kullanımına neden olmaktadır.. Bu proje kapsamında ERP sisteminden stok, üretim ve planlama verileri alınarak MTS ürünlerin güncel stok seviyeleri günlük olarak kontrol edilecektir. Geliştirilecek RPA robotu, ürün bazında tanımlı maksimum stok seviyeleri ile mevcut stok miktarlarını karşılaştıracak, limit aşımı olan ürünleri tespit edecek ve ilgili ekipleri otomatik olarak bilgilendirecektir.. RPA sayesinde manuel rapor kontrol süreçleri ortadan kaldırılarak erken aksiyon alınması, fazla üretimin önlenmesi ve stok seviyelerinin hedeflenen aralıkta tutulması amaçlanmaktadır.. Beklenen Kazanımlar. Maksimum stok aşımı tespit süresinde %90'a varan azalma. Manuel rapor hazırlama süresinde azalma. Fazla üretim kaynaklı stok maliyetlerinin düşürülmesi. Planlama kararlarının daha proaktif yönetilmesi. Stok devir hızının artırılması. Üretim ve depo kapasitesinin daha verimli kullanılması. Başarı Kriteri: Maksimum stok seviyesini aşan tüm MTS ürünlerin günlük olarak otomatik tespit edilmesi ve ilgili aksiyon sahiplerine zamanında bildirilmesi.</t>
+  </si>
+  <si>
+    <t>1. Süreç Analizi Mevcut stok kontrol süreci incelendi. Manuel takip edilen raporlar değerlendirildi. Maksimum stok takibi yapılan ürün grupları belirlendi. 2. Gereksinimlerin Belirlenmesi Kontrol edilecek veri kaynakları tanımlandı. ERP sisteminden çekilecek alanlar belirlendi. Malzeme kodu Malzeme açıklaması Mevcut stok miktarı Maksimum stok seviyesi Planlı üretim miktarı Açık sipariş miktarı 3. İş Kuralı Tasarımı Maksimum stok hesaplama mantığı oluşturuldu. Aşım kriterleri tanımlandı. Kritik eşik ve tolerans seviyeleri belirlendi. 4. RPA Tasarım Çalışması Veri çekme akışı tasarlandı. Kontrol algoritması oluşturuldu. Bildirim ve raporlama senaryoları belirlendi.</t>
+  </si>
+  <si>
+    <t>1. ERP Veri Entegrasyonunun Tamamlanması ERP sisteminden otomatik veri çekilmesi. Veri doğrulama kontrollerinin eklenmesi. 2. RPA Geliştirme Çalışmaları Günlük tetikleme mekanizmasının kurulması. Ürün bazında stok kontrol modülünün geliştirilmesi. Stok aşımı hesaplama algoritmasının entegrasyonu. 3. Otomatik Bildirim Yapısının Kurulması Kritik ürünlerin e-posta ile bildirilmesi. Planlama ekibine günlük özet rapor gönderilmesi. Bölüm yöneticilerine haftalık durum raporu oluşturulması. 4. Dashboard ve Raporlama Aşım yaşanan ürün listesinin oluşturulması. Ürün bazında stok trendlerinin görüntülenmesi. Aksiyon takibi için KPI ekranlarının hazırlanması. 5. Test ve Doğrulama Pilot ürün grubu üzerinde test yapılması. Sonuçların manuel kontroller ile karşılaştırılması. Hata senaryolarının doğrulanması. 6. Canlı Kullanıma Geçiş RPA'nın üretim ortamına alınması. Kullanıcı eğitimlerinin tamamlanması. Performans takibinin başlatılması.</t>
+  </si>
+  <si>
+    <t>TZY Planlama Power BI Dashboard</t>
+  </si>
+  <si>
+    <t>TZY Planlama Power BI Dashboard projesinin amacı, üretim planlama süreçlerinde kullanılan Bütçe-Fiili Üretim, Kapasite Kullanımı, Fabrika Doluluk, Fazla Üretimler, Plana Uyum, Teyitsiz Siparişler, Stok Analizleri ve Müşteri bazlı raporların tek bir platform üzerinde birleştirilmesidir. Bu proje ile farklı kaynaklardan manuel olarak takip edilen veriler merkezi bir veri modeli altında toplanacak, yöneticilerin ve planlama ekiplerinin operasyonel performansı gerçek zamanlı izleyebilmesi sağlanacaktır. Dashboard; karar alma süreçlerini hızlandıracak, raporlama sürelerini azaltacak ve üretim planlama süreçlerinde görünürlüğü artıracaktır. Beklenen Kazanımlar Raporlama sürelerinde azalma Üretim planlama süreçlerinde görünürlük artışı Kapasite kullanımının etkin yönetimi Fazla üretimlerin azaltılması Stok seviyelerinin daha etkin kontrolü Yönetim karar süreçlerinin hızlandırılması Tek ekran üzerinden tüm planlama raporlarına erişim sağlanması Veri odaklı karar alma kültürünün desteklenmesi</t>
+  </si>
+  <si>
+    <t>1. İş İhtiyaçlarının Analiz Edilmesi ,Üretim planlama süreçlerinin incelenmesi, Kullanıcı beklentilerinin belirlenmesi ,Mevcut raporların envanter çalışmasının yapılması ,Kritik KPI'ların belirlenmesi 2. Dashboard Kapsamının Belirlenmesi Yönetim ekranlarının tanımlanması, Operasyonel raporların kategorize edilmesi ,Kullanıcı bazlı görünüm ihtiyaçlarının belirlenmesi 3. Veri Kaynaklarının Tespiti SAP veri kaynaklarının belirlenmesi, Excel ve yardımcı veri setlerinin tanımlanması Veri sahiplerinin belirlenmesi 4. Tasarım Çalışmaları Dashboard menü yapısının oluşturulması Navigasyon tasarımının hazırlanması ,Sayfa hiyerarşisinin tanımlanması, 5. KPI ve Rapor Tanımları, Bütçe-Fiili Üretim KPI'ları, Kapasite Kullanım KPI'ları, Fabrika Doluluk KPI'ları, Fazla Üretim KPI'ları, Sipariş Yönetimi KPI'ları, Stok ve Malzeme KPI'ları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faz 1: Veri Hazırlık ve Modelleme , Veri kaynaklarının entegrasyonu, Veri modeli ve ilişkilerin oluşturulması, KPI ve analiz hesaplamalarının geliştirilmesi  Faz 2: Dashboard Geliştirme,  Yönetici Özeti Dashboard, Üretim Planlama Dashboard, Sipariş Yönetimi Dashboard, Stok ve Malzeme Dashboard  Faz 3: Test ve Doğrulama,  KPI ve veri doğruluk kontrolleri, Kullanıcı kabul testleri, Performans ve optimizasyon çalışmaları  Faz 4: Canlıya Geçiş,  Power BI Service yayınlama ve yetkilendirme, Kullanıcı eğitimleri ve dokümantasyon,                                                                   </t>
   </si>
   <si>
     <t>Envanter Yönetimi</t>
@@ -2440,6 +2402,59 @@
 Müşteri deneyimini iyileştirmek
 Kategori Pazarlama tarafından yürütülen ürün yönetimi sürecine girdi ve öneriler sağlamak. (nihai müşteri talepleri)</t>
   </si>
+  <si>
+    <t xml:space="preserve">Ürün bilgilerinin ve karakteristik tanımlarının düzenli takibi ve kontrolü için power BI'da Ürün Dashboard çalışması tamamlanmıştır.
+Haftalık toplantılar ile ürün bilgilerindeki eksiklikler tespit edilmekte ve çalışmalar yapılmaktadır.
+Bölüm KPI'larına Ürün Ana Veri İyileştirme Endeksi eklenmiştir.
+</t>
+  </si>
+  <si>
+    <t>Piyasa kanalı tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+Kalite tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+Planlama stratejileri tanımlarının revizyonu yapılmıştır. Kod bazlı takip edilmekte ve eksiklikler giderilmektedir.
+DFU tanımları takip edilmekte ve eksiklikler giderilmektedir.
+Üretim kontrol notu takip edilmekte ve eksiklikler giderilmektedir.
+Ürün hiyerarşisi uyumsuzlukları tespit edilmekte ve düzeltilmektedir.
+Ürün hiyerarşisi tanımı yanlış olan kodlar tespit edilmekte ve düzeltilmektedir.
+Gömme rezervuar ürün grubunda set kodları ayrıştırılmıştır.
+Marka tanımları takip edilmekte ve eksiklikler giderilmektedir.
+Faturalama için ambalaj tipi tanımları takip edilmekte ve eksiklikler giderilmektedir.
+Orijin kodu bilgisinin düzenlenmesine yönelik çalışmalar devam etmektedir.
+SKM CTDA eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
+SKM Ebat eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
+SKM Kısa Kod eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
+Vitrifiye Renk tanımı eksikliklerinin giderilmesine yönelik çalışmalar devam etmektedir.
+Mükerrer açılan kodların tespiti ve düzenlenmesine yönelik çalışmalar devam etmektedir.</t>
+  </si>
+  <si>
+    <t>Vitrifiye ürün grubu için palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
+Vitrifiye ürün grubu için ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
+Mobilya ürün grubu için ürün hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.</t>
+  </si>
+  <si>
+    <t>SKM ürün grubu için palet hacim bilgilerinin kontrolü ve eksikliklerin giderilmesi sağlanmıştır.
+SKM ürün grubu için (numune kodlar) ürün ve palet kg bilgileri kontrol edilerek eksiklikler giderilecektir.
+Vitrifiye ürün grubu için ürün ve palet kg bilgileri kontrol edilerek eksiklikler giderilecektir.
+Vitrifiye ürün grubu için palet içi miktar bilgileri kontrol edilerek eksiklikler giderilecektir.</t>
+  </si>
+  <si>
+    <t>Tahmin modelinin ve uygulamanın oluşturulmasına yönelik proje adımları tamamlanmıştır.
+Veri setinin analizi ve yeni tahmin modelinin tasarımı oluşturulmuştur. (6 DFU)
+Modelin eğitimi tamamlanarak uygulama ile devreye alınmıştır.
+Tahmin sonuçları yıl sonuna kadar izlenecektir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İstekler belirlenerek kavramsal tasarım dokümanı IT birimine iletilerek mutabakat sağlamıştır.
+İş akış dokümanı oluşturulmuştur.
+IT tarafından platform kararı verilmiştir.
+Proje planı ve backloglar oluşturulmuştur. (agile proje yönetimi)
+Toplam 8 sprint ile proje tamamlanmıştır.
+Sprint-1 kapsamında sistemsel düzenlemeler , sprint-2 kapsamında senaryo ve rollerin oluşturulması, excel ile verilerin yüklenmesi/raporlanması ve rol bazlı yetki düzenlemeleri yapılmıştır.
+Sprint-3 kapsamında DFU bazlı revizyonlar, katsayı ile revizyonlar ve iş akış durumunun gösterilmesi, sprint-4 kapsamında ise kullanıcı bazlı test ortamına erişim, iş akışının onaylanması ve yürütülmesi, değişiklik takibinin yapılması ve dönem bazlı kilitleme yapılmıştır.
+Sprint-5 ve sprint-6 kapsamında dönem bazlı kilitleme ve süreç onaylama/ilerleme adımları, tahmin karşılaştırmaları, piyasa bazında revizyonların yapılması ve yetkilendirme çalışmaları yürütülmüştür.
+Sprint-7 ve sprint-8 kapsamında raporlama ekranları, paralel ve sıralı çalışma modu, senaryo liste yönetimi ve revizyon geçmişi görüntüleme yapılmıştır.
+</t>
+  </si>
 </sst>
 </file>
 
@@ -2448,7 +2463,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2978,28 +2993,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:M109"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <dimension ref="A1:M111"/>
+  <sheetFormatPr defaultColWidth="8.89453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.28515625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="6.3125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="12.3125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="18.89453125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="15.1015625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.3125" style="11" customWidth="1"/>
     <col min="7" max="7" width="10" style="11" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="14" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="62.42578125" style="11" customWidth="1"/>
-    <col min="12" max="12" width="89.140625" style="11" customWidth="1"/>
-    <col min="13" max="13" width="63.28515625" style="13" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="12" customWidth="1"/>
-    <col min="15" max="16384" width="8.85546875" style="12"/>
+    <col min="8" max="8" width="11.1015625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="11.3125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="12.41796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="71.3125" style="11" customWidth="1"/>
+    <col min="12" max="12" width="70.89453125" style="11" customWidth="1"/>
+    <col min="13" max="13" width="75.7890625" style="13" customWidth="1"/>
+    <col min="14" max="14" width="8.89453125" style="12" customWidth="1"/>
+    <col min="15" max="16384" width="8.89453125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="7" customFormat="1" ht="43.5">
+    <row r="1" spans="1:13" s="7" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3040,7 +3054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="240" hidden="1">
+    <row r="2" spans="1:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -3064,7 +3078,7 @@
         <v>45809</v>
       </c>
       <c r="I2" s="10">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>17</v>
@@ -3073,13 +3087,13 @@
         <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>19</v>
+        <v>469</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="120" hidden="1">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="111" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -3096,29 +3110,29 @@
         <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="10">
         <v>45962</v>
       </c>
       <c r="I3" s="10">
-        <v>46234</v>
+        <v>46387</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>23</v>
+        <v>471</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="120" hidden="1">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="8">
         <v>1</v>
       </c>
@@ -3135,29 +3149,29 @@
         <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="10">
         <v>46113</v>
       </c>
       <c r="I4" s="10">
-        <v>46265</v>
+        <v>46326</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="45" hidden="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="8">
         <v>1</v>
       </c>
@@ -3174,10 +3188,10 @@
         <v>15</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H5" s="10">
         <v>46204</v>
@@ -3186,17 +3200,17 @@
         <v>46326</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="105" hidden="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="8">
         <v>1</v>
       </c>
@@ -3210,23 +3224,23 @@
         <v>14</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="10"/>
       <c r="I6" s="10"/>
       <c r="J6" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:13" ht="45" hidden="1">
+    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="8">
         <v>1</v>
       </c>
@@ -3240,23 +3254,23 @@
         <v>14</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="9" t="s">
-        <v>40</v>
-      </c>
       <c r="L7" s="13"/>
     </row>
-    <row r="8" spans="1:13" ht="45" hidden="1">
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="8">
         <v>1</v>
       </c>
@@ -3270,23 +3284,23 @@
         <v>14</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
       <c r="J8" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L8" s="13"/>
     </row>
-    <row r="9" spans="1:13" ht="45" hidden="1">
+    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="8">
         <v>1</v>
       </c>
@@ -3300,23 +3314,23 @@
         <v>14</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
       <c r="J9" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:13" ht="45" hidden="1">
+    <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="8">
         <v>1</v>
       </c>
@@ -3330,25 +3344,25 @@
         <v>14</v>
       </c>
       <c r="E10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
       <c r="J10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="45" hidden="1">
+    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="8">
         <v>1</v>
       </c>
@@ -3362,25 +3376,25 @@
         <v>14</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
       <c r="J11" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L11" s="13"/>
     </row>
-    <row r="12" spans="1:13" ht="150" hidden="1">
+    <row r="12" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8">
         <v>1</v>
       </c>
@@ -3391,13 +3405,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="10">
@@ -3407,19 +3421,19 @@
         <v>45930</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="135" hidden="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="8">
         <v>1</v>
       </c>
@@ -3430,13 +3444,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="10">
@@ -3446,17 +3460,17 @@
         <v>46022</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:13" ht="90" hidden="1">
+    <row r="14" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -3467,13 +3481,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="10">
@@ -3483,19 +3497,17 @@
         <v>46234</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="105" hidden="1">
+        <v>473</v>
+      </c>
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="8">
         <v>1</v>
       </c>
@@ -3506,28 +3518,28 @@
         <v>2</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
       <c r="J15" s="9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="L15" s="13"/>
     </row>
-    <row r="16" spans="1:13" ht="60" hidden="1">
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8">
         <v>1</v>
       </c>
@@ -3538,28 +3550,28 @@
         <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
       <c r="J16" s="9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L16" s="13"/>
     </row>
-    <row r="17" spans="1:13" ht="165" hidden="1">
+    <row r="17" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="8">
         <v>1</v>
       </c>
@@ -3570,13 +3582,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="10">
@@ -3586,17 +3598,17 @@
         <v>46112</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="1:13" ht="135" hidden="1">
+    <row r="18" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="8">
         <v>1</v>
       </c>
@@ -3607,13 +3619,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="10">
@@ -3626,16 +3638,16 @@
         <v>17</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="90" hidden="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="8">
         <v>1</v>
       </c>
@@ -3646,13 +3658,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="10">
@@ -3662,19 +3674,19 @@
         <v>46112</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="165" hidden="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="273.60000000000002" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="8">
         <v>1</v>
       </c>
@@ -3685,16 +3697,16 @@
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H20" s="10">
         <v>46023</v>
@@ -3703,19 +3715,17 @@
         <v>46234</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="90" hidden="1">
+        <v>474</v>
+      </c>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="8">
         <v>1</v>
       </c>
@@ -3726,16 +3736,16 @@
         <v>3</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="H21" s="10">
         <v>46174</v>
@@ -3744,14 +3754,14 @@
         <v>46295</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="L21" s="13"/>
     </row>
-    <row r="22" spans="1:13" ht="60" hidden="1">
+    <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="8">
         <v>1</v>
       </c>
@@ -3762,13 +3772,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="10">
@@ -3778,14 +3788,14 @@
         <v>46295</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="L22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="105" hidden="1">
+    <row r="23" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="8">
         <v>1</v>
       </c>
@@ -3796,16 +3806,16 @@
         <v>3</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H23" s="10">
         <v>46327</v>
@@ -3814,14 +3824,14 @@
         <v>46387</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="L23" s="13"/>
     </row>
-    <row r="24" spans="1:13" ht="120" hidden="1">
+    <row r="24" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="8">
         <v>1</v>
       </c>
@@ -3832,13 +3842,13 @@
         <v>4</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="10">
@@ -3848,19 +3858,19 @@
         <v>46112</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="60" hidden="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8">
         <v>1</v>
       </c>
@@ -3871,13 +3881,13 @@
         <v>4</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="10">
@@ -3887,17 +3897,17 @@
         <v>46203</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="45" hidden="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8">
         <v>1</v>
       </c>
@@ -3908,13 +3918,13 @@
         <v>4</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E26" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="10">
@@ -3924,34 +3934,34 @@
         <v>46265</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="150" hidden="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="8">
         <v>2</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C27" s="8">
         <v>1</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="10">
@@ -3961,33 +3971,33 @@
         <v>46112</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="120" hidden="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="8">
         <v>2</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C28" s="8">
         <v>1</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="10">
@@ -3997,101 +4007,101 @@
         <v>46203</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" spans="1:13" ht="60" hidden="1">
+    <row r="29" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="8">
         <v>2</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C29" s="8">
         <v>1</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
       <c r="J29" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="L29" s="13"/>
     </row>
-    <row r="30" spans="1:13" ht="60" hidden="1">
+    <row r="30" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8">
         <v>2</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C30" s="8">
         <v>1</v>
       </c>
       <c r="D30" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E30" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
       <c r="J30" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="L30" s="13"/>
     </row>
-    <row r="31" spans="1:13" ht="390" hidden="1">
+    <row r="31" spans="1:13" ht="259.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="8">
         <v>2</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C31" s="8">
         <v>1</v>
       </c>
       <c r="D31" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H31" s="10">
         <v>46174</v>
@@ -4103,30 +4113,30 @@
         <v>17</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="M31" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="144.75" hidden="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8">
         <v>2</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C32" s="8">
         <v>1</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="10">
@@ -4136,36 +4146,36 @@
         <v>46356</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="87" hidden="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="8">
         <v>2</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C33" s="8">
         <v>1</v>
       </c>
       <c r="D33" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="10">
@@ -4175,34 +4185,34 @@
         <v>46356</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M33" s="15"/>
     </row>
-    <row r="34" spans="1:13" ht="159" hidden="1">
+    <row r="34" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="8">
         <v>2</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C34" s="8">
         <v>1</v>
       </c>
       <c r="D34" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E34" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="10">
@@ -4212,379 +4222,379 @@
         <v>46356</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="M34" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="120">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="216" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="8">
         <v>2</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C35" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>145</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="G35" s="2"/>
       <c r="H35" s="10">
-        <v>45839</v>
-      </c>
-      <c r="I35" s="10">
-        <v>46112</v>
+        <v>46266</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>136</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="60">
+        <v>138</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="8">
         <v>2</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C36" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="10">
+        <v>46266</v>
+      </c>
+      <c r="I36" s="10">
+        <v>46539</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="M36" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="L36" s="13"/>
-    </row>
-    <row r="37" spans="1:13" ht="409.6">
+    </row>
+    <row r="37" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="8">
         <v>2</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C37" s="8">
         <v>2</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H37" s="10">
-        <v>46023</v>
+        <v>45839</v>
       </c>
       <c r="I37" s="10">
-        <v>46203</v>
+        <v>46112</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="M37" s="11"/>
-    </row>
-    <row r="38" spans="1:13" ht="409.5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="8">
         <v>2</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C38" s="8">
         <v>2</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G38" s="13"/>
-      <c r="H38" s="10">
-        <v>46023</v>
-      </c>
-      <c r="I38" s="10">
-        <v>46295</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
       <c r="J38" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="M38" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="188.25">
+        <v>64</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="L38" s="13"/>
+    </row>
+    <row r="39" spans="1:13" ht="374.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="8">
         <v>2</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C39" s="8">
         <v>2</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G39" s="13"/>
+        <v>152</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="H39" s="10">
         <v>46023</v>
       </c>
       <c r="I39" s="10">
-        <v>46192</v>
+        <v>46203</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="L39" s="15" t="s">
-        <v>161</v>
+        <v>154</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>155</v>
       </c>
       <c r="M39" s="11"/>
     </row>
-    <row r="40" spans="1:13" ht="174">
+    <row r="40" spans="1:13" ht="374.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="8">
         <v>2</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C40" s="8">
         <v>2</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G40" s="13"/>
       <c r="H40" s="10">
         <v>46023</v>
       </c>
       <c r="I40" s="10">
-        <v>46174</v>
+        <v>46295</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="L40" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="M40" s="11"/>
-    </row>
-    <row r="41" spans="1:13" ht="346.5">
+        <v>157</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="244.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="8">
         <v>2</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C41" s="8">
         <v>2</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G41" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="G41" s="13"/>
       <c r="H41" s="10">
-        <v>45870</v>
+        <v>46023</v>
       </c>
       <c r="I41" s="10">
-        <v>46295</v>
+        <v>46192</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L41" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="M41" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="231.95">
+        <v>161</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="M41" s="11"/>
+    </row>
+    <row r="42" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="8">
         <v>2</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C42" s="8">
         <v>2</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G42" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="G42" s="13"/>
       <c r="H42" s="10">
-        <v>46181</v>
+        <v>46023</v>
       </c>
       <c r="I42" s="10">
-        <v>46387</v>
+        <v>46174</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="L42" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="M42" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="217.5" hidden="1">
+        <v>164</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="M42" s="11"/>
+    </row>
+    <row r="43" spans="1:13" ht="360" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="8">
         <v>2</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C43" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="10">
-        <v>46023</v>
+        <v>45870</v>
       </c>
       <c r="I43" s="10">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="L43" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="M43" s="15" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="245.25">
+        <v>167</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="M43" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="201.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="8">
         <v>2</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C44" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="10">
-        <v>46023</v>
+        <v>46181</v>
       </c>
       <c r="I44" s="10">
         <v>46387</v>
@@ -4593,72 +4603,72 @@
         <v>17</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="L44" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="M44" s="15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="346.5">
+        <v>171</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="M44" s="17" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="216" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="8">
         <v>2</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C45" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="10">
-        <v>45901</v>
+        <v>46023</v>
       </c>
       <c r="I45" s="10">
-        <v>46387</v>
+        <v>46265</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="M45" s="15" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="159">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="259.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="8">
         <v>2</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C46" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="10">
@@ -4671,115 +4681,115 @@
         <v>17</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="M46" s="15" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="274.5" hidden="1">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="316.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="C47" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="10">
-        <v>45839</v>
+        <v>45901</v>
       </c>
       <c r="I47" s="10">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="L47" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="M47" s="18" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="144.75" hidden="1">
+        <v>186</v>
+      </c>
+      <c r="M47" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="C48" s="8">
         <v>2</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="10">
-        <v>45809</v>
+        <v>46023</v>
       </c>
       <c r="I48" s="10">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="L48" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="M48" s="11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="72.75" hidden="1">
+        <v>190</v>
+      </c>
+      <c r="M48" s="15" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="230.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="8">
         <v>3</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C49" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="10">
-        <v>46113</v>
+        <v>45839</v>
       </c>
       <c r="I49" s="10">
         <v>46203</v>
@@ -4788,616 +4798,618 @@
         <v>17</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L49" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="M49" s="11" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="115.5" hidden="1">
+        <v>196</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="M49" s="18" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="8">
         <v>3</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C50" s="8">
         <v>2</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="10">
-        <v>45962</v>
+        <v>45809</v>
       </c>
       <c r="I50" s="10">
-        <v>46022</v>
+        <v>46203</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="L50" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="M50" s="11"/>
-    </row>
-    <row r="51" spans="1:13" ht="409.6" hidden="1">
+        <v>202</v>
+      </c>
+      <c r="L50" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="8">
         <v>3</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C51" s="8">
         <v>2</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>212</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="G51" s="2"/>
       <c r="H51" s="10">
-        <v>45778</v>
+        <v>46113</v>
       </c>
       <c r="I51" s="10">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="174" hidden="1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="8">
         <v>3</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C52" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="10">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I52" s="10">
-        <v>46203</v>
+        <v>46022</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="M52" s="11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="87" hidden="1">
+        <v>211</v>
+      </c>
+      <c r="M52" s="11"/>
+    </row>
+    <row r="53" spans="1:13" ht="409.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="C53" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G53" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>213</v>
+      </c>
       <c r="H53" s="10">
-        <v>45870</v>
+        <v>45778</v>
       </c>
       <c r="I53" s="10">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="89.25" hidden="1" customHeight="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="172.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="C54" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="10">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I54" s="10">
-        <v>46265</v>
+        <v>46203</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="M54" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="72.75" hidden="1">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="8">
         <v>4</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C55" s="8">
         <v>1</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="10">
-        <v>46023</v>
+        <v>45870</v>
       </c>
       <c r="I55" s="10">
-        <v>46295</v>
+        <v>46234</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="86.45" hidden="1">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="89.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="8">
         <v>4</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C56" s="8">
         <v>1</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="10">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I56" s="10">
         <v>46265</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="100.7" hidden="1">
+        <v>232</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="8">
         <v>4</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C57" s="8">
         <v>1</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="10">
         <v>46023</v>
       </c>
       <c r="I57" s="10">
-        <v>46387</v>
+        <v>46295</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="M57" s="13" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="57.6" hidden="1">
+        <v>236</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="8">
         <v>4</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C58" s="8">
         <v>1</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>246</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="G58" s="2"/>
       <c r="H58" s="10">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I58" s="10">
-        <v>46356</v>
+        <v>46265</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="M58" s="11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="86.45" hidden="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="8">
         <v>4</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C59" s="8">
         <v>1</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="10">
-        <v>45962</v>
+        <v>46023</v>
       </c>
       <c r="I59" s="10">
-        <v>46265</v>
+        <v>46387</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="M59" s="11" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="28.7" hidden="1">
+        <v>243</v>
+      </c>
+      <c r="M59" s="13" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="8">
         <v>4</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C60" s="8">
         <v>1</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G60" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="H60" s="10">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="I60" s="10">
-        <v>46295</v>
+        <v>46356</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="M60" s="11" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="72" hidden="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="8">
         <v>4</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C61" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="10">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I61" s="10">
-        <v>46203</v>
+        <v>46265</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="100.7" hidden="1">
+        <v>254</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="8">
         <v>4</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C62" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="10">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="I62" s="10">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="M62" s="11" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="86.45" hidden="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="8">
         <v>4</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C63" s="8">
         <v>2</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="10">
         <v>45931</v>
       </c>
       <c r="I63" s="10">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="M63" s="11" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="92.25" hidden="1" customHeight="1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="8">
         <v>4</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C64" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="10">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I64" s="10">
-        <v>46387</v>
+        <v>46265</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K64" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="L64" s="12"/>
-      <c r="M64" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="100.7" hidden="1">
+      <c r="K64" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="8">
         <v>4</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C65" s="8">
         <v>2</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="10">
-        <v>45809</v>
+        <v>45931</v>
       </c>
       <c r="I65" s="10">
         <v>46387</v>
@@ -5406,37 +5418,37 @@
         <v>17</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="M65" s="11" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="115.35" hidden="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="92.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="8">
         <v>4</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C66" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>276</v>
+        <v>225</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="10">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="I66" s="10">
         <v>46387</v>
@@ -5444,1707 +5456,1771 @@
       <c r="J66" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K66" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L66" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="M66" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="86.45" hidden="1">
+      <c r="K66" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="L66" s="12"/>
+      <c r="M66" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="8">
         <v>4</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C67" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="10">
-        <v>45931</v>
+        <v>45809</v>
       </c>
       <c r="I67" s="10">
-        <v>46265</v>
+        <v>46387</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K67" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="8">
+        <v>4</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="8">
+        <v>2</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="10">
+        <v>45992</v>
+      </c>
+      <c r="I68" s="10">
+        <v>46387</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="8">
+        <v>4</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C69" s="8">
+        <v>3</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="L67" s="11" t="s">
+      <c r="G69" s="2"/>
+      <c r="H69" s="10">
+        <v>45931</v>
+      </c>
+      <c r="I69" s="10">
+        <v>46265</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="M67" s="11" t="s">
+      <c r="L69" s="11" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" ht="150" hidden="1">
-      <c r="A68" s="20">
-        <v>5</v>
-      </c>
-      <c r="B68" s="21" t="s">
+      <c r="M69" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C68" s="20">
-        <v>1</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="E68" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="F68" s="22" t="s">
-        <v>294</v>
-      </c>
-      <c r="G68" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="H68" s="23">
-        <v>45931</v>
-      </c>
-      <c r="I68" s="23">
-        <v>46387</v>
-      </c>
-      <c r="J68" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="K68" s="22" t="s">
-        <v>296</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="105" hidden="1">
-      <c r="A69" s="20">
-        <v>5</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="C69" s="20">
-        <v>1</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="E69" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="F69" s="22" t="s">
-        <v>299</v>
-      </c>
-      <c r="G69" s="22" t="s">
-        <v>295</v>
-      </c>
-      <c r="H69" s="23">
-        <v>45962</v>
-      </c>
-      <c r="I69" s="23">
-        <v>46387</v>
-      </c>
-      <c r="J69" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="K69" s="22" t="s">
-        <v>300</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="180" hidden="1">
+    </row>
+    <row r="70" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="20">
         <v>5</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C70" s="20">
         <v>1</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H70" s="23">
         <v>45931</v>
       </c>
       <c r="I70" s="23">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="J70" s="22" t="s">
         <v>17</v>
       </c>
       <c r="K70" s="22" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="90" hidden="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="20">
         <v>5</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C71" s="20">
         <v>1</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H71" s="23">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I71" s="23">
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="J71" s="22" t="s">
         <v>17</v>
       </c>
       <c r="K71" s="22" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="135" hidden="1">
+        <v>302</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="20">
         <v>5</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C72" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="G72" s="22"/>
+        <v>304</v>
+      </c>
+      <c r="G72" s="22" t="s">
+        <v>296</v>
+      </c>
       <c r="H72" s="23">
         <v>45931</v>
       </c>
       <c r="I72" s="23">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="J72" s="22" t="s">
         <v>17</v>
       </c>
       <c r="K72" s="22" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="M72" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="165" hidden="1">
+        <v>306</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="20">
         <v>5</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C73" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="F73" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="G73" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="H73" s="23">
+        <v>45931</v>
+      </c>
+      <c r="I73" s="23">
+        <v>46295</v>
+      </c>
+      <c r="J73" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="M73" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E73" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="F73" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="G73" s="22"/>
-      <c r="H73" s="23">
-        <v>46174</v>
-      </c>
-      <c r="I73" s="23">
-        <v>46387</v>
-      </c>
-      <c r="J73" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="K73" s="22" t="s">
-        <v>318</v>
-      </c>
-      <c r="L73" s="24"/>
-      <c r="M73" s="24"/>
-    </row>
-    <row r="74" spans="1:13" ht="120" hidden="1">
+    </row>
+    <row r="74" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="20">
         <v>5</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C74" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="G74" s="22"/>
       <c r="H74" s="23">
-        <v>46054</v>
+        <v>45931</v>
       </c>
       <c r="I74" s="23">
-        <v>46356</v>
+        <v>46387</v>
       </c>
       <c r="J74" s="22" t="s">
         <v>17</v>
       </c>
       <c r="K74" s="22" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="45" hidden="1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="20">
         <v>5</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C75" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="G75" s="22"/>
       <c r="H75" s="23">
-        <v>46023</v>
+        <v>46174</v>
       </c>
       <c r="I75" s="23">
-        <v>46203</v>
+        <v>46387</v>
       </c>
       <c r="J75" s="22" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K75" s="22" t="s">
-        <v>326</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="M75" s="25" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="75" hidden="1">
+        <v>319</v>
+      </c>
+      <c r="L75" s="24"/>
+      <c r="M75" s="24"/>
+    </row>
+    <row r="76" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="20">
         <v>5</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C76" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G76" s="22"/>
       <c r="H76" s="23">
-        <v>45962</v>
+        <v>46054</v>
       </c>
       <c r="I76" s="23">
-        <v>46326</v>
+        <v>46356</v>
       </c>
       <c r="J76" s="22" t="s">
         <v>17</v>
       </c>
       <c r="K76" s="22" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="M76" s="25" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="75" hidden="1">
+        <v>324</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="20">
         <v>5</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C77" s="20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>13</v>
+        <v>321</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="G77" s="22"/>
       <c r="H77" s="23">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="I77" s="23">
-        <v>46356</v>
+        <v>46203</v>
       </c>
       <c r="J77" s="22" t="s">
         <v>17</v>
       </c>
       <c r="K77" s="22" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="75" hidden="1">
+        <v>328</v>
+      </c>
+      <c r="M77" s="25" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="20">
         <v>5</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C78" s="20">
         <v>4</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>13</v>
+        <v>261</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="G78" s="22"/>
       <c r="H78" s="23">
-        <v>46023</v>
+        <v>45962</v>
       </c>
       <c r="I78" s="23">
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="J78" s="22" t="s">
         <v>17</v>
       </c>
       <c r="K78" s="22" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="45" hidden="1">
+        <v>333</v>
+      </c>
+      <c r="M78" s="25" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="20">
         <v>5</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C79" s="20">
         <v>4</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E79" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G79" s="22"/>
       <c r="H79" s="23">
+        <v>46113</v>
+      </c>
+      <c r="I79" s="23">
+        <v>46356</v>
+      </c>
+      <c r="J79" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="20">
+        <v>5</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C80" s="20">
+        <v>4</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="G80" s="22"/>
+      <c r="H80" s="23">
+        <v>46023</v>
+      </c>
+      <c r="I80" s="23">
+        <v>46234</v>
+      </c>
+      <c r="J80" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="20">
+        <v>5</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C81" s="20">
+        <v>4</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="G81" s="22"/>
+      <c r="H81" s="23">
         <v>45931</v>
       </c>
-      <c r="I79" s="23">
+      <c r="I81" s="23">
         <v>46112</v>
       </c>
-      <c r="J79" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="K79" s="22" t="s">
-        <v>343</v>
-      </c>
-      <c r="L79" s="1" t="s">
+      <c r="J81" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="K81" s="22" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" ht="90" hidden="1">
-      <c r="A80" s="8">
-        <v>6</v>
-      </c>
-      <c r="B80" s="9" t="s">
+      <c r="L81" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C80" s="8">
-        <v>1</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="H80" s="10">
-        <v>45778</v>
-      </c>
-      <c r="I80" s="10">
-        <v>45869</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="M80" s="11"/>
-    </row>
-    <row r="81" spans="1:13" ht="90" hidden="1">
-      <c r="A81" s="8">
-        <v>6</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="C81" s="8">
-        <v>1</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="H81" s="10">
-        <v>45931</v>
-      </c>
-      <c r="I81" s="10">
-        <v>46295</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="L81" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="M81" s="11" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="90" hidden="1">
+    </row>
+    <row r="82" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="8">
         <v>6</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C82" s="8">
         <v>1</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H82" s="10">
-        <v>45931</v>
+        <v>45778</v>
       </c>
       <c r="I82" s="10">
-        <v>46203</v>
+        <v>45869</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="L82" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="M82" s="11" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="120" hidden="1">
+        <v>351</v>
+      </c>
+      <c r="M82" s="11"/>
+    </row>
+    <row r="83" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="8">
         <v>6</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C83" s="8">
         <v>1</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H83" s="10">
         <v>45931</v>
       </c>
       <c r="I83" s="10">
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>358</v>
+        <v>17</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L83" s="11" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="M83" s="11" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="90" hidden="1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="8">
         <v>6</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C84" s="8">
         <v>1</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H84" s="10">
         <v>45931</v>
       </c>
       <c r="I84" s="10">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>358</v>
+        <v>17</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="M84" s="11" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="135" hidden="1">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="8">
         <v>6</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C85" s="8">
         <v>1</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H85" s="10">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I85" s="10">
-        <v>46387</v>
+        <v>46203</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="M85" s="11" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="120" hidden="1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="8">
         <v>6</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C86" s="8">
         <v>1</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H86" s="10">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I86" s="10">
         <v>46387</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L86" s="11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M86" s="11" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="30" hidden="1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="8">
         <v>6</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C87" s="8">
         <v>1</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
+        <v>350</v>
+      </c>
+      <c r="H87" s="10">
+        <v>46023</v>
+      </c>
+      <c r="I87" s="10">
+        <v>46387</v>
+      </c>
       <c r="J87" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K87" s="9"/>
-      <c r="L87" s="13"/>
-    </row>
-    <row r="88" spans="1:13" ht="30" hidden="1">
+        <v>359</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="L87" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="M87" s="11" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="8">
         <v>6</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C88" s="8">
         <v>1</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="H88" s="10"/>
-      <c r="I88" s="10"/>
+        <v>350</v>
+      </c>
+      <c r="H88" s="10">
+        <v>46023</v>
+      </c>
+      <c r="I88" s="10">
+        <v>46387</v>
+      </c>
       <c r="J88" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K88" s="9"/>
-      <c r="L88" s="13"/>
-    </row>
-    <row r="89" spans="1:13" ht="30" hidden="1">
+        <v>359</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="L88" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="M88" s="11" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="8">
         <v>6</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C89" s="8">
         <v>1</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H89" s="10"/>
       <c r="I89" s="10"/>
       <c r="J89" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K89" s="9"/>
       <c r="L89" s="13"/>
     </row>
-    <row r="90" spans="1:13" ht="165" hidden="1">
+    <row r="90" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="8">
         <v>6</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C90" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="H90" s="10">
-        <v>46023</v>
-      </c>
-      <c r="I90" s="10">
-        <v>46203</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="H90" s="10"/>
+      <c r="I90" s="10"/>
       <c r="J90" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="L90" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="M90" s="11" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="120" hidden="1">
+        <v>64</v>
+      </c>
+      <c r="K90" s="9"/>
+      <c r="L90" s="13"/>
+    </row>
+    <row r="91" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="8">
         <v>6</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C91" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G91" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="E91" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="H91" s="10">
-        <v>46204</v>
-      </c>
-      <c r="I91" s="10">
-        <v>46387</v>
-      </c>
+      <c r="H91" s="10"/>
+      <c r="I91" s="10"/>
       <c r="J91" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="L91" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="M91" s="18" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="195" hidden="1">
+        <v>64</v>
+      </c>
+      <c r="K91" s="9"/>
+      <c r="L91" s="13"/>
+    </row>
+    <row r="92" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="8">
         <v>6</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C92" s="8">
         <v>2</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H92" s="10">
         <v>46023</v>
       </c>
       <c r="I92" s="10">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="L92" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="M92" s="18"/>
-    </row>
-    <row r="93" spans="1:13" ht="150" hidden="1">
+        <v>381</v>
+      </c>
+      <c r="L92" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="M92" s="11" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="8">
         <v>6</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C93" s="8">
         <v>2</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E93" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="H93" s="10">
+        <v>46204</v>
+      </c>
+      <c r="I93" s="10">
+        <v>46387</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="L93" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="M93" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="H93" s="10">
-        <v>45992</v>
-      </c>
-      <c r="I93" s="10">
-        <v>46142</v>
-      </c>
-      <c r="J93" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="L93" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="M93" s="18" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="120" hidden="1">
+    </row>
+    <row r="94" spans="1:13" ht="187.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="8">
         <v>6</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C94" s="8">
         <v>2</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="H94" s="10">
         <v>46023</v>
       </c>
       <c r="I94" s="10">
-        <v>46387</v>
+        <v>46142</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>358</v>
+        <v>64</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="L94" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="M94" s="18" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="195" hidden="1">
+        <v>393</v>
+      </c>
+      <c r="M94" s="18"/>
+    </row>
+    <row r="95" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="8">
         <v>6</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C95" s="8">
         <v>2</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="H95" s="10">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="I95" s="10">
-        <v>46357</v>
+        <v>46142</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="L95" s="18" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="M95" s="18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="120" hidden="1">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="8">
         <v>6</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C96" s="8">
         <v>2</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="H96" s="10">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="I96" s="10">
-        <v>46053</v>
+        <v>46387</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>57</v>
+        <v>359</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="L96" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="M96" s="18"/>
-    </row>
-    <row r="97" spans="1:13" ht="120" hidden="1">
+        <v>403</v>
+      </c>
+      <c r="M96" s="18" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="8">
         <v>6</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C97" s="8">
         <v>2</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="H97" s="10">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="I97" s="10">
-        <v>46203</v>
+        <v>46357</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L97" s="18" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="M97" s="18" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="135" hidden="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="8">
         <v>6</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C98" s="8">
         <v>2</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H98" s="10">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I98" s="10">
-        <v>46203</v>
+        <v>46053</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>358</v>
+        <v>53</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="L98" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="M98" s="11" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="60" hidden="1">
+        <v>413</v>
+      </c>
+      <c r="M98" s="18"/>
+    </row>
+    <row r="99" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="8">
         <v>6</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C99" s="8">
         <v>2</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H99" s="10">
-        <v>46174</v>
+        <v>45931</v>
       </c>
       <c r="I99" s="10">
-        <v>46295</v>
+        <v>46203</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>17</v>
+        <v>359</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="L99" s="11" t="s">
-        <v>422</v>
+        <v>412</v>
+      </c>
+      <c r="L99" s="18" t="s">
+        <v>415</v>
       </c>
       <c r="M99" s="18" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="105" hidden="1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="8">
         <v>6</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C100" s="8">
         <v>2</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H100" s="10">
         <v>46023</v>
       </c>
       <c r="I100" s="10">
-        <v>46264</v>
+        <v>46203</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="L100" s="18" t="s">
-        <v>426</v>
-      </c>
-      <c r="M100" s="18" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="165" hidden="1">
+        <v>419</v>
+      </c>
+      <c r="M100" s="11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="8">
         <v>6</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C101" s="8">
         <v>2</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H101" s="10">
         <v>46174</v>
       </c>
       <c r="I101" s="10">
-        <v>46264</v>
+        <v>46295</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="L101" s="18" t="s">
-        <v>430</v>
+        <v>422</v>
+      </c>
+      <c r="L101" s="11" t="s">
+        <v>423</v>
       </c>
       <c r="M101" s="18" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="135" hidden="1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="8">
         <v>6</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C102" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>433</v>
+        <v>378</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="G102" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="H102" s="10">
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="I102" s="10">
-        <v>46157</v>
+        <v>46264</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="L102" s="18" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="M102" s="18" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" ht="90" hidden="1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="8">
         <v>6</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C103" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>432</v>
+        <v>377</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>433</v>
+        <v>378</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="G103" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>380</v>
+      </c>
       <c r="H103" s="10">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="I103" s="10">
-        <v>46387</v>
+        <v>46264</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="L103" s="13" t="s">
-        <v>440</v>
+        <v>430</v>
+      </c>
+      <c r="L103" s="18" t="s">
+        <v>431</v>
       </c>
       <c r="M103" s="18" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" ht="150" hidden="1">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="8">
         <v>6</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C104" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>445</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="G104" s="2"/>
       <c r="H104" s="10">
-        <v>46023</v>
+        <v>45931</v>
       </c>
       <c r="I104" s="10">
-        <v>46357</v>
+        <v>46157</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="L104" s="18" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="M104" s="18" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="75" hidden="1">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="8">
         <v>6</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C105" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="G105" s="2"/>
       <c r="H105" s="10">
-        <v>46023</v>
+        <v>46173</v>
       </c>
       <c r="I105" s="10">
-        <v>46082</v>
+        <v>46387</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="L105" s="18" t="s">
-        <v>452</v>
-      </c>
-      <c r="M105" s="18"/>
-    </row>
-    <row r="106" spans="1:13" ht="90" hidden="1">
+        <v>440</v>
+      </c>
+      <c r="L105" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="M105" s="18" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="8">
         <v>6</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C106" s="8">
         <v>4</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E106" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="H106" s="10">
+        <v>46023</v>
+      </c>
+      <c r="I106" s="10">
+        <v>46357</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="L106" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="M106" s="18" t="s">
         <v>449</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="G106" s="2"/>
-      <c r="H106" s="10">
-        <v>45901</v>
-      </c>
-      <c r="I106" s="10">
-        <v>46112</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="L106" s="18" t="s">
-        <v>455</v>
-      </c>
-      <c r="M106" s="18"/>
-    </row>
-    <row r="107" spans="1:13" ht="165" hidden="1">
+    </row>
+    <row r="107" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="8">
         <v>6</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C107" s="8">
         <v>4</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="G107" s="2"/>
       <c r="H107" s="10">
-        <v>45901</v>
+        <v>46023</v>
       </c>
       <c r="I107" s="10">
-        <v>46112</v>
+        <v>46082</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>358</v>
+        <v>53</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="L107" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="M107" s="18" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" ht="300" hidden="1">
+        <v>453</v>
+      </c>
+      <c r="M107" s="18"/>
+    </row>
+    <row r="108" spans="1:13" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="8">
         <v>6</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C108" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="10">
-        <v>46174</v>
+        <v>45901</v>
       </c>
       <c r="I108" s="10">
-        <v>46295</v>
+        <v>46112</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="L108" s="18"/>
-      <c r="M108" s="18" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" ht="165" hidden="1">
+        <v>455</v>
+      </c>
+      <c r="L108" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="M108" s="18"/>
+    </row>
+    <row r="109" spans="1:13" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="8">
         <v>6</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C109" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="G109" s="2"/>
       <c r="H109" s="10">
+        <v>45901</v>
+      </c>
+      <c r="I109" s="10">
+        <v>46112</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="L109" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="M109" s="18" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="244.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="8">
+        <v>6</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C110" s="8">
+        <v>5</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G110" s="2"/>
+      <c r="H110" s="10">
+        <v>46174</v>
+      </c>
+      <c r="I110" s="10">
+        <v>46295</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="L110" s="18"/>
+      <c r="M110" s="18" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="8">
+        <v>6</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C111" s="8">
+        <v>5</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="G111" s="2"/>
+      <c r="H111" s="10">
         <v>46235</v>
       </c>
-      <c r="I109" s="10">
+      <c r="I111" s="10">
         <v>46356</v>
       </c>
-      <c r="J109" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="L109" s="18"/>
-      <c r="M109" s="18" t="s">
+      <c r="J111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K111" s="2" t="s">
         <v>467</v>
       </c>
+      <c r="L111" s="18"/>
+      <c r="M111" s="18" t="s">
+        <v>468</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M109" xr:uid="{2379EA82-C523-4C6E-A6A0-9CE229873D43}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Planlama"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Envanter Yönetimi"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M109">
-    <sortCondition ref="A9:A109"/>
-    <sortCondition ref="C9:C109"/>
-    <sortCondition ref="E9:E109"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:M111">
+    <sortCondition ref="A9:A111"/>
+    <sortCondition ref="C9:C111"/>
+    <sortCondition ref="E9:E111"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
